--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -645,7 +645,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P2" t="n">
         <v>68.45</v>
@@ -674,7 +674,7 @@
         <v>55.29</v>
       </c>
       <c r="X2" t="n">
-        <v>16.65</v>
+        <v>16.87</v>
       </c>
       <c r="Y2" t="n">
         <v>13.89</v>
@@ -683,7 +683,7 @@
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="3">
@@ -750,7 +750,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P3" t="n">
         <v>374.79</v>
@@ -779,16 +779,16 @@
         <v>33.22</v>
       </c>
       <c r="X3" t="n">
-        <v>20.05</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.01</v>
+        <v>16.02</v>
       </c>
       <c r="Z3" t="n">
         <v>-16.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="4">
@@ -855,7 +855,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P4" t="n">
         <v>197.98</v>
@@ -884,10 +884,10 @@
         <v>52.16</v>
       </c>
       <c r="X4" t="n">
-        <v>21.17</v>
+        <v>21.18</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.85</v>
+        <v>20.86</v>
       </c>
       <c r="Z4" t="n">
         <v>-33.01</v>
@@ -1036,13 +1036,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P6" t="n">
-        <v>46.585</v>
+        <v>161.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.185</v>
+        <v>151.2</v>
       </c>
       <c r="R6" t="n">
-        <v>39.5759</v>
+        <v>145.0529</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>5.73</v>
+        <v>5.06</v>
       </c>
       <c r="U6" t="n">
-        <v>9.56</v>
+        <v>8.25</v>
       </c>
       <c r="V6" t="n">
-        <v>21.55</v>
+        <v>12.98</v>
       </c>
       <c r="W6" t="n">
-        <v>41</v>
+        <v>24.91</v>
       </c>
       <c r="X6" t="n">
-        <v>8.789999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.3</v>
+        <v>13.74</v>
       </c>
       <c r="Z6" t="n">
-        <v>-22.01</v>
+        <v>-20.96</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1158,7 +1158,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1170,16 +1170,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P7" t="n">
-        <v>161.58</v>
+        <v>46.585</v>
       </c>
       <c r="Q7" t="n">
-        <v>151.2</v>
+        <v>43.185</v>
       </c>
       <c r="R7" t="n">
-        <v>145.0529</v>
+        <v>39.5759</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>5.06</v>
+        <v>5.73</v>
       </c>
       <c r="U7" t="n">
-        <v>8.25</v>
+        <v>9.56</v>
       </c>
       <c r="V7" t="n">
-        <v>12.98</v>
+        <v>21.55</v>
       </c>
       <c r="W7" t="n">
-        <v>24.91</v>
+        <v>41</v>
       </c>
       <c r="X7" t="n">
-        <v>12.25</v>
+        <v>8.65</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.73</v>
+        <v>16.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>-20.96</v>
+        <v>-22.01</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.75</v>
+        <v>0.41</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1216,13 +1216,13 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>68</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1275,7 +1275,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P8" t="n">
         <v>122.82</v>
@@ -1304,10 +1304,10 @@
         <v>23.05</v>
       </c>
       <c r="X8" t="n">
-        <v>12.87</v>
+        <v>12.96</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.2</v>
+        <v>14.21</v>
       </c>
       <c r="Z8" t="n">
         <v>-21.63</v>
@@ -1380,7 +1380,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P9" t="n">
         <v>74.5</v>
@@ -1409,7 +1409,7 @@
         <v>18.22</v>
       </c>
       <c r="X9" t="n">
-        <v>11.41</v>
+        <v>11.46</v>
       </c>
       <c r="Y9" t="n">
         <v>14.16</v>
@@ -1418,7 +1418,7 @@
         <v>-20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.3</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1485,7 +1485,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P10" t="n">
         <v>98.95999999999999</v>
@@ -1517,7 +1517,7 @@
         <v>14.24</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.28</v>
+        <v>17.29</v>
       </c>
       <c r="Z10" t="n">
         <v>-23.45</v>
@@ -1590,7 +1590,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P11" t="n">
         <v>124.59</v>
@@ -1619,16 +1619,16 @@
         <v>24.81</v>
       </c>
       <c r="X11" t="n">
-        <v>14.66</v>
+        <v>14.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.2</v>
+        <v>15.21</v>
       </c>
       <c r="Z11" t="n">
         <v>-23.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1695,7 +1695,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P12" t="n">
         <v>624.26</v>
@@ -1724,7 +1724,7 @@
         <v>35.42</v>
       </c>
       <c r="X12" t="n">
-        <v>18.25</v>
+        <v>18.43</v>
       </c>
       <c r="Y12" t="n">
         <v>19.89</v>
@@ -1733,7 +1733,7 @@
         <v>-31.11</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
         <v>-4</v>
       </c>
       <c r="AI12" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>68.09999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="13">
@@ -1800,7 +1800,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P13" t="n">
         <v>62.86</v>
@@ -1829,7 +1829,7 @@
         <v>15.84</v>
       </c>
       <c r="X13" t="n">
-        <v>9.91</v>
+        <v>9.94</v>
       </c>
       <c r="Y13" t="n">
         <v>14.49</v>
@@ -1905,7 +1905,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P14" t="n">
         <v>17.672</v>
@@ -1934,10 +1934,10 @@
         <v>40.14</v>
       </c>
       <c r="X14" t="n">
-        <v>11.99</v>
+        <v>11.98</v>
       </c>
       <c r="Y14" t="n">
-        <v>21.98</v>
+        <v>21.99</v>
       </c>
       <c r="Z14" t="n">
         <v>-35.29</v>
@@ -2115,7 +2115,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P16" t="n">
         <v>33.935</v>
@@ -2144,10 +2144,10 @@
         <v>26.27</v>
       </c>
       <c r="X16" t="n">
-        <v>11.45</v>
+        <v>11.42</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.3</v>
+        <v>24.31</v>
       </c>
       <c r="Z16" t="n">
         <v>-33.89</v>
@@ -2220,7 +2220,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P17" t="n">
         <v>64.45999999999999</v>
@@ -2249,7 +2249,7 @@
         <v>0.26</v>
       </c>
       <c r="X17" t="n">
-        <v>6.45</v>
+        <v>6.6</v>
       </c>
       <c r="Y17" t="n">
         <v>10.18</v>
@@ -2258,7 +2258,7 @@
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="18">
@@ -2325,7 +2325,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P18" t="n">
         <v>91.03</v>
@@ -2354,10 +2354,10 @@
         <v>146.16</v>
       </c>
       <c r="X18" t="n">
-        <v>36.5</v>
+        <v>36.51</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.95</v>
+        <v>30.96</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
@@ -2459,10 +2459,10 @@
         <v>75.33</v>
       </c>
       <c r="X19" t="n">
-        <v>16.3</v>
+        <v>16.31</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.12</v>
+        <v>28.13</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
@@ -2535,7 +2535,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P20" t="n">
         <v>4.891</v>
@@ -2564,7 +2564,7 @@
         <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.38</v>
+        <v>-1.39</v>
       </c>
       <c r="Y20" t="n">
         <v>4.66</v>
@@ -2640,7 +2640,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P21" t="n">
         <v>23.56</v>
@@ -2669,16 +2669,16 @@
         <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.69</v>
+        <v>-1.72</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="Z21" t="n">
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -645,16 +645,16 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P2" t="n">
-        <v>68.45</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>59.9388</v>
+        <v>60.1912</v>
       </c>
       <c r="R2" t="n">
-        <v>53.3503</v>
+        <v>53.476</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>14.6</v>
+        <v>15.57</v>
       </c>
       <c r="U2" t="n">
-        <v>18.14</v>
+        <v>19.19</v>
       </c>
       <c r="V2" t="n">
-        <v>35.33</v>
+        <v>39.91</v>
       </c>
       <c r="W2" t="n">
-        <v>55.29</v>
+        <v>58.4</v>
       </c>
       <c r="X2" t="n">
-        <v>16.87</v>
+        <v>17.1</v>
       </c>
       <c r="Y2" t="n">
         <v>13.89</v>
@@ -683,7 +683,7 @@
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
@@ -750,16 +750,16 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P3" t="n">
-        <v>374.79</v>
+        <v>377.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>387.4872</v>
+        <v>386.4334</v>
       </c>
       <c r="R3" t="n">
-        <v>356.7072</v>
+        <v>357.1957</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-3.63</v>
+        <v>-2.78</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.91</v>
       </c>
       <c r="V3" t="n">
-        <v>10.9</v>
+        <v>11.67</v>
       </c>
       <c r="W3" t="n">
-        <v>33.22</v>
+        <v>34.14</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>20.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.02</v>
+        <v>16.01</v>
       </c>
       <c r="Z3" t="n">
         <v>-16.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>80.7</v>
+        <v>81.2</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.7</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +855,16 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P4" t="n">
-        <v>197.98</v>
+        <v>199.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>166.0064</v>
+        <v>166.913</v>
       </c>
       <c r="R4" t="n">
-        <v>154.4474</v>
+        <v>154.7564</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>18.29</v>
+        <v>18.51</v>
       </c>
       <c r="U4" t="n">
-        <v>31.15</v>
+        <v>31.22</v>
       </c>
       <c r="V4" t="n">
-        <v>29.26</v>
+        <v>32.7</v>
       </c>
       <c r="W4" t="n">
-        <v>52.16</v>
+        <v>54.21</v>
       </c>
       <c r="X4" t="n">
-        <v>21.18</v>
+        <v>21.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.86</v>
+        <v>20.85</v>
       </c>
       <c r="Z4" t="n">
         <v>-33.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>-5</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>75.8</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="5">
@@ -963,13 +963,13 @@
         <v>4.66</v>
       </c>
       <c r="P5" t="n">
-        <v>9.717000000000001</v>
+        <v>9.769</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.259</v>
+        <v>9.2721</v>
       </c>
       <c r="R5" t="n">
-        <v>8.869999999999999</v>
+        <v>8.878399999999999</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,19 +977,19 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>4.92</v>
+        <v>5.45</v>
       </c>
       <c r="V5" t="n">
-        <v>11.69</v>
+        <v>13.59</v>
       </c>
       <c r="W5" t="n">
-        <v>22.44</v>
+        <v>24.24</v>
       </c>
       <c r="X5" t="n">
-        <v>11.82</v>
+        <v>11.94</v>
       </c>
       <c r="Y5" t="n">
         <v>13.4</v>
@@ -998,7 +998,7 @@
         <v>-19.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.3</v>
+        <v>73.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>67.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P6" t="n">
-        <v>161.58</v>
+        <v>47.005</v>
       </c>
       <c r="Q6" t="n">
-        <v>151.2</v>
+        <v>43.2967</v>
       </c>
       <c r="R6" t="n">
-        <v>145.0529</v>
+        <v>39.6407</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>5.06</v>
+        <v>5.89</v>
       </c>
       <c r="U6" t="n">
-        <v>8.25</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>12.98</v>
+        <v>24.14</v>
       </c>
       <c r="W6" t="n">
-        <v>24.91</v>
+        <v>43.09</v>
       </c>
       <c r="X6" t="n">
-        <v>12.3</v>
+        <v>8.84</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.74</v>
+        <v>16.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>-20.96</v>
+        <v>-22.01</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.75</v>
+        <v>0.42</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>72</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>68</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1158,7 +1158,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1170,16 +1170,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P7" t="n">
-        <v>46.585</v>
+        <v>162.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>43.185</v>
+        <v>151.4934</v>
       </c>
       <c r="R7" t="n">
-        <v>39.5759</v>
+        <v>145.2057</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>5.73</v>
+        <v>5.85</v>
       </c>
       <c r="U7" t="n">
-        <v>9.56</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>21.55</v>
+        <v>15.18</v>
       </c>
       <c r="W7" t="n">
-        <v>41</v>
+        <v>26.65</v>
       </c>
       <c r="X7" t="n">
-        <v>8.65</v>
+        <v>12.43</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.31</v>
+        <v>13.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>-22.01</v>
+        <v>-20.96</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.41</v>
+        <v>0.76</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1216,13 +1216,13 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>69.90000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -1275,16 +1275,16 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P8" t="n">
-        <v>122.82</v>
+        <v>123.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>114.9492</v>
+        <v>115.1654</v>
       </c>
       <c r="R8" t="n">
-        <v>111.0207</v>
+        <v>111.1285</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>4.99</v>
+        <v>5.71</v>
       </c>
       <c r="U8" t="n">
-        <v>8.279999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>11.89</v>
+        <v>13.97</v>
       </c>
       <c r="W8" t="n">
-        <v>23.05</v>
+        <v>24.67</v>
       </c>
       <c r="X8" t="n">
-        <v>12.96</v>
+        <v>13.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
       <c r="Z8" t="n">
         <v>-21.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>71.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>67.2</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1380,16 +1380,16 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P9" t="n">
-        <v>74.5</v>
+        <v>74.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>70.4928</v>
+        <v>70.59520000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>68.0501</v>
+        <v>68.1117</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,19 +1397,19 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>3.7</v>
+        <v>4.28</v>
       </c>
       <c r="U9" t="n">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
       <c r="V9" t="n">
-        <v>11.78</v>
+        <v>13.6</v>
       </c>
       <c r="W9" t="n">
-        <v>18.22</v>
+        <v>20.17</v>
       </c>
       <c r="X9" t="n">
-        <v>11.46</v>
+        <v>11.55</v>
       </c>
       <c r="Y9" t="n">
         <v>14.16</v>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="10">
@@ -1485,16 +1485,16 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P10" t="n">
-        <v>98.95999999999999</v>
+        <v>99.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>88.9038</v>
+        <v>89.21980000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>84.01900000000001</v>
+        <v>84.13</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,19 +1502,19 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>8.52</v>
+        <v>9.32</v>
       </c>
       <c r="U10" t="n">
-        <v>15.55</v>
+        <v>15.64</v>
       </c>
       <c r="V10" t="n">
-        <v>21.41</v>
+        <v>23.99</v>
       </c>
       <c r="W10" t="n">
-        <v>28.47</v>
+        <v>30.71</v>
       </c>
       <c r="X10" t="n">
-        <v>14.24</v>
+        <v>14.42</v>
       </c>
       <c r="Y10" t="n">
         <v>17.29</v>
@@ -1523,7 +1523,7 @@
         <v>-23.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>68.5</v>
+        <v>69.7</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>68.5</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="11">
@@ -1590,16 +1590,16 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P11" t="n">
-        <v>124.59</v>
+        <v>125.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>115.3704</v>
+        <v>115.6198</v>
       </c>
       <c r="R11" t="n">
-        <v>111.7465</v>
+        <v>111.8554</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,22 +1607,22 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>5.94</v>
+        <v>6.34</v>
       </c>
       <c r="U11" t="n">
-        <v>10.92</v>
+        <v>11.11</v>
       </c>
       <c r="V11" t="n">
-        <v>12.05</v>
+        <v>13.76</v>
       </c>
       <c r="W11" t="n">
-        <v>24.81</v>
+        <v>26.36</v>
       </c>
       <c r="X11" t="n">
-        <v>14.77</v>
+        <v>14.84</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.21</v>
+        <v>15.2</v>
       </c>
       <c r="Z11" t="n">
         <v>-23.28</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>67.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>67.59999999999999</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="12">
@@ -1695,16 +1695,16 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P12" t="n">
-        <v>624.26</v>
+        <v>627.9400000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>552.0444</v>
+        <v>554.0558</v>
       </c>
       <c r="R12" t="n">
-        <v>526.89</v>
+        <v>527.6201</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,19 +1712,19 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>10.74</v>
+        <v>10.6</v>
       </c>
       <c r="U12" t="n">
-        <v>20.97</v>
+        <v>21.18</v>
       </c>
       <c r="V12" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="W12" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="X12" t="n">
         <v>18.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="X12" t="n">
-        <v>18.43</v>
       </c>
       <c r="Y12" t="n">
         <v>19.89</v>
@@ -1747,11 +1747,11 @@
         <v>-4</v>
       </c>
       <c r="AI12" t="n">
-        <v>64.2</v>
+        <v>65.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>68.2</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="13">
@@ -1800,16 +1800,16 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P13" t="n">
-        <v>62.86</v>
+        <v>63.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.28</v>
+        <v>60.3569</v>
       </c>
       <c r="R13" t="n">
-        <v>58.0206</v>
+        <v>58.0758</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,19 +1817,19 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>2.71</v>
+        <v>4.24</v>
       </c>
       <c r="U13" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>11.39</v>
+        <v>14.47</v>
       </c>
       <c r="W13" t="n">
-        <v>15.84</v>
+        <v>17.79</v>
       </c>
       <c r="X13" t="n">
-        <v>9.94</v>
+        <v>10.14</v>
       </c>
       <c r="Y13" t="n">
         <v>14.49</v>
@@ -1838,7 +1838,7 @@
         <v>-20.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>63.6</v>
+        <v>64.8</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>63.6</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="14">
@@ -1905,16 +1905,16 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P14" t="n">
-        <v>17.672</v>
+        <v>17.946</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.1631</v>
+        <v>15.2406</v>
       </c>
       <c r="R14" t="n">
-        <v>14.1744</v>
+        <v>14.1996</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1922,19 +1922,19 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>13.01</v>
+        <v>11.66</v>
       </c>
       <c r="U14" t="n">
-        <v>24.96</v>
+        <v>26.08</v>
       </c>
       <c r="V14" t="n">
-        <v>28.79</v>
+        <v>34.01</v>
       </c>
       <c r="W14" t="n">
-        <v>40.14</v>
+        <v>43.36</v>
       </c>
       <c r="X14" t="n">
-        <v>11.98</v>
+        <v>12.31</v>
       </c>
       <c r="Y14" t="n">
         <v>21.99</v>
@@ -1943,7 +1943,7 @@
         <v>-35.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1957,7 +1957,7 @@
         <v>-5</v>
       </c>
       <c r="AI14" t="n">
-        <v>61.8</v>
+        <v>63.8</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>66.8</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="15">
@@ -2013,13 +2013,13 @@
         <v>3.02</v>
       </c>
       <c r="P15" t="n">
-        <v>54.24</v>
+        <v>54.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>57.6542</v>
+        <v>57.5128</v>
       </c>
       <c r="R15" t="n">
-        <v>55.2581</v>
+        <v>55.2853</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,28 +2027,28 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>-6.31</v>
+        <v>-2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>3.59</v>
+        <v>6.14</v>
       </c>
       <c r="W15" t="n">
-        <v>15.2</v>
+        <v>16.5</v>
       </c>
       <c r="X15" t="n">
-        <v>41.8</v>
+        <v>42.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>21.52</v>
+        <v>21.51</v>
       </c>
       <c r="Z15" t="n">
         <v>-18.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>61.2</v>
+        <v>62.2</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>54.2</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="16">
@@ -2115,16 +2115,16 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P16" t="n">
-        <v>33.935</v>
+        <v>34.135</v>
       </c>
       <c r="Q16" t="n">
-        <v>27.7077</v>
+        <v>27.8625</v>
       </c>
       <c r="R16" t="n">
-        <v>26.8726</v>
+        <v>26.912</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>24.78</v>
+        <v>27.27</v>
       </c>
       <c r="U16" t="n">
-        <v>34.02</v>
+        <v>35.97</v>
       </c>
       <c r="V16" t="n">
-        <v>22.44</v>
+        <v>25.7</v>
       </c>
       <c r="W16" t="n">
-        <v>26.27</v>
+        <v>26.43</v>
       </c>
       <c r="X16" t="n">
-        <v>11.42</v>
+        <v>11.54</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.31</v>
+        <v>24.3</v>
       </c>
       <c r="Z16" t="n">
         <v>-33.89</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>61.1</v>
+        <v>61.8</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>61.1</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="17">
@@ -2220,16 +2220,16 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P17" t="n">
-        <v>64.45999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.3816</v>
+        <v>63.382</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0112</v>
+        <v>63.0235</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>2.24</v>
+        <v>3.13</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V17" t="n">
-        <v>2.28</v>
+        <v>3.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0.26</v>
+        <v>0.97</v>
       </c>
       <c r="X17" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
       <c r="Y17" t="n">
         <v>10.18</v>
@@ -2258,7 +2258,7 @@
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>59.6</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>59.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -2325,16 +2325,16 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P18" t="n">
-        <v>91.03</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>70.9872</v>
+        <v>71.6362</v>
       </c>
       <c r="R18" t="n">
-        <v>56.4856</v>
+        <v>56.7487</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,28 +2342,28 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>23.72</v>
+        <v>22.11</v>
       </c>
       <c r="U18" t="n">
-        <v>48.5</v>
+        <v>50.91</v>
       </c>
       <c r="V18" t="n">
-        <v>79.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="W18" t="n">
-        <v>146.16</v>
+        <v>157.55</v>
       </c>
       <c r="X18" t="n">
-        <v>36.51</v>
+        <v>37.18</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.96</v>
+        <v>30.97</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
         <v>-23</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>101.01</v>
+        <v>102.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>83.08920000000001</v>
+        <v>83.624</v>
       </c>
       <c r="R19" t="n">
-        <v>75.4306</v>
+        <v>75.6191</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,19 +2447,19 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>17.41</v>
+        <v>18.07</v>
       </c>
       <c r="U19" t="n">
-        <v>33.08</v>
+        <v>34.01</v>
       </c>
       <c r="V19" t="n">
-        <v>40.86</v>
+        <v>47.16</v>
       </c>
       <c r="W19" t="n">
-        <v>75.33</v>
+        <v>81.75</v>
       </c>
       <c r="X19" t="n">
-        <v>16.31</v>
+        <v>16.66</v>
       </c>
       <c r="Y19" t="n">
         <v>28.13</v>
@@ -2468,7 +2468,7 @@
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2535,16 +2535,16 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P20" t="n">
-        <v>4.891</v>
+        <v>4.9175</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9077</v>
+        <v>4.9074</v>
       </c>
       <c r="R20" t="n">
-        <v>4.9271</v>
+        <v>4.9272</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>-0.85</v>
+        <v>-0.08</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.73</v>
+        <v>-1.2</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.88</v>
+        <v>-0.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.39</v>
+        <v>-1.28</v>
       </c>
       <c r="Y20" t="n">
         <v>4.66</v>
@@ -2573,7 +2573,7 @@
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.73</v>
+        <v>-0.7</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>32.9</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="21">
@@ -2640,16 +2640,16 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P21" t="n">
-        <v>23.56</v>
+        <v>23.685</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6306</v>
+        <v>23.6292</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7484</v>
+        <v>23.749</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>-0.7</v>
+        <v>-0.06</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.87</v>
+        <v>-1.39</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9</v>
+        <v>-0.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.72</v>
+        <v>-1.61</v>
       </c>
       <c r="Y21" t="n">
         <v>4.79</v>
@@ -2678,7 +2678,7 @@
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -648,13 +648,13 @@
         <v>5.04</v>
       </c>
       <c r="P2" t="n">
-        <v>69.18000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>60.1912</v>
+        <v>60.1956</v>
       </c>
       <c r="R2" t="n">
-        <v>53.476</v>
+        <v>53.4771</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,22 +662,22 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>15.57</v>
+        <v>15.94</v>
       </c>
       <c r="U2" t="n">
-        <v>19.19</v>
+        <v>19.57</v>
       </c>
       <c r="V2" t="n">
-        <v>39.91</v>
+        <v>40.36</v>
       </c>
       <c r="W2" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
       <c r="X2" t="n">
-        <v>17.1</v>
+        <v>17.18</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.89</v>
+        <v>13.9</v>
       </c>
       <c r="Z2" t="n">
         <v>-17.8</v>
@@ -753,13 +753,13 @@
         <v>5.04</v>
       </c>
       <c r="P3" t="n">
-        <v>377.11</v>
+        <v>377.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>386.4334</v>
+        <v>386.4492</v>
       </c>
       <c r="R3" t="n">
-        <v>357.1957</v>
+        <v>357.1996</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,19 +767,19 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-2.78</v>
+        <v>-2.58</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.91</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>11.67</v>
+        <v>11.9</v>
       </c>
       <c r="W3" t="n">
-        <v>34.14</v>
+        <v>34.42</v>
       </c>
       <c r="X3" t="n">
-        <v>20.13</v>
+        <v>20.18</v>
       </c>
       <c r="Y3" t="n">
         <v>16.01</v>
@@ -788,7 +788,7 @@
         <v>-16.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -858,13 +858,13 @@
         <v>5.04</v>
       </c>
       <c r="P4" t="n">
-        <v>199.5</v>
+        <v>200.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>166.913</v>
+        <v>166.929</v>
       </c>
       <c r="R4" t="n">
-        <v>154.7564</v>
+        <v>154.7604</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>18.51</v>
+        <v>18.99</v>
       </c>
       <c r="U4" t="n">
-        <v>31.22</v>
+        <v>31.75</v>
       </c>
       <c r="V4" t="n">
-        <v>32.7</v>
+        <v>33.23</v>
       </c>
       <c r="W4" t="n">
-        <v>54.21</v>
+        <v>54.83</v>
       </c>
       <c r="X4" t="n">
-        <v>21.35</v>
+        <v>21.45</v>
       </c>
       <c r="Y4" t="n">
         <v>20.85</v>
@@ -907,7 +907,7 @@
         <v>-5</v>
       </c>
       <c r="AI4" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -925,30 +925,30 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>74.8</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FGQI.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fidelity Global Quality Income UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -960,16 +960,16 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>4.66</v>
+        <v>5.04</v>
       </c>
       <c r="P5" t="n">
-        <v>9.769</v>
+        <v>47.395</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.2721</v>
+        <v>43.3045</v>
       </c>
       <c r="R5" t="n">
-        <v>8.878399999999999</v>
+        <v>39.6427</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>4.1</v>
+        <v>6.77</v>
       </c>
       <c r="U5" t="n">
-        <v>5.45</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>13.59</v>
+        <v>25.17</v>
       </c>
       <c r="W5" t="n">
-        <v>24.24</v>
+        <v>44.28</v>
       </c>
       <c r="X5" t="n">
-        <v>11.94</v>
+        <v>9.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.4</v>
+        <v>16.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>-19.89</v>
+        <v>-22.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1030,30 +1030,30 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>68.2</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>FGQI.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Fidelity Global Quality Income UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Satellite</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Quality Dividend</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.04</v>
+        <v>4.66</v>
       </c>
       <c r="P6" t="n">
-        <v>47.005</v>
+        <v>9.797000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.2967</v>
+        <v>9.272600000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>39.6407</v>
+        <v>8.8786</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>5.89</v>
+        <v>4.39</v>
       </c>
       <c r="U6" t="n">
-        <v>8.970000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="V6" t="n">
-        <v>24.14</v>
+        <v>13.92</v>
       </c>
       <c r="W6" t="n">
-        <v>43.09</v>
+        <v>24.59</v>
       </c>
       <c r="X6" t="n">
-        <v>8.84</v>
+        <v>12.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.3</v>
+        <v>13.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>-22.01</v>
+        <v>-19.89</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>73.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>71.09999999999999</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="7">
@@ -1173,13 +1173,13 @@
         <v>5.04</v>
       </c>
       <c r="P7" t="n">
-        <v>162.59</v>
+        <v>162.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>151.4934</v>
+        <v>151.497</v>
       </c>
       <c r="R7" t="n">
-        <v>145.2057</v>
+        <v>145.2066</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>5.85</v>
+        <v>5.96</v>
       </c>
       <c r="U7" t="n">
-        <v>8.470000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="V7" t="n">
-        <v>15.18</v>
+        <v>15.31</v>
       </c>
       <c r="W7" t="n">
-        <v>26.65</v>
+        <v>26.79</v>
       </c>
       <c r="X7" t="n">
-        <v>12.43</v>
+        <v>12.46</v>
       </c>
       <c r="Y7" t="n">
         <v>13.74</v>
@@ -1278,13 +1278,13 @@
         <v>5.04</v>
       </c>
       <c r="P8" t="n">
-        <v>123.42</v>
+        <v>123.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>115.1654</v>
+        <v>115.1678</v>
       </c>
       <c r="R8" t="n">
-        <v>111.1285</v>
+        <v>111.1291</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>5.71</v>
+        <v>5.82</v>
       </c>
       <c r="U8" t="n">
-        <v>8.539999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>13.97</v>
+        <v>14.08</v>
       </c>
       <c r="W8" t="n">
-        <v>24.67</v>
+        <v>24.79</v>
       </c>
       <c r="X8" t="n">
-        <v>13.06</v>
+        <v>13.08</v>
       </c>
       <c r="Y8" t="n">
         <v>14.2</v>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>68.09999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="9">
@@ -1383,13 +1383,13 @@
         <v>5.04</v>
       </c>
       <c r="P9" t="n">
-        <v>74.84</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>70.59520000000001</v>
+        <v>70.5976</v>
       </c>
       <c r="R9" t="n">
-        <v>68.1117</v>
+        <v>68.1123</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,19 +1397,19 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>4.28</v>
+        <v>4.44</v>
       </c>
       <c r="U9" t="n">
-        <v>6.01</v>
+        <v>6.18</v>
       </c>
       <c r="V9" t="n">
-        <v>13.6</v>
+        <v>13.78</v>
       </c>
       <c r="W9" t="n">
-        <v>20.17</v>
+        <v>20.36</v>
       </c>
       <c r="X9" t="n">
-        <v>11.55</v>
+        <v>11.59</v>
       </c>
       <c r="Y9" t="n">
         <v>14.16</v>
@@ -1418,7 +1418,7 @@
         <v>-20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>66.2</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1488,13 +1488,13 @@
         <v>5.04</v>
       </c>
       <c r="P10" t="n">
-        <v>99.81</v>
+        <v>100.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>89.21980000000001</v>
+        <v>89.2248</v>
       </c>
       <c r="R10" t="n">
-        <v>84.13</v>
+        <v>84.1313</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,19 +1502,19 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>9.32</v>
+        <v>9.59</v>
       </c>
       <c r="U10" t="n">
-        <v>15.64</v>
+        <v>15.93</v>
       </c>
       <c r="V10" t="n">
-        <v>23.99</v>
+        <v>24.3</v>
       </c>
       <c r="W10" t="n">
-        <v>30.71</v>
+        <v>31.04</v>
       </c>
       <c r="X10" t="n">
-        <v>14.42</v>
+        <v>14.48</v>
       </c>
       <c r="Y10" t="n">
         <v>17.29</v>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="11">
@@ -1593,13 +1593,13 @@
         <v>5.04</v>
       </c>
       <c r="P11" t="n">
-        <v>125.03</v>
+        <v>124.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>115.6198</v>
+        <v>115.6166</v>
       </c>
       <c r="R11" t="n">
-        <v>111.8554</v>
+        <v>111.8546</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>6.34</v>
+        <v>6.2</v>
       </c>
       <c r="U11" t="n">
-        <v>11.11</v>
+        <v>10.97</v>
       </c>
       <c r="V11" t="n">
-        <v>13.76</v>
+        <v>13.61</v>
       </c>
       <c r="W11" t="n">
-        <v>26.36</v>
+        <v>26.2</v>
       </c>
       <c r="X11" t="n">
-        <v>14.84</v>
+        <v>14.81</v>
       </c>
       <c r="Y11" t="n">
         <v>15.2</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,19 +1660,19 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco Nasdaq-100 UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nasdaq / Tech</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1698,13 +1698,13 @@
         <v>5.04</v>
       </c>
       <c r="P12" t="n">
-        <v>627.9400000000001</v>
+        <v>63.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>554.0558</v>
+        <v>60.3669</v>
       </c>
       <c r="R12" t="n">
-        <v>527.6201</v>
+        <v>58.0783</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,28 +1712,28 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>10.6</v>
+        <v>5.06</v>
       </c>
       <c r="U12" t="n">
-        <v>21.18</v>
+        <v>2.47</v>
       </c>
       <c r="V12" t="n">
-        <v>21.13</v>
+        <v>15.37</v>
       </c>
       <c r="W12" t="n">
-        <v>37.22</v>
+        <v>18.72</v>
       </c>
       <c r="X12" t="n">
-        <v>18.55</v>
+        <v>10.32</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.89</v>
+        <v>14.51</v>
       </c>
       <c r="Z12" t="n">
-        <v>-31.11</v>
+        <v>-20.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,19 +1765,19 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>69.2</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>EQQQ.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>Invesco Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1788,7 +1788,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Nasdaq / Tech</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1803,13 +1803,13 @@
         <v>5.04</v>
       </c>
       <c r="P13" t="n">
-        <v>63.47</v>
+        <v>626.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.3569</v>
+        <v>554.0362</v>
       </c>
       <c r="R13" t="n">
-        <v>58.0758</v>
+        <v>527.6152</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,28 +1817,28 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>4.24</v>
+        <v>10.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>20.99</v>
       </c>
       <c r="V13" t="n">
-        <v>14.47</v>
+        <v>20.94</v>
       </c>
       <c r="W13" t="n">
-        <v>17.79</v>
+        <v>37</v>
       </c>
       <c r="X13" t="n">
-        <v>10.14</v>
+        <v>18.51</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.49</v>
+        <v>19.89</v>
       </c>
       <c r="Z13" t="n">
-        <v>-20.85</v>
+        <v>-31.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI13" t="n">
-        <v>64.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>64.8</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1908,13 +1908,13 @@
         <v>5.04</v>
       </c>
       <c r="P14" t="n">
-        <v>17.946</v>
+        <v>18.012</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.2406</v>
+        <v>15.242</v>
       </c>
       <c r="R14" t="n">
-        <v>14.1996</v>
+        <v>14.2</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>11.66</v>
+        <v>12.07</v>
       </c>
       <c r="U14" t="n">
-        <v>26.08</v>
+        <v>26.54</v>
       </c>
       <c r="V14" t="n">
-        <v>34.01</v>
+        <v>34.5</v>
       </c>
       <c r="W14" t="n">
-        <v>43.36</v>
+        <v>43.89</v>
       </c>
       <c r="X14" t="n">
-        <v>12.31</v>
+        <v>12.39</v>
       </c>
       <c r="Y14" t="n">
-        <v>21.99</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
         <v>-35.29</v>
@@ -1957,7 +1957,7 @@
         <v>-5</v>
       </c>
       <c r="AI14" t="n">
-        <v>63.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2013,13 +2013,13 @@
         <v>3.02</v>
       </c>
       <c r="P15" t="n">
-        <v>54.62</v>
+        <v>54.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>57.5128</v>
+        <v>57.5198</v>
       </c>
       <c r="R15" t="n">
-        <v>55.2853</v>
+        <v>55.2871</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,28 +2027,28 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>-2.9</v>
+        <v>-2.28</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>6.14</v>
+        <v>6.82</v>
       </c>
       <c r="W15" t="n">
-        <v>16.5</v>
+        <v>17.24</v>
       </c>
       <c r="X15" t="n">
-        <v>42.06</v>
+        <v>42.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>21.51</v>
+        <v>21.52</v>
       </c>
       <c r="Z15" t="n">
         <v>-18.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>62.2</v>
+        <v>62.6</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="16">
@@ -2118,13 +2118,13 @@
         <v>5.04</v>
       </c>
       <c r="P16" t="n">
-        <v>34.135</v>
+        <v>34.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>27.8625</v>
+        <v>27.8696</v>
       </c>
       <c r="R16" t="n">
-        <v>26.912</v>
+        <v>26.9138</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2132,28 +2132,28 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>27.27</v>
+        <v>28.6</v>
       </c>
       <c r="U16" t="n">
-        <v>35.97</v>
+        <v>37.38</v>
       </c>
       <c r="V16" t="n">
-        <v>25.7</v>
+        <v>27.01</v>
       </c>
       <c r="W16" t="n">
-        <v>26.43</v>
+        <v>27.74</v>
       </c>
       <c r="X16" t="n">
-        <v>11.54</v>
+        <v>11.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.3</v>
+        <v>24.31</v>
       </c>
       <c r="Z16" t="n">
         <v>-33.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>61.8</v>
+        <v>62.5</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>61.8</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="17">
@@ -2223,13 +2223,13 @@
         <v>5.04</v>
       </c>
       <c r="P17" t="n">
-        <v>64.59999999999999</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.382</v>
+        <v>63.3836</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0235</v>
+        <v>63.0239</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="V17" t="n">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
       <c r="Y17" t="n">
         <v>10.18</v>
@@ -2328,13 +2328,13 @@
         <v>5.04</v>
       </c>
       <c r="P18" t="n">
-        <v>93.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>71.6362</v>
+        <v>71.6182</v>
       </c>
       <c r="R18" t="n">
-        <v>56.7487</v>
+        <v>56.7442</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,28 +2342,28 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>22.11</v>
+        <v>20.93</v>
       </c>
       <c r="U18" t="n">
-        <v>50.91</v>
+        <v>49.46</v>
       </c>
       <c r="V18" t="n">
-        <v>89.22</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>157.55</v>
+        <v>155.07</v>
       </c>
       <c r="X18" t="n">
-        <v>37.18</v>
+        <v>36.91</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.97</v>
+        <v>30.96</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
         <v>-23</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="19">
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>102.6</v>
+        <v>102.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>83.624</v>
+        <v>83.6236</v>
       </c>
       <c r="R19" t="n">
-        <v>75.6191</v>
+        <v>75.619</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,22 +2447,22 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>18.07</v>
+        <v>18.04</v>
       </c>
       <c r="U19" t="n">
-        <v>34.01</v>
+        <v>33.99</v>
       </c>
       <c r="V19" t="n">
-        <v>47.16</v>
+        <v>47.13</v>
       </c>
       <c r="W19" t="n">
-        <v>81.75</v>
+        <v>81.72</v>
       </c>
       <c r="X19" t="n">
-        <v>16.66</v>
+        <v>16.65</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.13</v>
+        <v>28.12</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
@@ -2538,7 +2538,7 @@
         <v>5.04</v>
       </c>
       <c r="P20" t="n">
-        <v>4.9175</v>
+        <v>4.917</v>
       </c>
       <c r="Q20" t="n">
         <v>4.9074</v>
@@ -2552,16 +2552,16 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2</v>
+        <v>-1.21</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="W20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
         <v>-1.28</v>
@@ -2643,13 +2643,13 @@
         <v>5.04</v>
       </c>
       <c r="P21" t="n">
-        <v>23.685</v>
+        <v>23.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6292</v>
+        <v>23.6289</v>
       </c>
       <c r="R21" t="n">
-        <v>23.749</v>
+        <v>23.7489</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.39</v>
+        <v>-1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.25</v>
+        <v>-0.32</v>
       </c>
       <c r="W21" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.61</v>
+        <v>-1.62</v>
       </c>
       <c r="Y21" t="n">
         <v>4.79</v>
@@ -2678,7 +2678,7 @@
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -645,7 +645,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P2" t="n">
         <v>69.40000000000001</v>
@@ -674,10 +674,10 @@
         <v>58.9</v>
       </c>
       <c r="X2" t="n">
-        <v>17.18</v>
+        <v>17.16</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="Z2" t="n">
         <v>-17.8</v>
@@ -750,7 +750,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P3" t="n">
         <v>377.9</v>
@@ -779,16 +779,16 @@
         <v>34.42</v>
       </c>
       <c r="X3" t="n">
-        <v>20.18</v>
+        <v>20.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.01</v>
+        <v>16.02</v>
       </c>
       <c r="Z3" t="n">
         <v>-16.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="4">
@@ -855,7 +855,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P4" t="n">
         <v>200.3</v>
@@ -884,16 +884,16 @@
         <v>54.83</v>
       </c>
       <c r="X4" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.85</v>
+        <v>20.86</v>
       </c>
       <c r="Z4" t="n">
         <v>-33.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>-5</v>
       </c>
       <c r="AI4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +960,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P5" t="n">
         <v>47.395</v>
@@ -989,7 +989,7 @@
         <v>44.28</v>
       </c>
       <c r="X5" t="n">
-        <v>9.02</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Y5" t="n">
         <v>16.32</v>
@@ -998,7 +998,7 @@
         <v>-22.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P7" t="n">
         <v>162.77</v>
@@ -1199,7 +1199,7 @@
         <v>26.79</v>
       </c>
       <c r="X7" t="n">
-        <v>12.46</v>
+        <v>12.38</v>
       </c>
       <c r="Y7" t="n">
         <v>13.74</v>
@@ -1275,7 +1275,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P8" t="n">
         <v>123.54</v>
@@ -1304,10 +1304,10 @@
         <v>24.79</v>
       </c>
       <c r="X8" t="n">
-        <v>13.08</v>
+        <v>13.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.2</v>
+        <v>14.21</v>
       </c>
       <c r="Z8" t="n">
         <v>-21.63</v>
@@ -1380,7 +1380,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P9" t="n">
         <v>74.95999999999999</v>
@@ -1409,7 +1409,7 @@
         <v>20.36</v>
       </c>
       <c r="X9" t="n">
-        <v>11.59</v>
+        <v>11.55</v>
       </c>
       <c r="Y9" t="n">
         <v>14.16</v>
@@ -1418,7 +1418,7 @@
         <v>-20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>66.40000000000001</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="10">
@@ -1485,7 +1485,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P10" t="n">
         <v>100.06</v>
@@ -1514,7 +1514,7 @@
         <v>31.04</v>
       </c>
       <c r="X10" t="n">
-        <v>14.48</v>
+        <v>14.32</v>
       </c>
       <c r="Y10" t="n">
         <v>17.29</v>
@@ -1523,7 +1523,7 @@
         <v>-23.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1590,7 +1590,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P11" t="n">
         <v>124.87</v>
@@ -1619,10 +1619,10 @@
         <v>26.2</v>
       </c>
       <c r="X11" t="n">
-        <v>14.81</v>
+        <v>14.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.2</v>
+        <v>15.21</v>
       </c>
       <c r="Z11" t="n">
         <v>-23.28</v>
@@ -1695,7 +1695,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P12" t="n">
         <v>63.97</v>
@@ -1724,10 +1724,10 @@
         <v>18.72</v>
       </c>
       <c r="X12" t="n">
-        <v>10.32</v>
+        <v>10.34</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.51</v>
+        <v>14.52</v>
       </c>
       <c r="Z12" t="n">
         <v>-20.85</v>
@@ -1800,7 +1800,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P13" t="n">
         <v>626.96</v>
@@ -1829,7 +1829,7 @@
         <v>37</v>
       </c>
       <c r="X13" t="n">
-        <v>18.51</v>
+        <v>18.29</v>
       </c>
       <c r="Y13" t="n">
         <v>19.89</v>
@@ -1838,7 +1838,7 @@
         <v>-31.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
         <v>-4</v>
       </c>
       <c r="AI13" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1905,7 +1905,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P14" t="n">
         <v>18.012</v>
@@ -1934,10 +1934,10 @@
         <v>43.89</v>
       </c>
       <c r="X14" t="n">
-        <v>12.39</v>
+        <v>12.27</v>
       </c>
       <c r="Y14" t="n">
-        <v>22</v>
+        <v>22.01</v>
       </c>
       <c r="Z14" t="n">
         <v>-35.29</v>
@@ -2115,7 +2115,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P16" t="n">
         <v>34.49</v>
@@ -2144,7 +2144,7 @@
         <v>27.74</v>
       </c>
       <c r="X16" t="n">
-        <v>11.77</v>
+        <v>11.49</v>
       </c>
       <c r="Y16" t="n">
         <v>24.31</v>
@@ -2153,7 +2153,7 @@
         <v>-33.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="17">
@@ -2220,7 +2220,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P17" t="n">
         <v>64.68000000000001</v>
@@ -2249,7 +2249,7 @@
         <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
       <c r="Y17" t="n">
         <v>10.18</v>
@@ -2258,7 +2258,7 @@
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="18">
@@ -2325,7 +2325,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P18" t="n">
         <v>92.5</v>
@@ -2354,10 +2354,10 @@
         <v>155.07</v>
       </c>
       <c r="X18" t="n">
-        <v>36.91</v>
+        <v>36.93</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.96</v>
+        <v>30.97</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
@@ -2459,16 +2459,16 @@
         <v>81.72</v>
       </c>
       <c r="X19" t="n">
-        <v>16.65</v>
+        <v>16.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.12</v>
+        <v>28.13</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2535,7 +2535,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P20" t="n">
         <v>4.917</v>
@@ -2564,7 +2564,7 @@
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.28</v>
+        <v>-1.31</v>
       </c>
       <c r="Y20" t="n">
         <v>4.66</v>
@@ -2573,7 +2573,7 @@
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="21">
@@ -2640,7 +2640,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P21" t="n">
         <v>23.67</v>
@@ -2669,7 +2669,7 @@
         <v>2.25</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.62</v>
+        <v>-1.66</v>
       </c>
       <c r="Y21" t="n">
         <v>4.79</v>
@@ -2678,7 +2678,7 @@
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -648,13 +648,13 @@
         <v>5.03</v>
       </c>
       <c r="P2" t="n">
-        <v>69.40000000000001</v>
+        <v>70.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>60.1956</v>
+        <v>60.476</v>
       </c>
       <c r="R2" t="n">
-        <v>53.4771</v>
+        <v>53.6047</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>15.94</v>
+        <v>16.82</v>
       </c>
       <c r="U2" t="n">
-        <v>19.57</v>
+        <v>21.21</v>
       </c>
       <c r="V2" t="n">
-        <v>40.36</v>
+        <v>41.62</v>
       </c>
       <c r="W2" t="n">
-        <v>58.9</v>
+        <v>62.17</v>
       </c>
       <c r="X2" t="n">
-        <v>17.16</v>
+        <v>17.22</v>
       </c>
       <c r="Y2" t="n">
         <v>13.91</v>
@@ -721,24 +721,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -750,16 +750,16 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>5.03</v>
+        <v>3.03</v>
       </c>
       <c r="P3" t="n">
-        <v>377.9</v>
+        <v>55.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>386.4492</v>
+        <v>57.3888</v>
       </c>
       <c r="R3" t="n">
-        <v>357.1996</v>
+        <v>55.3157</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-2.58</v>
+        <v>-0.11</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.720000000000001</v>
+        <v>-5.94</v>
       </c>
       <c r="V3" t="n">
-        <v>11.9</v>
+        <v>10.03</v>
       </c>
       <c r="W3" t="n">
-        <v>34.42</v>
+        <v>20.46</v>
       </c>
       <c r="X3" t="n">
-        <v>20.01</v>
+        <v>42.94</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.02</v>
+        <v>21.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>-16.7</v>
+        <v>-18.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -796,13 +796,13 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.2</v>
+        <v>80.2</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Utile come protezione macro/geopolitica.</t>
+          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -826,24 +826,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -858,13 +858,13 @@
         <v>5.03</v>
       </c>
       <c r="P4" t="n">
-        <v>200.3</v>
+        <v>373.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>166.929</v>
+        <v>385.337</v>
       </c>
       <c r="R4" t="n">
-        <v>154.7604</v>
+        <v>357.6605</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>18.99</v>
+        <v>-2.77</v>
       </c>
       <c r="U4" t="n">
-        <v>31.75</v>
+        <v>-12.2</v>
       </c>
       <c r="V4" t="n">
-        <v>33.23</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>54.83</v>
+        <v>30.72</v>
       </c>
       <c r="X4" t="n">
-        <v>21.25</v>
+        <v>19.81</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.86</v>
+        <v>16.03</v>
       </c>
       <c r="Z4" t="n">
-        <v>-33.01</v>
+        <v>-16.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.92</v>
+        <v>1.11</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -901,13 +901,13 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>75.8</v>
+        <v>79.7</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Utile come protezione macro/geopolitica.</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -925,30 +925,30 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>74.8</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -963,13 +963,13 @@
         <v>5.03</v>
       </c>
       <c r="P5" t="n">
-        <v>47.395</v>
+        <v>203.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>43.3045</v>
+        <v>167.9346</v>
       </c>
       <c r="R5" t="n">
-        <v>39.6427</v>
+        <v>155.0818</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>6.77</v>
+        <v>19.72</v>
       </c>
       <c r="U5" t="n">
-        <v>9.880000000000001</v>
+        <v>36.57</v>
       </c>
       <c r="V5" t="n">
-        <v>25.17</v>
+        <v>35.13</v>
       </c>
       <c r="W5" t="n">
-        <v>44.28</v>
+        <v>59.13</v>
       </c>
       <c r="X5" t="n">
-        <v>8.859999999999999</v>
+        <v>21.61</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.32</v>
+        <v>20.87</v>
       </c>
       <c r="Z5" t="n">
-        <v>-22.01</v>
+        <v>-33.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1030,30 +1030,30 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>71.59999999999999</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FGQI.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fidelity Global Quality Income UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>4.66</v>
+        <v>5.03</v>
       </c>
       <c r="P6" t="n">
-        <v>9.797000000000001</v>
+        <v>47.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.272600000000001</v>
+        <v>43.4476</v>
       </c>
       <c r="R6" t="n">
-        <v>8.8786</v>
+        <v>39.71</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>4.39</v>
+        <v>7.71</v>
       </c>
       <c r="U6" t="n">
-        <v>5.75</v>
+        <v>11.31</v>
       </c>
       <c r="V6" t="n">
-        <v>13.92</v>
+        <v>26.3</v>
       </c>
       <c r="W6" t="n">
-        <v>24.59</v>
+        <v>45.89</v>
       </c>
       <c r="X6" t="n">
-        <v>12.01</v>
+        <v>8.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.4</v>
+        <v>16.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>-19.89</v>
+        <v>-22.01</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.75</v>
+        <v>0.42</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>73.5</v>
+        <v>74.2</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1135,30 +1135,30 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>68.5</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>FGQI.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>Fidelity Global Quality Income UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Satellite</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Quality Dividend</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1170,16 +1170,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.03</v>
+        <v>4.67</v>
       </c>
       <c r="P7" t="n">
-        <v>162.77</v>
+        <v>9.739000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>151.497</v>
+        <v>9.2857</v>
       </c>
       <c r="R7" t="n">
-        <v>145.2066</v>
+        <v>8.8864</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>5.96</v>
+        <v>4.07</v>
       </c>
       <c r="U7" t="n">
-        <v>8.59</v>
+        <v>5.55</v>
       </c>
       <c r="V7" t="n">
-        <v>15.31</v>
+        <v>12.83</v>
       </c>
       <c r="W7" t="n">
-        <v>26.79</v>
+        <v>25.1</v>
       </c>
       <c r="X7" t="n">
-        <v>12.38</v>
+        <v>11.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.74</v>
+        <v>13.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>-20.96</v>
+        <v>-19.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1216,13 +1216,13 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>69</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1278,13 +1278,13 @@
         <v>5.03</v>
       </c>
       <c r="P8" t="n">
-        <v>123.54</v>
+        <v>162.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>115.1678</v>
+        <v>151.8096</v>
       </c>
       <c r="R8" t="n">
-        <v>111.1291</v>
+        <v>145.3521</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="U8" t="n">
-        <v>8.640000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="V8" t="n">
-        <v>14.08</v>
+        <v>14.83</v>
       </c>
       <c r="W8" t="n">
-        <v>24.79</v>
+        <v>27.9</v>
       </c>
       <c r="X8" t="n">
-        <v>13.01</v>
+        <v>12.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.21</v>
+        <v>13.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>-21.63</v>
+        <v>-20.96</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1345,30 +1345,30 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>68.2</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Quality Factor UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1383,13 +1383,13 @@
         <v>5.03</v>
       </c>
       <c r="P9" t="n">
-        <v>74.95999999999999</v>
+        <v>123.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>70.5976</v>
+        <v>115.3898</v>
       </c>
       <c r="R9" t="n">
-        <v>68.1123</v>
+        <v>111.2297</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,28 +1397,28 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>4.44</v>
+        <v>5.58</v>
       </c>
       <c r="U9" t="n">
-        <v>6.18</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>13.78</v>
+        <v>13.4</v>
       </c>
       <c r="W9" t="n">
-        <v>20.36</v>
+        <v>25.71</v>
       </c>
       <c r="X9" t="n">
-        <v>11.55</v>
+        <v>12.86</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.16</v>
+        <v>14.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>-20.6</v>
+        <v>-21.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>66.3</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IWMO.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
+          <t>iShares MSCI World Quality Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1473,7 +1473,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         <v>5.03</v>
       </c>
       <c r="P10" t="n">
-        <v>100.06</v>
+        <v>74.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>89.2248</v>
+        <v>70.7004</v>
       </c>
       <c r="R10" t="n">
-        <v>84.1313</v>
+        <v>68.1683</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,28 +1502,28 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>9.59</v>
+        <v>4.14</v>
       </c>
       <c r="U10" t="n">
-        <v>15.93</v>
+        <v>6.14</v>
       </c>
       <c r="V10" t="n">
-        <v>24.3</v>
+        <v>12.63</v>
       </c>
       <c r="W10" t="n">
-        <v>31.04</v>
+        <v>20.97</v>
       </c>
       <c r="X10" t="n">
-        <v>14.32</v>
+        <v>11.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.29</v>
+        <v>14.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>-23.45</v>
+        <v>-20.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>69.8</v>
+        <v>71.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,30 +1555,30 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>69.8</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VUAA.MI</t>
+          <t>IWMO.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard S&amp;P 500 UCITS ETF</t>
+          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USA Large Cap</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         <v>5.03</v>
       </c>
       <c r="P11" t="n">
-        <v>124.87</v>
+        <v>100.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>115.6166</v>
+        <v>89.5754</v>
       </c>
       <c r="R11" t="n">
-        <v>111.8546</v>
+        <v>84.2414</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,28 +1607,28 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>6.2</v>
+        <v>10.49</v>
       </c>
       <c r="U11" t="n">
-        <v>10.97</v>
+        <v>17.98</v>
       </c>
       <c r="V11" t="n">
-        <v>13.61</v>
+        <v>25.02</v>
       </c>
       <c r="W11" t="n">
-        <v>26.2</v>
+        <v>32.91</v>
       </c>
       <c r="X11" t="n">
-        <v>14.74</v>
+        <v>14.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.21</v>
+        <v>17.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>-23.28</v>
+        <v>-23.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>68.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,19 +1660,19 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>68.2</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>VUAA.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>Vanguard S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>USA Large Cap</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1698,13 +1698,13 @@
         <v>5.03</v>
       </c>
       <c r="P12" t="n">
-        <v>63.97</v>
+        <v>124.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>60.3669</v>
+        <v>115.8708</v>
       </c>
       <c r="R12" t="n">
-        <v>58.0783</v>
+        <v>111.9564</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,28 +1712,28 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>5.06</v>
+        <v>6.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2.47</v>
+        <v>11.82</v>
       </c>
       <c r="V12" t="n">
-        <v>15.37</v>
+        <v>13.1</v>
       </c>
       <c r="W12" t="n">
-        <v>18.72</v>
+        <v>27.78</v>
       </c>
       <c r="X12" t="n">
-        <v>10.34</v>
+        <v>14.64</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.52</v>
+        <v>15.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>-20.85</v>
+        <v>-23.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>65.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.3</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1803,13 +1803,13 @@
         <v>5.03</v>
       </c>
       <c r="P13" t="n">
-        <v>626.96</v>
+        <v>629.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>554.0362</v>
+        <v>556.1654</v>
       </c>
       <c r="R13" t="n">
-        <v>527.6152</v>
+        <v>528.3268</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,19 +1817,19 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>10.42</v>
+        <v>11.03</v>
       </c>
       <c r="U13" t="n">
-        <v>20.99</v>
+        <v>23.06</v>
       </c>
       <c r="V13" t="n">
-        <v>20.94</v>
+        <v>20.85</v>
       </c>
       <c r="W13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="X13" t="n">
-        <v>18.29</v>
+        <v>18.37</v>
       </c>
       <c r="Y13" t="n">
         <v>19.89</v>
@@ -1852,7 +1852,7 @@
         <v>-4</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>65.7</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1870,30 +1870,30 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>69</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         <v>5.03</v>
       </c>
       <c r="P14" t="n">
-        <v>18.012</v>
+        <v>63.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.242</v>
+        <v>60.4435</v>
       </c>
       <c r="R14" t="n">
-        <v>14.2</v>
+        <v>58.1283</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>12.07</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>26.54</v>
+        <v>1.59</v>
       </c>
       <c r="V14" t="n">
-        <v>34.5</v>
+        <v>13.73</v>
       </c>
       <c r="W14" t="n">
-        <v>43.89</v>
+        <v>18.2</v>
       </c>
       <c r="X14" t="n">
-        <v>12.27</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
-        <v>22.01</v>
+        <v>14.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>-35.29</v>
+        <v>-20.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>64.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Drawdown storico importante.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -1975,19 +1975,19 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>69.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1998,7 +1998,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2010,45 +2010,45 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>3.02</v>
+        <v>5.03</v>
       </c>
       <c r="P15" t="n">
-        <v>54.97</v>
+        <v>17.924</v>
       </c>
       <c r="Q15" t="n">
-        <v>57.5198</v>
+        <v>15.3233</v>
       </c>
       <c r="R15" t="n">
-        <v>55.2871</v>
+        <v>14.2242</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>-2.28</v>
+        <v>11.2</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.050000000000001</v>
+        <v>28.56</v>
       </c>
       <c r="V15" t="n">
-        <v>6.82</v>
+        <v>33.22</v>
       </c>
       <c r="W15" t="n">
-        <v>17.24</v>
+        <v>45.87</v>
       </c>
       <c r="X15" t="n">
-        <v>42.36</v>
+        <v>11.98</v>
       </c>
       <c r="Y15" t="n">
-        <v>21.52</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>-18.73</v>
+        <v>-35.29</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.88</v>
+        <v>0.45</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2056,13 +2056,13 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI15" t="n">
-        <v>62.6</v>
+        <v>64.2</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Drawdown storico importante.</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>55.6</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="16">
@@ -2118,13 +2118,13 @@
         <v>5.03</v>
       </c>
       <c r="P16" t="n">
-        <v>34.49</v>
+        <v>34.505</v>
       </c>
       <c r="Q16" t="n">
-        <v>27.8696</v>
+        <v>28.0281</v>
       </c>
       <c r="R16" t="n">
-        <v>26.9138</v>
+        <v>26.9528</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2132,19 +2132,19 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>28.6</v>
+        <v>26.42</v>
       </c>
       <c r="U16" t="n">
-        <v>37.38</v>
+        <v>47.84</v>
       </c>
       <c r="V16" t="n">
-        <v>27.01</v>
+        <v>26.76</v>
       </c>
       <c r="W16" t="n">
-        <v>27.74</v>
+        <v>28.7</v>
       </c>
       <c r="X16" t="n">
-        <v>11.49</v>
+        <v>11.47</v>
       </c>
       <c r="Y16" t="n">
         <v>24.31</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="17">
@@ -2223,13 +2223,13 @@
         <v>5.03</v>
       </c>
       <c r="P17" t="n">
-        <v>64.68000000000001</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.3836</v>
+        <v>63.3652</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0239</v>
+        <v>63.0316</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,28 +2237,28 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>3.26</v>
+        <v>2.37</v>
       </c>
       <c r="U17" t="n">
-        <v>0.62</v>
+        <v>-0.53</v>
       </c>
       <c r="V17" t="n">
-        <v>3.14</v>
+        <v>2.41</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="X17" t="n">
-        <v>6.62</v>
+        <v>6.41</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="Z17" t="n">
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>59.9</v>
+        <v>59.5</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>59.9</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="18">
@@ -2328,13 +2328,13 @@
         <v>5.03</v>
       </c>
       <c r="P18" t="n">
-        <v>92.5</v>
+        <v>94.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>71.6182</v>
+        <v>72.31180000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>56.7442</v>
+        <v>57.0084</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>20.93</v>
+        <v>24.64</v>
       </c>
       <c r="U18" t="n">
-        <v>49.46</v>
+        <v>53.65</v>
       </c>
       <c r="V18" t="n">
-        <v>87.40000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="W18" t="n">
-        <v>155.07</v>
+        <v>166.97</v>
       </c>
       <c r="X18" t="n">
-        <v>36.93</v>
+        <v>37.11</v>
       </c>
       <c r="Y18" t="n">
         <v>30.97</v>
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>102.58</v>
+        <v>103.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>83.6236</v>
+        <v>84.21080000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>75.619</v>
+        <v>75.8129</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,19 +2447,19 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>18.04</v>
+        <v>20.26</v>
       </c>
       <c r="U19" t="n">
-        <v>33.99</v>
+        <v>39.08</v>
       </c>
       <c r="V19" t="n">
-        <v>47.13</v>
+        <v>48.16</v>
       </c>
       <c r="W19" t="n">
-        <v>81.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>16.45</v>
+        <v>16.49</v>
       </c>
       <c r="Y19" t="n">
         <v>28.13</v>
@@ -2468,7 +2468,7 @@
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2538,10 +2538,10 @@
         <v>5.03</v>
       </c>
       <c r="P20" t="n">
-        <v>4.917</v>
+        <v>4.9025</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9074</v>
+        <v>4.9072</v>
       </c>
       <c r="R20" t="n">
         <v>4.9272</v>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>-0.09</v>
+        <v>-0.25</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.21</v>
+        <v>-1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.31</v>
+        <v>-1.34</v>
       </c>
       <c r="Y20" t="n">
         <v>4.66</v>
@@ -2573,7 +2573,7 @@
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="21">
@@ -2643,10 +2643,10 @@
         <v>5.03</v>
       </c>
       <c r="P21" t="n">
-        <v>23.67</v>
+        <v>23.615</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6289</v>
+        <v>23.6277</v>
       </c>
       <c r="R21" t="n">
         <v>23.7489</v>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.46</v>
+        <v>-1.81</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.32</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.66</v>
+        <v>-1.67</v>
       </c>
       <c r="Y21" t="n">
         <v>4.79</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -648,13 +648,13 @@
         <v>5.03</v>
       </c>
       <c r="P2" t="n">
-        <v>70.13</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>60.476</v>
+        <v>60.7476</v>
       </c>
       <c r="R2" t="n">
-        <v>53.6047</v>
+        <v>53.7313</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>16.82</v>
+        <v>16.93</v>
       </c>
       <c r="U2" t="n">
-        <v>21.21</v>
+        <v>20.52</v>
       </c>
       <c r="V2" t="n">
-        <v>41.62</v>
+        <v>41.17</v>
       </c>
       <c r="W2" t="n">
-        <v>62.17</v>
+        <v>59.88</v>
       </c>
       <c r="X2" t="n">
-        <v>17.22</v>
+        <v>17.07</v>
       </c>
       <c r="Y2" t="n">
         <v>13.91</v>
@@ -683,7 +683,7 @@
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -715,30 +715,30 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -750,16 +750,16 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>3.03</v>
+        <v>5.03</v>
       </c>
       <c r="P3" t="n">
-        <v>55.72</v>
+        <v>367.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>57.3888</v>
+        <v>384.1868</v>
       </c>
       <c r="R3" t="n">
-        <v>55.3157</v>
+        <v>358.0886</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-0.11</v>
+        <v>-2.31</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.94</v>
+        <v>-12.51</v>
       </c>
       <c r="V3" t="n">
-        <v>10.03</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>20.46</v>
+        <v>29.82</v>
       </c>
       <c r="X3" t="n">
-        <v>42.94</v>
+        <v>19.41</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.52</v>
+        <v>16.04</v>
       </c>
       <c r="Z3" t="n">
-        <v>-18.73</v>
+        <v>-16.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>1.08</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -796,22 +796,22 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>80.2</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Utile come protezione macro/geopolitica.</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -820,30 +820,30 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>73.2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -858,13 +858,13 @@
         <v>5.03</v>
       </c>
       <c r="P4" t="n">
-        <v>373.08</v>
+        <v>202.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>385.337</v>
+        <v>168.922</v>
       </c>
       <c r="R4" t="n">
-        <v>357.6605</v>
+        <v>155.3976</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>-2.77</v>
+        <v>21.01</v>
       </c>
       <c r="U4" t="n">
-        <v>-12.2</v>
+        <v>34.52</v>
       </c>
       <c r="V4" t="n">
-        <v>9.619999999999999</v>
+        <v>34.22</v>
       </c>
       <c r="W4" t="n">
-        <v>30.72</v>
+        <v>56.88</v>
       </c>
       <c r="X4" t="n">
-        <v>19.81</v>
+        <v>21.26</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.03</v>
+        <v>20.87</v>
       </c>
       <c r="Z4" t="n">
-        <v>-16.7</v>
+        <v>-33.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -901,13 +901,13 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.7</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Utile come protezione macro/geopolitica.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -925,30 +925,30 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>71.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -963,13 +963,13 @@
         <v>5.03</v>
       </c>
       <c r="P5" t="n">
-        <v>203.31</v>
+        <v>47.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>167.9346</v>
+        <v>43.5901</v>
       </c>
       <c r="R5" t="n">
-        <v>155.0818</v>
+        <v>39.7769</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>19.72</v>
+        <v>9.16</v>
       </c>
       <c r="U5" t="n">
-        <v>36.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>35.13</v>
+        <v>26.09</v>
       </c>
       <c r="W5" t="n">
-        <v>59.13</v>
+        <v>45.96</v>
       </c>
       <c r="X5" t="n">
-        <v>21.61</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>20.87</v>
+        <v>16.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>-33.01</v>
+        <v>-22.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>76.3</v>
+        <v>74.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1030,30 +1030,30 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>75.3</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>FGQI.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Fidelity Global Quality Income UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Satellite</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Quality Dividend</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.03</v>
+        <v>4.67</v>
       </c>
       <c r="P6" t="n">
-        <v>47.8</v>
+        <v>9.733000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.4476</v>
+        <v>9.2987</v>
       </c>
       <c r="R6" t="n">
-        <v>39.71</v>
+        <v>8.894399999999999</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>7.71</v>
+        <v>4.12</v>
       </c>
       <c r="U6" t="n">
-        <v>11.31</v>
+        <v>4.98</v>
       </c>
       <c r="V6" t="n">
-        <v>26.3</v>
+        <v>12.28</v>
       </c>
       <c r="W6" t="n">
-        <v>45.89</v>
+        <v>23.81</v>
       </c>
       <c r="X6" t="n">
-        <v>8.92</v>
+        <v>11.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.32</v>
+        <v>13.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>-22.01</v>
+        <v>-19.89</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>74.2</v>
+        <v>72.8</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1135,30 +1135,30 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.2</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FGQI.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fidelity Global Quality Income UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1170,16 +1170,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>4.67</v>
+        <v>5.03</v>
       </c>
       <c r="P7" t="n">
-        <v>9.739000000000001</v>
+        <v>162.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.2857</v>
+        <v>152.1218</v>
       </c>
       <c r="R7" t="n">
-        <v>8.8864</v>
+        <v>145.497</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,25 +1187,25 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>4.07</v>
+        <v>6.16</v>
       </c>
       <c r="U7" t="n">
-        <v>5.55</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>12.83</v>
+        <v>14.03</v>
       </c>
       <c r="W7" t="n">
-        <v>25.1</v>
+        <v>26.62</v>
       </c>
       <c r="X7" t="n">
-        <v>11.85</v>
+        <v>12.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.4</v>
+        <v>13.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>-19.89</v>
+        <v>-20.96</v>
       </c>
       <c r="AA7" t="n">
         <v>0.74</v>
@@ -1216,13 +1216,13 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>73.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1278,13 +1278,13 @@
         <v>5.03</v>
       </c>
       <c r="P8" t="n">
-        <v>162.56</v>
+        <v>122.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>151.8096</v>
+        <v>115.6092</v>
       </c>
       <c r="R8" t="n">
-        <v>145.3521</v>
+        <v>111.3301</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>5.92</v>
+        <v>5.67</v>
       </c>
       <c r="U8" t="n">
-        <v>9.19</v>
+        <v>8.34</v>
       </c>
       <c r="V8" t="n">
-        <v>14.83</v>
+        <v>12.45</v>
       </c>
       <c r="W8" t="n">
-        <v>27.9</v>
+        <v>24.24</v>
       </c>
       <c r="X8" t="n">
-        <v>12.28</v>
+        <v>12.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.74</v>
+        <v>14.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>-20.96</v>
+        <v>-21.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1345,30 +1345,30 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>69.09999999999999</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
+          <t>iShares MSCI World Quality Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1383,13 +1383,13 @@
         <v>5.03</v>
       </c>
       <c r="P9" t="n">
-        <v>123.13</v>
+        <v>74.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>115.3898</v>
+        <v>70.8028</v>
       </c>
       <c r="R9" t="n">
-        <v>111.2297</v>
+        <v>68.2244</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,28 +1397,28 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>5.58</v>
+        <v>4.36</v>
       </c>
       <c r="U9" t="n">
-        <v>9.039999999999999</v>
+        <v>5.37</v>
       </c>
       <c r="V9" t="n">
-        <v>13.4</v>
+        <v>11.48</v>
       </c>
       <c r="W9" t="n">
-        <v>25.71</v>
+        <v>19.74</v>
       </c>
       <c r="X9" t="n">
-        <v>12.86</v>
+        <v>11.26</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.21</v>
+        <v>14.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>-21.63</v>
+        <v>-20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>72.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>68.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>IWMO.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Quality Factor UCITS ETF</t>
+          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1473,7 +1473,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         <v>5.03</v>
       </c>
       <c r="P10" t="n">
-        <v>74.53</v>
+        <v>100.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>70.7004</v>
+        <v>89.92319999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>68.1683</v>
+        <v>84.3497</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,28 +1502,28 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>4.14</v>
+        <v>11.52</v>
       </c>
       <c r="U10" t="n">
-        <v>6.14</v>
+        <v>17.21</v>
       </c>
       <c r="V10" t="n">
-        <v>12.63</v>
+        <v>23.39</v>
       </c>
       <c r="W10" t="n">
-        <v>20.97</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
-        <v>11.38</v>
+        <v>14.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.17</v>
+        <v>17.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>-20.6</v>
+        <v>-23.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>71.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,30 +1555,30 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>66.2</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IWMO.MI</t>
+          <t>VUAA.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
+          <t>Vanguard S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>USA Large Cap</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         <v>5.03</v>
       </c>
       <c r="P11" t="n">
-        <v>100.6</v>
+        <v>124.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>89.5754</v>
+        <v>116.1226</v>
       </c>
       <c r="R11" t="n">
-        <v>84.2414</v>
+        <v>112.059</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,28 +1607,28 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>10.49</v>
+        <v>6.31</v>
       </c>
       <c r="U11" t="n">
-        <v>17.98</v>
+        <v>11.1</v>
       </c>
       <c r="V11" t="n">
-        <v>25.02</v>
+        <v>12.06</v>
       </c>
       <c r="W11" t="n">
-        <v>32.91</v>
+        <v>26.5</v>
       </c>
       <c r="X11" t="n">
-        <v>14.4</v>
+        <v>14.56</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.29</v>
+        <v>15.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>-23.45</v>
+        <v>-23.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>70.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,19 +1660,19 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>70.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VUAA.MI</t>
+          <t>EQQQ.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard S&amp;P 500 UCITS ETF</t>
+          <t>Invesco Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USA Large Cap</t>
+          <t>Nasdaq / Tech</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1698,13 +1698,13 @@
         <v>5.03</v>
       </c>
       <c r="P12" t="n">
-        <v>124.75</v>
+        <v>628.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>115.8708</v>
+        <v>558.2842000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>111.9564</v>
+        <v>529.039</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,28 +1712,28 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>6.2</v>
+        <v>11.95</v>
       </c>
       <c r="U12" t="n">
-        <v>11.82</v>
+        <v>21.58</v>
       </c>
       <c r="V12" t="n">
-        <v>13.1</v>
+        <v>19.68</v>
       </c>
       <c r="W12" t="n">
-        <v>27.78</v>
+        <v>38.24</v>
       </c>
       <c r="X12" t="n">
-        <v>14.64</v>
+        <v>18.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.21</v>
+        <v>19.89</v>
       </c>
       <c r="Z12" t="n">
-        <v>-23.28</v>
+        <v>-31.11</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI12" t="n">
-        <v>68.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,19 +1765,19 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>68.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco Nasdaq-100 UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1788,7 +1788,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nasdaq / Tech</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1803,13 +1803,13 @@
         <v>5.03</v>
       </c>
       <c r="P13" t="n">
-        <v>629.64</v>
+        <v>63.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>556.1654</v>
+        <v>60.5266</v>
       </c>
       <c r="R13" t="n">
-        <v>528.3268</v>
+        <v>58.178</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,28 +1817,28 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>11.03</v>
+        <v>4.4</v>
       </c>
       <c r="U13" t="n">
-        <v>23.06</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>20.85</v>
+        <v>13.51</v>
       </c>
       <c r="W13" t="n">
-        <v>40</v>
+        <v>16.73</v>
       </c>
       <c r="X13" t="n">
-        <v>18.37</v>
+        <v>9.85</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.89</v>
+        <v>14.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>-31.11</v>
+        <v>-20.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>65.7</v>
+        <v>64.2</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -1870,30 +1870,30 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>69.7</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1905,45 +1905,45 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>5.03</v>
+        <v>3.03</v>
       </c>
       <c r="P14" t="n">
-        <v>63.15</v>
+        <v>55.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>60.4435</v>
+        <v>57.2476</v>
       </c>
       <c r="R14" t="n">
-        <v>58.1283</v>
+        <v>55.3373</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>-0.52</v>
       </c>
       <c r="U14" t="n">
-        <v>1.59</v>
+        <v>-6.9</v>
       </c>
       <c r="V14" t="n">
-        <v>13.73</v>
+        <v>8.6</v>
       </c>
       <c r="W14" t="n">
-        <v>18.2</v>
+        <v>18.24</v>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
+        <v>42.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.53</v>
+        <v>21.51</v>
       </c>
       <c r="Z14" t="n">
-        <v>-20.85</v>
+        <v>-18.73</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.55</v>
+        <v>1.88</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1951,13 +1951,13 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>64.59999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>64.59999999999999</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="15">
@@ -2013,13 +2013,13 @@
         <v>5.03</v>
       </c>
       <c r="P15" t="n">
-        <v>17.924</v>
+        <v>17.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.3233</v>
+        <v>15.4032</v>
       </c>
       <c r="R15" t="n">
-        <v>14.2242</v>
+        <v>14.2476</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,28 +2027,28 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>11.2</v>
+        <v>12.57</v>
       </c>
       <c r="U15" t="n">
-        <v>28.56</v>
+        <v>24.32</v>
       </c>
       <c r="V15" t="n">
-        <v>33.22</v>
+        <v>30.77</v>
       </c>
       <c r="W15" t="n">
-        <v>45.87</v>
+        <v>42.62</v>
       </c>
       <c r="X15" t="n">
-        <v>11.98</v>
+        <v>11.57</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>22.01</v>
       </c>
       <c r="Z15" t="n">
         <v>-35.29</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         <v>-5</v>
       </c>
       <c r="AI15" t="n">
-        <v>64.2</v>
+        <v>62.7</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>69.2</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="16">
@@ -2118,13 +2118,13 @@
         <v>5.03</v>
       </c>
       <c r="P16" t="n">
-        <v>34.505</v>
+        <v>33.605</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.0281</v>
+        <v>28.1698</v>
       </c>
       <c r="R16" t="n">
-        <v>26.9528</v>
+        <v>26.9886</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2132,28 +2132,28 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>26.42</v>
+        <v>23.07</v>
       </c>
       <c r="U16" t="n">
-        <v>47.84</v>
+        <v>44.69</v>
       </c>
       <c r="V16" t="n">
-        <v>26.76</v>
+        <v>23.48</v>
       </c>
       <c r="W16" t="n">
-        <v>28.7</v>
+        <v>23.91</v>
       </c>
       <c r="X16" t="n">
-        <v>11.47</v>
+        <v>10.67</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.31</v>
+        <v>24.34</v>
       </c>
       <c r="Z16" t="n">
         <v>-33.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="17">
@@ -2223,13 +2223,13 @@
         <v>5.03</v>
       </c>
       <c r="P17" t="n">
-        <v>64.04000000000001</v>
+        <v>63.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.3652</v>
+        <v>63.3378</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0316</v>
+        <v>63.0386</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.53</v>
+        <v>-0.9</v>
       </c>
       <c r="V17" t="n">
-        <v>2.41</v>
+        <v>1.99</v>
       </c>
       <c r="W17" t="n">
-        <v>0.55</v>
+        <v>-0.19</v>
       </c>
       <c r="X17" t="n">
-        <v>6.41</v>
+        <v>6.27</v>
       </c>
       <c r="Y17" t="n">
         <v>10.19</v>
@@ -2258,7 +2258,7 @@
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>59.5</v>
+        <v>59.1</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>59.5</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="18">
@@ -2328,13 +2328,13 @@
         <v>5.03</v>
       </c>
       <c r="P18" t="n">
-        <v>94.28</v>
+        <v>93.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>72.31180000000001</v>
+        <v>72.98820000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>57.0084</v>
+        <v>57.2705</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,28 +2342,28 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>24.64</v>
+        <v>28.26</v>
       </c>
       <c r="U18" t="n">
-        <v>53.65</v>
+        <v>49.23</v>
       </c>
       <c r="V18" t="n">
-        <v>88.77</v>
+        <v>86.12</v>
       </c>
       <c r="W18" t="n">
-        <v>166.97</v>
+        <v>160.02</v>
       </c>
       <c r="X18" t="n">
-        <v>37.11</v>
+        <v>36.57</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.97</v>
+        <v>30.98</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
         <v>-23</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="19">
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>103.74</v>
+        <v>102.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>84.21080000000001</v>
+        <v>84.77079999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>75.8129</v>
+        <v>75.9991</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,28 +2447,28 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>20.26</v>
+        <v>21.16</v>
       </c>
       <c r="U19" t="n">
-        <v>39.08</v>
+        <v>34.03</v>
       </c>
       <c r="V19" t="n">
-        <v>48.16</v>
+        <v>45.59</v>
       </c>
       <c r="W19" t="n">
-        <v>81.43000000000001</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>16.49</v>
+        <v>15.84</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.13</v>
+        <v>28.14</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>68</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="20">
@@ -2538,13 +2538,13 @@
         <v>5.03</v>
       </c>
       <c r="P20" t="n">
-        <v>4.9025</v>
+        <v>4.917</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9072</v>
+        <v>4.9075</v>
       </c>
       <c r="R20" t="n">
-        <v>4.9272</v>
+        <v>4.9273</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2552,28 +2552,28 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>-0.25</v>
+        <v>0.19</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.67</v>
+        <v>-1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6</v>
+        <v>-0.33</v>
       </c>
       <c r="W20" t="n">
         <v>1.67</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.34</v>
+        <v>-1.29</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.66</v>
+        <v>4.67</v>
       </c>
       <c r="Z20" t="n">
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="21">
@@ -2643,13 +2643,13 @@
         <v>5.03</v>
       </c>
       <c r="P21" t="n">
-        <v>23.615</v>
+        <v>23.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6277</v>
+        <v>23.6292</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7489</v>
+        <v>23.7492</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>-0.15</v>
+        <v>0.34</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.81</v>
+        <v>-1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.67</v>
+        <v>-1.61</v>
       </c>
       <c r="Y21" t="n">
         <v>4.79</v>
@@ -2678,7 +2678,7 @@
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.77</v>
+        <v>-0.75</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.4</v>
+        <v>32.7</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -648,13 +648,13 @@
         <v>5.03</v>
       </c>
       <c r="P2" t="n">
-        <v>69.90000000000001</v>
+        <v>70.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>60.7476</v>
+        <v>61.0222</v>
       </c>
       <c r="R2" t="n">
-        <v>53.7313</v>
+        <v>53.8604</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>16.93</v>
+        <v>16.35</v>
       </c>
       <c r="U2" t="n">
-        <v>20.52</v>
+        <v>20.86</v>
       </c>
       <c r="V2" t="n">
-        <v>41.17</v>
+        <v>42.75</v>
       </c>
       <c r="W2" t="n">
-        <v>59.88</v>
+        <v>60.31</v>
       </c>
       <c r="X2" t="n">
-        <v>17.07</v>
+        <v>17.46</v>
       </c>
       <c r="Y2" t="n">
         <v>13.91</v>
@@ -683,7 +683,7 @@
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -715,30 +715,30 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>81.90000000000001</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -750,16 +750,16 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>5.03</v>
+        <v>3.04</v>
       </c>
       <c r="P3" t="n">
-        <v>367.06</v>
+        <v>57.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>384.1868</v>
+        <v>57.1474</v>
       </c>
       <c r="R3" t="n">
-        <v>358.0886</v>
+        <v>55.3689</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-2.31</v>
+        <v>3.9</v>
       </c>
       <c r="U3" t="n">
-        <v>-12.51</v>
+        <v>-3.62</v>
       </c>
       <c r="V3" t="n">
-        <v>8.140000000000001</v>
+        <v>16.23</v>
       </c>
       <c r="W3" t="n">
-        <v>29.82</v>
+        <v>20.87</v>
       </c>
       <c r="X3" t="n">
-        <v>19.41</v>
+        <v>44.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.04</v>
+        <v>21.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>-16.7</v>
+        <v>-18.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.08</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -796,22 +796,22 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Utile come protezione macro/geopolitica.</t>
+          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -820,30 +820,30 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -858,13 +858,13 @@
         <v>5.03</v>
       </c>
       <c r="P4" t="n">
-        <v>202.37</v>
+        <v>369.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>168.922</v>
+        <v>383.2456</v>
       </c>
       <c r="R4" t="n">
-        <v>155.3976</v>
+        <v>358.5416</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>21.01</v>
+        <v>-1.09</v>
       </c>
       <c r="U4" t="n">
-        <v>34.52</v>
+        <v>-12.86</v>
       </c>
       <c r="V4" t="n">
-        <v>34.22</v>
+        <v>8.49</v>
       </c>
       <c r="W4" t="n">
-        <v>56.88</v>
+        <v>32.14</v>
       </c>
       <c r="X4" t="n">
-        <v>21.26</v>
+        <v>19.52</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.87</v>
+        <v>16.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>-33.01</v>
+        <v>-16.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.92</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -901,13 +901,13 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>76</v>
+        <v>79.7</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Utile come protezione macro/geopolitica.</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -925,30 +925,30 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -963,13 +963,13 @@
         <v>5.03</v>
       </c>
       <c r="P5" t="n">
-        <v>47.84</v>
+        <v>206.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>43.5901</v>
+        <v>169.9418</v>
       </c>
       <c r="R5" t="n">
-        <v>39.7769</v>
+        <v>155.7301</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>9.16</v>
+        <v>21.36</v>
       </c>
       <c r="U5" t="n">
-        <v>9.619999999999999</v>
+        <v>35.27</v>
       </c>
       <c r="V5" t="n">
-        <v>26.09</v>
+        <v>40.69</v>
       </c>
       <c r="W5" t="n">
-        <v>45.96</v>
+        <v>58.74</v>
       </c>
       <c r="X5" t="n">
-        <v>8.789999999999999</v>
+        <v>21.87</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.32</v>
+        <v>20.88</v>
       </c>
       <c r="Z5" t="n">
-        <v>-22.01</v>
+        <v>-33.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.42</v>
+        <v>0.95</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1030,30 +1030,30 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>72.2</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FGQI.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fidelity Global Quality Income UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>4.67</v>
+        <v>5.03</v>
       </c>
       <c r="P6" t="n">
-        <v>9.733000000000001</v>
+        <v>47.955</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.2987</v>
+        <v>43.7231</v>
       </c>
       <c r="R6" t="n">
-        <v>8.894399999999999</v>
+        <v>39.8451</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>4.12</v>
+        <v>8.94</v>
       </c>
       <c r="U6" t="n">
-        <v>4.98</v>
+        <v>9.24</v>
       </c>
       <c r="V6" t="n">
-        <v>12.28</v>
+        <v>28.82</v>
       </c>
       <c r="W6" t="n">
-        <v>23.81</v>
+        <v>46.54</v>
       </c>
       <c r="X6" t="n">
-        <v>11.83</v>
+        <v>8.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.39</v>
+        <v>16.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>-19.89</v>
+        <v>-22.01</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.73</v>
+        <v>0.41</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,31 +1111,31 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Monitorare secondo score e trend.</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
         <v>72.8</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>Accumulate Carefully</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Monitorare secondo score e trend.</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>67.8</v>
       </c>
     </row>
     <row r="7">
@@ -1173,13 +1173,13 @@
         <v>5.03</v>
       </c>
       <c r="P7" t="n">
-        <v>162.29</v>
+        <v>162.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>152.1218</v>
+        <v>152.43</v>
       </c>
       <c r="R7" t="n">
-        <v>145.497</v>
+        <v>145.6434</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>6.16</v>
+        <v>6.33</v>
       </c>
       <c r="U7" t="n">
-        <v>8.380000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="V7" t="n">
-        <v>14.03</v>
+        <v>15.73</v>
       </c>
       <c r="W7" t="n">
-        <v>26.62</v>
+        <v>26.19</v>
       </c>
       <c r="X7" t="n">
-        <v>12.15</v>
+        <v>12.36</v>
       </c>
       <c r="Y7" t="n">
         <v>13.74</v>
@@ -1208,7 +1208,7 @@
         <v>-20.96</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1240,30 +1240,30 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>FGQI.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
+          <t>Fidelity Global Quality Income UCITS ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Satellite</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Quality Dividend</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1275,16 +1275,16 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>5.03</v>
+        <v>4.67</v>
       </c>
       <c r="P8" t="n">
-        <v>122.86</v>
+        <v>9.715</v>
       </c>
       <c r="Q8" t="n">
-        <v>115.6092</v>
+        <v>9.3102</v>
       </c>
       <c r="R8" t="n">
-        <v>111.3301</v>
+        <v>8.9023</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>5.67</v>
+        <v>4.21</v>
       </c>
       <c r="U8" t="n">
-        <v>8.34</v>
+        <v>4.29</v>
       </c>
       <c r="V8" t="n">
-        <v>12.45</v>
+        <v>12.65</v>
       </c>
       <c r="W8" t="n">
-        <v>24.24</v>
+        <v>22.84</v>
       </c>
       <c r="X8" t="n">
-        <v>12.73</v>
+        <v>11.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.21</v>
+        <v>13.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>-21.63</v>
+        <v>-19.89</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1321,13 +1321,13 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>71.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -1345,30 +1345,30 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Quality Factor UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1383,13 +1383,13 @@
         <v>5.03</v>
       </c>
       <c r="P9" t="n">
-        <v>74.37</v>
+        <v>123.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>70.8028</v>
+        <v>115.8292</v>
       </c>
       <c r="R9" t="n">
-        <v>68.2244</v>
+        <v>111.4307</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,28 +1397,28 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>4.36</v>
+        <v>5.86</v>
       </c>
       <c r="U9" t="n">
-        <v>5.37</v>
+        <v>7.83</v>
       </c>
       <c r="V9" t="n">
-        <v>11.48</v>
+        <v>13.9</v>
       </c>
       <c r="W9" t="n">
-        <v>19.74</v>
+        <v>23.59</v>
       </c>
       <c r="X9" t="n">
-        <v>11.26</v>
+        <v>12.94</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.17</v>
+        <v>14.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>-20.6</v>
+        <v>-21.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.59999999999999</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IWMO.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
+          <t>iShares MSCI World Quality Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1473,7 +1473,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         <v>5.03</v>
       </c>
       <c r="P10" t="n">
-        <v>100.12</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>89.92319999999999</v>
+        <v>70.90219999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>84.3497</v>
+        <v>68.2801</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,28 +1502,28 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>11.52</v>
+        <v>4.38</v>
       </c>
       <c r="U10" t="n">
-        <v>17.21</v>
+        <v>4.6</v>
       </c>
       <c r="V10" t="n">
-        <v>23.39</v>
+        <v>12.18</v>
       </c>
       <c r="W10" t="n">
-        <v>31</v>
+        <v>18.9</v>
       </c>
       <c r="X10" t="n">
-        <v>14.25</v>
+        <v>11.44</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.29</v>
+        <v>14.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>-23.45</v>
+        <v>-20.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>69.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,30 +1555,30 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>69.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VUAA.MI</t>
+          <t>IWMO.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard S&amp;P 500 UCITS ETF</t>
+          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USA Large Cap</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         <v>5.03</v>
       </c>
       <c r="P11" t="n">
-        <v>124.58</v>
+        <v>100.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>116.1226</v>
+        <v>90.2632</v>
       </c>
       <c r="R11" t="n">
-        <v>112.059</v>
+        <v>84.4575</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,28 +1607,28 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>6.31</v>
+        <v>10.95</v>
       </c>
       <c r="U11" t="n">
-        <v>11.1</v>
+        <v>15.78</v>
       </c>
       <c r="V11" t="n">
-        <v>12.06</v>
+        <v>26.74</v>
       </c>
       <c r="W11" t="n">
-        <v>26.5</v>
+        <v>30.42</v>
       </c>
       <c r="X11" t="n">
-        <v>14.56</v>
+        <v>14.47</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.21</v>
+        <v>17.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>-23.28</v>
+        <v>-23.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>67.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,19 +1660,19 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>67.90000000000001</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.MI</t>
+          <t>VUAA.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco Nasdaq-100 UCITS ETF</t>
+          <t>Vanguard S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nasdaq / Tech</t>
+          <t>USA Large Cap</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1698,13 +1698,13 @@
         <v>5.03</v>
       </c>
       <c r="P12" t="n">
-        <v>628.3</v>
+        <v>125.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>558.2842000000001</v>
+        <v>116.3828</v>
       </c>
       <c r="R12" t="n">
-        <v>529.039</v>
+        <v>112.1632</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,28 +1712,28 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>11.95</v>
+        <v>6.44</v>
       </c>
       <c r="U12" t="n">
-        <v>21.58</v>
+        <v>10.75</v>
       </c>
       <c r="V12" t="n">
-        <v>19.68</v>
+        <v>14.09</v>
       </c>
       <c r="W12" t="n">
-        <v>38.24</v>
+        <v>25.84</v>
       </c>
       <c r="X12" t="n">
-        <v>18.25</v>
+        <v>14.81</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.89</v>
+        <v>15.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>-31.11</v>
+        <v>-23.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>65.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,19 +1765,19 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>69.09999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>EQQQ.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>Invesco Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1788,7 +1788,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Nasdaq / Tech</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1803,13 +1803,13 @@
         <v>5.03</v>
       </c>
       <c r="P13" t="n">
-        <v>63.15</v>
+        <v>633.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.5266</v>
+        <v>560.4712</v>
       </c>
       <c r="R13" t="n">
-        <v>58.178</v>
+        <v>529.7727</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,28 +1817,28 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>4.4</v>
+        <v>11.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>21.24</v>
       </c>
       <c r="V13" t="n">
-        <v>13.51</v>
+        <v>23.8</v>
       </c>
       <c r="W13" t="n">
-        <v>16.73</v>
+        <v>38.06</v>
       </c>
       <c r="X13" t="n">
-        <v>9.85</v>
+        <v>18.62</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.52</v>
+        <v>19.89</v>
       </c>
       <c r="Z13" t="n">
-        <v>-20.85</v>
+        <v>-31.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI13" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -1870,30 +1870,30 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>64.2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1905,45 +1905,45 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>3.03</v>
+        <v>5.03</v>
       </c>
       <c r="P14" t="n">
-        <v>55.17</v>
+        <v>62.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>57.2476</v>
+        <v>60.5988</v>
       </c>
       <c r="R14" t="n">
-        <v>55.3373</v>
+        <v>58.2264</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>-0.52</v>
+        <v>4.52</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.9</v>
+        <v>0.23</v>
       </c>
       <c r="V14" t="n">
-        <v>8.6</v>
+        <v>13.45</v>
       </c>
       <c r="W14" t="n">
-        <v>18.24</v>
+        <v>16.09</v>
       </c>
       <c r="X14" t="n">
-        <v>42.4</v>
+        <v>9.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>21.51</v>
+        <v>14.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>-18.73</v>
+        <v>-20.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.88</v>
+        <v>0.54</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1951,13 +1951,13 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>63.2</v>
+        <v>64</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>56.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2013,13 +2013,13 @@
         <v>5.03</v>
       </c>
       <c r="P15" t="n">
-        <v>17.73</v>
+        <v>17.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.4032</v>
+        <v>15.4844</v>
       </c>
       <c r="R15" t="n">
-        <v>14.2476</v>
+        <v>14.2729</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,19 +2027,19 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>12.57</v>
+        <v>13.48</v>
       </c>
       <c r="U15" t="n">
-        <v>24.32</v>
+        <v>23.74</v>
       </c>
       <c r="V15" t="n">
-        <v>30.77</v>
+        <v>36.23</v>
       </c>
       <c r="W15" t="n">
-        <v>42.62</v>
+        <v>42.69</v>
       </c>
       <c r="X15" t="n">
-        <v>11.57</v>
+        <v>11.94</v>
       </c>
       <c r="Y15" t="n">
         <v>22.01</v>
@@ -2048,7 +2048,7 @@
         <v>-35.29</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         <v>-5</v>
       </c>
       <c r="AI15" t="n">
-        <v>62.7</v>
+        <v>63.7</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>67.7</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="16">
@@ -2118,13 +2118,13 @@
         <v>5.03</v>
       </c>
       <c r="P16" t="n">
-        <v>33.605</v>
+        <v>34.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.1698</v>
+        <v>28.3326</v>
       </c>
       <c r="R16" t="n">
-        <v>26.9886</v>
+        <v>27.0287</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2132,28 +2132,28 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>23.07</v>
+        <v>25.46</v>
       </c>
       <c r="U16" t="n">
-        <v>44.69</v>
+        <v>45.9</v>
       </c>
       <c r="V16" t="n">
-        <v>23.48</v>
+        <v>28.49</v>
       </c>
       <c r="W16" t="n">
-        <v>23.91</v>
+        <v>24.98</v>
       </c>
       <c r="X16" t="n">
-        <v>10.67</v>
+        <v>11.41</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.34</v>
+        <v>24.35</v>
       </c>
       <c r="Z16" t="n">
         <v>-33.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>60.5</v>
+        <v>62</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>60.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -2223,13 +2223,13 @@
         <v>5.03</v>
       </c>
       <c r="P17" t="n">
-        <v>63.91</v>
+        <v>63.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.3378</v>
+        <v>63.3064</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0386</v>
+        <v>63.0454</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,28 +2237,28 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9</v>
+        <v>-1.19</v>
       </c>
       <c r="V17" t="n">
-        <v>1.99</v>
+        <v>0.79</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.19</v>
+        <v>-0.89</v>
       </c>
       <c r="X17" t="n">
-        <v>6.27</v>
+        <v>6.36</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="Z17" t="n">
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>59.1</v>
+        <v>58.8</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>59.1</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="18">
@@ -2328,13 +2328,13 @@
         <v>5.03</v>
       </c>
       <c r="P18" t="n">
-        <v>93.45</v>
+        <v>95.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>72.98820000000001</v>
+        <v>73.6884</v>
       </c>
       <c r="R18" t="n">
-        <v>57.2705</v>
+        <v>57.5464</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,28 +2342,28 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>28.26</v>
+        <v>27.41</v>
       </c>
       <c r="U18" t="n">
-        <v>49.23</v>
+        <v>51.16</v>
       </c>
       <c r="V18" t="n">
-        <v>86.12</v>
+        <v>100.71</v>
       </c>
       <c r="W18" t="n">
-        <v>160.02</v>
+        <v>161.62</v>
       </c>
       <c r="X18" t="n">
-        <v>36.57</v>
+        <v>37.32</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.98</v>
+        <v>30.99</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
         <v>-23</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>102.32</v>
+        <v>105.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>84.77079999999999</v>
+        <v>85.35120000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>75.9991</v>
+        <v>76.19750000000001</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,28 +2447,28 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>21.16</v>
+        <v>22.84</v>
       </c>
       <c r="U19" t="n">
-        <v>34.03</v>
+        <v>35.81</v>
       </c>
       <c r="V19" t="n">
-        <v>45.59</v>
+        <v>56.33</v>
       </c>
       <c r="W19" t="n">
-        <v>76.31999999999999</v>
+        <v>81.16</v>
       </c>
       <c r="X19" t="n">
-        <v>15.84</v>
+        <v>16.68</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.14</v>
+        <v>28.16</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>67.8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2538,13 +2538,13 @@
         <v>5.03</v>
       </c>
       <c r="P20" t="n">
-        <v>4.917</v>
+        <v>4.9235</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9075</v>
+        <v>4.9076</v>
       </c>
       <c r="R20" t="n">
-        <v>4.9273</v>
+        <v>4.9274</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.48</v>
+        <v>-1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.29</v>
+        <v>-1.27</v>
       </c>
       <c r="Y20" t="n">
         <v>4.67</v>
@@ -2573,7 +2573,7 @@
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="21">
@@ -2643,13 +2643,13 @@
         <v>5.03</v>
       </c>
       <c r="P21" t="n">
-        <v>23.7</v>
+        <v>23.725</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6292</v>
+        <v>23.6302</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7492</v>
+        <v>23.7497</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.48</v>
+        <v>-1.37</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.32</v>
+        <v>-0.46</v>
       </c>
       <c r="W21" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.61</v>
+        <v>-1.59</v>
       </c>
       <c r="Y21" t="n">
         <v>4.79</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -648,13 +648,13 @@
         <v>5.03</v>
       </c>
       <c r="P2" t="n">
-        <v>70.52</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>61.0222</v>
+        <v>61.3006</v>
       </c>
       <c r="R2" t="n">
-        <v>53.8604</v>
+        <v>53.9912</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>16.35</v>
+        <v>15.38</v>
       </c>
       <c r="U2" t="n">
-        <v>20.86</v>
+        <v>21.84</v>
       </c>
       <c r="V2" t="n">
-        <v>42.75</v>
+        <v>41.61</v>
       </c>
       <c r="W2" t="n">
-        <v>60.31</v>
+        <v>61.71</v>
       </c>
       <c r="X2" t="n">
-        <v>17.46</v>
+        <v>17.48</v>
       </c>
       <c r="Y2" t="n">
         <v>13.91</v>
@@ -753,13 +753,13 @@
         <v>3.04</v>
       </c>
       <c r="P3" t="n">
-        <v>57.25</v>
+        <v>56.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>57.1474</v>
+        <v>57.0308</v>
       </c>
       <c r="R3" t="n">
-        <v>55.3689</v>
+        <v>55.4029</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>3.9</v>
+        <v>1.82</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.62</v>
+        <v>-3.67</v>
       </c>
       <c r="V3" t="n">
-        <v>16.23</v>
+        <v>15.24</v>
       </c>
       <c r="W3" t="n">
-        <v>20.87</v>
+        <v>19.81</v>
       </c>
       <c r="X3" t="n">
-        <v>44.08</v>
+        <v>43.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.6</v>
+        <v>21.59</v>
       </c>
       <c r="Z3" t="n">
         <v>-18.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>82</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>75</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -858,13 +858,13 @@
         <v>5.03</v>
       </c>
       <c r="P4" t="n">
-        <v>369.96</v>
+        <v>377.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>383.2456</v>
+        <v>382.4396</v>
       </c>
       <c r="R4" t="n">
-        <v>358.5416</v>
+        <v>359.026</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>-1.09</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-12.86</v>
+        <v>-10.81</v>
       </c>
       <c r="V4" t="n">
-        <v>8.49</v>
+        <v>10.21</v>
       </c>
       <c r="W4" t="n">
-        <v>32.14</v>
+        <v>34.21</v>
       </c>
       <c r="X4" t="n">
-        <v>19.52</v>
+        <v>20.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.05</v>
+        <v>16.07</v>
       </c>
       <c r="Z4" t="n">
         <v>-16.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -907,11 +907,11 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>71.7</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -963,13 +963,13 @@
         <v>5.03</v>
       </c>
       <c r="P5" t="n">
-        <v>206.33</v>
+        <v>210.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>169.9418</v>
+        <v>171.0414</v>
       </c>
       <c r="R5" t="n">
-        <v>155.7301</v>
+        <v>156.0836</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>21.36</v>
+        <v>24.57</v>
       </c>
       <c r="U5" t="n">
-        <v>35.27</v>
+        <v>38.06</v>
       </c>
       <c r="V5" t="n">
-        <v>40.69</v>
+        <v>40.31</v>
       </c>
       <c r="W5" t="n">
-        <v>58.74</v>
+        <v>61.67</v>
       </c>
       <c r="X5" t="n">
-        <v>21.87</v>
+        <v>22.39</v>
       </c>
       <c r="Y5" t="n">
-        <v>20.88</v>
+        <v>20.9</v>
       </c>
       <c r="Z5" t="n">
         <v>-33.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
         <v>-5</v>
       </c>
       <c r="AI5" t="n">
-        <v>76.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>75.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1068,13 +1068,13 @@
         <v>5.03</v>
       </c>
       <c r="P6" t="n">
-        <v>47.955</v>
+        <v>47.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.7231</v>
+        <v>43.8504</v>
       </c>
       <c r="R6" t="n">
-        <v>39.8451</v>
+        <v>39.9115</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>8.94</v>
+        <v>8.32</v>
       </c>
       <c r="U6" t="n">
-        <v>9.24</v>
+        <v>10.12</v>
       </c>
       <c r="V6" t="n">
-        <v>28.82</v>
+        <v>27.37</v>
       </c>
       <c r="W6" t="n">
-        <v>46.54</v>
+        <v>46.48</v>
       </c>
       <c r="X6" t="n">
-        <v>8.77</v>
+        <v>8.57</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.32</v>
+        <v>16.31</v>
       </c>
       <c r="Z6" t="n">
         <v>-22.01</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>74.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1173,13 +1173,13 @@
         <v>5.03</v>
       </c>
       <c r="P7" t="n">
-        <v>162.8</v>
+        <v>163.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>152.43</v>
+        <v>152.7362</v>
       </c>
       <c r="R7" t="n">
-        <v>145.6434</v>
+        <v>145.7892</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>6.33</v>
+        <v>5.92</v>
       </c>
       <c r="U7" t="n">
-        <v>7.92</v>
+        <v>8.4</v>
       </c>
       <c r="V7" t="n">
-        <v>15.73</v>
+        <v>14.46</v>
       </c>
       <c r="W7" t="n">
-        <v>26.19</v>
+        <v>26.28</v>
       </c>
       <c r="X7" t="n">
-        <v>12.36</v>
+        <v>12.31</v>
       </c>
       <c r="Y7" t="n">
         <v>13.74</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="8">
@@ -1275,16 +1275,16 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="P8" t="n">
-        <v>9.715</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.3102</v>
+        <v>9.3223</v>
       </c>
       <c r="R8" t="n">
-        <v>8.9023</v>
+        <v>8.9102</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>4.21</v>
+        <v>3.73</v>
       </c>
       <c r="U8" t="n">
-        <v>4.29</v>
+        <v>4.64</v>
       </c>
       <c r="V8" t="n">
-        <v>12.65</v>
+        <v>11.77</v>
       </c>
       <c r="W8" t="n">
-        <v>22.84</v>
+        <v>22.99</v>
       </c>
       <c r="X8" t="n">
-        <v>11.77</v>
+        <v>11.81</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.39</v>
+        <v>13.38</v>
       </c>
       <c r="Z8" t="n">
         <v>-19.89</v>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>67.59999999999999</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="9">
@@ -1383,13 +1383,13 @@
         <v>5.03</v>
       </c>
       <c r="P9" t="n">
-        <v>123.16</v>
+        <v>123.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>115.8292</v>
+        <v>116.0496</v>
       </c>
       <c r="R9" t="n">
-        <v>111.4307</v>
+        <v>111.5316</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,19 +1397,19 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>5.86</v>
+        <v>5.43</v>
       </c>
       <c r="U9" t="n">
-        <v>7.83</v>
+        <v>8.23</v>
       </c>
       <c r="V9" t="n">
-        <v>13.9</v>
+        <v>12.67</v>
       </c>
       <c r="W9" t="n">
-        <v>23.59</v>
+        <v>23.71</v>
       </c>
       <c r="X9" t="n">
-        <v>12.94</v>
+        <v>12.92</v>
       </c>
       <c r="Y9" t="n">
         <v>14.21</v>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.7</v>
+        <v>71.5</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>67.7</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="10">
@@ -1488,13 +1488,13 @@
         <v>5.03</v>
       </c>
       <c r="P10" t="n">
-        <v>74.34999999999999</v>
+        <v>74.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>70.90219999999999</v>
+        <v>70.997</v>
       </c>
       <c r="R10" t="n">
-        <v>68.2801</v>
+        <v>68.3355</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,19 +1502,19 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>4.38</v>
+        <v>3.73</v>
       </c>
       <c r="U10" t="n">
-        <v>4.6</v>
+        <v>4.77</v>
       </c>
       <c r="V10" t="n">
-        <v>12.18</v>
+        <v>11.04</v>
       </c>
       <c r="W10" t="n">
-        <v>18.9</v>
+        <v>18.49</v>
       </c>
       <c r="X10" t="n">
-        <v>11.44</v>
+        <v>11.35</v>
       </c>
       <c r="Y10" t="n">
         <v>14.16</v>
@@ -1523,7 +1523,7 @@
         <v>-20.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>70.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="11">
@@ -1593,13 +1593,13 @@
         <v>5.03</v>
       </c>
       <c r="P11" t="n">
-        <v>100.44</v>
+        <v>99.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>90.2632</v>
+        <v>90.5836</v>
       </c>
       <c r="R11" t="n">
-        <v>84.4575</v>
+        <v>84.5615</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>10.95</v>
+        <v>8.42</v>
       </c>
       <c r="U11" t="n">
-        <v>15.78</v>
+        <v>15.54</v>
       </c>
       <c r="V11" t="n">
-        <v>26.74</v>
+        <v>23.93</v>
       </c>
       <c r="W11" t="n">
-        <v>30.42</v>
+        <v>29.25</v>
       </c>
       <c r="X11" t="n">
-        <v>14.47</v>
+        <v>14.1</v>
       </c>
       <c r="Y11" t="n">
         <v>17.29</v>
@@ -1628,7 +1628,7 @@
         <v>-23.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>70.2</v>
+        <v>69.2</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>70.2</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="12">
@@ -1698,13 +1698,13 @@
         <v>5.03</v>
       </c>
       <c r="P12" t="n">
-        <v>125.11</v>
+        <v>125.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>116.3828</v>
+        <v>116.6426</v>
       </c>
       <c r="R12" t="n">
-        <v>112.1632</v>
+        <v>112.2682</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,19 +1712,19 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>6.44</v>
+        <v>6.32</v>
       </c>
       <c r="U12" t="n">
-        <v>10.75</v>
+        <v>11.21</v>
       </c>
       <c r="V12" t="n">
-        <v>14.09</v>
+        <v>12.39</v>
       </c>
       <c r="W12" t="n">
-        <v>25.84</v>
+        <v>25.38</v>
       </c>
       <c r="X12" t="n">
-        <v>14.81</v>
+        <v>14.79</v>
       </c>
       <c r="Y12" t="n">
         <v>15.21</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="13">
@@ -1803,13 +1803,13 @@
         <v>5.03</v>
       </c>
       <c r="P13" t="n">
-        <v>633.77</v>
+        <v>635.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>560.4712</v>
+        <v>562.6676</v>
       </c>
       <c r="R13" t="n">
-        <v>529.7727</v>
+        <v>530.4944</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,19 +1817,19 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>11.65</v>
+        <v>11.74</v>
       </c>
       <c r="U13" t="n">
-        <v>21.24</v>
+        <v>22.52</v>
       </c>
       <c r="V13" t="n">
-        <v>23.8</v>
+        <v>20.96</v>
       </c>
       <c r="W13" t="n">
-        <v>38.06</v>
+        <v>37.41</v>
       </c>
       <c r="X13" t="n">
-        <v>18.62</v>
+        <v>18.74</v>
       </c>
       <c r="Y13" t="n">
         <v>19.89</v>
@@ -1852,7 +1852,7 @@
         <v>-4</v>
       </c>
       <c r="AI13" t="n">
-        <v>66</v>
+        <v>65.3</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>70</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="14">
@@ -1908,13 +1908,13 @@
         <v>5.03</v>
       </c>
       <c r="P14" t="n">
-        <v>62.88</v>
+        <v>62.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>60.5988</v>
+        <v>60.6656</v>
       </c>
       <c r="R14" t="n">
-        <v>58.2264</v>
+        <v>58.2728</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1922,19 +1922,19 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>4.52</v>
+        <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>0.23</v>
+        <v>0.48</v>
       </c>
       <c r="V14" t="n">
-        <v>13.45</v>
+        <v>13.34</v>
       </c>
       <c r="W14" t="n">
-        <v>16.09</v>
+        <v>17.03</v>
       </c>
       <c r="X14" t="n">
-        <v>9.9</v>
+        <v>9.75</v>
       </c>
       <c r="Y14" t="n">
         <v>14.52</v>
@@ -1943,7 +1943,7 @@
         <v>-20.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1975,19 +1975,19 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>ISPY.MI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF</t>
+          <t>L&amp;G Cyber Security UCITS ETF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1998,7 +1998,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2013,13 +2013,13 @@
         <v>5.03</v>
       </c>
       <c r="P15" t="n">
-        <v>17.93</v>
+        <v>35.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.4844</v>
+        <v>28.5101</v>
       </c>
       <c r="R15" t="n">
-        <v>14.2729</v>
+        <v>27.0751</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,28 +2027,28 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>13.48</v>
+        <v>29.05</v>
       </c>
       <c r="U15" t="n">
-        <v>23.74</v>
+        <v>46.29</v>
       </c>
       <c r="V15" t="n">
-        <v>36.23</v>
+        <v>29.34</v>
       </c>
       <c r="W15" t="n">
-        <v>42.69</v>
+        <v>28.44</v>
       </c>
       <c r="X15" t="n">
-        <v>11.94</v>
+        <v>12.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.01</v>
+        <v>24.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>-35.29</v>
+        <v>-33.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.7</v>
+        <v>63.2</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Drawdown storico importante.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -2080,19 +2080,19 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>68.7</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ISPY.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L&amp;G Cyber Security UCITS ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2103,7 +2103,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2118,13 +2118,13 @@
         <v>5.03</v>
       </c>
       <c r="P16" t="n">
-        <v>34.3</v>
+        <v>17.864</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.3326</v>
+        <v>15.5663</v>
       </c>
       <c r="R16" t="n">
-        <v>27.0287</v>
+        <v>14.2972</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2132,28 +2132,28 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>25.46</v>
+        <v>11.15</v>
       </c>
       <c r="U16" t="n">
-        <v>45.9</v>
+        <v>23.75</v>
       </c>
       <c r="V16" t="n">
-        <v>28.49</v>
+        <v>31.99</v>
       </c>
       <c r="W16" t="n">
-        <v>24.98</v>
+        <v>42.52</v>
       </c>
       <c r="X16" t="n">
-        <v>11.41</v>
+        <v>11.79</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.35</v>
+        <v>22.01</v>
       </c>
       <c r="Z16" t="n">
-        <v>-33.89</v>
+        <v>-35.29</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Drawdown storico importante.</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
@@ -2223,13 +2223,13 @@
         <v>5.03</v>
       </c>
       <c r="P17" t="n">
-        <v>63.68</v>
+        <v>63.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.3064</v>
+        <v>63.2716</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0454</v>
+        <v>63.0527</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>1.15</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.19</v>
+        <v>-1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.89</v>
+        <v>-0.95</v>
       </c>
       <c r="X17" t="n">
-        <v>6.36</v>
+        <v>6.34</v>
       </c>
       <c r="Y17" t="n">
         <v>10.18</v>
@@ -2328,13 +2328,13 @@
         <v>5.03</v>
       </c>
       <c r="P18" t="n">
-        <v>95.7</v>
+        <v>95.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>73.6884</v>
+        <v>74.3848</v>
       </c>
       <c r="R18" t="n">
-        <v>57.5464</v>
+        <v>57.8151</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>27.41</v>
+        <v>24.55</v>
       </c>
       <c r="U18" t="n">
-        <v>51.16</v>
+        <v>54.98</v>
       </c>
       <c r="V18" t="n">
-        <v>100.71</v>
+        <v>90.36</v>
       </c>
       <c r="W18" t="n">
-        <v>161.62</v>
+        <v>159.7</v>
       </c>
       <c r="X18" t="n">
-        <v>37.32</v>
+        <v>37.28</v>
       </c>
       <c r="Y18" t="n">
         <v>30.99</v>
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>105.13</v>
+        <v>105.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>85.35120000000001</v>
+        <v>85.93899999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>76.19750000000001</v>
+        <v>76.3985</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,19 +2447,19 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>22.84</v>
+        <v>21.58</v>
       </c>
       <c r="U19" t="n">
-        <v>35.81</v>
+        <v>37.6</v>
       </c>
       <c r="V19" t="n">
-        <v>56.33</v>
+        <v>50.58</v>
       </c>
       <c r="W19" t="n">
-        <v>81.16</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>16.68</v>
+        <v>16.78</v>
       </c>
       <c r="Y19" t="n">
         <v>28.16</v>
@@ -2538,33 +2538,33 @@
         <v>5.03</v>
       </c>
       <c r="P20" t="n">
-        <v>4.9235</v>
+        <v>4.9295</v>
       </c>
       <c r="Q20" t="n">
         <v>4.9076</v>
       </c>
       <c r="R20" t="n">
-        <v>4.9274</v>
+        <v>4.9275</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.22</v>
+        <v>-1.23</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.27</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.27</v>
+        <v>-1.23</v>
       </c>
       <c r="Y20" t="n">
         <v>4.67</v>
@@ -2573,7 +2573,7 @@
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,11 +2587,11 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>36.4</v>
+        <v>52.5</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>33.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="21">
@@ -2643,13 +2643,13 @@
         <v>5.03</v>
       </c>
       <c r="P21" t="n">
-        <v>23.725</v>
+        <v>23.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6302</v>
+        <v>23.6303</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7497</v>
+        <v>23.7502</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="U21" t="n">
         <v>-1.37</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.46</v>
+        <v>-0.21</v>
       </c>
       <c r="W21" t="n">
-        <v>1.69</v>
+        <v>2.13</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.59</v>
+        <v>-1.57</v>
       </c>
       <c r="Y21" t="n">
         <v>4.79</v>
@@ -2678,7 +2678,7 @@
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.75</v>
+        <v>-0.74</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -648,13 +648,13 @@
         <v>5.03</v>
       </c>
       <c r="P2" t="n">
-        <v>70.95999999999999</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>61.3006</v>
+        <v>61.5902</v>
       </c>
       <c r="R2" t="n">
-        <v>53.9912</v>
+        <v>54.121</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>15.38</v>
+        <v>15.27</v>
       </c>
       <c r="U2" t="n">
-        <v>21.84</v>
+        <v>22.65</v>
       </c>
       <c r="V2" t="n">
-        <v>41.61</v>
+        <v>41.65</v>
       </c>
       <c r="W2" t="n">
-        <v>61.71</v>
+        <v>63.52</v>
       </c>
       <c r="X2" t="n">
-        <v>17.48</v>
+        <v>17.44</v>
       </c>
       <c r="Y2" t="n">
         <v>13.91</v>
@@ -753,13 +753,13 @@
         <v>3.04</v>
       </c>
       <c r="P3" t="n">
-        <v>56.99</v>
+        <v>56.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>57.0308</v>
+        <v>56.8998</v>
       </c>
       <c r="R3" t="n">
-        <v>55.4029</v>
+        <v>55.4351</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,19 +767,19 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>1.82</v>
+        <v>-0.86</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.67</v>
+        <v>-4.61</v>
       </c>
       <c r="V3" t="n">
-        <v>15.24</v>
+        <v>12.92</v>
       </c>
       <c r="W3" t="n">
-        <v>19.81</v>
+        <v>19.52</v>
       </c>
       <c r="X3" t="n">
-        <v>43.8</v>
+        <v>43.11</v>
       </c>
       <c r="Y3" t="n">
         <v>21.59</v>
@@ -788,7 +788,7 @@
         <v>-18.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>74.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -858,13 +858,13 @@
         <v>5.03</v>
       </c>
       <c r="P4" t="n">
-        <v>377.2</v>
+        <v>370</v>
       </c>
       <c r="Q4" t="n">
-        <v>382.4396</v>
+        <v>381.6882</v>
       </c>
       <c r="R4" t="n">
-        <v>359.026</v>
+        <v>359.4747</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="U4" t="n">
-        <v>-10.81</v>
+        <v>-13.13</v>
       </c>
       <c r="V4" t="n">
-        <v>10.21</v>
+        <v>7.36</v>
       </c>
       <c r="W4" t="n">
-        <v>34.21</v>
+        <v>31.6</v>
       </c>
       <c r="X4" t="n">
-        <v>20.1</v>
+        <v>19.51</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.07</v>
+        <v>16.09</v>
       </c>
       <c r="Z4" t="n">
         <v>-16.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -907,11 +907,11 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>80.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -925,30 +925,30 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>72.90000000000001</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -963,13 +963,13 @@
         <v>5.03</v>
       </c>
       <c r="P5" t="n">
-        <v>210.99</v>
+        <v>48.955</v>
       </c>
       <c r="Q5" t="n">
-        <v>171.0414</v>
+        <v>44.003</v>
       </c>
       <c r="R5" t="n">
-        <v>156.0836</v>
+        <v>39.9835</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>24.57</v>
+        <v>8.93</v>
       </c>
       <c r="U5" t="n">
-        <v>38.06</v>
+        <v>12.79</v>
       </c>
       <c r="V5" t="n">
-        <v>40.31</v>
+        <v>30.39</v>
       </c>
       <c r="W5" t="n">
-        <v>61.67</v>
+        <v>49.76</v>
       </c>
       <c r="X5" t="n">
-        <v>22.39</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>20.9</v>
+        <v>16.34</v>
       </c>
       <c r="Z5" t="n">
-        <v>-33.01</v>
+        <v>-22.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.98</v>
+        <v>0.42</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>76.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1068,13 +1068,13 @@
         <v>5.03</v>
       </c>
       <c r="P6" t="n">
-        <v>47.98</v>
+        <v>163.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.8504</v>
+        <v>153.0768</v>
       </c>
       <c r="R6" t="n">
-        <v>39.9115</v>
+        <v>145.9373</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>8.32</v>
+        <v>6.04</v>
       </c>
       <c r="U6" t="n">
-        <v>10.12</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>27.37</v>
+        <v>14.8</v>
       </c>
       <c r="W6" t="n">
-        <v>46.48</v>
+        <v>27.46</v>
       </c>
       <c r="X6" t="n">
-        <v>8.57</v>
+        <v>12.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.31</v>
+        <v>13.74</v>
       </c>
       <c r="Z6" t="n">
-        <v>-22.01</v>
+        <v>-20.96</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>74.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1135,30 +1135,30 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.40000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>FGQI.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>Fidelity Global Quality Income UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Satellite</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Quality Dividend</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1170,16 +1170,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.03</v>
+        <v>4.68</v>
       </c>
       <c r="P7" t="n">
-        <v>163.11</v>
+        <v>9.744999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>152.7362</v>
+        <v>9.336</v>
       </c>
       <c r="R7" t="n">
-        <v>145.7892</v>
+        <v>8.9178</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>5.92</v>
+        <v>4.16</v>
       </c>
       <c r="U7" t="n">
-        <v>8.4</v>
+        <v>5.01</v>
       </c>
       <c r="V7" t="n">
-        <v>14.46</v>
+        <v>11.47</v>
       </c>
       <c r="W7" t="n">
-        <v>26.28</v>
+        <v>23.5</v>
       </c>
       <c r="X7" t="n">
-        <v>12.31</v>
+        <v>11.83</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.74</v>
+        <v>13.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>-20.96</v>
+        <v>-19.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1216,13 +1216,13 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.7</v>
+        <v>72.5</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1240,30 +1240,30 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>68.7</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FGQI.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fidelity Global Quality Income UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1275,16 +1275,16 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>4.68</v>
+        <v>5.03</v>
       </c>
       <c r="P8" t="n">
-        <v>9.734999999999999</v>
+        <v>123.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.3223</v>
+        <v>116.2908</v>
       </c>
       <c r="R8" t="n">
-        <v>8.9102</v>
+        <v>111.6325</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>3.73</v>
+        <v>5.37</v>
       </c>
       <c r="U8" t="n">
-        <v>4.64</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>11.77</v>
+        <v>12.72</v>
       </c>
       <c r="W8" t="n">
-        <v>22.99</v>
+        <v>24.62</v>
       </c>
       <c r="X8" t="n">
-        <v>11.81</v>
+        <v>12.89</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.38</v>
+        <v>14.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>-19.89</v>
+        <v>-21.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1321,13 +1321,13 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.5</v>
+        <v>71.8</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -1345,30 +1345,30 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>67.5</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1383,13 +1383,13 @@
         <v>5.03</v>
       </c>
       <c r="P9" t="n">
-        <v>123.43</v>
+        <v>220.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>116.0496</v>
+        <v>172.3296</v>
       </c>
       <c r="R9" t="n">
-        <v>111.5316</v>
+        <v>156.4821</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,28 +1397,28 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>5.43</v>
+        <v>24.73</v>
       </c>
       <c r="U9" t="n">
-        <v>8.23</v>
+        <v>45.07</v>
       </c>
       <c r="V9" t="n">
-        <v>12.67</v>
+        <v>46.35</v>
       </c>
       <c r="W9" t="n">
-        <v>23.71</v>
+        <v>70.19</v>
       </c>
       <c r="X9" t="n">
-        <v>12.92</v>
+        <v>23.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.21</v>
+        <v>20.98</v>
       </c>
       <c r="Z9" t="n">
-        <v>-21.63</v>
+        <v>-33.01</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.77</v>
+        <v>1.01</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.5</v>
+        <v>70.8</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>67.5</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="10">
@@ -1488,13 +1488,13 @@
         <v>5.03</v>
       </c>
       <c r="P10" t="n">
-        <v>74.22</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>70.997</v>
+        <v>71.0996</v>
       </c>
       <c r="R10" t="n">
-        <v>68.3355</v>
+        <v>68.3895</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,19 +1502,19 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="U10" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="V10" t="n">
-        <v>11.04</v>
+        <v>10.57</v>
       </c>
       <c r="W10" t="n">
-        <v>18.49</v>
+        <v>18.93</v>
       </c>
       <c r="X10" t="n">
-        <v>11.35</v>
+        <v>11.21</v>
       </c>
       <c r="Y10" t="n">
         <v>14.16</v>
@@ -1523,7 +1523,7 @@
         <v>-20.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         <v>5.03</v>
       </c>
       <c r="P11" t="n">
-        <v>99.7</v>
+        <v>100.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>90.5836</v>
+        <v>90.9076</v>
       </c>
       <c r="R11" t="n">
-        <v>84.5615</v>
+        <v>84.6671</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>8.42</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>15.54</v>
+        <v>16.99</v>
       </c>
       <c r="V11" t="n">
-        <v>23.93</v>
+        <v>24.79</v>
       </c>
       <c r="W11" t="n">
-        <v>29.25</v>
+        <v>30.37</v>
       </c>
       <c r="X11" t="n">
-        <v>14.1</v>
+        <v>14.12</v>
       </c>
       <c r="Y11" t="n">
         <v>17.29</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1698,13 +1698,13 @@
         <v>5.03</v>
       </c>
       <c r="P12" t="n">
-        <v>125.25</v>
+        <v>125.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>116.6426</v>
+        <v>116.9282</v>
       </c>
       <c r="R12" t="n">
-        <v>112.2682</v>
+        <v>112.3748</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,19 +1712,19 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>6.32</v>
+        <v>6.15</v>
       </c>
       <c r="U12" t="n">
-        <v>11.21</v>
+        <v>12.48</v>
       </c>
       <c r="V12" t="n">
-        <v>12.39</v>
+        <v>12.79</v>
       </c>
       <c r="W12" t="n">
-        <v>25.38</v>
+        <v>26.88</v>
       </c>
       <c r="X12" t="n">
-        <v>14.79</v>
+        <v>14.83</v>
       </c>
       <c r="Y12" t="n">
         <v>15.21</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>67.8</v>
+        <v>68.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,30 +1765,30 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>67.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.MI</t>
+          <t>ISPY.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco Nasdaq-100 UCITS ETF</t>
+          <t>L&amp;G Cyber Security UCITS ETF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nasdaq / Tech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1803,13 +1803,13 @@
         <v>5.03</v>
       </c>
       <c r="P13" t="n">
-        <v>635.34</v>
+        <v>37.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>562.6676</v>
+        <v>28.7313</v>
       </c>
       <c r="R13" t="n">
-        <v>530.4944</v>
+        <v>27.135</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,28 +1817,28 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>11.74</v>
+        <v>32.92</v>
       </c>
       <c r="U13" t="n">
-        <v>22.52</v>
+        <v>60.08</v>
       </c>
       <c r="V13" t="n">
-        <v>20.96</v>
+        <v>38.45</v>
       </c>
       <c r="W13" t="n">
-        <v>37.41</v>
+        <v>40.04</v>
       </c>
       <c r="X13" t="n">
-        <v>18.74</v>
+        <v>13.32</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.89</v>
+        <v>24.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>-31.11</v>
+        <v>-33.89</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.84</v>
+        <v>0.46</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>65.3</v>
+        <v>67.5</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1870,19 +1870,19 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>69.3</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>EQQQ.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>Invesco Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1893,7 +1893,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Nasdaq / Tech</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         <v>5.03</v>
       </c>
       <c r="P14" t="n">
-        <v>62.98</v>
+        <v>641.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>60.6656</v>
+        <v>565.0358</v>
       </c>
       <c r="R14" t="n">
-        <v>58.2728</v>
+        <v>531.2375</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>3.16</v>
+        <v>11.14</v>
       </c>
       <c r="U14" t="n">
-        <v>0.48</v>
+        <v>24.23</v>
       </c>
       <c r="V14" t="n">
-        <v>13.34</v>
+        <v>22.38</v>
       </c>
       <c r="W14" t="n">
-        <v>17.03</v>
+        <v>39.21</v>
       </c>
       <c r="X14" t="n">
-        <v>9.75</v>
+        <v>18.82</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.52</v>
+        <v>19.89</v>
       </c>
       <c r="Z14" t="n">
-        <v>-20.85</v>
+        <v>-31.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1954,14 +1954,14 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI14" t="n">
-        <v>64.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -1975,19 +1975,19 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>64.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ISPY.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L&amp;G Cyber Security UCITS ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1998,7 +1998,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2013,13 +2013,13 @@
         <v>5.03</v>
       </c>
       <c r="P15" t="n">
-        <v>35.16</v>
+        <v>18.026</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.5101</v>
+        <v>15.6511</v>
       </c>
       <c r="R15" t="n">
-        <v>27.0751</v>
+        <v>14.3224</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,28 +2027,28 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>29.05</v>
+        <v>11.22</v>
       </c>
       <c r="U15" t="n">
-        <v>46.29</v>
+        <v>25.81</v>
       </c>
       <c r="V15" t="n">
-        <v>29.34</v>
+        <v>32.99</v>
       </c>
       <c r="W15" t="n">
-        <v>28.44</v>
+        <v>44.72</v>
       </c>
       <c r="X15" t="n">
-        <v>12.1</v>
+        <v>11.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>24.37</v>
+        <v>22.01</v>
       </c>
       <c r="Z15" t="n">
-        <v>-33.89</v>
+        <v>-35.29</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.2</v>
+        <v>63.8</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Drawdown storico importante.</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -2080,30 +2080,30 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>63.2</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2118,13 +2118,13 @@
         <v>5.03</v>
       </c>
       <c r="P16" t="n">
-        <v>17.864</v>
+        <v>62.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.5663</v>
+        <v>60.7334</v>
       </c>
       <c r="R16" t="n">
-        <v>14.2972</v>
+        <v>58.3166</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2132,28 +2132,28 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>11.15</v>
+        <v>3.71</v>
       </c>
       <c r="U16" t="n">
-        <v>23.75</v>
+        <v>-0.19</v>
       </c>
       <c r="V16" t="n">
-        <v>31.99</v>
+        <v>11.68</v>
       </c>
       <c r="W16" t="n">
-        <v>42.52</v>
+        <v>16.47</v>
       </c>
       <c r="X16" t="n">
-        <v>11.79</v>
+        <v>9.57</v>
       </c>
       <c r="Y16" t="n">
-        <v>22.01</v>
+        <v>14.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>-35.29</v>
+        <v>-20.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>63</v>
+        <v>63.6</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Drawdown storico importante.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>68</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="17">
@@ -2223,13 +2223,13 @@
         <v>5.03</v>
       </c>
       <c r="P17" t="n">
-        <v>63.51</v>
+        <v>63.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.2716</v>
+        <v>63.2558</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0527</v>
+        <v>63.0606</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.84</v>
+        <v>-2.09</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.95</v>
+        <v>0.27</v>
       </c>
       <c r="X17" t="n">
-        <v>6.34</v>
+        <v>6.35</v>
       </c>
       <c r="Y17" t="n">
         <v>10.18</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>58.8</v>
+        <v>59.1</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>58.8</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="18">
@@ -2328,13 +2328,13 @@
         <v>5.03</v>
       </c>
       <c r="P18" t="n">
-        <v>95.22</v>
+        <v>96.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>74.3848</v>
+        <v>75.10080000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>57.8151</v>
+        <v>58.0907</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>24.55</v>
+        <v>25.4</v>
       </c>
       <c r="U18" t="n">
-        <v>54.98</v>
+        <v>59.04</v>
       </c>
       <c r="V18" t="n">
-        <v>90.36</v>
+        <v>96.31</v>
       </c>
       <c r="W18" t="n">
-        <v>159.7</v>
+        <v>165.05</v>
       </c>
       <c r="X18" t="n">
-        <v>37.28</v>
+        <v>37.37</v>
       </c>
       <c r="Y18" t="n">
         <v>30.99</v>
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>105.65</v>
+        <v>109.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>85.93899999999999</v>
+        <v>86.6044</v>
       </c>
       <c r="R19" t="n">
-        <v>76.3985</v>
+        <v>76.6204</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,28 +2447,28 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>21.58</v>
+        <v>21.9</v>
       </c>
       <c r="U19" t="n">
-        <v>37.6</v>
+        <v>45.78</v>
       </c>
       <c r="V19" t="n">
-        <v>50.58</v>
+        <v>57.27</v>
       </c>
       <c r="W19" t="n">
-        <v>82.84999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="X19" t="n">
-        <v>16.78</v>
+        <v>17.37</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.16</v>
+        <v>28.21</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>53</v>
+        <v>53.2</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="20">
@@ -2538,33 +2538,33 @@
         <v>5.03</v>
       </c>
       <c r="P20" t="n">
-        <v>4.9295</v>
+        <v>4.911</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9076</v>
+        <v>4.9075</v>
       </c>
       <c r="R20" t="n">
-        <v>4.9275</v>
+        <v>4.9276</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.23</v>
+        <v>-1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.23</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>1.94</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.23</v>
+        <v>-1.3</v>
       </c>
       <c r="Y20" t="n">
         <v>4.67</v>
@@ -2573,7 +2573,7 @@
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,11 +2587,11 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>52.5</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>49.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
@@ -2643,13 +2643,13 @@
         <v>5.03</v>
       </c>
       <c r="P21" t="n">
-        <v>23.74</v>
+        <v>23.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6303</v>
+        <v>23.6284</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7502</v>
+        <v>23.7506</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,28 +2657,28 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0.42</v>
+        <v>0.08</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.37</v>
+        <v>-2.21</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.21</v>
+        <v>-1.07</v>
       </c>
       <c r="W21" t="n">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.57</v>
+        <v>-1.68</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="Z21" t="n">
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.74</v>
+        <v>-0.77</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.8</v>
+        <v>35.2</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -648,13 +648,13 @@
         <v>5.03</v>
       </c>
       <c r="P2" t="n">
-        <v>71.48999999999999</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>61.5902</v>
+        <v>61.9172</v>
       </c>
       <c r="R2" t="n">
-        <v>54.121</v>
+        <v>54.2535</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>15.27</v>
+        <v>14.3</v>
       </c>
       <c r="U2" t="n">
-        <v>22.65</v>
+        <v>25.04</v>
       </c>
       <c r="V2" t="n">
-        <v>41.65</v>
+        <v>41.8</v>
       </c>
       <c r="W2" t="n">
-        <v>63.52</v>
+        <v>65.92</v>
       </c>
       <c r="X2" t="n">
-        <v>17.44</v>
+        <v>17.55</v>
       </c>
       <c r="Y2" t="n">
         <v>13.91</v>
@@ -683,7 +683,7 @@
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -721,24 +721,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -750,16 +750,16 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>3.04</v>
+        <v>5.03</v>
       </c>
       <c r="P3" t="n">
-        <v>56.25</v>
+        <v>372.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>56.8998</v>
+        <v>381.4838</v>
       </c>
       <c r="R3" t="n">
-        <v>55.4351</v>
+        <v>359.9466</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-0.86</v>
+        <v>-1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.61</v>
+        <v>-14.62</v>
       </c>
       <c r="V3" t="n">
-        <v>12.92</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
-        <v>19.52</v>
+        <v>33.48</v>
       </c>
       <c r="X3" t="n">
-        <v>43.11</v>
+        <v>19.96</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.59</v>
+        <v>16.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>-18.73</v>
+        <v>-16.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>1.12</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -796,13 +796,13 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Utile come protezione macro/geopolitica.</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -820,30 +820,30 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>73.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -858,13 +858,13 @@
         <v>5.03</v>
       </c>
       <c r="P4" t="n">
-        <v>370</v>
+        <v>49.485</v>
       </c>
       <c r="Q4" t="n">
-        <v>381.6882</v>
+        <v>44.1833</v>
       </c>
       <c r="R4" t="n">
-        <v>359.4747</v>
+        <v>40.0571</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>-0.72</v>
+        <v>8.01</v>
       </c>
       <c r="U4" t="n">
-        <v>-13.13</v>
+        <v>15.28</v>
       </c>
       <c r="V4" t="n">
-        <v>7.36</v>
+        <v>30.38</v>
       </c>
       <c r="W4" t="n">
-        <v>31.6</v>
+        <v>52.99</v>
       </c>
       <c r="X4" t="n">
-        <v>19.51</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.09</v>
+        <v>16.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>-16.7</v>
+        <v>-22.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -901,13 +901,13 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.3</v>
+        <v>76.2</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Utile come protezione macro/geopolitica.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>71.3</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -948,7 +948,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -963,13 +963,13 @@
         <v>5.03</v>
       </c>
       <c r="P5" t="n">
-        <v>48.955</v>
+        <v>164.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.003</v>
+        <v>153.4884</v>
       </c>
       <c r="R5" t="n">
-        <v>39.9835</v>
+        <v>146.0864</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>8.93</v>
+        <v>5.67</v>
       </c>
       <c r="U5" t="n">
-        <v>12.79</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>30.39</v>
+        <v>14.15</v>
       </c>
       <c r="W5" t="n">
-        <v>49.76</v>
+        <v>28.26</v>
       </c>
       <c r="X5" t="n">
-        <v>8.880000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.34</v>
+        <v>13.74</v>
       </c>
       <c r="Z5" t="n">
-        <v>-22.01</v>
+        <v>-20.96</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>76</v>
+        <v>73.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1030,30 +1030,30 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>74</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>FGQI.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>Fidelity Global Quality Income UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Satellite</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Quality Dividend</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.03</v>
+        <v>4.69</v>
       </c>
       <c r="P6" t="n">
-        <v>163.88</v>
+        <v>9.797000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>153.0768</v>
+        <v>9.3535</v>
       </c>
       <c r="R6" t="n">
-        <v>145.9373</v>
+        <v>8.925700000000001</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>6.04</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="n">
-        <v>9.359999999999999</v>
+        <v>5.27</v>
       </c>
       <c r="V6" t="n">
-        <v>14.8</v>
+        <v>10.91</v>
       </c>
       <c r="W6" t="n">
-        <v>27.46</v>
+        <v>24.3</v>
       </c>
       <c r="X6" t="n">
-        <v>12.32</v>
+        <v>11.94</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.74</v>
+        <v>13.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>-20.96</v>
+        <v>-19.89</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>73</v>
+        <v>72.7</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1135,30 +1135,30 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FGQI.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fidelity Global Quality Income UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1170,16 +1170,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>4.68</v>
+        <v>5.03</v>
       </c>
       <c r="P7" t="n">
-        <v>9.744999999999999</v>
+        <v>124.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.336</v>
+        <v>116.5792</v>
       </c>
       <c r="R7" t="n">
-        <v>8.9178</v>
+        <v>111.733</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>4.16</v>
+        <v>5.13</v>
       </c>
       <c r="U7" t="n">
-        <v>5.01</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>11.47</v>
+        <v>11.86</v>
       </c>
       <c r="W7" t="n">
-        <v>23.5</v>
+        <v>25.18</v>
       </c>
       <c r="X7" t="n">
-        <v>11.83</v>
+        <v>12.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.38</v>
+        <v>14.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>-19.89</v>
+        <v>-21.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1216,13 +1216,13 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.5</v>
+        <v>71.7</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1240,30 +1240,30 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1278,13 +1278,13 @@
         <v>5.03</v>
       </c>
       <c r="P8" t="n">
-        <v>123.76</v>
+        <v>220.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>116.2908</v>
+        <v>173.6708</v>
       </c>
       <c r="R8" t="n">
-        <v>111.6325</v>
+        <v>156.8762</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>5.37</v>
+        <v>22.05</v>
       </c>
       <c r="U8" t="n">
-        <v>8.960000000000001</v>
+        <v>44.23</v>
       </c>
       <c r="V8" t="n">
-        <v>12.72</v>
+        <v>44.92</v>
       </c>
       <c r="W8" t="n">
-        <v>24.62</v>
+        <v>70.23</v>
       </c>
       <c r="X8" t="n">
-        <v>12.89</v>
+        <v>23.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.21</v>
+        <v>20.98</v>
       </c>
       <c r="Z8" t="n">
-        <v>-21.63</v>
+        <v>-33.01</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1321,13 +1321,13 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AI8" t="n">
-        <v>71.8</v>
+        <v>70.8</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -1345,30 +1345,30 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>67.8</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>IWMO.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1383,13 +1383,13 @@
         <v>5.03</v>
       </c>
       <c r="P9" t="n">
-        <v>220.04</v>
+        <v>101.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>172.3296</v>
+        <v>91.30500000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>156.4821</v>
+        <v>84.77930000000001</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,28 +1397,28 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>24.73</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>45.07</v>
+        <v>19.18</v>
       </c>
       <c r="V9" t="n">
-        <v>46.35</v>
+        <v>24.16</v>
       </c>
       <c r="W9" t="n">
-        <v>70.19</v>
+        <v>32.33</v>
       </c>
       <c r="X9" t="n">
-        <v>23.15</v>
+        <v>14.48</v>
       </c>
       <c r="Y9" t="n">
-        <v>20.98</v>
+        <v>17.31</v>
       </c>
       <c r="Z9" t="n">
-        <v>-33.01</v>
+        <v>-23.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>75.8</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1488,13 +1488,13 @@
         <v>5.03</v>
       </c>
       <c r="P10" t="n">
-        <v>74.06999999999999</v>
+        <v>74.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>71.0996</v>
+        <v>71.2272</v>
       </c>
       <c r="R10" t="n">
-        <v>68.3895</v>
+        <v>68.44280000000001</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="V10" t="n">
-        <v>10.57</v>
+        <v>9.56</v>
       </c>
       <c r="W10" t="n">
-        <v>18.93</v>
+        <v>19</v>
       </c>
       <c r="X10" t="n">
         <v>11.21</v>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>70.2</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,30 +1555,30 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IWMO.MI</t>
+          <t>VUAA.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
+          <t>Vanguard S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>USA Large Cap</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         <v>5.03</v>
       </c>
       <c r="P11" t="n">
-        <v>100.14</v>
+        <v>126.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>90.9076</v>
+        <v>117.2528</v>
       </c>
       <c r="R11" t="n">
-        <v>84.6671</v>
+        <v>112.4791</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,28 +1607,28 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>8.619999999999999</v>
+        <v>5.69</v>
       </c>
       <c r="U11" t="n">
-        <v>16.99</v>
+        <v>11.84</v>
       </c>
       <c r="V11" t="n">
-        <v>24.79</v>
+        <v>11.8</v>
       </c>
       <c r="W11" t="n">
-        <v>30.37</v>
+        <v>27.27</v>
       </c>
       <c r="X11" t="n">
-        <v>14.12</v>
+        <v>14.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.29</v>
+        <v>15.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>-23.45</v>
+        <v>-23.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>69.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,30 +1660,30 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>69.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VUAA.MI</t>
+          <t>ISPY.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard S&amp;P 500 UCITS ETF</t>
+          <t>L&amp;G Cyber Security UCITS ETF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USA Large Cap</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1698,13 +1698,13 @@
         <v>5.03</v>
       </c>
       <c r="P12" t="n">
-        <v>125.89</v>
+        <v>37.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>116.9282</v>
+        <v>28.9554</v>
       </c>
       <c r="R12" t="n">
-        <v>112.3748</v>
+        <v>27.1937</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,28 +1712,28 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>6.15</v>
+        <v>29.58</v>
       </c>
       <c r="U12" t="n">
-        <v>12.48</v>
+        <v>55.74</v>
       </c>
       <c r="V12" t="n">
-        <v>12.79</v>
+        <v>38.27</v>
       </c>
       <c r="W12" t="n">
-        <v>26.88</v>
+        <v>39.42</v>
       </c>
       <c r="X12" t="n">
-        <v>14.83</v>
+        <v>13.27</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.21</v>
+        <v>24.58</v>
       </c>
       <c r="Z12" t="n">
-        <v>-23.28</v>
+        <v>-33.89</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.84</v>
+        <v>0.46</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>68.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,30 +1765,30 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>68.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ISPY.MI</t>
+          <t>EQQQ.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L&amp;G Cyber Security UCITS ETF</t>
+          <t>Invesco Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Nasdaq / Tech</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1803,13 +1803,13 @@
         <v>5.03</v>
       </c>
       <c r="P13" t="n">
-        <v>37.77</v>
+        <v>643.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.7313</v>
+        <v>567.6278</v>
       </c>
       <c r="R13" t="n">
-        <v>27.135</v>
+        <v>531.9691</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,28 +1817,28 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>32.92</v>
+        <v>10.02</v>
       </c>
       <c r="U13" t="n">
-        <v>60.08</v>
+        <v>23.74</v>
       </c>
       <c r="V13" t="n">
-        <v>38.45</v>
+        <v>20.87</v>
       </c>
       <c r="W13" t="n">
-        <v>40.04</v>
+        <v>40.71</v>
       </c>
       <c r="X13" t="n">
-        <v>13.32</v>
+        <v>18.99</v>
       </c>
       <c r="Y13" t="n">
-        <v>24.58</v>
+        <v>19.89</v>
       </c>
       <c r="Z13" t="n">
-        <v>-33.89</v>
+        <v>-31.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.46</v>
+        <v>0.85</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI13" t="n">
-        <v>67.5</v>
+        <v>66.2</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1870,19 +1870,19 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>67.5</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EQQQ.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco Nasdaq-100 UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1893,7 +1893,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nasdaq / Tech</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         <v>5.03</v>
       </c>
       <c r="P14" t="n">
-        <v>641.23</v>
+        <v>62.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>565.0358</v>
+        <v>60.838</v>
       </c>
       <c r="R14" t="n">
-        <v>531.2375</v>
+        <v>58.3626</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>11.14</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>24.23</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>22.38</v>
+        <v>11.23</v>
       </c>
       <c r="W14" t="n">
-        <v>39.21</v>
+        <v>16.96</v>
       </c>
       <c r="X14" t="n">
-        <v>18.82</v>
+        <v>9.69</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.89</v>
+        <v>14.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>-31.11</v>
+        <v>-20.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.85</v>
+        <v>0.53</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1954,14 +1954,14 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>66.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>70.09999999999999</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="15">
@@ -2013,13 +2013,13 @@
         <v>5.03</v>
       </c>
       <c r="P15" t="n">
-        <v>18.026</v>
+        <v>17.988</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.6511</v>
+        <v>15.7394</v>
       </c>
       <c r="R15" t="n">
-        <v>14.3224</v>
+        <v>14.3473</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,19 +2027,19 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>11.22</v>
+        <v>7.93</v>
       </c>
       <c r="U15" t="n">
-        <v>25.81</v>
+        <v>25.63</v>
       </c>
       <c r="V15" t="n">
-        <v>32.99</v>
+        <v>32.05</v>
       </c>
       <c r="W15" t="n">
-        <v>44.72</v>
+        <v>45.32</v>
       </c>
       <c r="X15" t="n">
-        <v>11.83</v>
+        <v>11.75</v>
       </c>
       <c r="Y15" t="n">
         <v>22.01</v>
@@ -2048,7 +2048,7 @@
         <v>-35.29</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         <v>-5</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2080,30 +2080,30 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2115,45 +2115,45 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>5.03</v>
+        <v>3.05</v>
       </c>
       <c r="P16" t="n">
-        <v>62.59</v>
+        <v>55.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.7334</v>
+        <v>56.7646</v>
       </c>
       <c r="R16" t="n">
-        <v>58.3166</v>
+        <v>55.462</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>3.71</v>
+        <v>-2.41</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.19</v>
+        <v>-10.58</v>
       </c>
       <c r="V16" t="n">
-        <v>11.68</v>
+        <v>9.51</v>
       </c>
       <c r="W16" t="n">
-        <v>16.47</v>
+        <v>17.11</v>
       </c>
       <c r="X16" t="n">
-        <v>9.57</v>
+        <v>42.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.52</v>
+        <v>21.62</v>
       </c>
       <c r="Z16" t="n">
-        <v>-20.85</v>
+        <v>-18.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.52</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2161,13 +2161,13 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>63.6</v>
+        <v>62.9</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>63.6</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="17">
@@ -2223,13 +2223,13 @@
         <v>5.03</v>
       </c>
       <c r="P17" t="n">
-        <v>63.77</v>
+        <v>63.61</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.2558</v>
+        <v>63.2512</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0606</v>
+        <v>63.0662</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.09</v>
+        <v>-3</v>
       </c>
       <c r="V17" t="n">
-        <v>0.74</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
-        <v>0.27</v>
+        <v>-0.64</v>
       </c>
       <c r="X17" t="n">
-        <v>6.35</v>
+        <v>6.15</v>
       </c>
       <c r="Y17" t="n">
         <v>10.18</v>
@@ -2258,7 +2258,7 @@
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>59.1</v>
+        <v>58.6</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>59.1</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="18">
@@ -2328,13 +2328,13 @@
         <v>5.03</v>
       </c>
       <c r="P18" t="n">
-        <v>96.73</v>
+        <v>99.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>75.10080000000001</v>
+        <v>75.8944</v>
       </c>
       <c r="R18" t="n">
-        <v>58.0907</v>
+        <v>58.3766</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,28 +2342,28 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>25.4</v>
+        <v>23.68</v>
       </c>
       <c r="U18" t="n">
-        <v>59.04</v>
+        <v>64.06</v>
       </c>
       <c r="V18" t="n">
-        <v>96.31</v>
+        <v>93.87</v>
       </c>
       <c r="W18" t="n">
-        <v>165.05</v>
+        <v>178.34</v>
       </c>
       <c r="X18" t="n">
-        <v>37.37</v>
+        <v>38.27</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.99</v>
+        <v>31.02</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
         <v>-23</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>72.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>109.93</v>
+        <v>111.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.6044</v>
+        <v>87.3296</v>
       </c>
       <c r="R19" t="n">
-        <v>76.6204</v>
+        <v>76.8489</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,19 +2447,19 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>21.9</v>
+        <v>20.56</v>
       </c>
       <c r="U19" t="n">
-        <v>45.78</v>
+        <v>48.1</v>
       </c>
       <c r="V19" t="n">
-        <v>57.27</v>
+        <v>56.32</v>
       </c>
       <c r="W19" t="n">
-        <v>93.5</v>
+        <v>96.94</v>
       </c>
       <c r="X19" t="n">
-        <v>17.37</v>
+        <v>17.42</v>
       </c>
       <c r="Y19" t="n">
         <v>28.21</v>
@@ -2538,13 +2538,13 @@
         <v>5.03</v>
       </c>
       <c r="P20" t="n">
-        <v>4.911</v>
+        <v>4.926</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9075</v>
+        <v>4.9077</v>
       </c>
       <c r="R20" t="n">
-        <v>4.9276</v>
+        <v>4.9278</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.74</v>
+        <v>-1.05</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3</v>
+        <v>-1.25</v>
       </c>
       <c r="Y20" t="n">
         <v>4.67</v>
@@ -2573,7 +2573,7 @@
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="21">
@@ -2643,13 +2643,13 @@
         <v>5.03</v>
       </c>
       <c r="P21" t="n">
-        <v>23.62</v>
+        <v>23.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6284</v>
+        <v>23.6306</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7506</v>
+        <v>23.7514</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.21</v>
+        <v>-1.19</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.07</v>
+        <v>-0.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.68</v>
+        <v>-1.58</v>
       </c>
       <c r="Y21" t="n">
         <v>4.8</v>
@@ -2678,7 +2678,7 @@
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.2</v>
+        <v>35.5</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -648,13 +648,13 @@
         <v>5.03</v>
       </c>
       <c r="P2" t="n">
-        <v>72.26000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>61.9172</v>
+        <v>62.2582</v>
       </c>
       <c r="R2" t="n">
-        <v>54.2535</v>
+        <v>54.3848</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>14.3</v>
+        <v>12.38</v>
       </c>
       <c r="U2" t="n">
-        <v>25.04</v>
+        <v>28.34</v>
       </c>
       <c r="V2" t="n">
-        <v>41.8</v>
+        <v>41.76</v>
       </c>
       <c r="W2" t="n">
-        <v>65.92</v>
+        <v>66.23</v>
       </c>
       <c r="X2" t="n">
-        <v>17.55</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
         <v>13.91</v>
@@ -683,7 +683,7 @@
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -753,13 +753,13 @@
         <v>5.03</v>
       </c>
       <c r="P3" t="n">
-        <v>372.59</v>
+        <v>368.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>381.4838</v>
+        <v>381.2146</v>
       </c>
       <c r="R3" t="n">
-        <v>359.9466</v>
+        <v>360.4047</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-1.01</v>
+        <v>-4.16</v>
       </c>
       <c r="U3" t="n">
-        <v>-14.62</v>
+        <v>-13.4</v>
       </c>
       <c r="V3" t="n">
-        <v>7.8</v>
+        <v>6.73</v>
       </c>
       <c r="W3" t="n">
-        <v>33.48</v>
+        <v>29.41</v>
       </c>
       <c r="X3" t="n">
-        <v>19.96</v>
+        <v>19.43</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.08</v>
+        <v>16.09</v>
       </c>
       <c r="Z3" t="n">
         <v>-16.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -802,11 +802,11 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>80.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -820,30 +820,30 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -858,13 +858,13 @@
         <v>5.03</v>
       </c>
       <c r="P4" t="n">
-        <v>49.485</v>
+        <v>218.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>44.1833</v>
+        <v>175.0164</v>
       </c>
       <c r="R4" t="n">
-        <v>40.0571</v>
+        <v>157.2651</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>8.01</v>
+        <v>19.36</v>
       </c>
       <c r="U4" t="n">
-        <v>15.28</v>
+        <v>45.71</v>
       </c>
       <c r="V4" t="n">
-        <v>30.38</v>
+        <v>43.86</v>
       </c>
       <c r="W4" t="n">
-        <v>52.99</v>
+        <v>69.13</v>
       </c>
       <c r="X4" t="n">
-        <v>9.130000000000001</v>
+        <v>22.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.34</v>
+        <v>20.98</v>
       </c>
       <c r="Z4" t="n">
-        <v>-22.01</v>
+        <v>-33.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.44</v>
+        <v>0.98</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -901,13 +901,13 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI4" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>74.2</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -948,7 +948,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -963,13 +963,13 @@
         <v>5.03</v>
       </c>
       <c r="P5" t="n">
-        <v>164.85</v>
+        <v>48.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>153.4884</v>
+        <v>44.3671</v>
       </c>
       <c r="R5" t="n">
-        <v>146.0864</v>
+        <v>40.1276</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>5.67</v>
+        <v>4.54</v>
       </c>
       <c r="U5" t="n">
-        <v>9.960000000000001</v>
+        <v>19.52</v>
       </c>
       <c r="V5" t="n">
-        <v>14.15</v>
+        <v>29.13</v>
       </c>
       <c r="W5" t="n">
-        <v>28.26</v>
+        <v>51.62</v>
       </c>
       <c r="X5" t="n">
-        <v>12.4</v>
+        <v>8.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.74</v>
+        <v>16.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>-20.96</v>
+        <v>-22.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.2</v>
+        <v>75.8</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1030,30 +1030,30 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>69.2</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FGQI.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fidelity Global Quality Income UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>4.69</v>
+        <v>5.03</v>
       </c>
       <c r="P6" t="n">
-        <v>9.797000000000001</v>
+        <v>164.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.3535</v>
+        <v>153.917</v>
       </c>
       <c r="R6" t="n">
-        <v>8.925700000000001</v>
+        <v>146.2316</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>4.25</v>
+        <v>3.87</v>
       </c>
       <c r="U6" t="n">
-        <v>5.27</v>
+        <v>11.11</v>
       </c>
       <c r="V6" t="n">
-        <v>10.91</v>
+        <v>13.76</v>
       </c>
       <c r="W6" t="n">
-        <v>24.3</v>
+        <v>28.34</v>
       </c>
       <c r="X6" t="n">
-        <v>11.94</v>
+        <v>12.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.37</v>
+        <v>13.74</v>
       </c>
       <c r="Z6" t="n">
-        <v>-19.89</v>
+        <v>-20.96</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>72.7</v>
+        <v>73</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1135,30 +1135,30 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>FGQI.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
+          <t>Fidelity Global Quality Income UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Satellite</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Quality Dividend</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1170,16 +1170,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.03</v>
+        <v>4.69</v>
       </c>
       <c r="P7" t="n">
-        <v>124.27</v>
+        <v>9.792999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>116.5792</v>
+        <v>9.3725</v>
       </c>
       <c r="R7" t="n">
-        <v>111.733</v>
+        <v>8.9335</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>5.13</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>9.109999999999999</v>
+        <v>6.71</v>
       </c>
       <c r="V7" t="n">
-        <v>11.86</v>
+        <v>11.01</v>
       </c>
       <c r="W7" t="n">
-        <v>25.18</v>
+        <v>25.09</v>
       </c>
       <c r="X7" t="n">
-        <v>12.92</v>
+        <v>11.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.21</v>
+        <v>13.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>-21.63</v>
+        <v>-19.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1216,13 +1216,13 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>71.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1240,30 +1240,30 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>67.7</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1278,13 +1278,13 @@
         <v>5.03</v>
       </c>
       <c r="P8" t="n">
-        <v>220.06</v>
+        <v>123.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>173.6708</v>
+        <v>116.8824</v>
       </c>
       <c r="R8" t="n">
-        <v>156.8762</v>
+        <v>111.8315</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>22.05</v>
+        <v>3.61</v>
       </c>
       <c r="U8" t="n">
-        <v>44.23</v>
+        <v>10.02</v>
       </c>
       <c r="V8" t="n">
-        <v>44.92</v>
+        <v>11.61</v>
       </c>
       <c r="W8" t="n">
-        <v>70.23</v>
+        <v>25.4</v>
       </c>
       <c r="X8" t="n">
-        <v>23.06</v>
+        <v>12.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>20.98</v>
+        <v>14.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>-33.01</v>
+        <v>-21.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1321,13 +1321,13 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>70.8</v>
+        <v>71.7</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>75.8</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="9">
@@ -1383,13 +1383,13 @@
         <v>5.03</v>
       </c>
       <c r="P9" t="n">
-        <v>101.95</v>
+        <v>103.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>91.30500000000001</v>
+        <v>91.7538</v>
       </c>
       <c r="R9" t="n">
-        <v>84.77930000000001</v>
+        <v>84.8993</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,28 +1397,28 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>8.300000000000001</v>
+        <v>7.77</v>
       </c>
       <c r="U9" t="n">
-        <v>19.18</v>
+        <v>24.01</v>
       </c>
       <c r="V9" t="n">
-        <v>24.16</v>
+        <v>25.72</v>
       </c>
       <c r="W9" t="n">
-        <v>32.33</v>
+        <v>33.88</v>
       </c>
       <c r="X9" t="n">
-        <v>14.48</v>
+        <v>14.78</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.31</v>
+        <v>17.32</v>
       </c>
       <c r="Z9" t="n">
         <v>-23.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>70.09999999999999</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -1488,13 +1488,13 @@
         <v>5.03</v>
       </c>
       <c r="P10" t="n">
-        <v>74.27</v>
+        <v>74.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>71.2272</v>
+        <v>71.3656</v>
       </c>
       <c r="R10" t="n">
-        <v>68.44280000000001</v>
+        <v>68.4957</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,19 +1502,19 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>4.68</v>
+        <v>5.65</v>
       </c>
       <c r="V10" t="n">
-        <v>9.56</v>
+        <v>9.65</v>
       </c>
       <c r="W10" t="n">
-        <v>19</v>
+        <v>19.78</v>
       </c>
       <c r="X10" t="n">
-        <v>11.21</v>
+        <v>11.1</v>
       </c>
       <c r="Y10" t="n">
         <v>14.16</v>
@@ -1523,7 +1523,7 @@
         <v>-20.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>70</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1593,13 +1593,13 @@
         <v>5.03</v>
       </c>
       <c r="P11" t="n">
-        <v>126.21</v>
+        <v>125.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>117.2528</v>
+        <v>117.5858</v>
       </c>
       <c r="R11" t="n">
-        <v>112.4791</v>
+        <v>112.5816</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>5.69</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>11.84</v>
+        <v>11.78</v>
       </c>
       <c r="V11" t="n">
-        <v>11.8</v>
+        <v>11.53</v>
       </c>
       <c r="W11" t="n">
-        <v>27.27</v>
+        <v>27.72</v>
       </c>
       <c r="X11" t="n">
-        <v>14.8</v>
+        <v>14.68</v>
       </c>
       <c r="Y11" t="n">
         <v>15.21</v>
@@ -1628,7 +1628,7 @@
         <v>-23.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1698,13 +1698,13 @@
         <v>5.03</v>
       </c>
       <c r="P12" t="n">
-        <v>37.65</v>
+        <v>37.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>28.9554</v>
+        <v>29.1874</v>
       </c>
       <c r="R12" t="n">
-        <v>27.1937</v>
+        <v>27.2528</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,19 +1712,19 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>29.58</v>
+        <v>31.69</v>
       </c>
       <c r="U12" t="n">
-        <v>55.74</v>
+        <v>51.47</v>
       </c>
       <c r="V12" t="n">
-        <v>38.27</v>
+        <v>38.69</v>
       </c>
       <c r="W12" t="n">
-        <v>39.42</v>
+        <v>39.07</v>
       </c>
       <c r="X12" t="n">
-        <v>13.27</v>
+        <v>13.21</v>
       </c>
       <c r="Y12" t="n">
         <v>24.58</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="13">
@@ -1803,13 +1803,13 @@
         <v>5.03</v>
       </c>
       <c r="P13" t="n">
-        <v>643.34</v>
+        <v>644.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>567.6278</v>
+        <v>570.3306</v>
       </c>
       <c r="R13" t="n">
-        <v>531.9691</v>
+        <v>532.7101</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,28 +1817,28 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>10.02</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>23.74</v>
+        <v>24.19</v>
       </c>
       <c r="V13" t="n">
-        <v>20.87</v>
+        <v>21.18</v>
       </c>
       <c r="W13" t="n">
-        <v>40.71</v>
+        <v>41.6</v>
       </c>
       <c r="X13" t="n">
-        <v>18.99</v>
+        <v>18.73</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.89</v>
+        <v>19.88</v>
       </c>
       <c r="Z13" t="n">
         <v>-31.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
         <v>-4</v>
       </c>
       <c r="AI13" t="n">
-        <v>66.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1870,30 +1870,30 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         <v>5.03</v>
       </c>
       <c r="P14" t="n">
-        <v>62.99</v>
+        <v>18.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>60.838</v>
+        <v>15.8344</v>
       </c>
       <c r="R14" t="n">
-        <v>58.3626</v>
+        <v>14.3732</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>6.44</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>30.05</v>
       </c>
       <c r="V14" t="n">
-        <v>11.23</v>
+        <v>32.45</v>
       </c>
       <c r="W14" t="n">
-        <v>16.96</v>
+        <v>47.94</v>
       </c>
       <c r="X14" t="n">
-        <v>9.69</v>
+        <v>11.78</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.52</v>
+        <v>22.01</v>
       </c>
       <c r="Z14" t="n">
-        <v>-20.85</v>
+        <v>-35.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI14" t="n">
-        <v>63.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Drawdown storico importante.</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -1975,30 +1975,30 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>63.7</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2013,13 +2013,13 @@
         <v>5.03</v>
       </c>
       <c r="P15" t="n">
-        <v>17.988</v>
+        <v>62.49</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.7394</v>
+        <v>60.9524</v>
       </c>
       <c r="R15" t="n">
-        <v>14.3473</v>
+        <v>58.4056</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,28 +2027,28 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>7.93</v>
+        <v>0.11</v>
       </c>
       <c r="U15" t="n">
-        <v>25.63</v>
+        <v>4.51</v>
       </c>
       <c r="V15" t="n">
-        <v>32.05</v>
+        <v>10.17</v>
       </c>
       <c r="W15" t="n">
-        <v>45.32</v>
+        <v>16.23</v>
       </c>
       <c r="X15" t="n">
-        <v>11.75</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.01</v>
+        <v>14.53</v>
       </c>
       <c r="Z15" t="n">
-        <v>-35.29</v>
+        <v>-20.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.44</v>
+        <v>0.51</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.7</v>
+        <v>63.1</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Drawdown storico importante.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>68.7</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="16">
@@ -2118,13 +2118,13 @@
         <v>3.05</v>
       </c>
       <c r="P16" t="n">
-        <v>55.02</v>
+        <v>54.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>56.7646</v>
+        <v>56.6414</v>
       </c>
       <c r="R16" t="n">
-        <v>55.462</v>
+        <v>55.4846</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2132,19 +2132,19 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>-2.41</v>
+        <v>-3.27</v>
       </c>
       <c r="U16" t="n">
-        <v>-10.58</v>
+        <v>-13.08</v>
       </c>
       <c r="V16" t="n">
-        <v>9.51</v>
+        <v>7.72</v>
       </c>
       <c r="W16" t="n">
-        <v>17.11</v>
+        <v>15.34</v>
       </c>
       <c r="X16" t="n">
-        <v>42.01</v>
+        <v>41.23</v>
       </c>
       <c r="Y16" t="n">
         <v>21.62</v>
@@ -2153,7 +2153,7 @@
         <v>-18.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>62.9</v>
+        <v>61.7</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>55.9</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="17">
@@ -2223,13 +2223,13 @@
         <v>5.03</v>
       </c>
       <c r="P17" t="n">
-        <v>63.61</v>
+        <v>63.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.2512</v>
+        <v>63.2618</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0662</v>
+        <v>63.0742</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="U17" t="n">
-        <v>-3</v>
+        <v>-2.21</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.57</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.64</v>
+        <v>0.06</v>
       </c>
       <c r="X17" t="n">
-        <v>6.15</v>
+        <v>6.11</v>
       </c>
       <c r="Y17" t="n">
         <v>10.18</v>
@@ -2258,7 +2258,7 @@
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>58.6</v>
+        <v>58.8</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>58.6</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="18">
@@ -2328,13 +2328,13 @@
         <v>5.03</v>
       </c>
       <c r="P18" t="n">
-        <v>99.55</v>
+        <v>101.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>75.8944</v>
+        <v>76.74720000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>58.3766</v>
+        <v>58.6729</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,28 +2342,28 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>23.68</v>
+        <v>20.93</v>
       </c>
       <c r="U18" t="n">
-        <v>64.06</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>93.87</v>
+        <v>98.69</v>
       </c>
       <c r="W18" t="n">
-        <v>178.34</v>
+        <v>185.25</v>
       </c>
       <c r="X18" t="n">
-        <v>38.27</v>
+        <v>38.51</v>
       </c>
       <c r="Y18" t="n">
-        <v>31.02</v>
+        <v>31.03</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
         <v>-23</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>72.59999999999999</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="19">
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>111.49</v>
+        <v>111.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>87.3296</v>
+        <v>88.06780000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>76.8489</v>
+        <v>77.07299999999999</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,19 +2447,19 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>20.56</v>
+        <v>18.77</v>
       </c>
       <c r="U19" t="n">
-        <v>48.1</v>
+        <v>51.89</v>
       </c>
       <c r="V19" t="n">
-        <v>56.32</v>
+        <v>56</v>
       </c>
       <c r="W19" t="n">
-        <v>96.94</v>
+        <v>91.53</v>
       </c>
       <c r="X19" t="n">
-        <v>17.42</v>
+        <v>17.1</v>
       </c>
       <c r="Y19" t="n">
         <v>28.21</v>
@@ -2468,7 +2468,7 @@
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2538,13 +2538,13 @@
         <v>5.03</v>
       </c>
       <c r="P20" t="n">
-        <v>4.926</v>
+        <v>4.9075</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9077</v>
+        <v>4.9081</v>
       </c>
       <c r="R20" t="n">
-        <v>4.9278</v>
+        <v>4.9279</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.05</v>
+        <v>-1.04</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.64</v>
+        <v>-0.96</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.25</v>
+        <v>-1.35</v>
       </c>
       <c r="Y20" t="n">
         <v>4.67</v>
@@ -2573,7 +2573,7 @@
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
@@ -2643,13 +2643,13 @@
         <v>5.03</v>
       </c>
       <c r="P21" t="n">
-        <v>23.73</v>
+        <v>23.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6306</v>
+        <v>23.6323</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7514</v>
+        <v>23.7517</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,28 +2657,28 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0.23</v>
+        <v>-0.42</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.19</v>
+        <v>-1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.65</v>
+        <v>-1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.58</v>
+        <v>-1.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="Z21" t="n">
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.74</v>
+        <v>-0.77</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.5</v>
+        <v>32.2</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -645,16 +645,16 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P2" t="n">
-        <v>72.27</v>
+        <v>70.39</v>
       </c>
       <c r="Q2" t="n">
-        <v>62.2582</v>
+        <v>62.89</v>
       </c>
       <c r="R2" t="n">
-        <v>54.3848</v>
+        <v>54.633</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,28 +662,28 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>12.38</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>28.34</v>
+        <v>24.36</v>
       </c>
       <c r="V2" t="n">
-        <v>41.76</v>
+        <v>37.7</v>
       </c>
       <c r="W2" t="n">
-        <v>66.23</v>
+        <v>60.91</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>16.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.91</v>
+        <v>13.94</v>
       </c>
       <c r="Z2" t="n">
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="3">
@@ -750,16 +750,16 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P3" t="n">
-        <v>368.17</v>
+        <v>362.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>381.2146</v>
+        <v>381.2578</v>
       </c>
       <c r="R3" t="n">
-        <v>360.4047</v>
+        <v>361.3086</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-4.16</v>
+        <v>-5.91</v>
       </c>
       <c r="U3" t="n">
-        <v>-13.4</v>
+        <v>-13.94</v>
       </c>
       <c r="V3" t="n">
-        <v>6.73</v>
+        <v>3.41</v>
       </c>
       <c r="W3" t="n">
-        <v>29.41</v>
+        <v>27.42</v>
       </c>
       <c r="X3" t="n">
-        <v>19.43</v>
+        <v>19.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.09</v>
+        <v>16.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>-16.7</v>
+        <v>-16.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>78.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>70.59999999999999</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +855,16 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P4" t="n">
-        <v>218.28</v>
+        <v>204.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>175.0164</v>
+        <v>177.3502</v>
       </c>
       <c r="R4" t="n">
-        <v>157.2651</v>
+        <v>157.9466</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>19.36</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>45.71</v>
+        <v>33.36</v>
       </c>
       <c r="V4" t="n">
-        <v>43.86</v>
+        <v>34.51</v>
       </c>
       <c r="W4" t="n">
-        <v>69.13</v>
+        <v>55.39</v>
       </c>
       <c r="X4" t="n">
-        <v>22.6</v>
+        <v>20.97</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.98</v>
+        <v>21.09</v>
       </c>
       <c r="Z4" t="n">
         <v>-33.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>-5</v>
       </c>
       <c r="AI4" t="n">
-        <v>76.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -925,30 +925,30 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>75.59999999999999</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>FGQI.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Fidelity Global Quality Income UCITS ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Satellite</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Quality Dividend</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -960,16 +960,16 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>5.03</v>
+        <v>4.7</v>
       </c>
       <c r="P5" t="n">
-        <v>48.92</v>
+        <v>9.805</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.3671</v>
+        <v>9.4084</v>
       </c>
       <c r="R5" t="n">
-        <v>40.1276</v>
+        <v>8.948499999999999</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>4.54</v>
+        <v>3.52</v>
       </c>
       <c r="U5" t="n">
-        <v>19.52</v>
+        <v>6.63</v>
       </c>
       <c r="V5" t="n">
-        <v>29.13</v>
+        <v>11.07</v>
       </c>
       <c r="W5" t="n">
-        <v>51.62</v>
+        <v>23.57</v>
       </c>
       <c r="X5" t="n">
-        <v>8.85</v>
+        <v>11.93</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.35</v>
+        <v>13.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>-22.01</v>
+        <v>-19.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>75.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>73.8</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,16 +1065,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P6" t="n">
-        <v>164.12</v>
+        <v>46.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>153.917</v>
+        <v>44.6609</v>
       </c>
       <c r="R6" t="n">
-        <v>146.2316</v>
+        <v>40.2517</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1082,28 +1082,28 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>3.87</v>
+        <v>-1.06</v>
       </c>
       <c r="U6" t="n">
-        <v>11.11</v>
+        <v>14.07</v>
       </c>
       <c r="V6" t="n">
-        <v>13.76</v>
+        <v>22.6</v>
       </c>
       <c r="W6" t="n">
-        <v>28.34</v>
+        <v>41.68</v>
       </c>
       <c r="X6" t="n">
-        <v>12.25</v>
+        <v>7.93</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.74</v>
+        <v>16.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>-20.96</v>
+        <v>-22.01</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.75</v>
+        <v>0.36</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1135,30 +1135,30 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>69</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FGQI.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fidelity Global Quality Income UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1170,16 +1170,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>4.69</v>
+        <v>5.04</v>
       </c>
       <c r="P7" t="n">
-        <v>9.792999999999999</v>
+        <v>162.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.3725</v>
+        <v>154.706</v>
       </c>
       <c r="R7" t="n">
-        <v>8.9335</v>
+        <v>146.5059</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>6.71</v>
+        <v>9.42</v>
       </c>
       <c r="V7" t="n">
-        <v>11.01</v>
+        <v>12.5</v>
       </c>
       <c r="W7" t="n">
-        <v>25.09</v>
+        <v>25.27</v>
       </c>
       <c r="X7" t="n">
-        <v>11.92</v>
+        <v>12.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.37</v>
+        <v>13.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>-19.89</v>
+        <v>-20.96</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1216,13 +1216,13 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1275,16 +1275,16 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P8" t="n">
-        <v>123.9</v>
+        <v>123.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>116.8824</v>
+        <v>117.4594</v>
       </c>
       <c r="R8" t="n">
-        <v>111.8315</v>
+        <v>112.0219</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>3.61</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>10.02</v>
+        <v>8.91</v>
       </c>
       <c r="V8" t="n">
-        <v>11.61</v>
+        <v>11.12</v>
       </c>
       <c r="W8" t="n">
-        <v>25.4</v>
+        <v>23.28</v>
       </c>
       <c r="X8" t="n">
-        <v>12.8</v>
+        <v>12.72</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
       <c r="Z8" t="n">
         <v>-21.63</v>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>71.7</v>
+        <v>71</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1345,19 +1345,19 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>67.7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IWMO.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
+          <t>iShares MSCI World Quality Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1380,16 +1380,16 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P9" t="n">
-        <v>103.29</v>
+        <v>74.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>91.7538</v>
+        <v>71.64619999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>84.8993</v>
+        <v>68.6027</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,28 +1397,28 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>7.77</v>
+        <v>3.11</v>
       </c>
       <c r="U9" t="n">
-        <v>24.01</v>
+        <v>6.22</v>
       </c>
       <c r="V9" t="n">
-        <v>25.72</v>
+        <v>10.2</v>
       </c>
       <c r="W9" t="n">
-        <v>33.88</v>
+        <v>18.66</v>
       </c>
       <c r="X9" t="n">
-        <v>14.78</v>
+        <v>11.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.32</v>
+        <v>14.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>-23.45</v>
+        <v>-20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>IWMO.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Quality Factor UCITS ETF</t>
+          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1473,7 +1473,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1485,16 +1485,16 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P10" t="n">
-        <v>74.23</v>
+        <v>100.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>71.3656</v>
+        <v>92.5526</v>
       </c>
       <c r="R10" t="n">
-        <v>68.4957</v>
+        <v>85.1207</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1502,28 +1502,28 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>4.99</v>
       </c>
       <c r="U10" t="n">
-        <v>5.65</v>
+        <v>20.49</v>
       </c>
       <c r="V10" t="n">
-        <v>9.65</v>
+        <v>22.9</v>
       </c>
       <c r="W10" t="n">
-        <v>19.78</v>
+        <v>29.22</v>
       </c>
       <c r="X10" t="n">
-        <v>11.1</v>
+        <v>14.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.16</v>
+        <v>17.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>-20.6</v>
+        <v>-23.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>70.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1590,16 +1590,16 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P11" t="n">
-        <v>125.8</v>
+        <v>125.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>117.5858</v>
+        <v>118.2278</v>
       </c>
       <c r="R11" t="n">
-        <v>112.5816</v>
+        <v>112.7791</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1607,22 +1607,22 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="U11" t="n">
-        <v>11.78</v>
+        <v>10.42</v>
       </c>
       <c r="V11" t="n">
-        <v>11.53</v>
+        <v>11.03</v>
       </c>
       <c r="W11" t="n">
-        <v>27.72</v>
+        <v>25.15</v>
       </c>
       <c r="X11" t="n">
-        <v>14.68</v>
+        <v>14.64</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.21</v>
+        <v>15.2</v>
       </c>
       <c r="Z11" t="n">
         <v>-23.28</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>68.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>68.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1695,16 +1695,16 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P12" t="n">
-        <v>37.73</v>
+        <v>36.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>29.1874</v>
+        <v>29.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.2528</v>
+        <v>27.3578</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1712,28 +1712,28 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>31.69</v>
+        <v>21.93</v>
       </c>
       <c r="U12" t="n">
-        <v>51.47</v>
+        <v>39.98</v>
       </c>
       <c r="V12" t="n">
-        <v>38.69</v>
+        <v>33.26</v>
       </c>
       <c r="W12" t="n">
-        <v>39.07</v>
+        <v>30.45</v>
       </c>
       <c r="X12" t="n">
-        <v>13.21</v>
+        <v>12.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>24.58</v>
+        <v>24.61</v>
       </c>
       <c r="Z12" t="n">
         <v>-33.89</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1747,11 +1747,11 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>67.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>67.3</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1800,16 +1800,16 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P13" t="n">
-        <v>644.3</v>
+        <v>628.0700000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>570.3306</v>
+        <v>575.314</v>
       </c>
       <c r="R13" t="n">
-        <v>532.7101</v>
+        <v>534.072</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1817,28 +1817,28 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>8.869999999999999</v>
+        <v>4.04</v>
       </c>
       <c r="U13" t="n">
-        <v>24.19</v>
+        <v>19.01</v>
       </c>
       <c r="V13" t="n">
-        <v>21.18</v>
+        <v>18</v>
       </c>
       <c r="W13" t="n">
-        <v>41.6</v>
+        <v>35.46</v>
       </c>
       <c r="X13" t="n">
-        <v>18.73</v>
+        <v>18.23</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.88</v>
+        <v>19.9</v>
       </c>
       <c r="Z13" t="n">
         <v>-31.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1852,11 +1852,11 @@
         <v>-4</v>
       </c>
       <c r="AI13" t="n">
-        <v>66.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -1870,30 +1870,30 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>70.40000000000001</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1905,16 +1905,16 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P14" t="n">
-        <v>18.17</v>
+        <v>62.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.8344</v>
+        <v>61.1718</v>
       </c>
       <c r="R14" t="n">
-        <v>14.3732</v>
+        <v>58.4895</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>6.44</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
-        <v>30.05</v>
+        <v>4.74</v>
       </c>
       <c r="V14" t="n">
-        <v>32.45</v>
+        <v>10.4</v>
       </c>
       <c r="W14" t="n">
-        <v>47.94</v>
+        <v>15.89</v>
       </c>
       <c r="X14" t="n">
-        <v>11.78</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>22.01</v>
+        <v>14.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>-35.29</v>
+        <v>-20.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.44</v>
+        <v>0.51</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>64.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Drawdown storico importante.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -1975,30 +1975,30 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>69.40000000000001</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2010,45 +2010,45 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>5.03</v>
+        <v>3.06</v>
       </c>
       <c r="P15" t="n">
-        <v>62.49</v>
+        <v>53.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>60.9524</v>
+        <v>56.4154</v>
       </c>
       <c r="R15" t="n">
-        <v>58.4056</v>
+        <v>55.524</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>0.11</v>
+        <v>-0.11</v>
       </c>
       <c r="U15" t="n">
-        <v>4.51</v>
+        <v>-11.78</v>
       </c>
       <c r="V15" t="n">
-        <v>10.17</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>16.23</v>
+        <v>12.56</v>
       </c>
       <c r="X15" t="n">
-        <v>9.460000000000001</v>
+        <v>40.64</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.53</v>
+        <v>21.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>-20.85</v>
+        <v>-18.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2056,13 +2056,13 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.1</v>
+        <v>61.1</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -2080,19 +2080,19 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>63.1</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2103,7 +2103,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2115,45 +2115,45 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>3.05</v>
+        <v>5.04</v>
       </c>
       <c r="P16" t="n">
-        <v>54.17</v>
+        <v>17.508</v>
       </c>
       <c r="Q16" t="n">
-        <v>56.6414</v>
+        <v>16.0044</v>
       </c>
       <c r="R16" t="n">
-        <v>55.4846</v>
+        <v>14.421</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>-3.27</v>
+        <v>1.18</v>
       </c>
       <c r="U16" t="n">
-        <v>-13.08</v>
+        <v>23.94</v>
       </c>
       <c r="V16" t="n">
-        <v>7.72</v>
+        <v>26.48</v>
       </c>
       <c r="W16" t="n">
-        <v>15.34</v>
+        <v>39.26</v>
       </c>
       <c r="X16" t="n">
-        <v>41.23</v>
+        <v>11.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>21.62</v>
+        <v>22.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>-18.73</v>
+        <v>-35.29</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>0.41</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2161,13 +2161,13 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI16" t="n">
-        <v>61.7</v>
+        <v>60.8</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Drawdown storico importante.</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>54.7</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="17">
@@ -2220,16 +2220,16 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P17" t="n">
-        <v>63.75</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.2618</v>
+        <v>63.2998</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0742</v>
+        <v>63.0909</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2237,28 +2237,28 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.21</v>
+        <v>-1.03</v>
       </c>
       <c r="V17" t="n">
-        <v>0.57</v>
+        <v>2.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0.06</v>
+        <v>0.95</v>
       </c>
       <c r="X17" t="n">
-        <v>6.11</v>
+        <v>6.36</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="Z17" t="n">
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>58.8</v>
+        <v>59.5</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>58.8</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="18">
@@ -2325,16 +2325,16 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P18" t="n">
-        <v>101.75</v>
+        <v>94.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>76.74720000000001</v>
+        <v>78.2212</v>
       </c>
       <c r="R18" t="n">
-        <v>58.6729</v>
+        <v>59.2109</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2342,28 +2342,28 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>20.93</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>71.98999999999999</v>
+        <v>56.58</v>
       </c>
       <c r="V18" t="n">
-        <v>98.69</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>185.25</v>
+        <v>153.29</v>
       </c>
       <c r="X18" t="n">
-        <v>38.51</v>
+        <v>36.71</v>
       </c>
       <c r="Y18" t="n">
-        <v>31.03</v>
+        <v>31.11</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
         <v>-23</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.7</v>
+        <v>54.2</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>72.7</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="19">
@@ -2433,13 +2433,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>111.2</v>
+        <v>104.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>88.06780000000001</v>
+        <v>89.3968</v>
       </c>
       <c r="R19" t="n">
-        <v>77.07299999999999</v>
+        <v>77.4868</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2447,28 +2447,28 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>18.77</v>
+        <v>11.54</v>
       </c>
       <c r="U19" t="n">
-        <v>51.89</v>
+        <v>40.48</v>
       </c>
       <c r="V19" t="n">
-        <v>56</v>
+        <v>46.14</v>
       </c>
       <c r="W19" t="n">
-        <v>91.53</v>
+        <v>76.67</v>
       </c>
       <c r="X19" t="n">
-        <v>17.1</v>
+        <v>15.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.21</v>
+        <v>28.28</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>68.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2535,13 +2535,13 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P20" t="n">
-        <v>4.9075</v>
+        <v>4.9015</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9081</v>
+        <v>4.909</v>
       </c>
       <c r="R20" t="n">
         <v>4.9279</v>
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>-0.3</v>
+        <v>-0.35</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.04</v>
+        <v>-0.9</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.96</v>
+        <v>-0.65</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="X20" t="n">
         <v>-1.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="Z20" t="n">
         <v>-17.02</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="21">
@@ -2640,16 +2640,16 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P21" t="n">
         <v>23.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6323</v>
+        <v>23.6365</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7517</v>
+        <v>23.7523</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,16 +2657,16 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.42</v>
+        <v>-1.15</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.11</v>
+        <v>-0.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.29</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="X21" t="n">
         <v>-1.7</v>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -645,7 +645,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P2" t="n">
         <v>70.39</v>
@@ -674,7 +674,7 @@
         <v>60.91</v>
       </c>
       <c r="X2" t="n">
-        <v>16.88</v>
+        <v>16.99</v>
       </c>
       <c r="Y2" t="n">
         <v>13.94</v>
@@ -683,7 +683,7 @@
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -750,7 +750,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P3" t="n">
         <v>362.44</v>
@@ -779,10 +779,10 @@
         <v>27.42</v>
       </c>
       <c r="X3" t="n">
-        <v>19.1</v>
+        <v>19.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.11</v>
+        <v>16.12</v>
       </c>
       <c r="Z3" t="n">
         <v>-16.95</v>
@@ -855,7 +855,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P4" t="n">
         <v>204.35</v>
@@ -884,7 +884,7 @@
         <v>55.39</v>
       </c>
       <c r="X4" t="n">
-        <v>20.97</v>
+        <v>20.89</v>
       </c>
       <c r="Y4" t="n">
         <v>21.09</v>
@@ -1065,7 +1065,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P6" t="n">
         <v>46.55</v>
@@ -1094,10 +1094,10 @@
         <v>41.68</v>
       </c>
       <c r="X6" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.43</v>
+        <v>16.44</v>
       </c>
       <c r="Z6" t="n">
         <v>-22.01</v>
@@ -1170,7 +1170,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P7" t="n">
         <v>162.31</v>
@@ -1199,10 +1199,10 @@
         <v>25.27</v>
       </c>
       <c r="X7" t="n">
-        <v>12.03</v>
+        <v>12.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.74</v>
+        <v>13.75</v>
       </c>
       <c r="Z7" t="n">
         <v>-20.96</v>
@@ -1275,7 +1275,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P8" t="n">
         <v>123.34</v>
@@ -1304,16 +1304,16 @@
         <v>23.28</v>
       </c>
       <c r="X8" t="n">
-        <v>12.72</v>
+        <v>12.71</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.2</v>
+        <v>14.21</v>
       </c>
       <c r="Z8" t="n">
         <v>-21.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1380,7 +1380,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P9" t="n">
         <v>74.67</v>
@@ -1409,7 +1409,7 @@
         <v>18.66</v>
       </c>
       <c r="X9" t="n">
-        <v>11.25</v>
+        <v>11.24</v>
       </c>
       <c r="Y9" t="n">
         <v>14.16</v>
@@ -1485,7 +1485,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P10" t="n">
         <v>100.51</v>
@@ -1514,7 +1514,7 @@
         <v>29.22</v>
       </c>
       <c r="X10" t="n">
-        <v>14.14</v>
+        <v>14.19</v>
       </c>
       <c r="Y10" t="n">
         <v>17.34</v>
@@ -1590,7 +1590,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P11" t="n">
         <v>125.19</v>
@@ -1622,7 +1622,7 @@
         <v>14.64</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.2</v>
+        <v>15.21</v>
       </c>
       <c r="Z11" t="n">
         <v>-23.28</v>
@@ -1695,7 +1695,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P12" t="n">
         <v>36.2</v>
@@ -1724,7 +1724,7 @@
         <v>30.45</v>
       </c>
       <c r="X12" t="n">
-        <v>12.13</v>
+        <v>11.82</v>
       </c>
       <c r="Y12" t="n">
         <v>24.61</v>
@@ -1733,7 +1733,7 @@
         <v>-33.89</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="13">
@@ -1800,7 +1800,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P13" t="n">
         <v>628.0700000000001</v>
@@ -1829,7 +1829,7 @@
         <v>35.46</v>
       </c>
       <c r="X13" t="n">
-        <v>18.23</v>
+        <v>18.15</v>
       </c>
       <c r="Y13" t="n">
         <v>19.9</v>
@@ -1838,7 +1838,7 @@
         <v>-31.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1905,7 +1905,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P14" t="n">
         <v>62.65</v>
@@ -1934,7 +1934,7 @@
         <v>15.89</v>
       </c>
       <c r="X14" t="n">
-        <v>9.470000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="Y14" t="n">
         <v>14.53</v>
@@ -2115,7 +2115,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P16" t="n">
         <v>17.508</v>
@@ -2144,16 +2144,16 @@
         <v>39.26</v>
       </c>
       <c r="X16" t="n">
-        <v>11.1</v>
+        <v>11.18</v>
       </c>
       <c r="Y16" t="n">
-        <v>22.05</v>
+        <v>22.06</v>
       </c>
       <c r="Z16" t="n">
         <v>-35.29</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
         <v>-5</v>
       </c>
       <c r="AI16" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2220,7 +2220,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P17" t="n">
         <v>64.51000000000001</v>
@@ -2249,10 +2249,10 @@
         <v>0.95</v>
       </c>
       <c r="X17" t="n">
-        <v>6.36</v>
+        <v>6.39</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.19</v>
+        <v>10.2</v>
       </c>
       <c r="Z17" t="n">
         <v>-12.85</v>
@@ -2325,7 +2325,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P18" t="n">
         <v>94.2</v>
@@ -2354,10 +2354,10 @@
         <v>153.29</v>
       </c>
       <c r="X18" t="n">
-        <v>36.71</v>
+        <v>36.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>31.11</v>
+        <v>31.13</v>
       </c>
       <c r="Z18" t="n">
         <v>-37.84</v>
@@ -2459,10 +2459,10 @@
         <v>76.67</v>
       </c>
       <c r="X19" t="n">
-        <v>15.7</v>
+        <v>15.72</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.28</v>
+        <v>28.29</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
@@ -2535,7 +2535,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P20" t="n">
         <v>4.9015</v>
@@ -2564,7 +2564,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.35</v>
+        <v>-1.37</v>
       </c>
       <c r="Y20" t="n">
         <v>4.68</v>
@@ -2640,7 +2640,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="P21" t="n">
         <v>23.61</v>
@@ -2669,7 +2669,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7</v>
+        <v>-1.73</v>
       </c>
       <c r="Y21" t="n">
         <v>4.81</v>
@@ -2678,7 +2678,7 @@
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,6 +608,11 @@
         </is>
       </c>
       <c r="AM1" t="inlineStr">
+        <is>
+          <t>Ultimo aggiornamento</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Score Finale Base</t>
         </is>
@@ -645,36 +650,36 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P2" t="n">
-        <v>70.39</v>
+        <v>70.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>62.89</v>
+        <v>63.4816</v>
       </c>
       <c r="R2" t="n">
-        <v>54.633</v>
+        <v>54.8731</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="U2" t="n">
-        <v>24.36</v>
+        <v>25.08</v>
       </c>
       <c r="V2" t="n">
-        <v>37.7</v>
+        <v>38.09</v>
       </c>
       <c r="W2" t="n">
-        <v>60.91</v>
+        <v>60.59</v>
       </c>
       <c r="X2" t="n">
-        <v>16.99</v>
+        <v>17.13</v>
       </c>
       <c r="Y2" t="n">
         <v>13.94</v>
@@ -683,7 +688,7 @@
         <v>-17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -697,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -706,39 +711,44 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>81.90000000000001</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -750,45 +760,45 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P3" t="n">
-        <v>362.44</v>
+        <v>207.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>381.2578</v>
+        <v>179.6608</v>
       </c>
       <c r="R3" t="n">
-        <v>361.3086</v>
+        <v>158.6131</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>-5.91</v>
+        <v>11.64</v>
       </c>
       <c r="U3" t="n">
-        <v>-13.94</v>
+        <v>34.28</v>
       </c>
       <c r="V3" t="n">
-        <v>3.41</v>
+        <v>35.67</v>
       </c>
       <c r="W3" t="n">
-        <v>27.42</v>
+        <v>55.33</v>
       </c>
       <c r="X3" t="n">
-        <v>19.09</v>
+        <v>21.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.12</v>
+        <v>21.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>-16.95</v>
+        <v>-33.01</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -796,13 +806,13 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI3" t="n">
-        <v>77.2</v>
+        <v>76</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -811,39 +821,44 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Utile come protezione macro/geopolitica.</t>
+          <t>Tema strutturale forte, ma con rischio euforia e concentrazione.</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>69.2</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -855,45 +870,45 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P4" t="n">
-        <v>204.35</v>
+        <v>47.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>177.3502</v>
+        <v>44.9254</v>
       </c>
       <c r="R4" t="n">
-        <v>157.9466</v>
+        <v>40.3696</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>8.619999999999999</v>
+        <v>3.62</v>
       </c>
       <c r="U4" t="n">
-        <v>33.36</v>
+        <v>13.3</v>
       </c>
       <c r="V4" t="n">
-        <v>34.51</v>
+        <v>25.12</v>
       </c>
       <c r="W4" t="n">
-        <v>55.39</v>
+        <v>42.29</v>
       </c>
       <c r="X4" t="n">
-        <v>20.89</v>
+        <v>8.27</v>
       </c>
       <c r="Y4" t="n">
-        <v>21.09</v>
+        <v>16.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>-33.01</v>
+        <v>-22.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9</v>
+        <v>0.38</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -901,13 +916,13 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>75.8</v>
+        <v>72.7</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -916,16 +931,21 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>74.8</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>70.7</v>
       </c>
     </row>
     <row r="5">
@@ -960,45 +980,45 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="P5" t="n">
-        <v>9.805</v>
+        <v>9.755000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.4084</v>
+        <v>9.4436</v>
       </c>
       <c r="R5" t="n">
-        <v>8.948499999999999</v>
+        <v>8.963200000000001</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="U5" t="n">
-        <v>6.63</v>
+        <v>6.45</v>
       </c>
       <c r="V5" t="n">
-        <v>11.07</v>
+        <v>10.94</v>
       </c>
       <c r="W5" t="n">
-        <v>23.57</v>
+        <v>22.21</v>
       </c>
       <c r="X5" t="n">
-        <v>11.93</v>
+        <v>11.79</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.36</v>
+        <v>13.35</v>
       </c>
       <c r="Z5" t="n">
         <v>-19.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1012,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1021,28 +1041,33 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>67.59999999999999</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1053,7 +1078,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Global Equity</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1065,45 +1090,45 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P6" t="n">
-        <v>46.55</v>
+        <v>161.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>44.6609</v>
+        <v>155.4222</v>
       </c>
       <c r="R6" t="n">
-        <v>40.2517</v>
+        <v>146.7647</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>-1.06</v>
+        <v>3.01</v>
       </c>
       <c r="U6" t="n">
-        <v>14.07</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>22.6</v>
+        <v>12.18</v>
       </c>
       <c r="W6" t="n">
-        <v>41.68</v>
+        <v>24.25</v>
       </c>
       <c r="X6" t="n">
-        <v>7.99</v>
+        <v>11.91</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.44</v>
+        <v>13.74</v>
       </c>
       <c r="Z6" t="n">
-        <v>-22.01</v>
+        <v>-20.96</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1111,13 +1136,13 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1126,28 +1151,33 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Buona base core di lungo periodo.</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>69.90000000000001</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>67.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1170,45 +1200,45 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P7" t="n">
-        <v>162.31</v>
+        <v>122.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>154.706</v>
+        <v>117.9788</v>
       </c>
       <c r="R7" t="n">
-        <v>146.5059</v>
+        <v>112.2</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="U7" t="n">
-        <v>9.42</v>
+        <v>8.34</v>
       </c>
       <c r="V7" t="n">
-        <v>12.5</v>
+        <v>10.28</v>
       </c>
       <c r="W7" t="n">
-        <v>25.27</v>
+        <v>21.84</v>
       </c>
       <c r="X7" t="n">
-        <v>12.04</v>
+        <v>12.49</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.75</v>
+        <v>14.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>-20.96</v>
+        <v>-21.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1222,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>71.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1236,34 +1266,39 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>67.90000000000001</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>66.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
+          <t>iShares MSCI World Quality Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1275,45 +1310,45 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P8" t="n">
-        <v>123.34</v>
+        <v>74.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>117.4594</v>
+        <v>71.9068</v>
       </c>
       <c r="R8" t="n">
-        <v>112.0219</v>
+        <v>68.7047</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="U8" t="n">
-        <v>8.91</v>
+        <v>6.03</v>
       </c>
       <c r="V8" t="n">
-        <v>11.12</v>
+        <v>9.44</v>
       </c>
       <c r="W8" t="n">
-        <v>23.28</v>
+        <v>17.38</v>
       </c>
       <c r="X8" t="n">
-        <v>12.71</v>
+        <v>11.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.21</v>
+        <v>14.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>-21.63</v>
+        <v>-20.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1321,13 +1356,13 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>70.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1336,28 +1371,33 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Buona base core di lungo periodo.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>66.90000000000001</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>64.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>IWMO.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Quality Factor UCITS ETF</t>
+          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1368,7 +1408,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1380,45 +1420,45 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P9" t="n">
-        <v>74.67</v>
+        <v>101.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>71.64619999999999</v>
+        <v>93.3168</v>
       </c>
       <c r="R9" t="n">
-        <v>68.6027</v>
+        <v>85.3378</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>3.11</v>
+        <v>5.21</v>
       </c>
       <c r="U9" t="n">
-        <v>6.22</v>
+        <v>19.87</v>
       </c>
       <c r="V9" t="n">
-        <v>10.2</v>
+        <v>23.5</v>
       </c>
       <c r="W9" t="n">
-        <v>18.66</v>
+        <v>29.96</v>
       </c>
       <c r="X9" t="n">
-        <v>11.24</v>
+        <v>14.32</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.16</v>
+        <v>17.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>-20.6</v>
+        <v>-23.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1426,13 +1466,13 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>69.3</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1441,39 +1481,44 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>65</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>69.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IWMO.MI</t>
+          <t>VUAA.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
+          <t>Vanguard S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>USA Large Cap</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1485,45 +1530,45 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P10" t="n">
-        <v>100.51</v>
+        <v>124.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>92.5526</v>
+        <v>118.8208</v>
       </c>
       <c r="R10" t="n">
-        <v>85.1207</v>
+        <v>112.965</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>4.99</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>20.49</v>
+        <v>10.1</v>
       </c>
       <c r="V10" t="n">
-        <v>22.9</v>
+        <v>10.13</v>
       </c>
       <c r="W10" t="n">
-        <v>29.22</v>
+        <v>23.5</v>
       </c>
       <c r="X10" t="n">
-        <v>14.19</v>
+        <v>14.34</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.34</v>
+        <v>15.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>-23.45</v>
+        <v>-23.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1537,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>68.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1546,28 +1591,33 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>68.90000000000001</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VUAA.MI</t>
+          <t>EQQQ.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard S&amp;P 500 UCITS ETF</t>
+          <t>Invesco Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1578,7 +1628,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USA Large Cap</t>
+          <t>Nasdaq / Tech</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1590,45 +1640,45 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P11" t="n">
-        <v>125.19</v>
+        <v>626.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>118.2278</v>
+        <v>580.038</v>
       </c>
       <c r="R11" t="n">
-        <v>112.7791</v>
+        <v>535.4049</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>3.45</v>
+        <v>4.38</v>
       </c>
       <c r="U11" t="n">
-        <v>10.42</v>
+        <v>18.91</v>
       </c>
       <c r="V11" t="n">
-        <v>11.03</v>
+        <v>17.24</v>
       </c>
       <c r="W11" t="n">
-        <v>25.15</v>
+        <v>34.55</v>
       </c>
       <c r="X11" t="n">
-        <v>14.64</v>
+        <v>17.97</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.21</v>
+        <v>19.89</v>
       </c>
       <c r="Z11" t="n">
-        <v>-23.28</v>
+        <v>-31.11</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1639,51 +1689,56 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI11" t="n">
-        <v>67.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>67.40000000000001</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>67.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ISPY.MI</t>
+          <t>EXSA.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L&amp;G Cyber Security UCITS ETF</t>
+          <t>iShares STOXX Europe 600 UCITS ETF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1695,45 +1750,45 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P12" t="n">
-        <v>36.2</v>
+        <v>62.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>29.6</v>
+        <v>61.3574</v>
       </c>
       <c r="R12" t="n">
-        <v>27.3578</v>
+        <v>58.5673</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>21.93</v>
+        <v>3.01</v>
       </c>
       <c r="U12" t="n">
-        <v>39.98</v>
+        <v>4.34</v>
       </c>
       <c r="V12" t="n">
-        <v>33.26</v>
+        <v>10.08</v>
       </c>
       <c r="W12" t="n">
-        <v>30.45</v>
+        <v>15.23</v>
       </c>
       <c r="X12" t="n">
-        <v>11.82</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>24.61</v>
+        <v>14.53</v>
       </c>
       <c r="Z12" t="n">
-        <v>-33.89</v>
+        <v>-20.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1747,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>64.3</v>
+        <v>62.8</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1756,39 +1811,44 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>64.3</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>62.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.MI</t>
+          <t>ISPY.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco Nasdaq-100 UCITS ETF</t>
+          <t>L&amp;G Cyber Security UCITS ETF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nasdaq / Tech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1800,45 +1860,45 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P13" t="n">
-        <v>628.0700000000001</v>
+        <v>35.345</v>
       </c>
       <c r="Q13" t="n">
-        <v>575.314</v>
+        <v>29.9609</v>
       </c>
       <c r="R13" t="n">
-        <v>534.072</v>
+        <v>27.4503</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>4.04</v>
+        <v>18.61</v>
       </c>
       <c r="U13" t="n">
-        <v>19.01</v>
+        <v>34.29</v>
       </c>
       <c r="V13" t="n">
-        <v>18</v>
+        <v>29.04</v>
       </c>
       <c r="W13" t="n">
-        <v>35.46</v>
+        <v>26.3</v>
       </c>
       <c r="X13" t="n">
-        <v>18.15</v>
+        <v>11.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.9</v>
+        <v>24.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>-31.11</v>
+        <v>-33.89</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1849,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>64</v>
+        <v>62.2</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1861,39 +1921,44 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM13" t="n">
-        <v>68</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>62.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXSA.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1905,45 +1970,45 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P14" t="n">
-        <v>62.65</v>
+        <v>361.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>61.1718</v>
+        <v>380.8078</v>
       </c>
       <c r="R14" t="n">
-        <v>58.4895</v>
+        <v>362.1728</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>-5.59</v>
       </c>
       <c r="U14" t="n">
-        <v>4.74</v>
+        <v>-16.44</v>
       </c>
       <c r="V14" t="n">
-        <v>10.4</v>
+        <v>3.57</v>
       </c>
       <c r="W14" t="n">
-        <v>15.89</v>
+        <v>28.17</v>
       </c>
       <c r="X14" t="n">
-        <v>9.43</v>
+        <v>19.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.53</v>
+        <v>16.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>-20.85</v>
+        <v>-17.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.51</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1951,13 +2016,13 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>63.1</v>
+        <v>61.3</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -1966,28 +2031,33 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Utile come protezione macro/geopolitica. Prezzo sotto media 200: trend non ancora convincente.</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM14" t="n">
-        <v>63.1</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>53.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1998,7 +2068,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2010,45 +2080,45 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>3.06</v>
+        <v>5.04</v>
       </c>
       <c r="P15" t="n">
-        <v>53.63</v>
+        <v>17.644</v>
       </c>
       <c r="Q15" t="n">
-        <v>56.4154</v>
+        <v>16.1679</v>
       </c>
       <c r="R15" t="n">
-        <v>55.524</v>
+        <v>14.467</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>-0.11</v>
+        <v>3.81</v>
       </c>
       <c r="U15" t="n">
-        <v>-11.78</v>
+        <v>24.57</v>
       </c>
       <c r="V15" t="n">
-        <v>8.789999999999999</v>
+        <v>25.69</v>
       </c>
       <c r="W15" t="n">
-        <v>12.56</v>
+        <v>39.08</v>
       </c>
       <c r="X15" t="n">
-        <v>40.64</v>
+        <v>11.37</v>
       </c>
       <c r="Y15" t="n">
-        <v>21.62</v>
+        <v>22.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>-18.73</v>
+        <v>-35.29</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>0.42</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2056,13 +2126,13 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI15" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2071,28 +2141,33 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Drawdown storico importante.</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM15" t="n">
-        <v>54.1</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>65.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2103,7 +2178,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2115,45 +2190,45 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>5.03</v>
+        <v>3.07</v>
       </c>
       <c r="P16" t="n">
-        <v>17.508</v>
+        <v>52.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.0044</v>
+        <v>56.1484</v>
       </c>
       <c r="R16" t="n">
-        <v>14.421</v>
+        <v>55.5596</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>1.18</v>
+        <v>0.32</v>
       </c>
       <c r="U16" t="n">
-        <v>23.94</v>
+        <v>-15.99</v>
       </c>
       <c r="V16" t="n">
-        <v>26.48</v>
+        <v>6.53</v>
       </c>
       <c r="W16" t="n">
-        <v>39.26</v>
+        <v>9.75</v>
       </c>
       <c r="X16" t="n">
-        <v>11.18</v>
+        <v>39.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>22.06</v>
+        <v>21.61</v>
       </c>
       <c r="Z16" t="n">
-        <v>-35.29</v>
+        <v>-18.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.42</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2161,13 +2236,13 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0</v>
       </c>
-      <c r="AH16" t="n">
-        <v>-5</v>
-      </c>
       <c r="AI16" t="n">
-        <v>60.9</v>
+        <v>59.6</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2176,16 +2251,21 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Drawdown storico importante.</t>
+          <t>Tema sostenuto dal contesto geopolitico, da usare come satellite. Prezzo sotto media 200: trend non ancora convincente.</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>65.90000000000001</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>52.6</v>
       </c>
     </row>
     <row r="17">
@@ -2220,36 +2300,36 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P17" t="n">
-        <v>64.51000000000001</v>
+        <v>63.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.2998</v>
+        <v>63.3216</v>
       </c>
       <c r="R17" t="n">
-        <v>63.0909</v>
+        <v>63.1006</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.03</v>
+        <v>-1.86</v>
       </c>
       <c r="V17" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="W17" t="n">
-        <v>0.95</v>
+        <v>-0.14</v>
       </c>
       <c r="X17" t="n">
-        <v>6.39</v>
+        <v>6.05</v>
       </c>
       <c r="Y17" t="n">
         <v>10.2</v>
@@ -2258,7 +2338,7 @@
         <v>-12.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2272,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>59.5</v>
+        <v>59</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2281,16 +2361,21 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>59.5</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -2325,36 +2410,36 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P18" t="n">
-        <v>94.2</v>
+        <v>97.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>78.2212</v>
+        <v>79.70059999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>59.2109</v>
+        <v>59.7567</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>9.029999999999999</v>
+        <v>13.88</v>
       </c>
       <c r="U18" t="n">
-        <v>56.58</v>
+        <v>60.83</v>
       </c>
       <c r="V18" t="n">
-        <v>81.29000000000001</v>
+        <v>83.58</v>
       </c>
       <c r="W18" t="n">
-        <v>153.29</v>
+        <v>157.82</v>
       </c>
       <c r="X18" t="n">
-        <v>36.88</v>
+        <v>37.64</v>
       </c>
       <c r="Y18" t="n">
         <v>31.13</v>
@@ -2363,7 +2448,7 @@
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2377,7 +2462,7 @@
         <v>-23</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2386,16 +2471,21 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Tema molto forte, ma ciclico e volatile. Volatilità elevata. Drawdown storico importante.</t>
+          <t>Tema molto forte, ma ciclico e volatile. Volatilità elevata: ingresso da valutare con prudenza. Drawdown storico importante.</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>72.2</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2433,42 +2523,42 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>104.94</v>
+        <v>106.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>89.3968</v>
+        <v>90.69280000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>77.4868</v>
+        <v>77.8993</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>11.54</v>
+        <v>14.97</v>
       </c>
       <c r="U19" t="n">
-        <v>40.48</v>
+        <v>40.84</v>
       </c>
       <c r="V19" t="n">
-        <v>46.14</v>
+        <v>46.77</v>
       </c>
       <c r="W19" t="n">
-        <v>76.67</v>
+        <v>76.91</v>
       </c>
       <c r="X19" t="n">
-        <v>15.72</v>
+        <v>15.99</v>
       </c>
       <c r="Y19" t="n">
-        <v>28.29</v>
+        <v>28.28</v>
       </c>
       <c r="Z19" t="n">
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2482,7 +2572,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2491,16 +2581,21 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato. Volatilità elevata. Drawdown storico importante.</t>
+          <t>Tema strutturale forte, ma con rischio euforia e concentrazione. Volatilità elevata: ingresso da valutare con prudenza. Drawdown storico importante.</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>67.59999999999999</v>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>67.7</v>
       </c>
     </row>
     <row r="20">
@@ -2535,16 +2630,16 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P20" t="n">
-        <v>4.9015</v>
+        <v>4.9045</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.909</v>
+        <v>4.9094</v>
       </c>
       <c r="R20" t="n">
-        <v>4.9279</v>
+        <v>4.9282</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2552,28 +2647,28 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>-0.35</v>
+        <v>0.2</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9</v>
+        <v>-0.97</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.65</v>
+        <v>-0.7</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.37</v>
+        <v>-1.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="Z20" t="n">
         <v>-17.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2581,13 +2676,13 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>35.9</v>
+        <v>38.9</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -2596,15 +2691,20 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Componente difensiva, utile per bilanciare rischio equity.</t>
+          <t>Componente difensiva utile per bilanciare il rischio equity. Prezzo sotto media 200: trend non ancora convincente.</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM20" t="n">
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
         <v>32.9</v>
       </c>
     </row>
@@ -2640,16 +2740,16 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="P21" t="n">
-        <v>23.61</v>
+        <v>23.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6365</v>
+        <v>23.6373</v>
       </c>
       <c r="R21" t="n">
-        <v>23.7523</v>
+        <v>23.753</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2657,19 +2757,19 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>-0.44</v>
+        <v>0.06</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.15</v>
+        <v>-1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8</v>
+        <v>-0.92</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.73</v>
+        <v>-1.77</v>
       </c>
       <c r="Y21" t="n">
         <v>4.81</v>
@@ -2686,13 +2786,13 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>35.1</v>
+        <v>38.1</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2701,15 +2801,20 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Componente difensiva, utile per bilanciare rischio equity.</t>
+          <t>Componente difensiva utile per bilanciare il rischio equity. Prezzo sotto media 200: trend non ancora convincente.</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
         <v>32.1</v>
       </c>
     </row>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -763,13 +763,13 @@
         <v>5.04</v>
       </c>
       <c r="P3" t="n">
-        <v>207.32</v>
+        <v>207.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>179.6608</v>
+        <v>179.6566</v>
       </c>
       <c r="R3" t="n">
-        <v>158.6131</v>
+        <v>158.6121</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>11.64</v>
+        <v>11.53</v>
       </c>
       <c r="U3" t="n">
-        <v>34.28</v>
+        <v>34.15</v>
       </c>
       <c r="V3" t="n">
-        <v>35.67</v>
+        <v>35.53</v>
       </c>
       <c r="W3" t="n">
-        <v>55.33</v>
+        <v>55.17</v>
       </c>
       <c r="X3" t="n">
-        <v>21.17</v>
+        <v>21.15</v>
       </c>
       <c r="Y3" t="n">
         <v>21.09</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -873,13 +873,13 @@
         <v>5.04</v>
       </c>
       <c r="P4" t="n">
-        <v>47.19</v>
+        <v>47.325</v>
       </c>
       <c r="Q4" t="n">
-        <v>44.9254</v>
+        <v>44.9281</v>
       </c>
       <c r="R4" t="n">
-        <v>40.3696</v>
+        <v>40.3703</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -887,28 +887,28 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="U4" t="n">
-        <v>13.3</v>
+        <v>13.63</v>
       </c>
       <c r="V4" t="n">
-        <v>25.12</v>
+        <v>25.48</v>
       </c>
       <c r="W4" t="n">
-        <v>42.29</v>
+        <v>42.7</v>
       </c>
       <c r="X4" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.44</v>
+        <v>16.45</v>
       </c>
       <c r="Z4" t="n">
         <v>-22.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>72.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -941,11 +941,11 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>70.7</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:21</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1093,13 +1093,13 @@
         <v>5.04</v>
       </c>
       <c r="P6" t="n">
-        <v>161.75</v>
+        <v>161.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>155.4222</v>
+        <v>155.4256</v>
       </c>
       <c r="R6" t="n">
-        <v>146.7647</v>
+        <v>146.7655</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
       <c r="U6" t="n">
-        <v>8.970000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="V6" t="n">
-        <v>12.18</v>
+        <v>12.3</v>
       </c>
       <c r="W6" t="n">
-        <v>24.25</v>
+        <v>24.38</v>
       </c>
       <c r="X6" t="n">
-        <v>11.91</v>
+        <v>11.94</v>
       </c>
       <c r="Y6" t="n">
         <v>13.74</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1203,13 +1203,13 @@
         <v>5.04</v>
       </c>
       <c r="P7" t="n">
-        <v>122.44</v>
+        <v>122.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>117.9788</v>
+        <v>117.9824</v>
       </c>
       <c r="R7" t="n">
-        <v>112.2</v>
+        <v>112.2009</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1217,19 +1217,19 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="U7" t="n">
-        <v>8.34</v>
+        <v>8.5</v>
       </c>
       <c r="V7" t="n">
-        <v>10.28</v>
+        <v>10.44</v>
       </c>
       <c r="W7" t="n">
-        <v>21.84</v>
+        <v>22.02</v>
       </c>
       <c r="X7" t="n">
-        <v>12.49</v>
+        <v>12.53</v>
       </c>
       <c r="Y7" t="n">
         <v>14.2</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1313,13 +1313,13 @@
         <v>5.04</v>
       </c>
       <c r="P8" t="n">
-        <v>74.22</v>
+        <v>74.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>71.9068</v>
+        <v>71.9096</v>
       </c>
       <c r="R8" t="n">
-        <v>68.7047</v>
+        <v>68.7054</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1327,19 +1327,19 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>6.03</v>
+        <v>6.23</v>
       </c>
       <c r="V8" t="n">
-        <v>9.44</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>17.38</v>
+        <v>17.6</v>
       </c>
       <c r="X8" t="n">
-        <v>11.05</v>
+        <v>11.09</v>
       </c>
       <c r="Y8" t="n">
         <v>14.16</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1381,11 +1381,11 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1423,13 +1423,13 @@
         <v>5.04</v>
       </c>
       <c r="P9" t="n">
-        <v>101.16</v>
+        <v>101.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>93.3168</v>
+        <v>93.3156</v>
       </c>
       <c r="R9" t="n">
-        <v>85.3378</v>
+        <v>85.33750000000001</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1437,19 +1437,19 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="U9" t="n">
-        <v>19.87</v>
+        <v>19.8</v>
       </c>
       <c r="V9" t="n">
-        <v>23.5</v>
+        <v>23.43</v>
       </c>
       <c r="W9" t="n">
-        <v>29.96</v>
+        <v>29.88</v>
       </c>
       <c r="X9" t="n">
-        <v>14.32</v>
+        <v>14.31</v>
       </c>
       <c r="Y9" t="n">
         <v>17.34</v>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1533,13 +1533,13 @@
         <v>5.04</v>
       </c>
       <c r="P10" t="n">
-        <v>124.12</v>
+        <v>124.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>118.8208</v>
+        <v>118.8216</v>
       </c>
       <c r="R10" t="n">
-        <v>112.965</v>
+        <v>112.9652</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1547,19 +1547,19 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>10.1</v>
+        <v>10.14</v>
       </c>
       <c r="V10" t="n">
-        <v>10.13</v>
+        <v>10.17</v>
       </c>
       <c r="W10" t="n">
-        <v>23.5</v>
+        <v>23.54</v>
       </c>
       <c r="X10" t="n">
-        <v>14.34</v>
+        <v>14.35</v>
       </c>
       <c r="Y10" t="n">
         <v>15.2</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN10" t="n">
@@ -1643,13 +1643,13 @@
         <v>5.04</v>
       </c>
       <c r="P11" t="n">
-        <v>626.7</v>
+        <v>626.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>580.038</v>
+        <v>580.0424</v>
       </c>
       <c r="R11" t="n">
-        <v>535.4049</v>
+        <v>535.4059999999999</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="U11" t="n">
-        <v>18.91</v>
+        <v>18.96</v>
       </c>
       <c r="V11" t="n">
-        <v>17.24</v>
+        <v>17.28</v>
       </c>
       <c r="W11" t="n">
-        <v>34.55</v>
+        <v>34.6</v>
       </c>
       <c r="X11" t="n">
-        <v>17.97</v>
+        <v>17.98</v>
       </c>
       <c r="Y11" t="n">
         <v>19.89</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1753,13 +1753,13 @@
         <v>5.04</v>
       </c>
       <c r="P12" t="n">
-        <v>62.57</v>
+        <v>62.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>61.3574</v>
+        <v>61.3626</v>
       </c>
       <c r="R12" t="n">
-        <v>58.5673</v>
+        <v>58.5686</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>3.01</v>
+        <v>3.44</v>
       </c>
       <c r="U12" t="n">
-        <v>4.34</v>
+        <v>4.78</v>
       </c>
       <c r="V12" t="n">
-        <v>10.08</v>
+        <v>10.54</v>
       </c>
       <c r="W12" t="n">
-        <v>15.23</v>
+        <v>15.71</v>
       </c>
       <c r="X12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Y12" t="n">
         <v>14.53</v>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>62.8</v>
+        <v>63.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -1821,11 +1821,11 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>62.8</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="13">
@@ -1863,13 +1863,13 @@
         <v>5.04</v>
       </c>
       <c r="P13" t="n">
-        <v>35.345</v>
+        <v>35.405</v>
       </c>
       <c r="Q13" t="n">
-        <v>29.9609</v>
+        <v>29.9621</v>
       </c>
       <c r="R13" t="n">
-        <v>27.4503</v>
+        <v>27.4506</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1877,19 +1877,19 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>18.61</v>
+        <v>18.81</v>
       </c>
       <c r="U13" t="n">
-        <v>34.29</v>
+        <v>34.52</v>
       </c>
       <c r="V13" t="n">
-        <v>29.04</v>
+        <v>29.26</v>
       </c>
       <c r="W13" t="n">
-        <v>26.3</v>
+        <v>26.51</v>
       </c>
       <c r="X13" t="n">
-        <v>11.14</v>
+        <v>11.18</v>
       </c>
       <c r="Y13" t="n">
         <v>24.61</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:21</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -1973,13 +1973,13 @@
         <v>5.04</v>
       </c>
       <c r="P14" t="n">
-        <v>361.12</v>
+        <v>360.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>380.8078</v>
+        <v>380.7974</v>
       </c>
       <c r="R14" t="n">
-        <v>362.1728</v>
+        <v>362.1702</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1987,28 +1987,28 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>-5.59</v>
+        <v>-5.73</v>
       </c>
       <c r="U14" t="n">
-        <v>-16.44</v>
+        <v>-16.56</v>
       </c>
       <c r="V14" t="n">
-        <v>3.57</v>
+        <v>3.42</v>
       </c>
       <c r="W14" t="n">
-        <v>28.17</v>
+        <v>27.98</v>
       </c>
       <c r="X14" t="n">
-        <v>19.03</v>
+        <v>18.99</v>
       </c>
       <c r="Y14" t="n">
         <v>16.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>-17.25</v>
+        <v>-17.37</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2041,11 +2041,11 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="15">
@@ -2083,13 +2083,13 @@
         <v>5.04</v>
       </c>
       <c r="P15" t="n">
-        <v>17.644</v>
+        <v>17.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.1679</v>
+        <v>16.1682</v>
       </c>
       <c r="R15" t="n">
-        <v>14.467</v>
+        <v>14.4671</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2097,19 +2097,19 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>3.81</v>
+        <v>3.91</v>
       </c>
       <c r="U15" t="n">
-        <v>24.57</v>
+        <v>24.68</v>
       </c>
       <c r="V15" t="n">
-        <v>25.69</v>
+        <v>25.8</v>
       </c>
       <c r="W15" t="n">
-        <v>39.08</v>
+        <v>39.21</v>
       </c>
       <c r="X15" t="n">
-        <v>11.37</v>
+        <v>11.39</v>
       </c>
       <c r="Y15" t="n">
         <v>22.05</v>
@@ -2118,7 +2118,7 @@
         <v>-35.29</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
         <v>-5</v>
       </c>
       <c r="AI15" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2151,11 +2151,11 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:21</t>
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="16">
@@ -2193,13 +2193,13 @@
         <v>3.07</v>
       </c>
       <c r="P16" t="n">
-        <v>52.8</v>
+        <v>53.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>56.1484</v>
+        <v>56.1534</v>
       </c>
       <c r="R16" t="n">
-        <v>55.5596</v>
+        <v>55.5609</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2207,28 +2207,28 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="U16" t="n">
-        <v>-15.99</v>
+        <v>-15.59</v>
       </c>
       <c r="V16" t="n">
-        <v>6.53</v>
+        <v>7.03</v>
       </c>
       <c r="W16" t="n">
-        <v>9.75</v>
+        <v>10.27</v>
       </c>
       <c r="X16" t="n">
-        <v>39.8</v>
+        <v>40.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>21.61</v>
+        <v>21.6</v>
       </c>
       <c r="Z16" t="n">
         <v>-18.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>59.6</v>
+        <v>59.9</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2261,11 +2261,11 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:21</t>
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>52.6</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="17">
@@ -2303,10 +2303,10 @@
         <v>5.04</v>
       </c>
       <c r="P17" t="n">
-        <v>63.79</v>
+        <v>63.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.3216</v>
+        <v>63.3214</v>
       </c>
       <c r="R17" t="n">
         <v>63.1006</v>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.86</v>
+        <v>-1.88</v>
       </c>
       <c r="V17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="X17" t="n">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="Y17" t="n">
         <v>10.2</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2413,13 +2413,13 @@
         <v>5.04</v>
       </c>
       <c r="P18" t="n">
-        <v>97.3</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>79.70059999999999</v>
+        <v>79.7054</v>
       </c>
       <c r="R18" t="n">
-        <v>59.7567</v>
+        <v>59.7579</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2427,19 +2427,19 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>13.88</v>
+        <v>14.16</v>
       </c>
       <c r="U18" t="n">
-        <v>60.83</v>
+        <v>61.22</v>
       </c>
       <c r="V18" t="n">
-        <v>83.58</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>157.82</v>
+        <v>158.45</v>
       </c>
       <c r="X18" t="n">
-        <v>37.64</v>
+        <v>37.71</v>
       </c>
       <c r="Y18" t="n">
         <v>31.13</v>
@@ -2448,7 +2448,7 @@
         <v>-37.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2523,13 +2523,13 @@
         <v>5.04</v>
       </c>
       <c r="P19" t="n">
-        <v>106.29</v>
+        <v>106.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>90.69280000000001</v>
+        <v>90.69580000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>77.8993</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2537,19 +2537,19 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>14.97</v>
+        <v>15.13</v>
       </c>
       <c r="U19" t="n">
-        <v>40.84</v>
+        <v>41.04</v>
       </c>
       <c r="V19" t="n">
-        <v>46.77</v>
+        <v>46.98</v>
       </c>
       <c r="W19" t="n">
-        <v>76.91</v>
+        <v>77.16</v>
       </c>
       <c r="X19" t="n">
-        <v>15.99</v>
+        <v>16.02</v>
       </c>
       <c r="Y19" t="n">
         <v>28.28</v>
@@ -2558,7 +2558,7 @@
         <v>-40.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2572,7 +2572,7 @@
         <v>-21</v>
       </c>
       <c r="AI19" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2591,11 +2591,11 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN19" t="n">
-        <v>67.7</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="20">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2743,10 +2743,10 @@
         <v>5.04</v>
       </c>
       <c r="P21" t="n">
-        <v>23.6</v>
+        <v>23.595</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.6373</v>
+        <v>23.6372</v>
       </c>
       <c r="R21" t="n">
         <v>23.753</v>
@@ -2757,16 +2757,16 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3</v>
+        <v>-1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.92</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
         <v>-1.77</v>
@@ -2778,7 +2778,7 @@
         <v>-18.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -2811,11 +2811,11 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:20</t>
         </is>
       </c>
       <c r="AN21" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.265</v>
+        <v>47.18</v>
       </c>
       <c r="F2" t="n">
         <v>79.3</v>
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
       <c r="J2" t="n">
         <v>65.5</v>
       </c>
       <c r="K2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>16.1</v>
+        <v>15.89</v>
       </c>
       <c r="O2" t="n">
-        <v>24.86</v>
+        <v>24.63</v>
       </c>
       <c r="P2" t="n">
-        <v>42.88</v>
+        <v>42.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.58</v>
+        <v>18.5</v>
       </c>
       <c r="R2" t="n">
-        <v>16.01</v>
+        <v>16</v>
       </c>
       <c r="S2" t="n">
         <v>-19.17</v>
@@ -637,10 +637,10 @@
         <v>1.16</v>
       </c>
       <c r="U2" t="n">
-        <v>44.9269</v>
+        <v>44.9252</v>
       </c>
       <c r="V2" t="n">
-        <v>40.37</v>
+        <v>40.3695</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -652,13 +652,13 @@
         <v>85</v>
       </c>
       <c r="Z2" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
       <c r="AA2" t="n">
         <v>65.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="AC2" t="n">
         <v>756</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70.92</v>
+        <v>70.89</v>
       </c>
       <c r="F3" t="n">
         <v>79.2</v>
@@ -706,7 +706,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -714,19 +714,19 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="N3" t="n">
-        <v>28.06</v>
+        <v>28.01</v>
       </c>
       <c r="O3" t="n">
-        <v>38.41</v>
+        <v>38.35</v>
       </c>
       <c r="P3" t="n">
-        <v>61.99</v>
+        <v>61.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.89</v>
+        <v>25.87</v>
       </c>
       <c r="R3" t="n">
         <v>13.61</v>
@@ -738,10 +738,10 @@
         <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>63.4818</v>
+        <v>63.4812</v>
       </c>
       <c r="V3" t="n">
-        <v>54.8732</v>
+        <v>54.873</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="AC3" t="n">
         <v>756</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.9</v>
+        <v>161.84</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -801,13 +801,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -815,19 +815,19 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="N4" t="n">
-        <v>10.59</v>
+        <v>10.55</v>
       </c>
       <c r="O4" t="n">
-        <v>12.23</v>
+        <v>12.19</v>
       </c>
       <c r="P4" t="n">
-        <v>24.37</v>
+        <v>24.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.25</v>
+        <v>17.24</v>
       </c>
       <c r="R4" t="n">
         <v>12.86</v>
@@ -839,10 +839,10 @@
         <v>1.34</v>
       </c>
       <c r="U4" t="n">
-        <v>155.4312</v>
+        <v>155.43</v>
       </c>
       <c r="V4" t="n">
-        <v>146.7657</v>
+        <v>146.7654</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>85</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="AA4" t="n">
         <v>67.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="AC4" t="n">
         <v>759</v>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.6</v>
+        <v>122.53</v>
       </c>
       <c r="F5" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="I5" t="n">
-        <v>75.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="N5" t="n">
-        <v>9.94</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>10.41</v>
+        <v>10.35</v>
       </c>
       <c r="P5" t="n">
-        <v>22.39</v>
+        <v>22.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.15</v>
+        <v>17.12</v>
       </c>
       <c r="R5" t="n">
         <v>13.13</v>
@@ -937,13 +937,13 @@
         <v>-21.63</v>
       </c>
       <c r="T5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="U5" t="n">
-        <v>117.982</v>
+        <v>117.9806</v>
       </c>
       <c r="V5" t="n">
-        <v>112.2008</v>
+        <v>112.2004</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>85</v>
       </c>
       <c r="Z5" t="n">
-        <v>75.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>66.90000000000001</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>692.4</v>
+        <v>692.16</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1003,13 +1003,13 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="N6" t="n">
-        <v>11.25</v>
+        <v>11.21</v>
       </c>
       <c r="O6" t="n">
-        <v>10.13</v>
+        <v>10.09</v>
       </c>
       <c r="P6" t="n">
-        <v>23.61</v>
+        <v>23.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.39</v>
+        <v>18.37</v>
       </c>
       <c r="R6" t="n">
         <v>14.09</v>
@@ -1041,10 +1041,10 @@
         <v>1.3</v>
       </c>
       <c r="U6" t="n">
-        <v>662.6672</v>
+        <v>662.6624</v>
       </c>
       <c r="V6" t="n">
-        <v>629.9944</v>
+        <v>629.9932</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1056,13 +1056,13 @@
         <v>85</v>
       </c>
       <c r="Z6" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>759</v>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.37</v>
+        <v>74.28</v>
       </c>
       <c r="F8" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>71</v>
+        <v>70.7</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1219,19 +1219,19 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2.71</v>
+        <v>2.58</v>
       </c>
       <c r="N8" t="n">
-        <v>7.55</v>
+        <v>7.42</v>
       </c>
       <c r="O8" t="n">
-        <v>9.82</v>
+        <v>9.69</v>
       </c>
       <c r="P8" t="n">
-        <v>18.18</v>
+        <v>18.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.08</v>
+        <v>15.04</v>
       </c>
       <c r="R8" t="n">
         <v>12.86</v>
@@ -1243,10 +1243,10 @@
         <v>1.17</v>
       </c>
       <c r="U8" t="n">
-        <v>71.9098</v>
+        <v>71.908</v>
       </c>
       <c r="V8" t="n">
-        <v>68.7055</v>
+        <v>68.705</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>85</v>
       </c>
       <c r="Z8" t="n">
-        <v>71</v>
+        <v>70.7</v>
       </c>
       <c r="AA8" t="n">
         <v>68.09999999999999</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.694</v>
+        <v>17.658</v>
       </c>
       <c r="F9" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61</v>
+        <v>61.9</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="N9" t="n">
-        <v>28.97</v>
+        <v>28.7</v>
       </c>
       <c r="O9" t="n">
-        <v>26.91</v>
+        <v>26.65</v>
       </c>
       <c r="P9" t="n">
-        <v>40.05</v>
+        <v>39.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.89</v>
+        <v>17.81</v>
       </c>
       <c r="R9" t="n">
         <v>21.32</v>
@@ -1344,10 +1344,10 @@
         <v>0.84</v>
       </c>
       <c r="U9" t="n">
-        <v>16.1689</v>
+        <v>16.1682</v>
       </c>
       <c r="V9" t="n">
-        <v>14.4672</v>
+        <v>14.4671</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>50.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>61</v>
+        <v>61.9</v>
       </c>
       <c r="AC9" t="n">
         <v>756</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.79</v>
+        <v>63.76</v>
       </c>
       <c r="F10" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>61.3</v>
       </c>
       <c r="I10" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="J10" t="n">
         <v>78.3</v>
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.88</v>
+        <v>-1.92</v>
       </c>
       <c r="O10" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.6</v>
+        <v>6.58</v>
       </c>
       <c r="R10" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="S10" t="n">
         <v>-12.85</v>
@@ -1445,10 +1445,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>63.3216</v>
+        <v>63.321</v>
       </c>
       <c r="V10" t="n">
-        <v>63.1006</v>
+        <v>63.1005</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>85</v>
       </c>
       <c r="Z10" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="AA10" t="n">
         <v>78.3</v>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.582</v>
+        <v>10.566</v>
       </c>
       <c r="F11" t="n">
         <v>64.3</v>
@@ -1522,19 +1522,19 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-1.1</v>
+        <v>-1.25</v>
       </c>
       <c r="N11" t="n">
-        <v>20.52</v>
+        <v>20.34</v>
       </c>
       <c r="O11" t="n">
-        <v>29.25</v>
+        <v>29.06</v>
       </c>
       <c r="P11" t="n">
-        <v>66.58</v>
+        <v>66.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="R11" t="n">
         <v>23.17</v>
@@ -1546,10 +1546,10 @@
         <v>0.14</v>
       </c>
       <c r="U11" t="n">
-        <v>10.1819</v>
+        <v>10.1816</v>
       </c>
       <c r="V11" t="n">
-        <v>8.756600000000001</v>
+        <v>8.756500000000001</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>360.45</v>
+        <v>360.24</v>
       </c>
       <c r="F13" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>70.3</v>
       </c>
       <c r="I13" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J13" t="n">
         <v>64.7</v>
@@ -1724,34 +1724,34 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-6.75</v>
+        <v>-6.81</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.9</v>
+        <v>-14.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="P13" t="n">
-        <v>27.52</v>
+        <v>27.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>26.93</v>
+        <v>26.9</v>
       </c>
       <c r="R13" t="n">
         <v>17.78</v>
       </c>
       <c r="S13" t="n">
-        <v>-17.4</v>
+        <v>-17.45</v>
       </c>
       <c r="T13" t="n">
         <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>380.7944</v>
+        <v>380.7902</v>
       </c>
       <c r="V13" t="n">
-        <v>362.1695</v>
+        <v>362.1684</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>35</v>
       </c>
       <c r="Z13" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="AA13" t="n">
         <v>64.7</v>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27.115</v>
+        <v>27.045</v>
       </c>
       <c r="F14" t="n">
         <v>42.9</v>
@@ -1811,13 +1811,13 @@
         <v>22.6</v>
       </c>
       <c r="I14" t="n">
-        <v>54.5</v>
+        <v>53.9</v>
       </c>
       <c r="J14" t="n">
         <v>15.4</v>
       </c>
       <c r="K14" t="n">
-        <v>51.8</v>
+        <v>53</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1825,19 +1825,19 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>12.51</v>
+        <v>12.22</v>
       </c>
       <c r="N14" t="n">
-        <v>8.630000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.63</v>
+        <v>-6.87</v>
       </c>
       <c r="P14" t="n">
-        <v>-14.5</v>
+        <v>-14.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.69</v>
+        <v>-1.78</v>
       </c>
       <c r="R14" t="n">
         <v>33.93</v>
@@ -1849,10 +1849,10 @@
         <v>-0.05</v>
       </c>
       <c r="U14" t="n">
-        <v>24.2693</v>
+        <v>24.2679</v>
       </c>
       <c r="V14" t="n">
-        <v>26.9679</v>
+        <v>26.9675</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1864,13 +1864,13 @@
         <v>85</v>
       </c>
       <c r="Z14" t="n">
-        <v>54.5</v>
+        <v>53.9</v>
       </c>
       <c r="AA14" t="n">
         <v>20.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>51.8</v>
+        <v>53</v>
       </c>
       <c r="AC14" t="n">
         <v>757</v>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.18</v>
+        <v>47.23</v>
       </c>
       <c r="F2" t="n">
         <v>79.3</v>
@@ -599,13 +599,13 @@
         <v>69.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>97.7</v>
+        <v>98</v>
       </c>
       <c r="J2" t="n">
         <v>65.5</v>
       </c>
       <c r="K2" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="N2" t="n">
-        <v>15.89</v>
+        <v>16.02</v>
       </c>
       <c r="O2" t="n">
-        <v>24.63</v>
+        <v>24.77</v>
       </c>
       <c r="P2" t="n">
-        <v>42.62</v>
+        <v>42.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.5</v>
+        <v>18.55</v>
       </c>
       <c r="R2" t="n">
         <v>16</v>
@@ -637,10 +637,10 @@
         <v>1.16</v>
       </c>
       <c r="U2" t="n">
-        <v>44.9252</v>
+        <v>44.9262</v>
       </c>
       <c r="V2" t="n">
-        <v>40.3695</v>
+        <v>40.3698</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -652,13 +652,13 @@
         <v>85</v>
       </c>
       <c r="Z2" t="n">
-        <v>97.7</v>
+        <v>98</v>
       </c>
       <c r="AA2" t="n">
         <v>65.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="AC2" t="n">
         <v>756</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70.89</v>
+        <v>70.86</v>
       </c>
       <c r="F3" t="n">
         <v>79.2</v>
@@ -706,7 +706,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -714,19 +714,19 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>6.91</v>
+        <v>6.86</v>
       </c>
       <c r="N3" t="n">
-        <v>28.01</v>
+        <v>27.95</v>
       </c>
       <c r="O3" t="n">
-        <v>38.35</v>
+        <v>38.29</v>
       </c>
       <c r="P3" t="n">
-        <v>61.92</v>
+        <v>61.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.87</v>
+        <v>25.86</v>
       </c>
       <c r="R3" t="n">
         <v>13.61</v>
@@ -738,10 +738,10 @@
         <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>63.4812</v>
+        <v>63.4806</v>
       </c>
       <c r="V3" t="n">
-        <v>54.873</v>
+        <v>54.8729</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="AC3" t="n">
         <v>756</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.84</v>
+        <v>161.8</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -801,13 +801,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -815,19 +815,19 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="O4" t="n">
-        <v>12.19</v>
+        <v>12.16</v>
       </c>
       <c r="P4" t="n">
-        <v>24.32</v>
+        <v>24.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.24</v>
+        <v>17.23</v>
       </c>
       <c r="R4" t="n">
         <v>12.86</v>
@@ -839,10 +839,10 @@
         <v>1.34</v>
       </c>
       <c r="U4" t="n">
-        <v>155.43</v>
+        <v>155.4292</v>
       </c>
       <c r="V4" t="n">
-        <v>146.7654</v>
+        <v>146.7652</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>85</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>67.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>759</v>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.53</v>
+        <v>122.56</v>
       </c>
       <c r="F5" t="n">
         <v>75.40000000000001</v>
@@ -902,7 +902,7 @@
         <v>71.8</v>
       </c>
       <c r="I5" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="N5" t="n">
-        <v>9.869999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10.35</v>
+        <v>10.37</v>
       </c>
       <c r="P5" t="n">
-        <v>22.32</v>
+        <v>22.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.12</v>
+        <v>17.13</v>
       </c>
       <c r="R5" t="n">
         <v>13.13</v>
@@ -940,10 +940,10 @@
         <v>1.3</v>
       </c>
       <c r="U5" t="n">
-        <v>117.9806</v>
+        <v>117.9812</v>
       </c>
       <c r="V5" t="n">
-        <v>112.2004</v>
+        <v>112.2006</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>85</v>
       </c>
       <c r="Z5" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="AA5" t="n">
         <v>66.90000000000001</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>692.16</v>
+        <v>692.04</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1009,7 +1009,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="N6" t="n">
-        <v>11.21</v>
+        <v>11.19</v>
       </c>
       <c r="O6" t="n">
-        <v>10.09</v>
+        <v>10.07</v>
       </c>
       <c r="P6" t="n">
-        <v>23.57</v>
+        <v>23.55</v>
       </c>
       <c r="Q6" t="n">
         <v>18.37</v>
@@ -1041,10 +1041,10 @@
         <v>1.3</v>
       </c>
       <c r="U6" t="n">
-        <v>662.6624</v>
+        <v>662.66</v>
       </c>
       <c r="V6" t="n">
-        <v>629.9932</v>
+        <v>629.9926</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="AC6" t="n">
         <v>759</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.87</v>
+        <v>62.88</v>
       </c>
       <c r="F7" t="n">
         <v>74.5</v>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="N7" t="n">
-        <v>6.84</v>
+        <v>6.85</v>
       </c>
       <c r="O7" t="n">
-        <v>10.53</v>
+        <v>10.55</v>
       </c>
       <c r="P7" t="n">
-        <v>15.84</v>
+        <v>15.86</v>
       </c>
       <c r="Q7" t="n">
         <v>13.82</v>
@@ -1142,10 +1142,10 @@
         <v>1.08</v>
       </c>
       <c r="U7" t="n">
-        <v>61.3452</v>
+        <v>61.3454</v>
       </c>
       <c r="V7" t="n">
-        <v>58.5816</v>
+        <v>58.5817</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.658</v>
+        <v>17.672</v>
       </c>
       <c r="F9" t="n">
         <v>69</v>
@@ -1312,7 +1312,7 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61.9</v>
+        <v>61.6</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="N9" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="O9" t="n">
-        <v>26.65</v>
+        <v>26.75</v>
       </c>
       <c r="P9" t="n">
-        <v>39.77</v>
+        <v>39.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.81</v>
+        <v>17.84</v>
       </c>
       <c r="R9" t="n">
         <v>21.32</v>
@@ -1344,7 +1344,7 @@
         <v>0.84</v>
       </c>
       <c r="U9" t="n">
-        <v>16.1682</v>
+        <v>16.1684</v>
       </c>
       <c r="V9" t="n">
         <v>14.4671</v>
@@ -1365,7 +1365,7 @@
         <v>50.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>61.9</v>
+        <v>61.6</v>
       </c>
       <c r="AC9" t="n">
         <v>756</v>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.76</v>
+        <v>63.73</v>
       </c>
       <c r="F10" t="n">
         <v>68.2</v>
@@ -1407,10 +1407,10 @@
         <v>61.3</v>
       </c>
       <c r="I10" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="J10" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K10" t="n">
         <v>82.8</v>
@@ -1421,19 +1421,19 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.92</v>
+        <v>-1.97</v>
       </c>
       <c r="O10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
       <c r="R10" t="n">
         <v>9.56</v>
@@ -1445,10 +1445,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>63.321</v>
+        <v>63.3204</v>
       </c>
       <c r="V10" t="n">
-        <v>63.1005</v>
+        <v>63.1003</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
         <v>85</v>
       </c>
       <c r="Z10" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="AB10" t="n">
         <v>82.8</v>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.566</v>
+        <v>10.574</v>
       </c>
       <c r="F11" t="n">
         <v>64.3</v>
@@ -1522,19 +1522,19 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-1.25</v>
+        <v>-1.17</v>
       </c>
       <c r="N11" t="n">
-        <v>20.34</v>
+        <v>20.43</v>
       </c>
       <c r="O11" t="n">
-        <v>29.06</v>
+        <v>29.15</v>
       </c>
       <c r="P11" t="n">
-        <v>66.33</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="R11" t="n">
         <v>23.17</v>
@@ -1546,7 +1546,7 @@
         <v>0.14</v>
       </c>
       <c r="U11" t="n">
-        <v>10.1816</v>
+        <v>10.1818</v>
       </c>
       <c r="V11" t="n">
         <v>8.756500000000001</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>360.24</v>
+        <v>360.49</v>
       </c>
       <c r="F13" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1707,16 +1707,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="I13" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="J13" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="K13" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1724,34 +1724,34 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-6.81</v>
+        <v>-6.74</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.95</v>
+        <v>-14.89</v>
       </c>
       <c r="O13" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>27.45</v>
+        <v>27.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>26.9</v>
+        <v>26.93</v>
       </c>
       <c r="R13" t="n">
         <v>17.78</v>
       </c>
       <c r="S13" t="n">
-        <v>-17.45</v>
+        <v>-17.39</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U13" t="n">
-        <v>380.7902</v>
+        <v>380.7952</v>
       </c>
       <c r="V13" t="n">
-        <v>362.1684</v>
+        <v>362.1697</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1763,13 +1763,13 @@
         <v>35</v>
       </c>
       <c r="Z13" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="AC13" t="n">
         <v>756</v>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.23</v>
+        <v>47.22</v>
       </c>
       <c r="F2" t="n">
         <v>79.3</v>
@@ -599,13 +599,13 @@
         <v>69.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>65.5</v>
       </c>
       <c r="K2" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="N2" t="n">
-        <v>16.02</v>
+        <v>15.99</v>
       </c>
       <c r="O2" t="n">
-        <v>24.77</v>
+        <v>24.74</v>
       </c>
       <c r="P2" t="n">
-        <v>42.78</v>
+        <v>42.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.55</v>
+        <v>18.54</v>
       </c>
       <c r="R2" t="n">
         <v>16</v>
@@ -637,10 +637,10 @@
         <v>1.16</v>
       </c>
       <c r="U2" t="n">
-        <v>44.9262</v>
+        <v>44.926</v>
       </c>
       <c r="V2" t="n">
-        <v>40.3698</v>
+        <v>40.3697</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -652,13 +652,13 @@
         <v>85</v>
       </c>
       <c r="Z2" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>65.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="AC2" t="n">
         <v>756</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.8</v>
+        <v>161.82</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -807,7 +807,7 @@
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="N4" t="n">
-        <v>10.52</v>
+        <v>10.53</v>
       </c>
       <c r="O4" t="n">
-        <v>12.16</v>
+        <v>12.17</v>
       </c>
       <c r="P4" t="n">
-        <v>24.29</v>
+        <v>24.3</v>
       </c>
       <c r="Q4" t="n">
         <v>17.23</v>
@@ -839,10 +839,10 @@
         <v>1.34</v>
       </c>
       <c r="U4" t="n">
-        <v>155.4292</v>
+        <v>155.4296</v>
       </c>
       <c r="V4" t="n">
-        <v>146.7652</v>
+        <v>146.7653</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>67.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="AC4" t="n">
         <v>759</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>692.04</v>
+        <v>691.92</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1009,7 +1009,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="N6" t="n">
-        <v>11.19</v>
+        <v>11.17</v>
       </c>
       <c r="O6" t="n">
-        <v>10.07</v>
+        <v>10.05</v>
       </c>
       <c r="P6" t="n">
-        <v>23.55</v>
+        <v>23.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.37</v>
+        <v>18.36</v>
       </c>
       <c r="R6" t="n">
         <v>14.09</v>
@@ -1041,10 +1041,10 @@
         <v>1.3</v>
       </c>
       <c r="U6" t="n">
-        <v>662.66</v>
+        <v>662.6576</v>
       </c>
       <c r="V6" t="n">
-        <v>629.9926</v>
+        <v>629.992</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>759</v>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.22</v>
+        <v>47.265</v>
       </c>
       <c r="F2" t="n">
         <v>79.3</v>
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="I2" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="J2" t="n">
         <v>65.5</v>
       </c>
       <c r="K2" t="n">
-        <v>78.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="N2" t="n">
-        <v>15.99</v>
+        <v>16.1</v>
       </c>
       <c r="O2" t="n">
-        <v>24.74</v>
+        <v>24.86</v>
       </c>
       <c r="P2" t="n">
-        <v>42.74</v>
+        <v>42.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.54</v>
+        <v>18.58</v>
       </c>
       <c r="R2" t="n">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="S2" t="n">
         <v>-19.17</v>
@@ -637,10 +637,10 @@
         <v>1.16</v>
       </c>
       <c r="U2" t="n">
-        <v>44.926</v>
+        <v>44.9269</v>
       </c>
       <c r="V2" t="n">
-        <v>40.3697</v>
+        <v>40.37</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -652,13 +652,13 @@
         <v>85</v>
       </c>
       <c r="Z2" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AA2" t="n">
         <v>65.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>78.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>756</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.82</v>
+        <v>161.88</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -801,13 +801,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -815,19 +815,19 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="N4" t="n">
-        <v>10.53</v>
+        <v>10.57</v>
       </c>
       <c r="O4" t="n">
-        <v>12.17</v>
+        <v>12.21</v>
       </c>
       <c r="P4" t="n">
-        <v>24.3</v>
+        <v>24.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.23</v>
+        <v>17.25</v>
       </c>
       <c r="R4" t="n">
         <v>12.86</v>
@@ -839,10 +839,10 @@
         <v>1.34</v>
       </c>
       <c r="U4" t="n">
-        <v>155.4296</v>
+        <v>155.4308</v>
       </c>
       <c r="V4" t="n">
-        <v>146.7653</v>
+        <v>146.7656</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>85</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="AA4" t="n">
         <v>67.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="AC4" t="n">
         <v>759</v>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.56</v>
+        <v>122.6</v>
       </c>
       <c r="F5" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="N5" t="n">
-        <v>9.9</v>
+        <v>9.94</v>
       </c>
       <c r="O5" t="n">
-        <v>10.37</v>
+        <v>10.41</v>
       </c>
       <c r="P5" t="n">
-        <v>22.35</v>
+        <v>22.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.13</v>
+        <v>17.15</v>
       </c>
       <c r="R5" t="n">
         <v>13.13</v>
@@ -937,13 +937,13 @@
         <v>-21.63</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="U5" t="n">
-        <v>117.9812</v>
+        <v>117.982</v>
       </c>
       <c r="V5" t="n">
-        <v>112.2006</v>
+        <v>112.2008</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>85</v>
       </c>
       <c r="Z5" t="n">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="AA5" t="n">
         <v>66.90000000000001</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>691.92</v>
+        <v>692.22</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1003,13 +1003,13 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="N6" t="n">
-        <v>11.17</v>
+        <v>11.22</v>
       </c>
       <c r="O6" t="n">
-        <v>10.05</v>
+        <v>10.1</v>
       </c>
       <c r="P6" t="n">
-        <v>23.53</v>
+        <v>23.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.36</v>
+        <v>18.38</v>
       </c>
       <c r="R6" t="n">
         <v>14.09</v>
@@ -1041,10 +1041,10 @@
         <v>1.3</v>
       </c>
       <c r="U6" t="n">
-        <v>662.6576</v>
+        <v>662.6636</v>
       </c>
       <c r="V6" t="n">
-        <v>629.992</v>
+        <v>629.9935</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1056,13 +1056,13 @@
         <v>85</v>
       </c>
       <c r="Z6" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="AA6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>759</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.88</v>
+        <v>62.91</v>
       </c>
       <c r="F7" t="n">
         <v>74.5</v>
@@ -1104,7 +1104,7 @@
         <v>70.3</v>
       </c>
       <c r="I7" t="n">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="N7" t="n">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="O7" t="n">
-        <v>10.55</v>
+        <v>10.6</v>
       </c>
       <c r="P7" t="n">
-        <v>15.86</v>
+        <v>15.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.82</v>
+        <v>13.84</v>
       </c>
       <c r="R7" t="n">
         <v>12.85</v>
@@ -1142,10 +1142,10 @@
         <v>1.08</v>
       </c>
       <c r="U7" t="n">
-        <v>61.3454</v>
+        <v>61.346</v>
       </c>
       <c r="V7" t="n">
-        <v>58.5817</v>
+        <v>58.5818</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>85</v>
       </c>
       <c r="Z7" t="n">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="AA7" t="n">
         <v>71.5</v>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.672</v>
+        <v>17.68</v>
       </c>
       <c r="F9" t="n">
         <v>69</v>
@@ -1312,7 +1312,7 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61.6</v>
+        <v>61.4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="N9" t="n">
-        <v>28.8</v>
+        <v>28.86</v>
       </c>
       <c r="O9" t="n">
-        <v>26.75</v>
+        <v>26.81</v>
       </c>
       <c r="P9" t="n">
-        <v>39.88</v>
+        <v>39.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.84</v>
+        <v>17.86</v>
       </c>
       <c r="R9" t="n">
         <v>21.32</v>
@@ -1344,10 +1344,10 @@
         <v>0.84</v>
       </c>
       <c r="U9" t="n">
-        <v>16.1684</v>
+        <v>16.1686</v>
       </c>
       <c r="V9" t="n">
-        <v>14.4671</v>
+        <v>14.4672</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>50.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>61.6</v>
+        <v>61.4</v>
       </c>
       <c r="AC9" t="n">
         <v>756</v>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.574</v>
+        <v>10.58</v>
       </c>
       <c r="F11" t="n">
         <v>64.3</v>
@@ -1522,19 +1522,19 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-1.17</v>
+        <v>-1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="O11" t="n">
-        <v>29.15</v>
+        <v>29.23</v>
       </c>
       <c r="P11" t="n">
-        <v>66.45999999999999</v>
+        <v>66.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
         <v>23.17</v>
@@ -1546,10 +1546,10 @@
         <v>0.14</v>
       </c>
       <c r="U11" t="n">
-        <v>10.1818</v>
+        <v>10.1819</v>
       </c>
       <c r="V11" t="n">
-        <v>8.756500000000001</v>
+        <v>8.756600000000001</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>360.49</v>
+        <v>360.46</v>
       </c>
       <c r="F13" t="n">
         <v>55.5</v>
@@ -1707,16 +1707,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70.5</v>
+        <v>70.3</v>
       </c>
       <c r="I13" t="n">
         <v>38.4</v>
       </c>
       <c r="J13" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="K13" t="n">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1724,16 +1724,16 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-6.74</v>
+        <v>-6.75</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.89</v>
+        <v>-14.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="P13" t="n">
-        <v>27.53</v>
+        <v>27.52</v>
       </c>
       <c r="Q13" t="n">
         <v>26.93</v>
@@ -1742,16 +1742,16 @@
         <v>17.78</v>
       </c>
       <c r="S13" t="n">
-        <v>-17.39</v>
+        <v>-17.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>380.7952</v>
+        <v>380.7946</v>
       </c>
       <c r="V13" t="n">
-        <v>362.1697</v>
+        <v>362.1695</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         <v>38.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="AC13" t="n">
         <v>756</v>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.265</v>
+        <v>47.25</v>
       </c>
       <c r="F2" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>69</v>
       </c>
       <c r="I2" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>65.5</v>
       </c>
       <c r="K2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="N2" t="n">
-        <v>16.1</v>
+        <v>16.06</v>
       </c>
       <c r="O2" t="n">
-        <v>24.86</v>
+        <v>24.82</v>
       </c>
       <c r="P2" t="n">
-        <v>42.88</v>
+        <v>42.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.58</v>
+        <v>18.56</v>
       </c>
       <c r="R2" t="n">
         <v>16.01</v>
@@ -637,10 +637,10 @@
         <v>1.16</v>
       </c>
       <c r="U2" t="n">
-        <v>44.9269</v>
+        <v>44.9266</v>
       </c>
       <c r="V2" t="n">
-        <v>40.37</v>
+        <v>40.3699</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -652,13 +652,13 @@
         <v>85</v>
       </c>
       <c r="Z2" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>65.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>756</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>692.22</v>
+        <v>692.1799999999999</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1003,7 +1003,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="N6" t="n">
-        <v>11.22</v>
+        <v>11.21</v>
       </c>
       <c r="O6" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="P6" t="n">
-        <v>23.58</v>
+        <v>23.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.38</v>
+        <v>18.37</v>
       </c>
       <c r="R6" t="n">
         <v>14.09</v>
@@ -1041,10 +1041,10 @@
         <v>1.3</v>
       </c>
       <c r="U6" t="n">
-        <v>662.6636</v>
+        <v>662.6627999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>629.9935</v>
+        <v>629.9933</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>85</v>
       </c>
       <c r="Z6" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>64.40000000000001</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.91</v>
+        <v>62.92</v>
       </c>
       <c r="F7" t="n">
         <v>74.5</v>
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="N7" t="n">
-        <v>6.9</v>
+        <v>6.92</v>
       </c>
       <c r="O7" t="n">
-        <v>10.6</v>
+        <v>10.62</v>
       </c>
       <c r="P7" t="n">
-        <v>15.91</v>
+        <v>15.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.84</v>
+        <v>13.85</v>
       </c>
       <c r="R7" t="n">
         <v>12.85</v>
@@ -1142,10 +1142,10 @@
         <v>1.08</v>
       </c>
       <c r="U7" t="n">
-        <v>61.346</v>
+        <v>61.3462</v>
       </c>
       <c r="V7" t="n">
-        <v>58.5818</v>
+        <v>58.5819</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.58</v>
+        <v>10.582</v>
       </c>
       <c r="F11" t="n">
         <v>64.3</v>
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-1.11</v>
+        <v>-1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>20.5</v>
+        <v>20.52</v>
       </c>
       <c r="O11" t="n">
-        <v>29.23</v>
+        <v>29.25</v>
       </c>
       <c r="P11" t="n">
-        <v>66.55</v>
+        <v>66.58</v>
       </c>
       <c r="Q11" t="n">
         <v>3.28</v>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AR15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,92 +474,167 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Priority Score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Entry Zone</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Risk Flag</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Azione Suggerita</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Trigger Monitoraggio</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>Rendimento 1M %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Rendimento 3M %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Rendimento 6M %</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Rendimento 12M %</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>CAGR %</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Volatilità %</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Max Drawdown %</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>MA50</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>MA200</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Note AI</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Errore Dati</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Trend Score</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Momentum Score</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Risk Score</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Entry Score</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Data Points</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Supporto 20D</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Supporto 60D</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Resistenza 20D</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Resistenza 60D</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Distanza MA50 %</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Distanza MA200 %</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Scenario Base</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Scenario Positivo</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Scenario Negativo</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Azione Pratica</t>
         </is>
       </c>
     </row>
@@ -585,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.25</v>
+        <v>47.345</v>
       </c>
       <c r="F2" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -599,69 +674,130 @@
         <v>69</v>
       </c>
       <c r="I2" t="n">
-        <v>98.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>65.5</v>
       </c>
       <c r="K2" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="L2" t="inlineStr">
+        <v>77.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="N2" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="O2" t="n">
-        <v>24.82</v>
-      </c>
-      <c r="P2" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>18.56</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Constructive entry zone</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Priorità watchlist</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
       </c>
       <c r="R2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="S2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="U2" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="V2" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="W2" t="n">
         <v>16.01</v>
       </c>
-      <c r="S2" t="n">
+      <c r="X2" t="n">
         <v>-19.17</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Y2" t="n">
         <v>1.16</v>
       </c>
-      <c r="U2" t="n">
-        <v>44.9266</v>
-      </c>
-      <c r="V2" t="n">
-        <v>40.3699</v>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="n">
+        <v>44.9285</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>40.3704</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
         <v>85</v>
       </c>
-      <c r="Z2" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AE2" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AF2" t="n">
         <v>65.5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AG2" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AH2" t="n">
         <v>756</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>44.985</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>49.485</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>49.485</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.4%.</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -686,7 +822,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70.86</v>
+        <v>70.91</v>
       </c>
       <c r="F3" t="n">
         <v>79.2</v>
@@ -706,63 +842,124 @@
         <v>69.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="L3" t="inlineStr">
+        <v>51.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="N3" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="O3" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="P3" t="n">
-        <v>61.85</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>25.86</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Extended - wait pullback</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Monitorare ingresso graduale</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>prezzo 11.7% sopra MA50: evitare inseguimento</t>
+        </is>
       </c>
       <c r="R3" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="S3" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="T3" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="U3" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="W3" t="n">
         <v>13.61</v>
       </c>
-      <c r="S3" t="n">
+      <c r="X3" t="n">
         <v>-17.8</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Y3" t="n">
         <v>1.9</v>
       </c>
-      <c r="U3" t="n">
-        <v>63.4806</v>
-      </c>
-      <c r="V3" t="n">
-        <v>54.8729</v>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="n">
+        <v>63.4816</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>54.8731</v>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
         <v>85</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AE3" t="n">
         <v>100</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AF3" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="AB3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AG3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AH3" t="n">
         <v>756</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -787,7 +984,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.88</v>
+        <v>161.78</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -801,69 +998,130 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="L4" t="inlineStr">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="L4" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="O4" t="n">
-        <v>12.21</v>
-      </c>
-      <c r="P4" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>17.25</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Constructive entry zone</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Priorità watchlist</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
       </c>
       <c r="R4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="T4" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="V4" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="W4" t="n">
         <v>12.86</v>
       </c>
-      <c r="S4" t="n">
+      <c r="X4" t="n">
         <v>-21.07</v>
       </c>
-      <c r="T4" t="n">
+      <c r="Y4" t="n">
         <v>1.34</v>
       </c>
-      <c r="U4" t="n">
-        <v>155.4308</v>
-      </c>
-      <c r="V4" t="n">
-        <v>146.7656</v>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="n">
+        <v>155.4288</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>146.7651</v>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
         <v>85</v>
       </c>
-      <c r="Z4" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AE4" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AF4" t="n">
         <v>67.7</v>
       </c>
-      <c r="AB4" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AG4" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AH4" t="n">
         <v>759</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>140.98</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -888,21 +1146,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.6</v>
+        <v>122.46</v>
       </c>
       <c r="F5" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="I5" t="n">
         <v>75.5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Accumulate Carefully</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>75.8</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -910,61 +1168,122 @@
       <c r="K5" t="n">
         <v>82.8</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>76</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="N5" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="O5" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="P5" t="n">
-        <v>22.39</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>17.15</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Constructive entry zone</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Priorità watchlist</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
       </c>
       <c r="R5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W5" t="n">
         <v>13.13</v>
       </c>
-      <c r="S5" t="n">
+      <c r="X5" t="n">
         <v>-21.63</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="U5" t="n">
-        <v>117.982</v>
-      </c>
-      <c r="V5" t="n">
-        <v>112.2008</v>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>117.9792</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>112.2001</v>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
         <v>85</v>
       </c>
-      <c r="Z5" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AE5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AF5" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AG5" t="n">
         <v>82.8</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AH5" t="n">
         <v>756</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>124.27</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>124.27</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -989,7 +1308,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>692.1799999999999</v>
+        <v>691.3200000000001</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1003,69 +1322,130 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>77.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="L6" t="inlineStr">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="N6" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="O6" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="P6" t="n">
-        <v>23.57</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>18.37</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Constructive entry zone</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Priorità watchlist</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
       </c>
       <c r="R6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="V6" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="W6" t="n">
         <v>14.09</v>
       </c>
-      <c r="S6" t="n">
+      <c r="X6" t="n">
         <v>-23.32</v>
       </c>
-      <c r="T6" t="n">
+      <c r="Y6" t="n">
         <v>1.3</v>
       </c>
-      <c r="U6" t="n">
-        <v>662.6627999999999</v>
-      </c>
-      <c r="V6" t="n">
-        <v>629.9933</v>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="n">
+        <v>662.6455999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>629.989</v>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
         <v>85</v>
       </c>
-      <c r="Z6" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="AE6" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AF6" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="AB6" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AG6" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="AH6" t="n">
         <v>759</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>680.66</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>597.92</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>703.9400000000001</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>703.9400000000001</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1090,7 +1470,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.92</v>
+        <v>62.89</v>
       </c>
       <c r="F7" t="n">
         <v>74.5</v>
@@ -1104,7 +1484,7 @@
         <v>70.3</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1112,61 +1492,122 @@
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="O7" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="P7" t="n">
-        <v>15.93</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>13.85</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Constructive entry zone</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Priorità watchlist</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
       </c>
       <c r="R7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="U7" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="V7" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="W7" t="n">
         <v>12.85</v>
       </c>
-      <c r="S7" t="n">
+      <c r="X7" t="n">
         <v>-16.33</v>
       </c>
-      <c r="T7" t="n">
+      <c r="Y7" t="n">
         <v>1.08</v>
       </c>
-      <c r="U7" t="n">
-        <v>61.3462</v>
-      </c>
-      <c r="V7" t="n">
-        <v>58.5819</v>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="Z7" t="n">
+        <v>61.3456</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>58.5817</v>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
         <v>85</v>
       </c>
-      <c r="Z7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AE7" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AF7" t="n">
         <v>71.5</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AG7" t="n">
         <v>82.8</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AH7" t="n">
         <v>760</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1213,61 +1654,122 @@
       <c r="K8" t="n">
         <v>82.8</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Constructive entry zone</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Monitorare ingresso graduale</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
         <v>2.58</v>
       </c>
-      <c r="N8" t="n">
+      <c r="S8" t="n">
         <v>7.42</v>
       </c>
-      <c r="O8" t="n">
+      <c r="T8" t="n">
         <v>9.69</v>
       </c>
-      <c r="P8" t="n">
+      <c r="U8" t="n">
         <v>18.04</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>15.04</v>
       </c>
-      <c r="R8" t="n">
+      <c r="W8" t="n">
         <v>12.86</v>
       </c>
-      <c r="S8" t="n">
+      <c r="X8" t="n">
         <v>-20.6</v>
       </c>
-      <c r="T8" t="n">
+      <c r="Y8" t="n">
         <v>1.17</v>
       </c>
-      <c r="U8" t="n">
+      <c r="Z8" t="n">
         <v>71.908</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AA8" t="n">
         <v>68.705</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
         <v>85</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AE8" t="n">
         <v>70.7</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AG8" t="n">
         <v>82.8</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AH8" t="n">
         <v>756</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>74.95999999999999</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>74.95999999999999</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1292,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.68</v>
+        <v>17.692</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1312,63 +1814,124 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="L9" t="inlineStr">
+        <v>61.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N9" t="n">
-        <v>28.86</v>
-      </c>
-      <c r="O9" t="n">
-        <v>26.81</v>
-      </c>
-      <c r="P9" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>17.86</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Monitor / partial entry only</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Medium-high risk</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
+        </is>
       </c>
       <c r="R9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S9" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="T9" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="V9" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="W9" t="n">
         <v>21.32</v>
       </c>
-      <c r="S9" t="n">
+      <c r="X9" t="n">
         <v>-29.37</v>
       </c>
-      <c r="T9" t="n">
+      <c r="Y9" t="n">
         <v>0.84</v>
       </c>
-      <c r="U9" t="n">
-        <v>16.1686</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="Z9" t="n">
+        <v>16.1688</v>
+      </c>
+      <c r="AA9" t="n">
         <v>14.4672</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
         <v>85</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AE9" t="n">
         <v>100</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AF9" t="n">
         <v>50.9</v>
       </c>
-      <c r="AB9" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AG9" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="AH9" t="n">
         <v>756</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>16.544</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>12.936</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1393,7 +1956,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.73</v>
+        <v>63.7</v>
       </c>
       <c r="F10" t="n">
         <v>68.2</v>
@@ -1407,7 +1970,7 @@
         <v>61.3</v>
       </c>
       <c r="I10" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="J10" t="n">
         <v>78.2</v>
@@ -1415,61 +1978,122 @@
       <c r="K10" t="n">
         <v>82.8</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.57</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Constructive entry zone</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Monitorare ingresso graduale</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+        </is>
       </c>
       <c r="R10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.56</v>
       </c>
-      <c r="S10" t="n">
+      <c r="X10" t="n">
         <v>-12.85</v>
       </c>
-      <c r="T10" t="n">
+      <c r="Y10" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="U10" t="n">
-        <v>63.3204</v>
-      </c>
-      <c r="V10" t="n">
-        <v>63.1003</v>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="Z10" t="n">
+        <v>63.3198</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>63.1002</v>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
         <v>85</v>
       </c>
-      <c r="Z10" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AE10" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AF10" t="n">
         <v>78.2</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AG10" t="n">
         <v>82.8</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AH10" t="n">
         <v>756</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.6%.</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1494,7 +2118,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.582</v>
+        <v>10.574</v>
       </c>
       <c r="F11" t="n">
         <v>64.3</v>
@@ -1516,61 +2140,122 @@
       <c r="K11" t="n">
         <v>82.8</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="O11" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>66.58</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.28</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Monitor / partial entry only</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>High risk</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
       </c>
       <c r="R11" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="T11" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="W11" t="n">
         <v>23.17</v>
       </c>
-      <c r="S11" t="n">
+      <c r="X11" t="n">
         <v>-44.26</v>
       </c>
-      <c r="T11" t="n">
+      <c r="Y11" t="n">
         <v>0.14</v>
       </c>
-      <c r="U11" t="n">
-        <v>10.1819</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.756600000000001</v>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="Z11" t="n">
+        <v>10.1818</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.756500000000001</v>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
         <v>85</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AE11" t="n">
         <v>100</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AF11" t="n">
         <v>36.8</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AG11" t="n">
         <v>82.8</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AH11" t="n">
         <v>756</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10.2879</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>8.7643</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.9%.</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1617,61 +2302,122 @@
       <c r="K12" t="n">
         <v>30.8</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Extended - wait pullback</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>High risk</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>prezzo 17.0% sopra MA50: evitare inseguimento</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
         <v>10.75</v>
       </c>
-      <c r="N12" t="n">
+      <c r="S12" t="n">
         <v>51.67</v>
       </c>
-      <c r="O12" t="n">
+      <c r="T12" t="n">
         <v>65.94</v>
       </c>
-      <c r="P12" t="n">
+      <c r="U12" t="n">
         <v>138.77</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="V12" t="n">
         <v>60.94</v>
       </c>
-      <c r="R12" t="n">
+      <c r="W12" t="n">
         <v>34.92</v>
       </c>
-      <c r="S12" t="n">
+      <c r="X12" t="n">
         <v>-35.74</v>
       </c>
-      <c r="T12" t="n">
+      <c r="Y12" t="n">
         <v>1.75</v>
       </c>
-      <c r="U12" t="n">
+      <c r="Z12" t="n">
         <v>511.287</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AA12" t="n">
         <v>397.8009</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
         <v>85</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AE12" t="n">
         <v>100</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AF12" t="n">
         <v>29.5</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AG12" t="n">
         <v>30.8</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AH12" t="n">
         <v>751</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>543.96</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>362.53</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>637.9</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>637.9</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>SMH: scenario base Hold / Monitor, score 61.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.0%.</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>360.46</v>
+        <v>360.84</v>
       </c>
       <c r="F13" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1707,72 +2453,133 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="J13" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="K13" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="L13" t="inlineStr">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="L13" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="P13" t="n">
-        <v>27.52</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>26.93</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Wait for trend repair</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Normal risk</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Osservare</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>prezzo 5.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+        </is>
       </c>
       <c r="R13" t="n">
+        <v>-6.65</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="V13" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="W13" t="n">
         <v>17.78</v>
       </c>
-      <c r="S13" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U13" t="n">
-        <v>380.7946</v>
-      </c>
-      <c r="V13" t="n">
-        <v>362.1695</v>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="n">
+        <v>-17.31</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>380.8022</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>362.1714</v>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
         <v>35</v>
       </c>
-      <c r="Z13" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AH13" t="n">
         <v>756</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>360.84</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>360.84</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>424.57</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.2%.</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 424.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 360.84 o peggioramento trend; rischio attuale: Normal risk.</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1797,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27.045</v>
+        <v>26.89</v>
       </c>
       <c r="F14" t="n">
-        <v>42.9</v>
+        <v>37.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1808,72 +2615,133 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="I14" t="n">
-        <v>53.9</v>
+        <v>52.6</v>
       </c>
       <c r="J14" t="n">
         <v>15.4</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="N14" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-6.87</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-14.72</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-1.78</v>
+        <v>51</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Extended - wait pullback</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>High risk</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>prezzo 10.8% sopra MA50: evitare inseguimento</t>
+        </is>
       </c>
       <c r="R14" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-15.21</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="W14" t="n">
         <v>33.93</v>
       </c>
-      <c r="S14" t="n">
+      <c r="X14" t="n">
         <v>-48.6</v>
       </c>
-      <c r="T14" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="U14" t="n">
-        <v>24.2679</v>
-      </c>
-      <c r="V14" t="n">
-        <v>26.9675</v>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>24.2648</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>26.9667</v>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AF14" t="n">
         <v>20.4</v>
       </c>
-      <c r="AB14" t="n">
-        <v>53</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AG14" t="n">
+        <v>51</v>
+      </c>
+      <c r="AH14" t="n">
         <v>757</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>20.205</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>WCLD.MI: scenario base High Risk, score 37.7, trend Recovery. Entry zone: Extended - wait pullback. Distanza da MA50: 10.8%.</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1918,45 +2786,94 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>No Data</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Evitare per ora</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Dati prezzo insufficienti.</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Nessun dato prezzo disponibile</t>
         </is>
       </c>
-      <c r="Y15" t="n">
+      <c r="AD15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AE15" t="n">
         <v>0</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AF15" t="n">
         <v>100</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AG15" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AH15" t="n">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>EUNA.MI: scenario base Avoid for Now, score 28.6, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -641,49 +641,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.345</v>
+        <v>70.8</v>
       </c>
       <c r="F2" t="n">
         <v>79.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>69</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>65.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>77.2</v>
+        <v>52.6</v>
       </c>
       <c r="L2" t="n">
-        <v>79.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -702,47 +702,47 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 11.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.29</v>
+        <v>6.77</v>
       </c>
       <c r="S2" t="n">
-        <v>16.3</v>
+        <v>27.84</v>
       </c>
       <c r="T2" t="n">
-        <v>25.07</v>
+        <v>38.17</v>
       </c>
       <c r="U2" t="n">
-        <v>43.12</v>
+        <v>61.72</v>
       </c>
       <c r="V2" t="n">
-        <v>18.64</v>
+        <v>25.82</v>
       </c>
       <c r="W2" t="n">
-        <v>16.01</v>
+        <v>13.61</v>
       </c>
       <c r="X2" t="n">
-        <v>-19.17</v>
+        <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>44.9285</v>
+        <v>63.4794</v>
       </c>
       <c r="AA2" t="n">
-        <v>40.3704</v>
+        <v>54.8726</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -750,48 +750,48 @@
         <v>85</v>
       </c>
       <c r="AE2" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>65.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>77.2</v>
+        <v>52.6</v>
       </c>
       <c r="AH2" t="n">
         <v>756</v>
       </c>
       <c r="AI2" t="n">
-        <v>44.985</v>
+        <v>65.27</v>
       </c>
       <c r="AJ2" t="n">
-        <v>39.31</v>
+        <v>54.81</v>
       </c>
       <c r="AK2" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="AL2" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.38</v>
+        <v>11.53</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.28</v>
+        <v>29.03</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.4%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.5%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -803,49 +803,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70.91</v>
+        <v>47.26</v>
       </c>
       <c r="F3" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>79.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>69.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="K3" t="n">
-        <v>51.9</v>
+        <v>78</v>
       </c>
       <c r="L3" t="n">
-        <v>65.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -864,47 +864,47 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>6.94</v>
+        <v>0.11</v>
       </c>
       <c r="S3" t="n">
-        <v>28.04</v>
+        <v>16.09</v>
       </c>
       <c r="T3" t="n">
-        <v>38.39</v>
+        <v>24.84</v>
       </c>
       <c r="U3" t="n">
-        <v>61.97</v>
+        <v>42.87</v>
       </c>
       <c r="V3" t="n">
-        <v>25.89</v>
+        <v>18.57</v>
       </c>
       <c r="W3" t="n">
-        <v>13.61</v>
+        <v>16.01</v>
       </c>
       <c r="X3" t="n">
-        <v>-17.8</v>
+        <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>63.4816</v>
+        <v>44.9268</v>
       </c>
       <c r="AA3" t="n">
-        <v>54.8731</v>
+        <v>40.3699</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -912,48 +912,48 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>69.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>51.9</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="n">
         <v>756</v>
       </c>
       <c r="AI3" t="n">
-        <v>65.27</v>
+        <v>44.985</v>
       </c>
       <c r="AJ3" t="n">
-        <v>54.81</v>
+        <v>39.31</v>
       </c>
       <c r="AK3" t="n">
-        <v>72.27</v>
+        <v>49.485</v>
       </c>
       <c r="AL3" t="n">
-        <v>72.27</v>
+        <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>11.7</v>
+        <v>5.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.23</v>
+        <v>17.07</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.78</v>
+        <v>161.7</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -998,13 +998,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>76.90000000000001</v>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="S4" t="n">
-        <v>10.51</v>
+        <v>10.45</v>
       </c>
       <c r="T4" t="n">
-        <v>12.14</v>
+        <v>12.09</v>
       </c>
       <c r="U4" t="n">
-        <v>24.27</v>
+        <v>24.21</v>
       </c>
       <c r="V4" t="n">
-        <v>17.23</v>
+        <v>17.21</v>
       </c>
       <c r="W4" t="n">
         <v>12.86</v>
@@ -1059,10 +1059,10 @@
         <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.4288</v>
+        <v>155.4272</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.7651</v>
+        <v>146.7647</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,13 +1074,13 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AH4" t="n">
         <v>759</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.23</v>
+        <v>10.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.46</v>
+        <v>122.43</v>
       </c>
       <c r="F5" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>71.8</v>
       </c>
       <c r="I5" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>9.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>10.28</v>
+        <v>10.26</v>
       </c>
       <c r="U5" t="n">
-        <v>22.25</v>
+        <v>22.22</v>
       </c>
       <c r="V5" t="n">
-        <v>17.1</v>
+        <v>17.09</v>
       </c>
       <c r="W5" t="n">
         <v>13.13</v>
@@ -1221,10 +1221,10 @@
         <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.9792</v>
+        <v>117.9786</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.2001</v>
+        <v>112.1999</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>691.3200000000001</v>
+        <v>691.26</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1328,7 +1328,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="L6" t="n">
         <v>75.3</v>
@@ -1359,16 +1359,16 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
       <c r="T6" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>23.42</v>
+        <v>23.41</v>
       </c>
       <c r="V6" t="n">
         <v>18.32</v>
@@ -1383,10 +1383,10 @@
         <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>662.6455999999999</v>
+        <v>662.6444</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.989</v>
+        <v>629.9887</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="AH6" t="n">
         <v>759</v>
@@ -1422,10 +1422,10 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.89</v>
+        <v>62.84</v>
       </c>
       <c r="F7" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>69.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>6.87</v>
+        <v>6.78</v>
       </c>
       <c r="T7" t="n">
-        <v>10.57</v>
+        <v>10.48</v>
       </c>
       <c r="U7" t="n">
-        <v>15.88</v>
+        <v>15.79</v>
       </c>
       <c r="V7" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
       <c r="W7" t="n">
         <v>12.85</v>
@@ -1542,13 +1542,13 @@
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.3456</v>
+        <v>61.3446</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.5817</v>
+        <v>58.5815</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>69.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1584,14 +1584,14 @@
         <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.35</v>
+        <v>7.27</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.28</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>72.7</v>
@@ -1646,7 +1646,7 @@
         <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>7.42</v>
+        <v>7.39</v>
       </c>
       <c r="T8" t="n">
-        <v>9.69</v>
+        <v>9.66</v>
       </c>
       <c r="U8" t="n">
-        <v>18.04</v>
+        <v>18</v>
       </c>
       <c r="V8" t="n">
-        <v>15.04</v>
+        <v>15.03</v>
       </c>
       <c r="W8" t="n">
         <v>12.86</v>
@@ -1707,10 +1707,10 @@
         <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.908</v>
+        <v>71.9076</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.705</v>
+        <v>68.70489999999999</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1746,10 +1746,10 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.109999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.692</v>
+        <v>17.68</v>
       </c>
       <c r="F9" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61.1</v>
+        <v>61.4</v>
       </c>
       <c r="L9" t="n">
-        <v>64.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,23 +1841,23 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="S9" t="n">
-        <v>28.95</v>
+        <v>28.86</v>
       </c>
       <c r="T9" t="n">
-        <v>26.9</v>
+        <v>26.81</v>
       </c>
       <c r="U9" t="n">
-        <v>40.03</v>
+        <v>39.94</v>
       </c>
       <c r="V9" t="n">
-        <v>17.88</v>
+        <v>17.86</v>
       </c>
       <c r="W9" t="n">
         <v>21.32</v>
@@ -1869,7 +1869,7 @@
         <v>0.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1688</v>
+        <v>16.1686</v>
       </c>
       <c r="AA9" t="n">
         <v>14.4672</v>
@@ -1890,7 +1890,7 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>61.1</v>
+        <v>61.4</v>
       </c>
       <c r="AH9" t="n">
         <v>756</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>9.42</v>
+        <v>9.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>22.29</v>
+        <v>22.21</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.3%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.574</v>
+        <v>10.562</v>
       </c>
       <c r="F11" t="n">
         <v>64.3</v>
@@ -2169,19 +2169,19 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-1.17</v>
+        <v>-1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>20.43</v>
+        <v>20.29</v>
       </c>
       <c r="T11" t="n">
-        <v>29.15</v>
+        <v>29.01</v>
       </c>
       <c r="U11" t="n">
-        <v>66.45999999999999</v>
+        <v>66.27</v>
       </c>
       <c r="V11" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="W11" t="n">
         <v>23.17</v>
@@ -2193,7 +2193,7 @@
         <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.1818</v>
+        <v>10.1815</v>
       </c>
       <c r="AA11" t="n">
         <v>8.756500000000001</v>
@@ -2232,14 +2232,14 @@
         <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.76</v>
+        <v>20.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.9%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>360.84</v>
+        <v>361</v>
       </c>
       <c r="F13" t="n">
         <v>55.6</v>
@@ -2456,7 +2456,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J13" t="n">
         <v>64.8</v>
@@ -2493,34 +2493,34 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.65</v>
+        <v>-6.61</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.81</v>
+        <v>-14.77</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U13" t="n">
-        <v>27.66</v>
+        <v>27.72</v>
       </c>
       <c r="V13" t="n">
-        <v>26.97</v>
+        <v>26.99</v>
       </c>
       <c r="W13" t="n">
         <v>17.78</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.31</v>
+        <v>-17.28</v>
       </c>
       <c r="Y13" t="n">
         <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.8022</v>
+        <v>380.8054</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.1714</v>
+        <v>362.1722</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="AF13" t="n">
         <v>64.8</v>
@@ -2544,10 +2544,10 @@
         <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>360.84</v>
+        <v>361</v>
       </c>
       <c r="AJ13" t="n">
-        <v>360.84</v>
+        <v>361</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
@@ -2556,10 +2556,10 @@
         <v>424.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.24</v>
+        <v>-5.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.37</v>
+        <v>-0.32</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 360.84 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 361.00 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70.8</v>
+        <v>70.81</v>
       </c>
       <c r="F2" t="n">
         <v>79.3</v>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
       <c r="S2" t="n">
-        <v>27.84</v>
+        <v>27.86</v>
       </c>
       <c r="T2" t="n">
-        <v>38.17</v>
+        <v>38.19</v>
       </c>
       <c r="U2" t="n">
-        <v>61.72</v>
+        <v>61.74</v>
       </c>
       <c r="V2" t="n">
-        <v>25.82</v>
+        <v>25.83</v>
       </c>
       <c r="W2" t="n">
         <v>13.61</v>
@@ -735,7 +735,7 @@
         <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.4794</v>
+        <v>63.4796</v>
       </c>
       <c r="AA2" t="n">
         <v>54.8726</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>11.53</v>
+        <v>11.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.03</v>
+        <v>29.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.5%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.6%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.26</v>
+        <v>47.24</v>
       </c>
       <c r="F3" t="n">
         <v>79.3</v>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="J3" t="n">
         <v>65.5</v>
       </c>
       <c r="K3" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="L3" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="S3" t="n">
-        <v>16.09</v>
+        <v>16.04</v>
       </c>
       <c r="T3" t="n">
-        <v>24.84</v>
+        <v>24.79</v>
       </c>
       <c r="U3" t="n">
-        <v>42.87</v>
+        <v>42.81</v>
       </c>
       <c r="V3" t="n">
-        <v>18.57</v>
+        <v>18.55</v>
       </c>
       <c r="W3" t="n">
-        <v>16.01</v>
+        <v>16</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
@@ -897,10 +897,10 @@
         <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.9268</v>
+        <v>44.9264</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.3699</v>
+        <v>40.3698</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,13 +912,13 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="AF3" t="n">
         <v>65.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="AH3" t="n">
         <v>756</v>
@@ -936,10 +936,10 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.19</v>
+        <v>5.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.07</v>
+        <v>17.02</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.7</v>
+        <v>161.68</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -1004,7 +1004,7 @@
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="L4" t="n">
         <v>76.90000000000001</v>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S4" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
       <c r="T4" t="n">
-        <v>12.09</v>
+        <v>12.08</v>
       </c>
       <c r="U4" t="n">
-        <v>24.21</v>
+        <v>24.2</v>
       </c>
       <c r="V4" t="n">
-        <v>17.21</v>
+        <v>17.2</v>
       </c>
       <c r="W4" t="n">
         <v>12.86</v>
@@ -1059,10 +1059,10 @@
         <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.4272</v>
+        <v>155.4268</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.7647</v>
+        <v>146.7646</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>67.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="AH4" t="n">
         <v>759</v>
@@ -1098,10 +1098,10 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.18</v>
+        <v>10.16</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.43</v>
+        <v>122.41</v>
       </c>
       <c r="F5" t="n">
         <v>75.3</v>
@@ -1197,16 +1197,16 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="T5" t="n">
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
       <c r="U5" t="n">
-        <v>22.22</v>
+        <v>22.2</v>
       </c>
       <c r="V5" t="n">
         <v>17.09</v>
@@ -1221,7 +1221,7 @@
         <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.9786</v>
+        <v>117.9782</v>
       </c>
       <c r="AA5" t="n">
         <v>112.1999</v>
@@ -1260,10 +1260,10 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.119999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>691.26</v>
+        <v>691.4</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1322,13 +1322,13 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>75.3</v>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S6" t="n">
-        <v>11.06</v>
+        <v>11.09</v>
       </c>
       <c r="T6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>23.41</v>
+        <v>23.43</v>
       </c>
       <c r="V6" t="n">
-        <v>18.32</v>
+        <v>18.33</v>
       </c>
       <c r="W6" t="n">
         <v>14.09</v>
@@ -1383,10 +1383,10 @@
         <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>662.6444</v>
+        <v>662.6472</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.9887</v>
+        <v>629.9894</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AH6" t="n">
         <v>759</v>
@@ -1422,10 +1422,10 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.68</v>
+        <v>17.67</v>
       </c>
       <c r="F9" t="n">
         <v>69</v>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61.4</v>
+        <v>61.6</v>
       </c>
       <c r="L9" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="S9" t="n">
-        <v>28.86</v>
+        <v>28.79</v>
       </c>
       <c r="T9" t="n">
-        <v>26.81</v>
+        <v>26.74</v>
       </c>
       <c r="U9" t="n">
-        <v>39.94</v>
+        <v>39.86</v>
       </c>
       <c r="V9" t="n">
-        <v>17.86</v>
+        <v>17.83</v>
       </c>
       <c r="W9" t="n">
         <v>21.32</v>
@@ -1869,10 +1869,10 @@
         <v>0.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1686</v>
+        <v>16.1684</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4672</v>
+        <v>14.4671</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>61.4</v>
+        <v>61.6</v>
       </c>
       <c r="AH9" t="n">
         <v>756</v>
@@ -1908,10 +1908,10 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>9.35</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>22.21</v>
+        <v>22.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>361</v>
+        <v>360.64</v>
       </c>
       <c r="F13" t="n">
         <v>55.6</v>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="I13" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="J13" t="n">
         <v>64.8</v>
       </c>
       <c r="K13" t="n">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="L13" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 5.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.61</v>
+        <v>-6.7</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.77</v>
+        <v>-14.85</v>
       </c>
       <c r="T13" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="U13" t="n">
-        <v>27.72</v>
+        <v>27.59</v>
       </c>
       <c r="V13" t="n">
-        <v>26.99</v>
+        <v>26.95</v>
       </c>
       <c r="W13" t="n">
         <v>17.78</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.28</v>
+        <v>-17.36</v>
       </c>
       <c r="Y13" t="n">
         <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.8054</v>
+        <v>380.7982</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.1722</v>
+        <v>362.1704</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,22 +2532,22 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="AF13" t="n">
         <v>64.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="AH13" t="n">
         <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>361</v>
+        <v>360.64</v>
       </c>
       <c r="AJ13" t="n">
-        <v>361</v>
+        <v>360.64</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
@@ -2556,14 +2556,14 @@
         <v>424.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.2</v>
+        <v>-5.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.32</v>
+        <v>-0.42</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.2%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 361.00 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 360.64 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -641,49 +641,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70.81</v>
+        <v>47.305</v>
       </c>
       <c r="F2" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>79.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>69.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="K2" t="n">
-        <v>52.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>66.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -702,47 +702,47 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 11.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>6.79</v>
+        <v>0.2</v>
       </c>
       <c r="S2" t="n">
-        <v>27.86</v>
+        <v>16.2</v>
       </c>
       <c r="T2" t="n">
-        <v>38.19</v>
+        <v>24.96</v>
       </c>
       <c r="U2" t="n">
-        <v>61.74</v>
+        <v>43</v>
       </c>
       <c r="V2" t="n">
-        <v>25.83</v>
+        <v>18.61</v>
       </c>
       <c r="W2" t="n">
-        <v>13.61</v>
+        <v>16.01</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.8</v>
+        <v>-19.17</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.4796</v>
+        <v>44.9277</v>
       </c>
       <c r="AA2" t="n">
-        <v>54.8726</v>
+        <v>40.3702</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -750,48 +750,48 @@
         <v>85</v>
       </c>
       <c r="AE2" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>52.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AH2" t="n">
         <v>756</v>
       </c>
       <c r="AI2" t="n">
-        <v>65.27</v>
+        <v>44.985</v>
       </c>
       <c r="AJ2" t="n">
-        <v>54.81</v>
+        <v>39.31</v>
       </c>
       <c r="AK2" t="n">
-        <v>72.27</v>
+        <v>49.485</v>
       </c>
       <c r="AL2" t="n">
-        <v>72.27</v>
+        <v>49.485</v>
       </c>
       <c r="AM2" t="n">
-        <v>11.55</v>
+        <v>5.29</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.04</v>
+        <v>17.18</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.6%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.3%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -803,50 +803,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.24</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="L3" t="n">
         <v>65.5</v>
       </c>
-      <c r="K3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>79.8</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Bullish</t>
@@ -854,7 +854,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -864,47 +864,47 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 11.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.06</v>
+        <v>6.97</v>
       </c>
       <c r="S3" t="n">
-        <v>16.04</v>
+        <v>28.08</v>
       </c>
       <c r="T3" t="n">
-        <v>24.79</v>
+        <v>38.43</v>
       </c>
       <c r="U3" t="n">
-        <v>42.81</v>
+        <v>62.01</v>
       </c>
       <c r="V3" t="n">
-        <v>18.55</v>
+        <v>25.9</v>
       </c>
       <c r="W3" t="n">
-        <v>16</v>
+        <v>13.61</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.17</v>
+        <v>-17.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.9264</v>
+        <v>63.482</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.3698</v>
+        <v>54.8732</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -912,48 +912,48 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>65.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>78.2</v>
+        <v>51.8</v>
       </c>
       <c r="AH3" t="n">
         <v>756</v>
       </c>
       <c r="AI3" t="n">
-        <v>44.985</v>
+        <v>65.27</v>
       </c>
       <c r="AJ3" t="n">
-        <v>39.31</v>
+        <v>54.81</v>
       </c>
       <c r="AK3" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="AL3" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.15</v>
+        <v>11.73</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.02</v>
+        <v>29.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.2%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.68</v>
+        <v>161.82</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -998,16 +998,16 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>77.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="L4" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="S4" t="n">
-        <v>10.44</v>
+        <v>10.53</v>
       </c>
       <c r="T4" t="n">
-        <v>12.08</v>
+        <v>12.17</v>
       </c>
       <c r="U4" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="V4" t="n">
-        <v>17.2</v>
+        <v>17.23</v>
       </c>
       <c r="W4" t="n">
         <v>12.86</v>
@@ -1059,10 +1059,10 @@
         <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.4268</v>
+        <v>155.4296</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.7646</v>
+        <v>146.7653</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,13 +1074,13 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>77.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="AH4" t="n">
         <v>759</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.02</v>
+        <v>4.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.16</v>
+        <v>10.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.41</v>
+        <v>122.52</v>
       </c>
       <c r="F5" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>71.8</v>
       </c>
       <c r="I5" t="n">
-        <v>75.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>9.77</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>10.24</v>
+        <v>10.34</v>
       </c>
       <c r="U5" t="n">
-        <v>22.2</v>
+        <v>22.31</v>
       </c>
       <c r="V5" t="n">
-        <v>17.09</v>
+        <v>17.12</v>
       </c>
       <c r="W5" t="n">
         <v>13.13</v>
@@ -1221,10 +1221,10 @@
         <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.9782</v>
+        <v>117.9804</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.1999</v>
+        <v>112.2004</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>75.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>691.4</v>
+        <v>692.16</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1322,16 +1322,16 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>81.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>11.09</v>
+        <v>11.21</v>
       </c>
       <c r="T6" t="n">
-        <v>9.970000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="U6" t="n">
-        <v>23.43</v>
+        <v>23.57</v>
       </c>
       <c r="V6" t="n">
-        <v>18.33</v>
+        <v>18.37</v>
       </c>
       <c r="W6" t="n">
         <v>14.09</v>
@@ -1383,10 +1383,10 @@
         <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>662.6472</v>
+        <v>662.6624</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.9894</v>
+        <v>629.9932</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AH6" t="n">
         <v>759</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.34</v>
+        <v>4.45</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.75</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.84</v>
+        <v>62.85</v>
       </c>
       <c r="F7" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S7" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="T7" t="n">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="U7" t="n">
-        <v>15.79</v>
+        <v>15.8</v>
       </c>
       <c r="V7" t="n">
-        <v>13.8</v>
+        <v>13.81</v>
       </c>
       <c r="W7" t="n">
         <v>12.85</v>
@@ -1545,7 +1545,7 @@
         <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.3446</v>
+        <v>61.3448</v>
       </c>
       <c r="AA7" t="n">
         <v>58.5815</v>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1584,14 +1584,14 @@
         <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.27</v>
+        <v>7.29</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.26000000000001</v>
+        <v>74.33</v>
       </c>
       <c r="F8" t="n">
-        <v>72.7</v>
+        <v>72.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>70.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="S8" t="n">
-        <v>7.39</v>
+        <v>7.49</v>
       </c>
       <c r="T8" t="n">
-        <v>9.66</v>
+        <v>9.76</v>
       </c>
       <c r="U8" t="n">
-        <v>18</v>
+        <v>18.12</v>
       </c>
       <c r="V8" t="n">
-        <v>15.03</v>
+        <v>15.06</v>
       </c>
       <c r="W8" t="n">
         <v>12.86</v>
@@ -1707,10 +1707,10 @@
         <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.9076</v>
+        <v>71.90900000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.70489999999999</v>
+        <v>68.70529999999999</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>70.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1746,14 +1746,14 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.27</v>
+        <v>3.37</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.09</v>
+        <v>8.19</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.67</v>
+        <v>17.69</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61.6</v>
+        <v>61.1</v>
       </c>
       <c r="L9" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,23 +1841,23 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo 9.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>28.79</v>
+        <v>28.94</v>
       </c>
       <c r="T9" t="n">
-        <v>26.74</v>
+        <v>26.88</v>
       </c>
       <c r="U9" t="n">
-        <v>39.86</v>
+        <v>40.02</v>
       </c>
       <c r="V9" t="n">
-        <v>17.83</v>
+        <v>17.88</v>
       </c>
       <c r="W9" t="n">
         <v>21.32</v>
@@ -1869,10 +1869,10 @@
         <v>0.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1684</v>
+        <v>16.1688</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4671</v>
+        <v>14.4672</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>61.6</v>
+        <v>61.1</v>
       </c>
       <c r="AH9" t="n">
         <v>756</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>9.289999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="AN9" t="n">
-        <v>22.14</v>
+        <v>22.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.3%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.7</v>
+        <v>63.74</v>
       </c>
       <c r="F10" t="n">
         <v>68.2</v>
@@ -1970,16 +1970,16 @@
         <v>61.3</v>
       </c>
       <c r="I10" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="J10" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K10" t="n">
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,19 +2007,19 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.02</v>
+        <v>-1.95</v>
       </c>
       <c r="T10" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="U10" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="V10" t="n">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="W10" t="n">
         <v>9.56</v>
@@ -2031,10 +2031,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.3198</v>
+        <v>63.3206</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.1002</v>
+        <v>63.1004</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="AG10" t="n">
         <v>82.8</v>
@@ -2070,14 +2070,14 @@
         <v>65.28</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.6%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.562</v>
+        <v>10.572</v>
       </c>
       <c r="F11" t="n">
         <v>64.3</v>
@@ -2169,19 +2169,19 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-1.28</v>
+        <v>-1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>20.29</v>
+        <v>20.41</v>
       </c>
       <c r="T11" t="n">
-        <v>29.01</v>
+        <v>29.13</v>
       </c>
       <c r="U11" t="n">
-        <v>66.27</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="W11" t="n">
         <v>23.17</v>
@@ -2193,7 +2193,7 @@
         <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.1815</v>
+        <v>10.1817</v>
       </c>
       <c r="AA11" t="n">
         <v>8.756500000000001</v>
@@ -2232,14 +2232,14 @@
         <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.74</v>
+        <v>3.83</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.62</v>
+        <v>20.73</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.7%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>360.64</v>
+        <v>360.75</v>
       </c>
       <c r="F13" t="n">
         <v>55.6</v>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>38.5</v>
@@ -2462,10 +2462,10 @@
         <v>64.8</v>
       </c>
       <c r="K13" t="n">
-        <v>67.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2493,34 +2493,34 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.7</v>
+        <v>-6.67</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.85</v>
+        <v>-14.83</v>
       </c>
       <c r="T13" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="U13" t="n">
-        <v>27.59</v>
+        <v>27.63</v>
       </c>
       <c r="V13" t="n">
-        <v>26.95</v>
+        <v>26.96</v>
       </c>
       <c r="W13" t="n">
         <v>17.78</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.36</v>
+        <v>-17.33</v>
       </c>
       <c r="Y13" t="n">
         <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.7982</v>
+        <v>380.8004</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.1704</v>
+        <v>362.171</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2538,16 +2538,16 @@
         <v>64.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AH13" t="n">
         <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>360.64</v>
+        <v>360.75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>360.64</v>
+        <v>360.75</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
@@ -2556,10 +2556,10 @@
         <v>424.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.29</v>
+        <v>-5.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.42</v>
+        <v>-0.39</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 360.64 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 360.75 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.89</v>
+        <v>26.875</v>
       </c>
       <c r="F14" t="n">
         <v>37.7</v>
@@ -2618,16 +2618,16 @@
         <v>22.4</v>
       </c>
       <c r="I14" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="J14" t="n">
         <v>15.4</v>
       </c>
       <c r="K14" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="L14" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2655,19 +2655,19 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>11.58</v>
+        <v>11.51</v>
       </c>
       <c r="S14" t="n">
-        <v>7.73</v>
+        <v>7.67</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.4</v>
+        <v>-7.46</v>
       </c>
       <c r="U14" t="n">
-        <v>-15.21</v>
+        <v>-15.26</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.96</v>
+        <v>-1.98</v>
       </c>
       <c r="W14" t="n">
         <v>33.93</v>
@@ -2679,7 +2679,7 @@
         <v>-0.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.2648</v>
+        <v>24.2645</v>
       </c>
       <c r="AA14" t="n">
         <v>26.9667</v>
@@ -2694,13 +2694,13 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="AF14" t="n">
         <v>20.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="AH14" t="n">
         <v>757</v>
@@ -2718,10 +2718,10 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>10.82</v>
+        <v>10.76</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.28</v>
+        <v>-0.34</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.82</v>
+        <v>161.72</v>
       </c>
       <c r="F4" t="n">
         <v>76.40000000000001</v>
@@ -998,16 +998,16 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>10.53</v>
+        <v>10.46</v>
       </c>
       <c r="T4" t="n">
-        <v>12.17</v>
+        <v>12.1</v>
       </c>
       <c r="U4" t="n">
-        <v>24.3</v>
+        <v>24.23</v>
       </c>
       <c r="V4" t="n">
-        <v>17.23</v>
+        <v>17.21</v>
       </c>
       <c r="W4" t="n">
         <v>12.86</v>
@@ -1059,10 +1059,10 @@
         <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.4296</v>
+        <v>155.4276</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.7653</v>
+        <v>146.7648</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,13 +1074,13 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AH4" t="n">
         <v>759</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.26</v>
+        <v>10.19</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.52</v>
+        <v>122.5</v>
       </c>
       <c r="F5" t="n">
         <v>75.40000000000001</v>
@@ -1160,7 +1160,7 @@
         <v>71.8</v>
       </c>
       <c r="I5" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1197,16 +1197,16 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S5" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="T5" t="n">
-        <v>10.34</v>
+        <v>10.32</v>
       </c>
       <c r="U5" t="n">
-        <v>22.31</v>
+        <v>22.29</v>
       </c>
       <c r="V5" t="n">
         <v>17.12</v>
@@ -1221,10 +1221,10 @@
         <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.9804</v>
+        <v>117.98</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.2004</v>
+        <v>112.2003</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>692.16</v>
+        <v>691.88</v>
       </c>
       <c r="F6" t="n">
         <v>74.8</v>
@@ -1322,13 +1322,13 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>75.2</v>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="S6" t="n">
-        <v>11.21</v>
+        <v>11.16</v>
       </c>
       <c r="T6" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="U6" t="n">
-        <v>23.57</v>
+        <v>23.52</v>
       </c>
       <c r="V6" t="n">
-        <v>18.37</v>
+        <v>18.36</v>
       </c>
       <c r="W6" t="n">
         <v>14.09</v>
@@ -1383,10 +1383,10 @@
         <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>662.6624</v>
+        <v>662.6568</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.9932</v>
+        <v>629.9918</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AH6" t="n">
         <v>759</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.869999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.69</v>
+        <v>17.71</v>
       </c>
       <c r="F9" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="L9" t="n">
-        <v>64.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,23 +1841,23 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="S9" t="n">
-        <v>28.94</v>
+        <v>29.08</v>
       </c>
       <c r="T9" t="n">
-        <v>26.88</v>
+        <v>27.03</v>
       </c>
       <c r="U9" t="n">
-        <v>40.02</v>
+        <v>40.18</v>
       </c>
       <c r="V9" t="n">
-        <v>17.88</v>
+        <v>17.92</v>
       </c>
       <c r="W9" t="n">
         <v>21.32</v>
@@ -1869,10 +1869,10 @@
         <v>0.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1688</v>
+        <v>16.1692</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4672</v>
+        <v>14.4673</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="AH9" t="n">
         <v>756</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>9.41</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>22.28</v>
+        <v>22.41</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>360.75</v>
+        <v>360.85</v>
       </c>
       <c r="F13" t="n">
         <v>55.6</v>
@@ -2456,7 +2456,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J13" t="n">
         <v>64.8</v>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 5.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.67</v>
+        <v>-6.65</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.83</v>
+        <v>-14.8</v>
       </c>
       <c r="T13" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="U13" t="n">
-        <v>27.63</v>
+        <v>27.66</v>
       </c>
       <c r="V13" t="n">
-        <v>26.96</v>
+        <v>26.97</v>
       </c>
       <c r="W13" t="n">
         <v>17.78</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.33</v>
+        <v>-17.31</v>
       </c>
       <c r="Y13" t="n">
         <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.8004</v>
+        <v>380.8024</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.171</v>
+        <v>362.1715</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="AF13" t="n">
         <v>64.8</v>
@@ -2544,10 +2544,10 @@
         <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>360.75</v>
+        <v>360.85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>360.75</v>
+        <v>360.85</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
@@ -2556,14 +2556,14 @@
         <v>424.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.27</v>
+        <v>-5.24</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.39</v>
+        <v>-0.36</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.2%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 360.75 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 360.85 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.875</v>
+        <v>26.88</v>
       </c>
       <c r="F14" t="n">
         <v>37.7</v>
@@ -2624,7 +2624,7 @@
         <v>15.4</v>
       </c>
       <c r="K14" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="L14" t="n">
         <v>21.9</v>
@@ -2655,16 +2655,16 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>11.51</v>
+        <v>11.54</v>
       </c>
       <c r="S14" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.46</v>
+        <v>-7.44</v>
       </c>
       <c r="U14" t="n">
-        <v>-15.26</v>
+        <v>-15.25</v>
       </c>
       <c r="V14" t="n">
         <v>-1.98</v>
@@ -2679,7 +2679,7 @@
         <v>-0.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.2645</v>
+        <v>24.2646</v>
       </c>
       <c r="AA14" t="n">
         <v>26.9667</v>
@@ -2700,7 +2700,7 @@
         <v>20.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="AH14" t="n">
         <v>757</v>
@@ -2718,10 +2718,10 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>10.76</v>
+        <v>10.78</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -641,29 +641,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.305</v>
+        <v>69.8</v>
       </c>
       <c r="F2" t="n">
-        <v>79.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>69</v>
+        <v>78.2</v>
       </c>
       <c r="I2" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>65.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>77.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="L2" t="n">
-        <v>79.7</v>
+        <v>70.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -702,47 +702,47 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 10.0% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.2</v>
+        <v>5.26</v>
       </c>
       <c r="S2" t="n">
-        <v>16.2</v>
+        <v>26.04</v>
       </c>
       <c r="T2" t="n">
-        <v>24.96</v>
+        <v>36.22</v>
       </c>
       <c r="U2" t="n">
-        <v>43</v>
+        <v>59.43</v>
       </c>
       <c r="V2" t="n">
-        <v>18.61</v>
+        <v>25.23</v>
       </c>
       <c r="W2" t="n">
-        <v>16.01</v>
+        <v>13.62</v>
       </c>
       <c r="X2" t="n">
-        <v>-19.17</v>
+        <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>44.9277</v>
+        <v>63.4594</v>
       </c>
       <c r="AA2" t="n">
-        <v>40.3702</v>
+        <v>54.8676</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -750,48 +750,48 @@
         <v>85</v>
       </c>
       <c r="AE2" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>65.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>77.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="AH2" t="n">
         <v>756</v>
       </c>
       <c r="AI2" t="n">
-        <v>44.985</v>
+        <v>65.27</v>
       </c>
       <c r="AJ2" t="n">
-        <v>39.31</v>
+        <v>54.81</v>
       </c>
       <c r="AK2" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="AL2" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.29</v>
+        <v>9.99</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.18</v>
+        <v>27.22</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.3%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.0%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -803,49 +803,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70.93000000000001</v>
+        <v>46.6</v>
       </c>
       <c r="F3" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>79.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="J3" t="n">
-        <v>69.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="K3" t="n">
-        <v>51.8</v>
+        <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>65.5</v>
+        <v>80.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -864,47 +864,47 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>6.97</v>
+        <v>-1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>28.08</v>
+        <v>14.47</v>
       </c>
       <c r="T3" t="n">
-        <v>38.43</v>
+        <v>23.1</v>
       </c>
       <c r="U3" t="n">
-        <v>62.01</v>
+        <v>40.87</v>
       </c>
       <c r="V3" t="n">
-        <v>25.9</v>
+        <v>18.02</v>
       </c>
       <c r="W3" t="n">
-        <v>13.61</v>
+        <v>15.98</v>
       </c>
       <c r="X3" t="n">
-        <v>-17.8</v>
+        <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>63.482</v>
+        <v>44.9136</v>
       </c>
       <c r="AA3" t="n">
-        <v>54.8732</v>
+        <v>40.3666</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -912,48 +912,48 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>69.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>51.8</v>
+        <v>82.8</v>
       </c>
       <c r="AH3" t="n">
         <v>756</v>
       </c>
       <c r="AI3" t="n">
-        <v>65.27</v>
+        <v>44.985</v>
       </c>
       <c r="AJ3" t="n">
-        <v>54.81</v>
+        <v>39.31</v>
       </c>
       <c r="AK3" t="n">
-        <v>72.27</v>
+        <v>49.485</v>
       </c>
       <c r="AL3" t="n">
-        <v>72.27</v>
+        <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>11.73</v>
+        <v>3.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.26</v>
+        <v>15.44</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.72</v>
+        <v>160.52</v>
       </c>
       <c r="F4" t="n">
-        <v>76.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>72.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I4" t="n">
-        <v>78</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>76.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>10.46</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>12.1</v>
+        <v>11.27</v>
       </c>
       <c r="U4" t="n">
-        <v>24.23</v>
+        <v>23.31</v>
       </c>
       <c r="V4" t="n">
-        <v>17.21</v>
+        <v>16.92</v>
       </c>
       <c r="W4" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.4276</v>
+        <v>155.4036</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.7648</v>
+        <v>146.7588</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,13 +1074,13 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>78</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH4" t="n">
         <v>759</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.05</v>
+        <v>3.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.19</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.5</v>
+        <v>121.72</v>
       </c>
       <c r="F5" t="n">
-        <v>75.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>75.5</v>
+        <v>74</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>75.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.13</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>9.85</v>
+        <v>9.15</v>
       </c>
       <c r="T5" t="n">
-        <v>10.32</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>22.29</v>
+        <v>21.51</v>
       </c>
       <c r="V5" t="n">
-        <v>17.12</v>
+        <v>16.87</v>
       </c>
       <c r="W5" t="n">
-        <v>13.13</v>
+        <v>13.14</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.98</v>
+        <v>117.9644</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.2003</v>
+        <v>112.1964</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>75.5</v>
+        <v>74</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.83</v>
+        <v>3.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.18</v>
+        <v>8.49</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.2%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>691.88</v>
+        <v>687.92</v>
       </c>
       <c r="F6" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>77.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>81.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>11.16</v>
+        <v>10.53</v>
       </c>
       <c r="T6" t="n">
-        <v>10.05</v>
+        <v>9.42</v>
       </c>
       <c r="U6" t="n">
-        <v>23.52</v>
+        <v>22.81</v>
       </c>
       <c r="V6" t="n">
-        <v>18.36</v>
+        <v>18.13</v>
       </c>
       <c r="W6" t="n">
-        <v>14.09</v>
+        <v>14.1</v>
       </c>
       <c r="X6" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>662.6568</v>
+        <v>662.5776</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.9918</v>
+        <v>629.972</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>77.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH6" t="n">
         <v>759</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.41</v>
+        <v>3.82</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.85</v>
+        <v>62.67</v>
       </c>
       <c r="F7" t="n">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>69.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>75.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="T7" t="n">
-        <v>10.5</v>
+        <v>10.18</v>
       </c>
       <c r="U7" t="n">
-        <v>15.8</v>
+        <v>15.47</v>
       </c>
       <c r="V7" t="n">
-        <v>13.81</v>
+        <v>13.7</v>
       </c>
       <c r="W7" t="n">
         <v>12.85</v>
@@ -1545,10 +1545,10 @@
         <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.3448</v>
+        <v>61.3412</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.5815</v>
+        <v>58.5806</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>69.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1584,14 +1584,14 @@
         <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.29</v>
+        <v>6.98</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.33</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65</v>
+        <v>64.8</v>
       </c>
       <c r="I8" t="n">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>74.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,38 +1679,38 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
-        <v>7.49</v>
+        <v>7.16</v>
       </c>
       <c r="T8" t="n">
-        <v>9.76</v>
+        <v>9.42</v>
       </c>
       <c r="U8" t="n">
-        <v>18.12</v>
+        <v>17.75</v>
       </c>
       <c r="V8" t="n">
-        <v>15.06</v>
+        <v>14.94</v>
       </c>
       <c r="W8" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.90900000000001</v>
+        <v>71.9044</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.70529999999999</v>
+        <v>68.7041</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1746,14 +1746,14 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.19</v>
+        <v>7.85</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.71</v>
+        <v>17.472</v>
       </c>
       <c r="F9" t="n">
-        <v>68.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>60.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>64.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,38 +1841,38 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1.05</v>
+        <v>-0.31</v>
       </c>
       <c r="S9" t="n">
-        <v>29.08</v>
+        <v>27.35</v>
       </c>
       <c r="T9" t="n">
-        <v>27.03</v>
+        <v>25.32</v>
       </c>
       <c r="U9" t="n">
-        <v>40.18</v>
+        <v>38.29</v>
       </c>
       <c r="V9" t="n">
-        <v>17.92</v>
+        <v>17.39</v>
       </c>
       <c r="W9" t="n">
-        <v>21.32</v>
+        <v>21.33</v>
       </c>
       <c r="X9" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1692</v>
+        <v>16.1644</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4673</v>
+        <v>14.4661</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>60.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AH9" t="n">
         <v>756</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>9.529999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>22.41</v>
+        <v>20.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.74</v>
+        <v>63.86</v>
       </c>
       <c r="F10" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>61.3</v>
       </c>
       <c r="I10" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
       <c r="J10" t="n">
         <v>78.3</v>
@@ -1979,7 +1979,7 @@
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,22 +2007,22 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.95</v>
+        <v>-1.77</v>
       </c>
       <c r="T10" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0.28</v>
+        <v>0.47</v>
       </c>
       <c r="V10" t="n">
-        <v>6.57</v>
+        <v>6.64</v>
       </c>
       <c r="W10" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>-12.85</v>
@@ -2031,10 +2031,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.3206</v>
+        <v>63.323</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.1004</v>
+        <v>63.101</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
       <c r="AF10" t="n">
         <v>78.3</v>
@@ -2070,14 +2070,14 @@
         <v>65.28</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.572</v>
+        <v>10.288</v>
       </c>
       <c r="F11" t="n">
-        <v>64.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31.2</v>
+        <v>30.4</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="K11" t="n">
         <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2169,34 +2169,34 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-1.19</v>
+        <v>-3.84</v>
       </c>
       <c r="S11" t="n">
-        <v>20.41</v>
+        <v>17.17</v>
       </c>
       <c r="T11" t="n">
-        <v>29.13</v>
+        <v>25.66</v>
       </c>
       <c r="U11" t="n">
-        <v>66.43000000000001</v>
+        <v>61.96</v>
       </c>
       <c r="V11" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="W11" t="n">
-        <v>23.17</v>
+        <v>23.22</v>
       </c>
       <c r="X11" t="n">
         <v>-44.26</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.1817</v>
+        <v>10.176</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.756500000000001</v>
+        <v>8.755100000000001</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="AG11" t="n">
         <v>82.8</v>
@@ -2232,14 +2232,14 @@
         <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.83</v>
+        <v>1.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.73</v>
+        <v>17.51</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>598.16</v>
+        <v>590.2506</v>
       </c>
       <c r="F12" t="n">
-        <v>61.9</v>
+        <v>63.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>58.7</v>
+        <v>58.2</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -2300,10 +2300,10 @@
         <v>24.5</v>
       </c>
       <c r="K12" t="n">
-        <v>30.8</v>
+        <v>40.8</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>32.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 17.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 14.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>10.75</v>
+        <v>4.19</v>
       </c>
       <c r="S12" t="n">
-        <v>51.67</v>
+        <v>48.55</v>
       </c>
       <c r="T12" t="n">
-        <v>65.94</v>
+        <v>62.47</v>
       </c>
       <c r="U12" t="n">
-        <v>138.77</v>
+        <v>134.28</v>
       </c>
       <c r="V12" t="n">
-        <v>60.94</v>
+        <v>60.12</v>
       </c>
       <c r="W12" t="n">
-        <v>34.92</v>
+        <v>34.91</v>
       </c>
       <c r="X12" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>511.287</v>
+        <v>515.607</v>
       </c>
       <c r="AA12" t="n">
-        <v>397.8009</v>
+        <v>399.3193</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         <v>29.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>30.8</v>
+        <v>40.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AI12" t="n">
         <v>543.96</v>
@@ -2394,14 +2394,14 @@
         <v>637.9</v>
       </c>
       <c r="AM12" t="n">
-        <v>16.99</v>
+        <v>14.48</v>
       </c>
       <c r="AN12" t="n">
-        <v>50.37</v>
+        <v>47.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 61.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.0%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.5%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>360.85</v>
+        <v>357.35</v>
       </c>
       <c r="F13" t="n">
-        <v>55.6</v>
+        <v>54.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I13" t="n">
-        <v>38.6</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
-        <v>64.8</v>
+        <v>64.2</v>
       </c>
       <c r="K13" t="n">
-        <v>67.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="L13" t="n">
-        <v>57.4</v>
+        <v>56.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,43 +2484,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 5.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.65</v>
+        <v>-7.55</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.8</v>
+        <v>-15.63</v>
       </c>
       <c r="T13" t="n">
-        <v>4.01</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>27.66</v>
+        <v>26.42</v>
       </c>
       <c r="V13" t="n">
-        <v>26.97</v>
+        <v>26.56</v>
       </c>
       <c r="W13" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.31</v>
+        <v>-18.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.8024</v>
+        <v>380.7324</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.1715</v>
+        <v>362.154</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,22 +2532,22 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>38.6</v>
+        <v>36.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>64.8</v>
+        <v>64.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="AH13" t="n">
         <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>360.85</v>
+        <v>357.35</v>
       </c>
       <c r="AJ13" t="n">
-        <v>360.85</v>
+        <v>357.35</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
@@ -2556,14 +2556,14 @@
         <v>424.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.24</v>
+        <v>-6.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.36</v>
+        <v>-1.33</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.2%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.1%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 360.85 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 357.35 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.88</v>
+        <v>26.56</v>
       </c>
       <c r="F14" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="I14" t="n">
-        <v>52.5</v>
+        <v>49.8</v>
       </c>
       <c r="J14" t="n">
         <v>15.4</v>
       </c>
       <c r="K14" t="n">
-        <v>51.1</v>
+        <v>56.3</v>
       </c>
       <c r="L14" t="n">
-        <v>21.9</v>
+        <v>25.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 10.8% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>11.54</v>
+        <v>10.21</v>
       </c>
       <c r="S14" t="n">
-        <v>7.69</v>
+        <v>6.41</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.44</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-15.25</v>
+        <v>-16.25</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.98</v>
+        <v>-2.37</v>
       </c>
       <c r="W14" t="n">
-        <v>33.93</v>
+        <v>33.95</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.2646</v>
+        <v>24.2582</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9667</v>
+        <v>26.9651</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,13 +2694,13 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>52.5</v>
+        <v>49.8</v>
       </c>
       <c r="AF14" t="n">
         <v>20.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>51.1</v>
+        <v>56.3</v>
       </c>
       <c r="AH14" t="n">
         <v>757</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>10.78</v>
+        <v>9.49</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.32</v>
+        <v>-1.5</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 37.7, trend Recovery. Entry zone: Extended - wait pullback. Distanza da MA50: 10.8%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 37.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.8</v>
+        <v>69.86</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -680,10 +680,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>58.8</v>
+        <v>58.4</v>
       </c>
       <c r="L2" t="n">
-        <v>70.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -707,23 +707,23 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 10.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>5.26</v>
+        <v>5.35</v>
       </c>
       <c r="S2" t="n">
-        <v>26.04</v>
+        <v>26.15</v>
       </c>
       <c r="T2" t="n">
-        <v>36.22</v>
+        <v>36.34</v>
       </c>
       <c r="U2" t="n">
-        <v>59.43</v>
+        <v>59.57</v>
       </c>
       <c r="V2" t="n">
-        <v>25.23</v>
+        <v>25.26</v>
       </c>
       <c r="W2" t="n">
         <v>13.62</v>
@@ -735,10 +735,10 @@
         <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.4594</v>
+        <v>63.4606</v>
       </c>
       <c r="AA2" t="n">
-        <v>54.8676</v>
+        <v>54.8679</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>58.8</v>
+        <v>58.4</v>
       </c>
       <c r="AH2" t="n">
         <v>756</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>9.99</v>
+        <v>10.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>27.22</v>
+        <v>27.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.0%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>160.52</v>
+        <v>160.66</v>
       </c>
       <c r="F4" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="I4" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="T4" t="n">
-        <v>11.27</v>
+        <v>11.37</v>
       </c>
       <c r="U4" t="n">
-        <v>23.31</v>
+        <v>23.41</v>
       </c>
       <c r="V4" t="n">
-        <v>16.92</v>
+        <v>16.96</v>
       </c>
       <c r="W4" t="n">
         <v>12.87</v>
@@ -1056,13 +1056,13 @@
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.4036</v>
+        <v>155.4064</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.7588</v>
+        <v>146.7595</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>121.72</v>
+        <v>121.77</v>
       </c>
       <c r="F5" t="n">
         <v>74.90000000000001</v>
@@ -1160,7 +1160,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>9.15</v>
+        <v>9.19</v>
       </c>
       <c r="T5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="U5" t="n">
-        <v>21.51</v>
+        <v>21.56</v>
       </c>
       <c r="V5" t="n">
-        <v>16.87</v>
+        <v>16.88</v>
       </c>
       <c r="W5" t="n">
         <v>13.14</v>
@@ -1221,10 +1221,10 @@
         <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.9644</v>
+        <v>117.9654</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.1964</v>
+        <v>112.1966</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1260,10 +1260,10 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>687.92</v>
+        <v>687.6</v>
       </c>
       <c r="F6" t="n">
-        <v>74.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="I6" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>10.53</v>
+        <v>10.48</v>
       </c>
       <c r="T6" t="n">
-        <v>9.42</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>22.81</v>
+        <v>22.76</v>
       </c>
       <c r="V6" t="n">
-        <v>18.13</v>
+        <v>18.11</v>
       </c>
       <c r="W6" t="n">
         <v>14.1</v>
@@ -1380,13 +1380,13 @@
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>662.5776</v>
+        <v>662.5712</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.972</v>
+        <v>629.9704</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.67</v>
+        <v>62.62</v>
       </c>
       <c r="F7" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S7" t="n">
-        <v>6.5</v>
+        <v>6.41</v>
       </c>
       <c r="T7" t="n">
-        <v>10.18</v>
+        <v>10.09</v>
       </c>
       <c r="U7" t="n">
-        <v>15.47</v>
+        <v>15.38</v>
       </c>
       <c r="V7" t="n">
-        <v>13.7</v>
+        <v>13.67</v>
       </c>
       <c r="W7" t="n">
         <v>12.85</v>
@@ -1542,13 +1542,13 @@
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.3412</v>
+        <v>61.3402</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.5806</v>
+        <v>58.5804</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1584,14 +1584,14 @@
         <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.98</v>
+        <v>6.9</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>70.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,23 +1679,23 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="S8" t="n">
-        <v>7.16</v>
+        <v>7.36</v>
       </c>
       <c r="T8" t="n">
-        <v>9.42</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>17.75</v>
+        <v>17.97</v>
       </c>
       <c r="V8" t="n">
-        <v>14.94</v>
+        <v>15.01</v>
       </c>
       <c r="W8" t="n">
         <v>12.87</v>
@@ -1704,13 +1704,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.9044</v>
+        <v>71.9072</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.7041</v>
+        <v>68.70480000000001</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>70.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1746,14 +1746,14 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.85</v>
+        <v>8.06</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.2%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.472</v>
+        <v>17.536</v>
       </c>
       <c r="F9" t="n">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>66.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="L9" t="n">
-        <v>68.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,23 +1841,23 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-0.31</v>
+        <v>0.06</v>
       </c>
       <c r="S9" t="n">
-        <v>27.35</v>
+        <v>27.81</v>
       </c>
       <c r="T9" t="n">
-        <v>25.32</v>
+        <v>25.78</v>
       </c>
       <c r="U9" t="n">
-        <v>38.29</v>
+        <v>38.8</v>
       </c>
       <c r="V9" t="n">
-        <v>17.39</v>
+        <v>17.54</v>
       </c>
       <c r="W9" t="n">
         <v>21.33</v>
@@ -1869,10 +1869,10 @@
         <v>0.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1644</v>
+        <v>16.1657</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4661</v>
+        <v>14.4664</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>66.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AH9" t="n">
         <v>756</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>8.09</v>
+        <v>8.48</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.78</v>
+        <v>21.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.5%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.86</v>
+        <v>63.81</v>
       </c>
       <c r="F10" t="n">
         <v>68.3</v>
@@ -1970,7 +1970,7 @@
         <v>61.3</v>
       </c>
       <c r="I10" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="J10" t="n">
         <v>78.3</v>
@@ -2007,19 +2007,19 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.77</v>
+        <v>-1.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="V10" t="n">
-        <v>6.64</v>
+        <v>6.61</v>
       </c>
       <c r="W10" t="n">
         <v>9.550000000000001</v>
@@ -2031,10 +2031,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.323</v>
+        <v>63.322</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.101</v>
+        <v>63.1007</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="AF10" t="n">
         <v>78.3</v>
@@ -2070,10 +2070,10 @@
         <v>65.28</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,14 +2114,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.288</v>
+        <v>578.25</v>
       </c>
       <c r="F11" t="n">
-        <v>64.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>30.4</v>
+        <v>57.6</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>31.7</v>
+        <v>24.5</v>
       </c>
       <c r="K11" t="n">
-        <v>82.8</v>
+        <v>49.9</v>
       </c>
       <c r="L11" t="n">
-        <v>58.1</v>
+        <v>39.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 12.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-3.84</v>
+        <v>2.07</v>
       </c>
       <c r="S11" t="n">
-        <v>17.17</v>
+        <v>45.53</v>
       </c>
       <c r="T11" t="n">
-        <v>25.66</v>
+        <v>59.17</v>
       </c>
       <c r="U11" t="n">
-        <v>61.96</v>
+        <v>129.51</v>
       </c>
       <c r="V11" t="n">
-        <v>2.32</v>
+        <v>59.02</v>
       </c>
       <c r="W11" t="n">
-        <v>23.22</v>
+        <v>34.96</v>
       </c>
       <c r="X11" t="n">
-        <v>-44.26</v>
+        <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>1.69</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.176</v>
+        <v>515.367</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.755100000000001</v>
+        <v>399.2593</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,45 +2211,45 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>36.7</v>
+        <v>29.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>82.8</v>
+        <v>49.9</v>
       </c>
       <c r="AH11" t="n">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="AI11" t="n">
-        <v>10.2879</v>
+        <v>543.96</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8.7643</v>
+        <v>362.53</v>
       </c>
       <c r="AK11" t="n">
-        <v>11.61</v>
+        <v>637.9</v>
       </c>
       <c r="AL11" t="n">
-        <v>11.61</v>
+        <v>637.9</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.1</v>
+        <v>12.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.51</v>
+        <v>44.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 64.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>590.2506</v>
+        <v>10.32</v>
       </c>
       <c r="F12" t="n">
-        <v>63.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>58.2</v>
+        <v>30.4</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>24.5</v>
+        <v>31.7</v>
       </c>
       <c r="K12" t="n">
-        <v>40.8</v>
+        <v>82.8</v>
       </c>
       <c r="L12" t="n">
-        <v>32.6</v>
+        <v>58.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 14.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4.19</v>
+        <v>-3.54</v>
       </c>
       <c r="S12" t="n">
-        <v>48.55</v>
+        <v>17.54</v>
       </c>
       <c r="T12" t="n">
-        <v>62.47</v>
+        <v>26.05</v>
       </c>
       <c r="U12" t="n">
-        <v>134.28</v>
+        <v>62.46</v>
       </c>
       <c r="V12" t="n">
-        <v>60.12</v>
+        <v>2.42</v>
       </c>
       <c r="W12" t="n">
-        <v>34.91</v>
+        <v>23.21</v>
       </c>
       <c r="X12" t="n">
-        <v>-35.74</v>
+        <v>-44.26</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>515.607</v>
+        <v>10.1767</v>
       </c>
       <c r="AA12" t="n">
-        <v>399.3193</v>
+        <v>8.7553</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2373,45 +2373,45 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>29.5</v>
+        <v>36.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>40.8</v>
+        <v>82.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="AI12" t="n">
-        <v>543.96</v>
+        <v>10.2879</v>
       </c>
       <c r="AJ12" t="n">
-        <v>362.53</v>
+        <v>8.7643</v>
       </c>
       <c r="AK12" t="n">
-        <v>637.9</v>
+        <v>11.61</v>
       </c>
       <c r="AL12" t="n">
-        <v>637.9</v>
+        <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>14.48</v>
+        <v>1.41</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.81</v>
+        <v>17.87</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.5%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>357.35</v>
+        <v>357.13</v>
       </c>
       <c r="F13" t="n">
         <v>54.5</v>
@@ -2453,13 +2453,13 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>66</v>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 6.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-7.55</v>
+        <v>-7.61</v>
       </c>
       <c r="S13" t="n">
-        <v>-15.63</v>
+        <v>-15.68</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="U13" t="n">
-        <v>26.42</v>
+        <v>26.35</v>
       </c>
       <c r="V13" t="n">
-        <v>26.56</v>
+        <v>26.54</v>
       </c>
       <c r="W13" t="n">
         <v>17.79</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.11</v>
+        <v>-18.16</v>
       </c>
       <c r="Y13" t="n">
         <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.7324</v>
+        <v>380.728</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.154</v>
+        <v>362.1529</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AG13" t="n">
         <v>66</v>
@@ -2544,10 +2544,10 @@
         <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>357.35</v>
+        <v>357.13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>357.35</v>
+        <v>357.13</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
@@ -2556,14 +2556,14 @@
         <v>424.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>-6.14</v>
+        <v>-6.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1.33</v>
+        <v>-1.39</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.1%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 357.35 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 357.13 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.56</v>
+        <v>26.565</v>
       </c>
       <c r="F14" t="n">
         <v>37.8</v>
@@ -2624,7 +2624,7 @@
         <v>15.4</v>
       </c>
       <c r="K14" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="L14" t="n">
         <v>25.1</v>
@@ -2655,19 +2655,19 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>10.21</v>
+        <v>10.23</v>
       </c>
       <c r="S14" t="n">
-        <v>6.41</v>
+        <v>6.43</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.52</v>
       </c>
       <c r="U14" t="n">
-        <v>-16.25</v>
+        <v>-16.24</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.37</v>
+        <v>-2.36</v>
       </c>
       <c r="W14" t="n">
         <v>33.95</v>
@@ -2679,7 +2679,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.2582</v>
+        <v>24.2583</v>
       </c>
       <c r="AA14" t="n">
         <v>26.9651</v>
@@ -2700,7 +2700,7 @@
         <v>20.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="AH14" t="n">
         <v>757</v>
@@ -2718,10 +2718,10 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>9.49</v>
+        <v>9.51</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.5</v>
+        <v>-1.48</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,18 +660,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.86</v>
+        <v>70.48</v>
       </c>
       <c r="F2" t="n">
-        <v>79.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.2</v>
+        <v>78.7</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>58.4</v>
+        <v>52.5</v>
       </c>
       <c r="L2" t="n">
-        <v>70.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -707,23 +707,23 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 11.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>5.35</v>
+        <v>8.5</v>
       </c>
       <c r="S2" t="n">
-        <v>26.15</v>
+        <v>24.52</v>
       </c>
       <c r="T2" t="n">
-        <v>36.34</v>
+        <v>37.87</v>
       </c>
       <c r="U2" t="n">
-        <v>59.57</v>
+        <v>61.12</v>
       </c>
       <c r="V2" t="n">
-        <v>25.26</v>
+        <v>25.67</v>
       </c>
       <c r="W2" t="n">
         <v>13.62</v>
@@ -732,17 +732,17 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.4606</v>
+        <v>63.1764</v>
       </c>
       <c r="AA2" t="n">
-        <v>54.8679</v>
+        <v>54.7527</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -756,13 +756,13 @@
         <v>69.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>58.4</v>
+        <v>52.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AI2" t="n">
-        <v>65.27</v>
+        <v>65.25</v>
       </c>
       <c r="AJ2" t="n">
         <v>54.81</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>10.08</v>
+        <v>11.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>27.32</v>
+        <v>28.72</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.6%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>46.6</v>
+        <v>46.46</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>78.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>68.5</v>
+        <v>68.3</v>
       </c>
       <c r="I3" t="n">
-        <v>94.3</v>
+        <v>93.2</v>
       </c>
       <c r="J3" t="n">
         <v>65.5</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>80.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-1.29</v>
+        <v>-1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>14.47</v>
+        <v>13.84</v>
       </c>
       <c r="T3" t="n">
-        <v>23.1</v>
+        <v>22.36</v>
       </c>
       <c r="U3" t="n">
-        <v>40.87</v>
+        <v>41.41</v>
       </c>
       <c r="V3" t="n">
-        <v>18.02</v>
+        <v>17.92</v>
       </c>
       <c r="W3" t="n">
-        <v>15.98</v>
+        <v>15.99</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.9136</v>
+        <v>44.7763</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.3666</v>
+        <v>40.3085</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>94.3</v>
+        <v>93.2</v>
       </c>
       <c r="AF3" t="n">
         <v>65.5</v>
@@ -921,7 +921,7 @@
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AI3" t="n">
         <v>44.985</v>
@@ -936,14 +936,14 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.44</v>
+        <v>15.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>160.66</v>
+        <v>161.56</v>
       </c>
       <c r="F4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>72.5</v>
+        <v>72.8</v>
       </c>
       <c r="I4" t="n">
-        <v>76.3</v>
+        <v>75.8</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="L4" t="n">
-        <v>76.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>2.16</v>
       </c>
       <c r="S4" t="n">
-        <v>9.74</v>
+        <v>8.91</v>
       </c>
       <c r="T4" t="n">
-        <v>11.37</v>
+        <v>11.96</v>
       </c>
       <c r="U4" t="n">
-        <v>23.41</v>
+        <v>24.58</v>
       </c>
       <c r="V4" t="n">
-        <v>16.96</v>
+        <v>17.2</v>
       </c>
       <c r="W4" t="n">
         <v>12.87</v>
@@ -1056,13 +1056,13 @@
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.4064</v>
+        <v>155.0524</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.7595</v>
+        <v>146.6353</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>76.3</v>
+        <v>75.8</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="AH4" t="n">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AI4" t="n">
-        <v>158.2</v>
+        <v>156.96</v>
       </c>
       <c r="AJ4" t="n">
         <v>140.98</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.470000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>121.77</v>
+        <v>122.67</v>
       </c>
       <c r="F5" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>82.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>75.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>2.64</v>
       </c>
       <c r="S5" t="n">
-        <v>9.19</v>
+        <v>8.32</v>
       </c>
       <c r="T5" t="n">
-        <v>9.66</v>
+        <v>10.51</v>
       </c>
       <c r="U5" t="n">
-        <v>21.56</v>
+        <v>22.61</v>
       </c>
       <c r="V5" t="n">
-        <v>16.88</v>
+        <v>17.19</v>
       </c>
       <c r="W5" t="n">
         <v>13.14</v>
@@ -1218,13 +1218,13 @@
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.9654</v>
+        <v>117.7098</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.1966</v>
+        <v>112.1115</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,19 +1236,19 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>82.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AI5" t="n">
-        <v>120.3</v>
+        <v>119.18</v>
       </c>
       <c r="AJ5" t="n">
         <v>107.5</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.23</v>
+        <v>4.21</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.529999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.2%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>687.6</v>
+        <v>693.26</v>
       </c>
       <c r="F6" t="n">
-        <v>74.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.2</v>
+        <v>70.7</v>
       </c>
       <c r="I6" t="n">
-        <v>76</v>
+        <v>75.7</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>82.8</v>
+        <v>79.2</v>
       </c>
       <c r="L6" t="n">
-        <v>75.3</v>
+        <v>74.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>2.74</v>
       </c>
       <c r="S6" t="n">
-        <v>10.48</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>9.369999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="U6" t="n">
-        <v>22.76</v>
+        <v>24.2</v>
       </c>
       <c r="V6" t="n">
-        <v>18.11</v>
+        <v>18.46</v>
       </c>
       <c r="W6" t="n">
         <v>14.1</v>
@@ -1380,13 +1380,13 @@
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>662.5712</v>
+        <v>660.9632</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.9704</v>
+        <v>629.4737</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,19 +1398,19 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>76</v>
+        <v>75.7</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>82.8</v>
+        <v>79.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AI6" t="n">
-        <v>680.66</v>
+        <v>673.5</v>
       </c>
       <c r="AJ6" t="n">
         <v>597.92</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.78</v>
+        <v>4.89</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.15</v>
+        <v>10.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.9%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.62</v>
+        <v>62.55</v>
       </c>
       <c r="F7" t="n">
-        <v>74.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>68.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>75.2</v>
+        <v>74.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>6.41</v>
+        <v>5.56</v>
       </c>
       <c r="T7" t="n">
-        <v>10.09</v>
+        <v>10.14</v>
       </c>
       <c r="U7" t="n">
-        <v>15.38</v>
+        <v>15.11</v>
       </c>
       <c r="V7" t="n">
-        <v>13.67</v>
+        <v>13.64</v>
       </c>
       <c r="W7" t="n">
         <v>12.85</v>
@@ -1545,10 +1545,10 @@
         <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.3402</v>
+        <v>61.2392</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.5804</v>
+        <v>58.5426</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>68.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1569,10 +1569,10 @@
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AI7" t="n">
-        <v>60.81</v>
+        <v>60.74</v>
       </c>
       <c r="AJ7" t="n">
         <v>56.7</v>
@@ -1584,14 +1584,14 @@
         <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.23999999999999</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65</v>
+        <v>65.2</v>
       </c>
       <c r="I8" t="n">
-        <v>70.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="S8" t="n">
-        <v>7.36</v>
+        <v>5.92</v>
       </c>
       <c r="T8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>17.97</v>
+        <v>18.32</v>
       </c>
       <c r="V8" t="n">
-        <v>15.01</v>
+        <v>15.15</v>
       </c>
       <c r="W8" t="n">
         <v>12.87</v>
@@ -1704,13 +1704,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.9072</v>
+        <v>71.77119999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.70480000000001</v>
+        <v>68.6544</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>70.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1731,10 +1731,10 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.11</v>
       </c>
       <c r="AJ8" t="n">
         <v>66.58</v>
@@ -1746,14 +1746,14 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.06</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.2%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.536</v>
+        <v>17.616</v>
       </c>
       <c r="F9" t="n">
-        <v>69.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>64.8</v>
+        <v>60.6</v>
       </c>
       <c r="L9" t="n">
-        <v>67.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,38 +1841,38 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo 8.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.06</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>27.81</v>
+        <v>24.71</v>
       </c>
       <c r="T9" t="n">
-        <v>25.78</v>
+        <v>27.26</v>
       </c>
       <c r="U9" t="n">
-        <v>38.8</v>
+        <v>40.12</v>
       </c>
       <c r="V9" t="n">
-        <v>17.54</v>
+        <v>17.74</v>
       </c>
       <c r="W9" t="n">
-        <v>21.33</v>
+        <v>21.34</v>
       </c>
       <c r="X9" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1657</v>
+        <v>16.083</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4664</v>
+        <v>14.4439</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>64.8</v>
+        <v>60.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AI9" t="n">
         <v>16.544</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>8.48</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.22</v>
+        <v>21.96</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.5%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.81</v>
+        <v>63.99</v>
       </c>
       <c r="F10" t="n">
         <v>68.3</v>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="I10" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="J10" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K10" t="n">
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>70.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.85</v>
+        <v>-1.83</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="U10" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="V10" t="n">
-        <v>6.61</v>
+        <v>6.72</v>
       </c>
       <c r="W10" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="X10" t="n">
         <v>-12.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.322</v>
+        <v>63.3138</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.1007</v>
+        <v>63.0971</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,16 +2046,16 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="AG10" t="n">
         <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AI10" t="n">
         <v>62.34</v>
@@ -2070,14 +2070,14 @@
         <v>65.28</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.8%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,14 +2114,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>578.25</v>
+        <v>10.584</v>
       </c>
       <c r="F11" t="n">
-        <v>64.5</v>
+        <v>64.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>57.6</v>
+        <v>31.2</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>24.5</v>
+        <v>31.8</v>
       </c>
       <c r="K11" t="n">
-        <v>49.9</v>
+        <v>81.7</v>
       </c>
       <c r="L11" t="n">
-        <v>39.6</v>
+        <v>57.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 12.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>2.07</v>
+        <v>3.48</v>
       </c>
       <c r="S11" t="n">
-        <v>45.53</v>
+        <v>20.32</v>
       </c>
       <c r="T11" t="n">
-        <v>59.17</v>
+        <v>29.65</v>
       </c>
       <c r="U11" t="n">
-        <v>129.51</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>59.02</v>
+        <v>3.3</v>
       </c>
       <c r="W11" t="n">
-        <v>34.96</v>
+        <v>23.18</v>
       </c>
       <c r="X11" t="n">
-        <v>-35.74</v>
+        <v>-44.26</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.69</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>515.367</v>
+        <v>10.1519</v>
       </c>
       <c r="AA11" t="n">
-        <v>399.2593</v>
+        <v>8.738899999999999</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,45 +2211,45 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>29.5</v>
+        <v>36.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>49.9</v>
+        <v>81.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="AI11" t="n">
-        <v>543.96</v>
+        <v>10.2879</v>
       </c>
       <c r="AJ11" t="n">
-        <v>362.53</v>
+        <v>8.7643</v>
       </c>
       <c r="AK11" t="n">
-        <v>637.9</v>
+        <v>11.61</v>
       </c>
       <c r="AL11" t="n">
-        <v>637.9</v>
+        <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>12.2</v>
+        <v>4.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.83</v>
+        <v>21.11</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 64.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.32</v>
+        <v>591.01</v>
       </c>
       <c r="F12" t="n">
-        <v>64.09999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30.4</v>
+        <v>57.5</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>31.7</v>
+        <v>24.5</v>
       </c>
       <c r="K12" t="n">
-        <v>82.8</v>
+        <v>40.3</v>
       </c>
       <c r="L12" t="n">
-        <v>58.1</v>
+        <v>32.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 14.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-3.54</v>
+        <v>4.32</v>
       </c>
       <c r="S12" t="n">
-        <v>17.54</v>
+        <v>48.75</v>
       </c>
       <c r="T12" t="n">
-        <v>26.05</v>
+        <v>62.68</v>
       </c>
       <c r="U12" t="n">
-        <v>62.46</v>
+        <v>134.58</v>
       </c>
       <c r="V12" t="n">
-        <v>2.42</v>
+        <v>58.73</v>
       </c>
       <c r="W12" t="n">
-        <v>23.21</v>
+        <v>34.89</v>
       </c>
       <c r="X12" t="n">
-        <v>-44.26</v>
+        <v>-35.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>1.68</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.1767</v>
+        <v>515.6222</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.7553</v>
+        <v>399.3231</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2373,45 +2373,45 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>36.7</v>
+        <v>29.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>82.8</v>
+        <v>40.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="AI12" t="n">
-        <v>10.2879</v>
+        <v>543.96</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8.7643</v>
+        <v>362.53</v>
       </c>
       <c r="AK12" t="n">
-        <v>11.61</v>
+        <v>637.9</v>
       </c>
       <c r="AL12" t="n">
-        <v>11.61</v>
+        <v>637.9</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.41</v>
+        <v>14.62</v>
       </c>
       <c r="AN12" t="n">
-        <v>17.87</v>
+        <v>48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.6%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>357.13</v>
+        <v>361.39</v>
       </c>
       <c r="F13" t="n">
-        <v>54.5</v>
+        <v>55.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>69.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>36.4</v>
+        <v>38.8</v>
       </c>
       <c r="J13" t="n">
-        <v>64.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>56.1</v>
+        <v>57.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,43 +2484,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 6.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-7.61</v>
+        <v>-6.18</v>
       </c>
       <c r="S13" t="n">
-        <v>-15.68</v>
+        <v>-14.19</v>
       </c>
       <c r="T13" t="n">
-        <v>2.93</v>
+        <v>3.11</v>
       </c>
       <c r="U13" t="n">
-        <v>26.35</v>
+        <v>27.05</v>
       </c>
       <c r="V13" t="n">
-        <v>26.54</v>
+        <v>27.08</v>
       </c>
       <c r="W13" t="n">
         <v>17.79</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.16</v>
+        <v>-17.19</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.728</v>
+        <v>380.915</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.1529</v>
+        <v>361.74</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,48 +2532,48 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>36.4</v>
+        <v>38.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>64.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AG13" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AH13" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AI13" t="n">
-        <v>357.13</v>
+        <v>361.39</v>
       </c>
       <c r="AJ13" t="n">
-        <v>357.13</v>
+        <v>361.39</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
       </c>
       <c r="AL13" t="n">
-        <v>424.57</v>
+        <v>428.69</v>
       </c>
       <c r="AM13" t="n">
-        <v>-6.2</v>
+        <v>-5.13</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1.39</v>
+        <v>-0.1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.1%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 424.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 428.69 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 357.13 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 361.39 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.565</v>
+        <v>27.13</v>
       </c>
       <c r="F14" t="n">
-        <v>37.8</v>
+        <v>42.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,28 +2615,28 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="I14" t="n">
-        <v>49.8</v>
+        <v>55.2</v>
       </c>
       <c r="J14" t="n">
         <v>15.4</v>
       </c>
       <c r="K14" t="n">
-        <v>56.2</v>
+        <v>50.2</v>
       </c>
       <c r="L14" t="n">
-        <v>25.1</v>
+        <v>21.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2651,23 +2651,23 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 12.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>10.23</v>
+        <v>11.03</v>
       </c>
       <c r="S14" t="n">
-        <v>6.43</v>
+        <v>8.69</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.52</v>
+        <v>-5.37</v>
       </c>
       <c r="U14" t="n">
-        <v>-16.24</v>
+        <v>-14.87</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.36</v>
+        <v>-1.67</v>
       </c>
       <c r="W14" t="n">
         <v>33.95</v>
@@ -2676,13 +2676,13 @@
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.2583</v>
+        <v>24.1953</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9651</v>
+        <v>26.9741</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2691,19 +2691,19 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AE14" t="n">
-        <v>49.8</v>
+        <v>55.2</v>
       </c>
       <c r="AF14" t="n">
         <v>20.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>56.2</v>
+        <v>50.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AI14" t="n">
         <v>23.01</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>9.51</v>
+        <v>12.13</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.48</v>
+        <v>0.58</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 37.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 42.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.1%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,18 +660,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70.48</v>
+        <v>69.09</v>
       </c>
       <c r="F2" t="n">
-        <v>79.2</v>
+        <v>80.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>52.5</v>
+        <v>63.2</v>
       </c>
       <c r="L2" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 11.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>8.5</v>
+        <v>4.19</v>
       </c>
       <c r="S2" t="n">
-        <v>24.52</v>
+        <v>24.76</v>
       </c>
       <c r="T2" t="n">
-        <v>37.87</v>
+        <v>34.84</v>
       </c>
       <c r="U2" t="n">
-        <v>61.12</v>
+        <v>57.81</v>
       </c>
       <c r="V2" t="n">
-        <v>25.67</v>
+        <v>24.71</v>
       </c>
       <c r="W2" t="n">
-        <v>13.62</v>
+        <v>13.67</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.1764</v>
+        <v>63.4452</v>
       </c>
       <c r="AA2" t="n">
-        <v>54.7527</v>
+        <v>54.864</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -756,13 +756,13 @@
         <v>69.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>52.5</v>
+        <v>63.2</v>
       </c>
       <c r="AH2" t="n">
         <v>755</v>
       </c>
       <c r="AI2" t="n">
-        <v>65.25</v>
+        <v>65.27</v>
       </c>
       <c r="AJ2" t="n">
         <v>54.81</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>11.56</v>
+        <v>8.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.72</v>
+        <v>25.93</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.6%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.9%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>46.46</v>
+        <v>46.1</v>
       </c>
       <c r="F3" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>68.3</v>
+        <v>68</v>
       </c>
       <c r="I3" t="n">
-        <v>93.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>65.5</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>79.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-1.25</v>
+        <v>-2.35</v>
       </c>
       <c r="S3" t="n">
-        <v>13.84</v>
+        <v>13.24</v>
       </c>
       <c r="T3" t="n">
-        <v>22.36</v>
+        <v>21.78</v>
       </c>
       <c r="U3" t="n">
-        <v>41.41</v>
+        <v>39.36</v>
       </c>
       <c r="V3" t="n">
-        <v>17.92</v>
+        <v>17.62</v>
       </c>
       <c r="W3" t="n">
-        <v>15.99</v>
+        <v>16</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.7763</v>
+        <v>44.9036</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.3085</v>
+        <v>40.3641</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>93.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AF3" t="n">
         <v>65.5</v>
@@ -936,14 +936,14 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.76</v>
+        <v>2.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.26</v>
+        <v>14.21</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161.56</v>
+        <v>159.5</v>
       </c>
       <c r="F4" t="n">
-        <v>75.8</v>
+        <v>75.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>75.8</v>
+        <v>74.5</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
       </c>
       <c r="K4" t="n">
-        <v>82</v>
+        <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2.16</v>
+        <v>0.55</v>
       </c>
       <c r="S4" t="n">
-        <v>8.91</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>11.96</v>
+        <v>10.56</v>
       </c>
       <c r="U4" t="n">
-        <v>24.58</v>
+        <v>22.52</v>
       </c>
       <c r="V4" t="n">
-        <v>17.2</v>
+        <v>16.62</v>
       </c>
       <c r="W4" t="n">
-        <v>12.87</v>
+        <v>12.89</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.0524</v>
+        <v>155.3832</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.6353</v>
+        <v>146.7537</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>75.8</v>
+        <v>74.5</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>82</v>
+        <v>82.8</v>
       </c>
       <c r="AH4" t="n">
         <v>758</v>
       </c>
       <c r="AI4" t="n">
-        <v>156.96</v>
+        <v>158.2</v>
       </c>
       <c r="AJ4" t="n">
         <v>140.98</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.18</v>
+        <v>8.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.67</v>
+        <v>120.88</v>
       </c>
       <c r="F5" t="n">
-        <v>74.8</v>
+        <v>74.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="I5" t="n">
-        <v>73.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>81.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>75.2</v>
+        <v>75</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.64</v>
+        <v>0.78</v>
       </c>
       <c r="S5" t="n">
-        <v>8.32</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>10.51</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>22.61</v>
+        <v>20.67</v>
       </c>
       <c r="V5" t="n">
-        <v>17.19</v>
+        <v>16.52</v>
       </c>
       <c r="W5" t="n">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.7098</v>
+        <v>117.9476</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.1115</v>
+        <v>112.1922</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,19 +1236,19 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>73.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>81.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AH5" t="n">
         <v>755</v>
       </c>
       <c r="AI5" t="n">
-        <v>119.18</v>
+        <v>120.3</v>
       </c>
       <c r="AJ5" t="n">
         <v>107.5</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.21</v>
+        <v>2.49</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.42</v>
+        <v>7.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,30 +1308,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>693.26</v>
+        <v>682.52</v>
       </c>
       <c r="F6" t="n">
+        <v>74</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="I6" t="n">
         <v>74.09999999999999</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Accumulate Carefully</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>75.7</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>79.2</v>
+        <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>74.2</v>
+        <v>74.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.74</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>9.630000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="T6" t="n">
-        <v>10.25</v>
+        <v>8.56</v>
       </c>
       <c r="U6" t="n">
-        <v>24.2</v>
+        <v>21.85</v>
       </c>
       <c r="V6" t="n">
-        <v>18.46</v>
+        <v>17.74</v>
       </c>
       <c r="W6" t="n">
-        <v>14.1</v>
+        <v>14.13</v>
       </c>
       <c r="X6" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>660.9632</v>
+        <v>662.4696</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.4737</v>
+        <v>629.9450000000001</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,19 +1398,19 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>75.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>79.2</v>
+        <v>82.8</v>
       </c>
       <c r="AH6" t="n">
         <v>758</v>
       </c>
       <c r="AI6" t="n">
-        <v>673.5</v>
+        <v>680.66</v>
       </c>
       <c r="AJ6" t="n">
         <v>597.92</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.89</v>
+        <v>3.03</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.13</v>
+        <v>8.35</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.9%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.55</v>
+        <v>62.22</v>
       </c>
       <c r="F7" t="n">
-        <v>73.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>69.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>67.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.04</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>5.56</v>
+        <v>5.73</v>
       </c>
       <c r="T7" t="n">
-        <v>10.14</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>15.11</v>
+        <v>14.64</v>
       </c>
       <c r="V7" t="n">
-        <v>13.64</v>
+        <v>13.41</v>
       </c>
       <c r="W7" t="n">
-        <v>12.85</v>
+        <v>12.86</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.2392</v>
+        <v>61.3322</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.5426</v>
+        <v>58.5784</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>67.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1572,7 +1572,7 @@
         <v>759</v>
       </c>
       <c r="AI7" t="n">
-        <v>60.74</v>
+        <v>60.81</v>
       </c>
       <c r="AJ7" t="n">
         <v>56.7</v>
@@ -1584,14 +1584,14 @@
         <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.85</v>
+        <v>6.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.45999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="F8" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1679,38 +1679,38 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="S8" t="n">
-        <v>5.92</v>
+        <v>6.72</v>
       </c>
       <c r="T8" t="n">
-        <v>9.890000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="U8" t="n">
-        <v>18.32</v>
+        <v>17.27</v>
       </c>
       <c r="V8" t="n">
-        <v>15.15</v>
+        <v>14.75</v>
       </c>
       <c r="W8" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.77119999999999</v>
+        <v>71.8984</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.6544</v>
+        <v>68.7026</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1734,7 +1734,7 @@
         <v>755</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.11</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>66.58</v>
@@ -1746,14 +1746,14 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.460000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.616</v>
+        <v>17.234</v>
       </c>
       <c r="F9" t="n">
-        <v>68.8</v>
+        <v>70.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>60.6</v>
+        <v>72.2</v>
       </c>
       <c r="L9" t="n">
-        <v>64.2</v>
+        <v>72.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1841,38 +1841,38 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>-1.67</v>
       </c>
       <c r="S9" t="n">
-        <v>24.71</v>
+        <v>25.61</v>
       </c>
       <c r="T9" t="n">
-        <v>27.26</v>
+        <v>23.61</v>
       </c>
       <c r="U9" t="n">
-        <v>40.12</v>
+        <v>36.41</v>
       </c>
       <c r="V9" t="n">
-        <v>17.74</v>
+        <v>16.46</v>
       </c>
       <c r="W9" t="n">
-        <v>21.34</v>
+        <v>21.37</v>
       </c>
       <c r="X9" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.083</v>
+        <v>16.1597</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4439</v>
+        <v>14.4649</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>60.6</v>
+        <v>72.2</v>
       </c>
       <c r="AH9" t="n">
         <v>755</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>9.529999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.96</v>
+        <v>19.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.7%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.99</v>
+        <v>63.71</v>
       </c>
       <c r="F10" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>61.5</v>
+        <v>61.3</v>
       </c>
       <c r="I10" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="J10" t="n">
         <v>78.2</v>
@@ -1979,7 +1979,7 @@
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>70.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,19 +2007,19 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.83</v>
+        <v>-2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="V10" t="n">
-        <v>6.72</v>
+        <v>6.61</v>
       </c>
       <c r="W10" t="n">
         <v>9.56</v>
@@ -2028,13 +2028,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.3138</v>
+        <v>63.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.0971</v>
+        <v>63.1002</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="AF10" t="n">
         <v>78.2</v>
@@ -2070,14 +2070,14 @@
         <v>65.28</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.07</v>
+        <v>0.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.42</v>
+        <v>0.97</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.1%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,14 +2114,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.584</v>
+        <v>570.91</v>
       </c>
       <c r="F11" t="n">
-        <v>64.2</v>
+        <v>65.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31.2</v>
+        <v>56.5</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>31.8</v>
+        <v>24.5</v>
       </c>
       <c r="K11" t="n">
-        <v>81.7</v>
+        <v>59.4</v>
       </c>
       <c r="L11" t="n">
-        <v>57.8</v>
+        <v>46.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 9.8% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>3.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>20.32</v>
+        <v>42.36</v>
       </c>
       <c r="T11" t="n">
-        <v>29.65</v>
+        <v>55.39</v>
       </c>
       <c r="U11" t="n">
-        <v>66.09999999999999</v>
+        <v>122.87</v>
       </c>
       <c r="V11" t="n">
-        <v>3.3</v>
+        <v>56.8</v>
       </c>
       <c r="W11" t="n">
-        <v>23.18</v>
+        <v>34.93</v>
       </c>
       <c r="X11" t="n">
-        <v>-44.26</v>
+        <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.1519</v>
+        <v>519.7898</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.738899999999999</v>
+        <v>400.714</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,45 +2211,45 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>36.8</v>
+        <v>29.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>81.7</v>
+        <v>59.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="AI11" t="n">
-        <v>10.2879</v>
+        <v>543.96</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8.7643</v>
+        <v>362.53</v>
       </c>
       <c r="AK11" t="n">
-        <v>11.61</v>
+        <v>637.9</v>
       </c>
       <c r="AL11" t="n">
-        <v>11.61</v>
+        <v>637.9</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.26</v>
+        <v>9.83</v>
       </c>
       <c r="AN11" t="n">
-        <v>21.11</v>
+        <v>42.47</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 65.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.8%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>591.01</v>
+        <v>10.182</v>
       </c>
       <c r="F12" t="n">
-        <v>63.1</v>
+        <v>64</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>57.5</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>24.5</v>
+        <v>31.7</v>
       </c>
       <c r="K12" t="n">
-        <v>40.3</v>
+        <v>82.8</v>
       </c>
       <c r="L12" t="n">
-        <v>32.2</v>
+        <v>58</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 14.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4.32</v>
+        <v>-4.83</v>
       </c>
       <c r="S12" t="n">
-        <v>48.75</v>
+        <v>15.96</v>
       </c>
       <c r="T12" t="n">
-        <v>62.68</v>
+        <v>24.37</v>
       </c>
       <c r="U12" t="n">
-        <v>134.58</v>
+        <v>60.29</v>
       </c>
       <c r="V12" t="n">
-        <v>58.73</v>
+        <v>1.75</v>
       </c>
       <c r="W12" t="n">
-        <v>34.89</v>
+        <v>23.28</v>
       </c>
       <c r="X12" t="n">
-        <v>-35.74</v>
+        <v>-44.26</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.68</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>515.6222</v>
+        <v>10.1739</v>
       </c>
       <c r="AA12" t="n">
-        <v>399.3231</v>
+        <v>8.7546</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2373,45 +2373,45 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>29.5</v>
+        <v>36.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>40.3</v>
+        <v>82.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AI12" t="n">
-        <v>543.96</v>
+        <v>10.182</v>
       </c>
       <c r="AJ12" t="n">
-        <v>362.53</v>
+        <v>8.7643</v>
       </c>
       <c r="AK12" t="n">
-        <v>637.9</v>
+        <v>11.61</v>
       </c>
       <c r="AL12" t="n">
-        <v>637.9</v>
+        <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>14.62</v>
+        <v>0.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>48</v>
+        <v>16.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.6%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.1%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>361.39</v>
+        <v>355.79</v>
       </c>
       <c r="F13" t="n">
-        <v>55.7</v>
+        <v>54.1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="I13" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="J13" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="K13" t="n">
-        <v>67.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>57.5</v>
+        <v>55.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,43 +2484,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 5.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.18</v>
+        <v>-7.96</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.19</v>
+        <v>-16</v>
       </c>
       <c r="T13" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
-        <v>27.05</v>
+        <v>25.87</v>
       </c>
       <c r="V13" t="n">
-        <v>27.08</v>
+        <v>26.54</v>
       </c>
       <c r="W13" t="n">
-        <v>17.79</v>
+        <v>17.81</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.19</v>
+        <v>-18.47</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.915</v>
+        <v>380.7012</v>
       </c>
       <c r="AA13" t="n">
-        <v>361.74</v>
+        <v>362.1462</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,48 +2532,48 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AH13" t="n">
         <v>755</v>
       </c>
       <c r="AI13" t="n">
-        <v>361.39</v>
+        <v>355.79</v>
       </c>
       <c r="AJ13" t="n">
-        <v>361.39</v>
+        <v>355.79</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
       </c>
       <c r="AL13" t="n">
-        <v>428.69</v>
+        <v>424.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.13</v>
+        <v>-6.54</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.1</v>
+        <v>-1.76</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.1%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 428.69 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 424.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 361.39 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 355.79 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27.13</v>
+        <v>26.22</v>
       </c>
       <c r="F14" t="n">
-        <v>42.8</v>
+        <v>37.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,28 +2615,28 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="I14" t="n">
-        <v>55.2</v>
+        <v>46.9</v>
       </c>
       <c r="J14" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="K14" t="n">
-        <v>50.2</v>
+        <v>61.8</v>
       </c>
       <c r="L14" t="n">
-        <v>21.9</v>
+        <v>28.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 12.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>11.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>8.69</v>
+        <v>5.05</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.37</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-14.87</v>
+        <v>-17.33</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.67</v>
+        <v>-3.14</v>
       </c>
       <c r="W14" t="n">
-        <v>33.95</v>
+        <v>34</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.1953</v>
+        <v>24.2514</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9741</v>
+        <v>26.9634</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2691,16 +2691,16 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>55.2</v>
+        <v>46.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>50.2</v>
+        <v>61.8</v>
       </c>
       <c r="AH14" t="n">
         <v>756</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>12.13</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.58</v>
+        <v>-2.76</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 42.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.1%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 37.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.09</v>
+        <v>68.89</v>
       </c>
       <c r="F2" t="n">
-        <v>80.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>63.2</v>
+        <v>66.3</v>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -702,43 +702,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 8.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>4.19</v>
+        <v>5.58</v>
       </c>
       <c r="S2" t="n">
-        <v>24.76</v>
+        <v>21.52</v>
       </c>
       <c r="T2" t="n">
-        <v>34.84</v>
+        <v>34.16</v>
       </c>
       <c r="U2" t="n">
-        <v>57.81</v>
+        <v>56.02</v>
       </c>
       <c r="V2" t="n">
-        <v>24.71</v>
+        <v>24.56</v>
       </c>
       <c r="W2" t="n">
-        <v>13.67</v>
+        <v>13.66</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.4452</v>
+        <v>63.7216</v>
       </c>
       <c r="AA2" t="n">
-        <v>54.864</v>
+        <v>54.9753</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>63.2</v>
+        <v>66.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI2" t="n">
         <v>65.27</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.9</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.93</v>
+        <v>25.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,21 +822,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>46.1</v>
+        <v>45.945</v>
       </c>
       <c r="F3" t="n">
-        <v>78.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>68</v>
+        <v>67.8</v>
       </c>
       <c r="I3" t="n">
-        <v>91.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="J3" t="n">
         <v>65.5</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>79.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,38 +873,38 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-2.35</v>
+        <v>0.89</v>
       </c>
       <c r="S3" t="n">
-        <v>13.24</v>
+        <v>10.31</v>
       </c>
       <c r="T3" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="U3" t="n">
-        <v>39.36</v>
+        <v>38.53</v>
       </c>
       <c r="V3" t="n">
-        <v>17.62</v>
+        <v>17.46</v>
       </c>
       <c r="W3" t="n">
-        <v>16</v>
+        <v>15.99</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.9036</v>
+        <v>45.0355</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.3641</v>
+        <v>40.42</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>91.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="AF3" t="n">
         <v>65.5</v>
@@ -921,7 +921,7 @@
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI3" t="n">
         <v>44.985</v>
@@ -936,14 +936,14 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.66</v>
+        <v>2.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.21</v>
+        <v>13.67</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>159.5</v>
+        <v>159.24</v>
       </c>
       <c r="F4" t="n">
-        <v>75.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="I4" t="n">
         <v>71.90000000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>74.5</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.55</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>8.949999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="T4" t="n">
-        <v>10.56</v>
+        <v>10.45</v>
       </c>
       <c r="U4" t="n">
-        <v>22.52</v>
+        <v>22.23</v>
       </c>
       <c r="V4" t="n">
-        <v>16.62</v>
+        <v>16.53</v>
       </c>
       <c r="W4" t="n">
         <v>12.89</v>
@@ -1056,13 +1056,13 @@
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.3832</v>
+        <v>155.7484</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.7537</v>
+        <v>146.8745</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>74.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
@@ -1083,7 +1083,7 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI4" t="n">
         <v>158.2</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.69</v>
+        <v>8.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>120.88</v>
+        <v>120.73</v>
       </c>
       <c r="F5" t="n">
-        <v>74.3</v>
+        <v>73.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>70.8</v>
       </c>
       <c r="I5" t="n">
-        <v>72.2</v>
+        <v>69.8</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.78</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>8.390000000000001</v>
+        <v>6.83</v>
       </c>
       <c r="T5" t="n">
-        <v>8.859999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="U5" t="n">
-        <v>20.67</v>
+        <v>20.14</v>
       </c>
       <c r="V5" t="n">
-        <v>16.52</v>
+        <v>16.45</v>
       </c>
       <c r="W5" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
@@ -1221,10 +1221,10 @@
         <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.9476</v>
+        <v>118.2122</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.1922</v>
+        <v>112.2751</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>72.2</v>
+        <v>69.8</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,7 +1245,7 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI5" t="n">
         <v>120.3</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.74</v>
+        <v>7.53</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>682.52</v>
+        <v>681.7</v>
       </c>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>73.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="I6" t="n">
-        <v>74.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>74.8</v>
+        <v>74.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>9.66</v>
+        <v>8.41</v>
       </c>
       <c r="T6" t="n">
-        <v>8.56</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>21.85</v>
+        <v>21.66</v>
       </c>
       <c r="V6" t="n">
-        <v>17.74</v>
+        <v>17.67</v>
       </c>
       <c r="W6" t="n">
-        <v>14.13</v>
+        <v>14.12</v>
       </c>
       <c r="X6" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>662.4696</v>
+        <v>664.1452</v>
       </c>
       <c r="AA6" t="n">
-        <v>629.9450000000001</v>
+        <v>630.4322</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>74.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
@@ -1407,10 +1407,10 @@
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI6" t="n">
-        <v>680.66</v>
+        <v>680.9400000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>597.92</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.03</v>
+        <v>2.64</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.35</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.22</v>
+        <v>62.16</v>
       </c>
       <c r="F7" t="n">
-        <v>73.7</v>
+        <v>72.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>67.3</v>
+        <v>63.9</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>74.7</v>
+        <v>73.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,22 +1521,22 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>2.34</v>
       </c>
       <c r="S7" t="n">
-        <v>5.73</v>
+        <v>3.59</v>
       </c>
       <c r="T7" t="n">
-        <v>9.390000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="U7" t="n">
-        <v>14.64</v>
+        <v>14.49</v>
       </c>
       <c r="V7" t="n">
-        <v>13.41</v>
+        <v>13.35</v>
       </c>
       <c r="W7" t="n">
-        <v>12.86</v>
+        <v>12.85</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
@@ -1545,10 +1545,10 @@
         <v>1.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.3322</v>
+        <v>61.4344</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.5784</v>
+        <v>58.6138</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>67.3</v>
+        <v>63.9</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1569,7 +1569,7 @@
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AI7" t="n">
         <v>60.81</v>
@@ -1584,14 +1584,14 @@
         <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.22</v>
+        <v>6.05</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.4%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.2%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73.8</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>72.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>69.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>73.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="S8" t="n">
-        <v>6.72</v>
+        <v>5.73</v>
       </c>
       <c r="T8" t="n">
-        <v>8.98</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>17.27</v>
+        <v>17.05</v>
       </c>
       <c r="V8" t="n">
-        <v>14.75</v>
+        <v>14.84</v>
       </c>
       <c r="W8" t="n">
         <v>12.88</v>
@@ -1707,10 +1707,10 @@
         <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.8984</v>
+        <v>72.047</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.7026</v>
+        <v>68.7529</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1731,10 +1731,10 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.94</v>
       </c>
       <c r="AJ8" t="n">
         <v>66.58</v>
@@ -1746,14 +1746,14 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.42</v>
+        <v>7.65</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.234</v>
+        <v>17.092</v>
       </c>
       <c r="F9" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>72.2</v>
+        <v>77.8</v>
       </c>
       <c r="L9" t="n">
-        <v>72.3</v>
+        <v>74</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,34 +1845,34 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-1.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>25.61</v>
+        <v>20.67</v>
       </c>
       <c r="T9" t="n">
-        <v>23.61</v>
+        <v>21.76</v>
       </c>
       <c r="U9" t="n">
-        <v>36.41</v>
+        <v>34.73</v>
       </c>
       <c r="V9" t="n">
-        <v>16.46</v>
+        <v>16.12</v>
       </c>
       <c r="W9" t="n">
-        <v>21.37</v>
+        <v>21.36</v>
       </c>
       <c r="X9" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1597</v>
+        <v>16.2409</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4649</v>
+        <v>14.4862</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>72.2</v>
+        <v>77.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI9" t="n">
         <v>16.544</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>6.65</v>
+        <v>5.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.14</v>
+        <v>17.99</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.7%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.71</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>61.3</v>
+        <v>61.9</v>
       </c>
       <c r="I10" t="n">
-        <v>48.1</v>
+        <v>49.9</v>
       </c>
       <c r="J10" t="n">
         <v>78.2</v>
@@ -1979,7 +1979,7 @@
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>70.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2003,23 +2003,23 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="S10" t="n">
-        <v>-2</v>
+        <v>-1.26</v>
       </c>
       <c r="T10" t="n">
-        <v>1.47</v>
+        <v>2.57</v>
       </c>
       <c r="U10" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="V10" t="n">
-        <v>6.61</v>
+        <v>6.86</v>
       </c>
       <c r="W10" t="n">
         <v>9.56</v>
@@ -2028,13 +2028,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.32</v>
+        <v>63.3432</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.1002</v>
+        <v>63.1035</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>48.1</v>
+        <v>49.9</v>
       </c>
       <c r="AF10" t="n">
         <v>78.2</v>
@@ -2055,10 +2055,10 @@
         <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI10" t="n">
-        <v>62.34</v>
+        <v>63.28</v>
       </c>
       <c r="AJ10" t="n">
         <v>62.06</v>
@@ -2067,22 +2067,22 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AL10" t="n">
-        <v>65.28</v>
+        <v>65.25</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.62</v>
+        <v>1.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.97</v>
+        <v>1.71</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.6%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.3%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.25 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>570.91</v>
+        <v>609.45</v>
       </c>
       <c r="F11" t="n">
-        <v>65.7</v>
+        <v>62.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>56.5</v>
+        <v>57.9</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="K11" t="n">
-        <v>59.4</v>
+        <v>33.8</v>
       </c>
       <c r="L11" t="n">
-        <v>46.7</v>
+        <v>27.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 9.8% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 16.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-0.9399999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="S11" t="n">
-        <v>42.36</v>
+        <v>57.02</v>
       </c>
       <c r="T11" t="n">
-        <v>55.39</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>122.87</v>
+        <v>133.28</v>
       </c>
       <c r="V11" t="n">
-        <v>56.8</v>
+        <v>60.17</v>
       </c>
       <c r="W11" t="n">
-        <v>34.93</v>
+        <v>35.11</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="Z11" t="n">
-        <v>519.7898</v>
+        <v>524.3108</v>
       </c>
       <c r="AA11" t="n">
-        <v>400.714</v>
+        <v>402.2962</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,13 +2211,13 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>59.4</v>
+        <v>33.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AI11" t="n">
         <v>543.96</v>
@@ -2232,14 +2232,14 @@
         <v>637.9</v>
       </c>
       <c r="AM11" t="n">
-        <v>9.83</v>
+        <v>16.24</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.47</v>
+        <v>51.49</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 65.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.8%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 62.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.2%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.182</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>64</v>
+        <v>57.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,23 +2291,23 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>29.3</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="J12" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="K12" t="n">
-        <v>82.8</v>
+        <v>75.7</v>
       </c>
       <c r="L12" t="n">
-        <v>58</v>
+        <v>51.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2331,34 +2331,34 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-4.83</v>
+        <v>-4.35</v>
       </c>
       <c r="S12" t="n">
-        <v>15.96</v>
+        <v>9.43</v>
       </c>
       <c r="T12" t="n">
-        <v>24.37</v>
+        <v>22.25</v>
       </c>
       <c r="U12" t="n">
-        <v>60.29</v>
+        <v>54.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.75</v>
+        <v>0.85</v>
       </c>
       <c r="W12" t="n">
-        <v>23.28</v>
+        <v>23.32</v>
       </c>
       <c r="X12" t="n">
         <v>-44.26</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.1739</v>
+        <v>10.1931</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.7546</v>
+        <v>8.769</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2367,22 +2367,22 @@
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>82.8</v>
+        <v>75.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI12" t="n">
-        <v>10.182</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AJ12" t="n">
         <v>8.7643</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.08</v>
+        <v>-2.73</v>
       </c>
       <c r="AN12" t="n">
-        <v>16.3</v>
+        <v>13.07</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.1%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 57.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>355.79</v>
+        <v>343.71</v>
       </c>
       <c r="F13" t="n">
-        <v>54.1</v>
+        <v>49.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>69.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>35.6</v>
+        <v>26</v>
       </c>
       <c r="J13" t="n">
-        <v>63.9</v>
+        <v>61.5</v>
       </c>
       <c r="K13" t="n">
-        <v>65.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="L13" t="n">
-        <v>55.6</v>
+        <v>50.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-7.96</v>
+        <v>-10.14</v>
       </c>
       <c r="S13" t="n">
-        <v>-16</v>
+        <v>-20.47</v>
       </c>
       <c r="T13" t="n">
-        <v>2.55</v>
+        <v>-1.43</v>
       </c>
       <c r="U13" t="n">
-        <v>25.87</v>
+        <v>21.99</v>
       </c>
       <c r="V13" t="n">
-        <v>26.54</v>
+        <v>25.05</v>
       </c>
       <c r="W13" t="n">
-        <v>17.81</v>
+        <v>17.91</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.47</v>
+        <v>-21.24</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.7012</v>
+        <v>380.0256</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.1462</v>
+        <v>362.4847</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,48 +2532,48 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>35.6</v>
+        <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>63.9</v>
+        <v>61.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>65.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="AH13" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>355.79</v>
+        <v>343.71</v>
       </c>
       <c r="AJ13" t="n">
-        <v>355.79</v>
+        <v>343.71</v>
       </c>
       <c r="AK13" t="n">
         <v>386.38</v>
       </c>
       <c r="AL13" t="n">
-        <v>424.57</v>
+        <v>417.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>-6.54</v>
+        <v>-9.56</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1.76</v>
+        <v>-5.18</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 49.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.6%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 424.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 417.50 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 355.79 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 343.71 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.22</v>
+        <v>26.52</v>
       </c>
       <c r="F14" t="n">
-        <v>37.8</v>
+        <v>38.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="I14" t="n">
-        <v>46.9</v>
+        <v>51.8</v>
       </c>
       <c r="J14" t="n">
         <v>15.3</v>
       </c>
       <c r="K14" t="n">
-        <v>61.8</v>
+        <v>58.3</v>
       </c>
       <c r="L14" t="n">
-        <v>28.5</v>
+        <v>27.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.0% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>8.800000000000001</v>
+        <v>11.29</v>
       </c>
       <c r="S14" t="n">
-        <v>5.05</v>
+        <v>7.98</v>
       </c>
       <c r="T14" t="n">
-        <v>-9.710000000000001</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-17.33</v>
+        <v>-16.09</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.14</v>
+        <v>-2.77</v>
       </c>
       <c r="W14" t="n">
-        <v>34</v>
+        <v>33.98</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.2514</v>
+        <v>24.3314</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9634</v>
+        <v>26.9534</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,19 +2694,19 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>46.9</v>
+        <v>51.8</v>
       </c>
       <c r="AF14" t="n">
         <v>20.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>61.8</v>
+        <v>58.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI14" t="n">
-        <v>23.01</v>
+        <v>23.625</v>
       </c>
       <c r="AJ14" t="n">
         <v>20.205</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.119999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="AN14" t="n">
-        <v>-2.76</v>
+        <v>-1.61</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 37.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 38.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.89</v>
+        <v>69.23</v>
       </c>
       <c r="F2" t="n">
         <v>80.90000000000001</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>66.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -707,23 +707,23 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>5.58</v>
+        <v>4.03</v>
       </c>
       <c r="S2" t="n">
-        <v>21.52</v>
+        <v>22.4</v>
       </c>
       <c r="T2" t="n">
-        <v>34.16</v>
+        <v>34.19</v>
       </c>
       <c r="U2" t="n">
-        <v>56.02</v>
+        <v>56.7</v>
       </c>
       <c r="V2" t="n">
-        <v>24.56</v>
+        <v>24.72</v>
       </c>
       <c r="W2" t="n">
         <v>13.66</v>
@@ -732,13 +732,13 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.7216</v>
+        <v>64.0026</v>
       </c>
       <c r="AA2" t="n">
-        <v>54.9753</v>
+        <v>55.0882</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>66.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI2" t="n">
         <v>65.27</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.109999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.31</v>
+        <v>25.67</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.2%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>45.945</v>
+        <v>46.425</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>67.8</v>
+        <v>68.3</v>
       </c>
       <c r="I3" t="n">
-        <v>87.2</v>
+        <v>90.2</v>
       </c>
       <c r="J3" t="n">
         <v>65.5</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>78.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.89</v>
+        <v>-0.78</v>
       </c>
       <c r="S3" t="n">
-        <v>10.31</v>
+        <v>12.08</v>
       </c>
       <c r="T3" t="n">
-        <v>21.82</v>
+        <v>22.72</v>
       </c>
       <c r="U3" t="n">
-        <v>38.53</v>
+        <v>38.75</v>
       </c>
       <c r="V3" t="n">
-        <v>17.46</v>
+        <v>17.84</v>
       </c>
       <c r="W3" t="n">
         <v>15.99</v>
@@ -894,13 +894,13 @@
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>45.0355</v>
+        <v>45.1736</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.42</v>
+        <v>40.4772</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>87.2</v>
+        <v>90.2</v>
       </c>
       <c r="AF3" t="n">
         <v>65.5</v>
@@ -921,7 +921,7 @@
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI3" t="n">
         <v>44.985</v>
@@ -936,14 +936,14 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="AN3" t="n">
-        <v>13.67</v>
+        <v>14.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 77.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>159.24</v>
+        <v>159.56</v>
       </c>
       <c r="F4" t="n">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="J4" t="n">
         <v>67.7</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>0.26</v>
       </c>
       <c r="S4" t="n">
-        <v>7.2</v>
+        <v>7.81</v>
       </c>
       <c r="T4" t="n">
-        <v>10.45</v>
+        <v>10.39</v>
       </c>
       <c r="U4" t="n">
-        <v>22.23</v>
+        <v>22.46</v>
       </c>
       <c r="V4" t="n">
-        <v>16.53</v>
+        <v>16.59</v>
       </c>
       <c r="W4" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.7484</v>
+        <v>156.1016</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.8745</v>
+        <v>146.9946</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AF4" t="n">
         <v>67.7</v>
@@ -1083,7 +1083,7 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AI4" t="n">
         <v>158.2</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.42</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>120.73</v>
+        <v>120.89</v>
       </c>
       <c r="F5" t="n">
-        <v>73.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>70.8</v>
       </c>
       <c r="I5" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>0.38</v>
       </c>
       <c r="S5" t="n">
-        <v>6.83</v>
+        <v>7.35</v>
       </c>
       <c r="T5" t="n">
-        <v>8.74</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>20.14</v>
+        <v>20.35</v>
       </c>
       <c r="V5" t="n">
-        <v>16.45</v>
+        <v>16.48</v>
       </c>
       <c r="W5" t="n">
-        <v>13.16</v>
+        <v>13.15</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
@@ -1221,10 +1221,10 @@
         <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>118.2122</v>
+        <v>118.4654</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.2751</v>
+        <v>112.3568</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,7 +1245,7 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI5" t="n">
         <v>120.3</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.53</v>
+        <v>7.59</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>681.7</v>
+        <v>62.56</v>
       </c>
       <c r="F6" t="n">
-        <v>73.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>72.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K6" t="n">
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>74.3</v>
+        <v>74.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="S6" t="n">
-        <v>8.41</v>
+        <v>4.85</v>
       </c>
       <c r="T6" t="n">
-        <v>8.460000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>21.66</v>
+        <v>15.52</v>
       </c>
       <c r="V6" t="n">
-        <v>17.67</v>
+        <v>13.58</v>
       </c>
       <c r="W6" t="n">
-        <v>14.12</v>
+        <v>12.85</v>
       </c>
       <c r="X6" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>664.1452</v>
+        <v>61.5328</v>
       </c>
       <c r="AA6" t="n">
-        <v>630.4322</v>
+        <v>58.6502</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>72.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AG6" t="n">
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AI6" t="n">
-        <v>680.9400000000001</v>
+        <v>60.81</v>
       </c>
       <c r="AJ6" t="n">
-        <v>597.92</v>
+        <v>56.7</v>
       </c>
       <c r="AK6" t="n">
-        <v>703.9400000000001</v>
+        <v>63.94</v>
       </c>
       <c r="AL6" t="n">
-        <v>703.9400000000001</v>
+        <v>63.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.64</v>
+        <v>1.67</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.130000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.7%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,14 +1466,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.16</v>
+        <v>681.24</v>
       </c>
       <c r="F7" t="n">
-        <v>72.8</v>
+        <v>73.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>69.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I7" t="n">
-        <v>63.9</v>
+        <v>72.2</v>
       </c>
       <c r="J7" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>73.8</v>
+        <v>74.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.34</v>
+        <v>0.09</v>
       </c>
       <c r="S7" t="n">
-        <v>3.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>8.83</v>
+        <v>8.32</v>
       </c>
       <c r="U7" t="n">
-        <v>14.49</v>
+        <v>21.44</v>
       </c>
       <c r="V7" t="n">
-        <v>13.35</v>
+        <v>17.62</v>
       </c>
       <c r="W7" t="n">
-        <v>12.85</v>
+        <v>14.11</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.4344</v>
+        <v>665.7612</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.6138</v>
+        <v>630.9031</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>63.9</v>
+        <v>72.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
@@ -1572,36 +1572,36 @@
         <v>760</v>
       </c>
       <c r="AI7" t="n">
-        <v>60.81</v>
+        <v>680.9400000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>56.7</v>
+        <v>597.92</v>
       </c>
       <c r="AK7" t="n">
-        <v>63.94</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AL7" t="n">
-        <v>63.94</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.18</v>
+        <v>2.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.05</v>
+        <v>7.98</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.2%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.01000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="F8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>64.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>67.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,38 +1679,38 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="S8" t="n">
-        <v>5.73</v>
+        <v>6.66</v>
       </c>
       <c r="T8" t="n">
-        <v>9.130000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="U8" t="n">
-        <v>17.05</v>
+        <v>17.86</v>
       </c>
       <c r="V8" t="n">
-        <v>14.84</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.047</v>
+        <v>72.1952</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.7529</v>
+        <v>68.804</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>67.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1731,7 +1731,7 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI8" t="n">
         <v>72.94</v>
@@ -1746,14 +1746,14 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.65</v>
+        <v>8.08</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.092</v>
+        <v>17.272</v>
       </c>
       <c r="F9" t="n">
-        <v>71</v>
+        <v>70.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1814,10 +1814,10 @@
         <v>45.9</v>
       </c>
       <c r="K9" t="n">
-        <v>77.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,34 +1845,34 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="S9" t="n">
-        <v>20.67</v>
+        <v>22.78</v>
       </c>
       <c r="T9" t="n">
-        <v>21.76</v>
+        <v>21.69</v>
       </c>
       <c r="U9" t="n">
-        <v>34.73</v>
+        <v>35.7</v>
       </c>
       <c r="V9" t="n">
-        <v>16.12</v>
+        <v>16.5</v>
       </c>
       <c r="W9" t="n">
-        <v>21.36</v>
+        <v>21.35</v>
       </c>
       <c r="X9" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.2409</v>
+        <v>16.3266</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.4862</v>
+        <v>14.5083</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         <v>50.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AH9" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI9" t="n">
         <v>16.544</v>
@@ -1908,14 +1908,14 @@
         <v>18.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.24</v>
+        <v>5.79</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.99</v>
+        <v>19.05</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.2%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64.18000000000001</v>
+        <v>64.31</v>
       </c>
       <c r="F10" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>61.9</v>
       </c>
       <c r="I10" t="n">
-        <v>49.9</v>
+        <v>51.4</v>
       </c>
       <c r="J10" t="n">
         <v>78.2</v>
@@ -1979,7 +1979,7 @@
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,19 +2007,19 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.26</v>
+        <v>-0.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="U10" t="n">
-        <v>0.47</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>6.86</v>
+        <v>6.93</v>
       </c>
       <c r="W10" t="n">
         <v>9.56</v>
@@ -2031,10 +2031,10 @@
         <v>0.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.3432</v>
+        <v>63.3538</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.1035</v>
+        <v>63.1068</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>49.9</v>
+        <v>51.4</v>
       </c>
       <c r="AF10" t="n">
         <v>78.2</v>
@@ -2055,10 +2055,10 @@
         <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI10" t="n">
-        <v>63.28</v>
+        <v>63.37</v>
       </c>
       <c r="AJ10" t="n">
         <v>62.06</v>
@@ -2070,14 +2070,14 @@
         <v>65.25</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.3%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.5%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>609.45</v>
+        <v>619.96</v>
       </c>
       <c r="F11" t="n">
-        <v>62.2</v>
+        <v>61.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>57.9</v>
+        <v>58.1</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -2138,10 +2138,10 @@
         <v>24.3</v>
       </c>
       <c r="K11" t="n">
-        <v>33.8</v>
+        <v>29.9</v>
       </c>
       <c r="L11" t="n">
-        <v>27.2</v>
+        <v>24.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 16.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 17.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>8.59</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>57.02</v>
+        <v>60.06</v>
       </c>
       <c r="T11" t="n">
-        <v>65.68000000000001</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>133.28</v>
+        <v>137.47</v>
       </c>
       <c r="V11" t="n">
-        <v>60.17</v>
+        <v>60.35</v>
       </c>
       <c r="W11" t="n">
-        <v>35.11</v>
+        <v>35.12</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Z11" t="n">
-        <v>524.3108</v>
+        <v>528.8706</v>
       </c>
       <c r="AA11" t="n">
-        <v>402.2962</v>
+        <v>403.9168</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>29.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>33.8</v>
+        <v>29.9</v>
       </c>
       <c r="AH11" t="n">
         <v>753</v>
@@ -2232,14 +2232,14 @@
         <v>637.9</v>
       </c>
       <c r="AM11" t="n">
-        <v>16.24</v>
+        <v>17.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>51.49</v>
+        <v>53.49</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 62.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.2%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 61.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.2%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.914999999999999</v>
+        <v>10.082</v>
       </c>
       <c r="F12" t="n">
-        <v>57.3</v>
+        <v>58</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>29.3</v>
+        <v>29.7</v>
       </c>
       <c r="I12" t="n">
-        <v>90.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>31.6</v>
       </c>
       <c r="K12" t="n">
-        <v>75.7</v>
+        <v>77.8</v>
       </c>
       <c r="L12" t="n">
-        <v>51.7</v>
+        <v>52.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2331,19 +2331,19 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-4.35</v>
+        <v>-6.59</v>
       </c>
       <c r="S12" t="n">
-        <v>9.43</v>
+        <v>9.83</v>
       </c>
       <c r="T12" t="n">
-        <v>22.25</v>
+        <v>22.47</v>
       </c>
       <c r="U12" t="n">
-        <v>54.52</v>
+        <v>56.47</v>
       </c>
       <c r="V12" t="n">
-        <v>0.85</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
         <v>23.32</v>
@@ -2352,13 +2352,13 @@
         <v>-44.26</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.1931</v>
+        <v>10.2175</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.769</v>
+        <v>8.7845</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>90.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AF12" t="n">
         <v>36.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>75.7</v>
+        <v>77.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI12" t="n">
         <v>9.914999999999999</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-2.73</v>
+        <v>-1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>13.07</v>
+        <v>14.77</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 57.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 58.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.3%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>343.71</v>
+        <v>340.82</v>
       </c>
       <c r="F13" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>25.1</v>
       </c>
       <c r="J13" t="n">
-        <v>61.5</v>
+        <v>61</v>
       </c>
       <c r="K13" t="n">
-        <v>60.9</v>
+        <v>60.1</v>
       </c>
       <c r="L13" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 9.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-10.14</v>
+        <v>-11.65</v>
       </c>
       <c r="S13" t="n">
-        <v>-20.47</v>
+        <v>-20.7</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.43</v>
+        <v>-2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>21.99</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
-        <v>25.05</v>
+        <v>24.66</v>
       </c>
       <c r="W13" t="n">
         <v>17.91</v>
       </c>
       <c r="X13" t="n">
-        <v>-21.24</v>
+        <v>-21.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>380.0256</v>
+        <v>379.2068</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.4847</v>
+        <v>362.8027</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,38 +2532,38 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>26</v>
+        <v>25.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>61.5</v>
+        <v>61</v>
       </c>
       <c r="AG13" t="n">
-        <v>60.9</v>
+        <v>60.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI13" t="n">
-        <v>343.71</v>
+        <v>340.82</v>
       </c>
       <c r="AJ13" t="n">
-        <v>343.71</v>
+        <v>340.82</v>
       </c>
       <c r="AK13" t="n">
-        <v>386.38</v>
+        <v>377.9</v>
       </c>
       <c r="AL13" t="n">
         <v>417.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>-9.56</v>
+        <v>-10.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>-5.18</v>
+        <v>-6.06</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 49.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.6%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 49.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.1%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.71 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 340.82 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.52</v>
+        <v>25.95</v>
       </c>
       <c r="F14" t="n">
-        <v>38.5</v>
+        <v>39.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="I14" t="n">
-        <v>51.8</v>
+        <v>48.3</v>
       </c>
       <c r="J14" t="n">
         <v>15.3</v>
       </c>
       <c r="K14" t="n">
-        <v>58.3</v>
+        <v>68.7</v>
       </c>
       <c r="L14" t="n">
-        <v>27.1</v>
+        <v>33.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,23 +2651,23 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 9.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>11.29</v>
+        <v>12.78</v>
       </c>
       <c r="S14" t="n">
-        <v>7.98</v>
+        <v>6.79</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.960000000000001</v>
+        <v>-11.45</v>
       </c>
       <c r="U14" t="n">
-        <v>-16.09</v>
+        <v>-17.3</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.77</v>
+        <v>-3.47</v>
       </c>
       <c r="W14" t="n">
         <v>33.98</v>
@@ -2676,13 +2676,13 @@
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.3314</v>
+        <v>24.3892</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9534</v>
+        <v>26.9372</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,19 +2694,19 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>51.8</v>
+        <v>48.3</v>
       </c>
       <c r="AF14" t="n">
         <v>20.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>58.3</v>
+        <v>68.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI14" t="n">
-        <v>23.625</v>
+        <v>24.07</v>
       </c>
       <c r="AJ14" t="n">
         <v>20.205</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.99</v>
+        <v>6.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.61</v>
+        <v>-3.66</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 38.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.23</v>
+        <v>71.22</v>
       </c>
       <c r="F2" t="n">
-        <v>80.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K2" t="n">
-        <v>66.09999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="L2" t="n">
-        <v>76.2</v>
+        <v>68.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -702,47 +702,47 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 8.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>4.03</v>
+        <v>5.64</v>
       </c>
       <c r="S2" t="n">
-        <v>22.4</v>
+        <v>26.93</v>
       </c>
       <c r="T2" t="n">
-        <v>34.19</v>
+        <v>37.44</v>
       </c>
       <c r="U2" t="n">
-        <v>56.7</v>
+        <v>60.57</v>
       </c>
       <c r="V2" t="n">
-        <v>24.72</v>
+        <v>25.63</v>
       </c>
       <c r="W2" t="n">
-        <v>13.66</v>
+        <v>13.75</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Z2" t="n">
-        <v>64.0026</v>
+        <v>64.3308</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.0882</v>
+        <v>55.2088</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -753,13 +753,13 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>66.09999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI2" t="n">
         <v>65.27</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.17</v>
+        <v>10.71</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.67</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.2%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.7%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,30 +822,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>46.425</v>
+        <v>47.86</v>
       </c>
       <c r="F3" t="n">
-        <v>77.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>68.3</v>
+        <v>69.2</v>
       </c>
       <c r="I3" t="n">
-        <v>90.2</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>82.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>79.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,38 +873,38 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-0.78</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>12.08</v>
+        <v>17.75</v>
       </c>
       <c r="T3" t="n">
-        <v>22.72</v>
+        <v>25.42</v>
       </c>
       <c r="U3" t="n">
-        <v>38.75</v>
+        <v>42.7</v>
       </c>
       <c r="V3" t="n">
-        <v>17.84</v>
+        <v>18.82</v>
       </c>
       <c r="W3" t="n">
-        <v>15.99</v>
+        <v>16.1</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>45.1736</v>
+        <v>45.3446</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.4772</v>
+        <v>40.5402</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -912,16 +912,16 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>90.2</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>82.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AH3" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI3" t="n">
         <v>44.985</v>
@@ -936,14 +936,14 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.77</v>
+        <v>5.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.69</v>
+        <v>18.06</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 77.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.5%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>159.56</v>
+        <v>162.46</v>
       </c>
       <c r="F4" t="n">
-        <v>74.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="I4" t="n">
-        <v>72.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>75.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.26</v>
+        <v>0.89</v>
       </c>
       <c r="S4" t="n">
-        <v>7.81</v>
+        <v>10.55</v>
       </c>
       <c r="T4" t="n">
-        <v>10.39</v>
+        <v>11.92</v>
       </c>
       <c r="U4" t="n">
-        <v>22.46</v>
+        <v>24.62</v>
       </c>
       <c r="V4" t="n">
-        <v>16.59</v>
+        <v>17.11</v>
       </c>
       <c r="W4" t="n">
-        <v>12.88</v>
+        <v>12.92</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>156.1016</v>
+        <v>156.5144</v>
       </c>
       <c r="AA4" t="n">
-        <v>146.9946</v>
+        <v>147.1249</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,16 +1074,16 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>72.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AG4" t="n">
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AI4" t="n">
         <v>158.2</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.550000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>120.89</v>
+        <v>122.82</v>
       </c>
       <c r="F5" t="n">
-        <v>73.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>70.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>70.5</v>
+        <v>75</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>74.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="S5" t="n">
-        <v>7.35</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>8.609999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>20.35</v>
+        <v>22.2</v>
       </c>
       <c r="V5" t="n">
-        <v>16.48</v>
+        <v>16.93</v>
       </c>
       <c r="W5" t="n">
-        <v>13.15</v>
+        <v>13.19</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>118.4654</v>
+        <v>118.7594</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.3568</v>
+        <v>112.4454</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>70.5</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,7 +1245,7 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI5" t="n">
         <v>120.3</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.05</v>
+        <v>3.42</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.59</v>
+        <v>9.23</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>62.56</v>
+        <v>63.0272</v>
       </c>
       <c r="F6" t="n">
-        <v>73.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="I6" t="n">
-        <v>66.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="J6" t="n">
         <v>71.5</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>74.5</v>
+        <v>76</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1350,43 +1350,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.11</v>
+        <v>2.92</v>
       </c>
       <c r="S6" t="n">
-        <v>4.85</v>
+        <v>7.44</v>
       </c>
       <c r="T6" t="n">
-        <v>9.470000000000001</v>
+        <v>11.69</v>
       </c>
       <c r="U6" t="n">
-        <v>15.52</v>
+        <v>18.08</v>
       </c>
       <c r="V6" t="n">
-        <v>13.58</v>
+        <v>13.98</v>
       </c>
       <c r="W6" t="n">
-        <v>12.85</v>
+        <v>12.9</v>
       </c>
       <c r="X6" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>61.5328</v>
+        <v>60.9692</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.6502</v>
+        <v>58.0466</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>66.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="AF6" t="n">
         <v>71.5</v>
@@ -1407,39 +1407,39 @@
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AI6" t="n">
-        <v>60.81</v>
+        <v>60.5943</v>
       </c>
       <c r="AJ6" t="n">
-        <v>56.7</v>
+        <v>56.0747</v>
       </c>
       <c r="AK6" t="n">
-        <v>63.94</v>
+        <v>63.2349</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.94</v>
+        <v>63.2349</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.67</v>
+        <v>3.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.67</v>
+        <v>8.58</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.7%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.23 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.07 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>681.24</v>
+        <v>691.86</v>
       </c>
       <c r="F7" t="n">
-        <v>73.5</v>
+        <v>74.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
       <c r="I7" t="n">
-        <v>72.2</v>
+        <v>76.5</v>
       </c>
       <c r="J7" t="n">
         <v>64.40000000000001</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>74.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="S7" t="n">
-        <v>8.470000000000001</v>
+        <v>10.75</v>
       </c>
       <c r="T7" t="n">
-        <v>8.32</v>
+        <v>9.42</v>
       </c>
       <c r="U7" t="n">
-        <v>21.44</v>
+        <v>23.25</v>
       </c>
       <c r="V7" t="n">
-        <v>17.62</v>
+        <v>18.05</v>
       </c>
       <c r="W7" t="n">
-        <v>14.11</v>
+        <v>14.15</v>
       </c>
       <c r="X7" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>665.7612</v>
+        <v>667.596</v>
       </c>
       <c r="AA7" t="n">
-        <v>630.9031</v>
+        <v>631.4109</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>72.2</v>
+        <v>76.5</v>
       </c>
       <c r="AF7" t="n">
         <v>64.40000000000001</v>
@@ -1569,7 +1569,7 @@
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AI7" t="n">
         <v>680.9400000000001</v>
@@ -1584,14 +1584,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.32</v>
+        <v>3.63</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.98</v>
+        <v>9.57</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74.36</v>
+        <v>75.27</v>
       </c>
       <c r="F8" t="n">
-        <v>72.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1646,16 +1646,16 @@
         <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>69.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="L8" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,22 +1683,22 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>6.66</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>9.42</v>
+        <v>10.25</v>
       </c>
       <c r="U8" t="n">
-        <v>17.86</v>
+        <v>19.1</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>15.11</v>
       </c>
       <c r="W8" t="n">
-        <v>12.87</v>
+        <v>12.89</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
@@ -1707,10 +1707,10 @@
         <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.1952</v>
+        <v>72.36199999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.804</v>
+        <v>68.8582</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI8" t="n">
         <v>72.94</v>
@@ -1740,25 +1740,25 @@
         <v>66.58</v>
       </c>
       <c r="AK8" t="n">
-        <v>74.95999999999999</v>
+        <v>75.27</v>
       </c>
       <c r="AL8" t="n">
-        <v>74.95999999999999</v>
+        <v>75.27</v>
       </c>
       <c r="AM8" t="n">
-        <v>3</v>
+        <v>4.02</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.08</v>
+        <v>9.31</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.272</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>70.8</v>
+        <v>69</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>62.2</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>50.5</v>
       </c>
       <c r="J9" t="n">
-        <v>45.9</v>
+        <v>78.2</v>
       </c>
       <c r="K9" t="n">
-        <v>75.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>73.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.43</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>22.78</v>
+        <v>-1.03</v>
       </c>
       <c r="T9" t="n">
-        <v>21.69</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>35.7</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>16.5</v>
+        <v>7.04</v>
       </c>
       <c r="W9" t="n">
-        <v>21.35</v>
+        <v>9.57</v>
       </c>
       <c r="X9" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.3266</v>
+        <v>63.3706</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.5083</v>
+        <v>63.1116</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,48 +1884,48 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>50.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>50.9</v>
+        <v>78.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>75.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI9" t="n">
-        <v>16.544</v>
+        <v>63.51</v>
       </c>
       <c r="AJ9" t="n">
-        <v>12.936</v>
+        <v>62.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>18.17</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AL9" t="n">
-        <v>18.17</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.79</v>
+        <v>1.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.05</v>
+        <v>1.87</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,29 +1937,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64.31</v>
+        <v>17.972</v>
       </c>
       <c r="F10" t="n">
-        <v>69.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>61.9</v>
+        <v>50.9</v>
       </c>
       <c r="I10" t="n">
-        <v>51.4</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>78.2</v>
+        <v>45.7</v>
       </c>
       <c r="K10" t="n">
-        <v>82.8</v>
+        <v>61.1</v>
       </c>
       <c r="L10" t="n">
-        <v>71.2</v>
+        <v>64.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,57 +1988,57 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3.16</v>
+        <v>3.56</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.42</v>
+        <v>29.69</v>
       </c>
       <c r="T10" t="n">
-        <v>2.73</v>
+        <v>26.21</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>40.98</v>
       </c>
       <c r="V10" t="n">
-        <v>6.93</v>
+        <v>17.57</v>
       </c>
       <c r="W10" t="n">
-        <v>9.56</v>
+        <v>21.47</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.85</v>
+        <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.3538</v>
+        <v>16.4273</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.1068</v>
+        <v>14.5329</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2046,48 +2046,48 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>51.4</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>78.2</v>
+        <v>50.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>82.8</v>
+        <v>61.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI10" t="n">
-        <v>63.37</v>
+        <v>16.544</v>
       </c>
       <c r="AJ10" t="n">
-        <v>62.06</v>
+        <v>12.936</v>
       </c>
       <c r="AK10" t="n">
-        <v>64.68000000000001</v>
+        <v>18.17</v>
       </c>
       <c r="AL10" t="n">
-        <v>65.25</v>
+        <v>18.17</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.51</v>
+        <v>9.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.91</v>
+        <v>23.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.5%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.25 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,14 +2114,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>619.96</v>
+        <v>10.4</v>
       </c>
       <c r="F11" t="n">
-        <v>61.6</v>
+        <v>63.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>58.1</v>
+        <v>31</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J11" t="n">
-        <v>24.3</v>
+        <v>32</v>
       </c>
       <c r="K11" t="n">
-        <v>29.9</v>
+        <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>24.2</v>
+        <v>57.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 17.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>8.300000000000001</v>
+        <v>-3.59</v>
       </c>
       <c r="S11" t="n">
-        <v>60.06</v>
+        <v>12.29</v>
       </c>
       <c r="T11" t="n">
-        <v>66.23999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="U11" t="n">
-        <v>137.47</v>
+        <v>59.54</v>
       </c>
       <c r="V11" t="n">
-        <v>60.35</v>
+        <v>2.87</v>
       </c>
       <c r="W11" t="n">
-        <v>35.12</v>
+        <v>23.42</v>
       </c>
       <c r="X11" t="n">
-        <v>-35.74</v>
+        <v>-43.61</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.72</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>528.8706</v>
+        <v>10.2478</v>
       </c>
       <c r="AA11" t="n">
-        <v>403.9168</v>
+        <v>8.801</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2208,48 +2208,48 @@
         <v>85</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>29.3</v>
+        <v>37</v>
       </c>
       <c r="AG11" t="n">
-        <v>29.9</v>
+        <v>82.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AI11" t="n">
-        <v>543.96</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>362.53</v>
+        <v>8.7643</v>
       </c>
       <c r="AK11" t="n">
-        <v>637.9</v>
+        <v>11.61</v>
       </c>
       <c r="AL11" t="n">
-        <v>637.9</v>
+        <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>17.22</v>
+        <v>1.49</v>
       </c>
       <c r="AN11" t="n">
-        <v>53.49</v>
+        <v>18.17</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 61.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.2%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 63.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.5%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.082</v>
+        <v>647.1</v>
       </c>
       <c r="F12" t="n">
-        <v>58</v>
+        <v>59.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,28 +2291,28 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>29.7</v>
+        <v>59.1</v>
       </c>
       <c r="I12" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>31.6</v>
+        <v>24.1</v>
       </c>
       <c r="K12" t="n">
-        <v>77.8</v>
+        <v>14</v>
       </c>
       <c r="L12" t="n">
-        <v>52.8</v>
+        <v>12.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 21.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-6.59</v>
+        <v>11.89</v>
       </c>
       <c r="S12" t="n">
-        <v>9.83</v>
+        <v>64.27</v>
       </c>
       <c r="T12" t="n">
-        <v>22.47</v>
+        <v>75.02</v>
       </c>
       <c r="U12" t="n">
-        <v>56.47</v>
+        <v>146.67</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>62.84</v>
       </c>
       <c r="W12" t="n">
-        <v>23.32</v>
+        <v>35.23</v>
       </c>
       <c r="X12" t="n">
-        <v>-44.26</v>
+        <v>-35.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.06</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.2175</v>
+        <v>533.9662</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.7845</v>
+        <v>405.6687</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2367,51 +2367,51 @@
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AE12" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>36.6</v>
+        <v>29.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>77.8</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.914999999999999</v>
+        <v>543.96</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8.7643</v>
+        <v>362.53</v>
       </c>
       <c r="AK12" t="n">
-        <v>11.61</v>
+        <v>647.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>11.61</v>
+        <v>647.1</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1.33</v>
+        <v>21.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.77</v>
+        <v>59.51</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 58.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.3%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 59.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.2%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 647.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>340.82</v>
+        <v>350.52</v>
       </c>
       <c r="F13" t="n">
-        <v>49.2</v>
+        <v>51.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>65.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="I13" t="n">
-        <v>25.1</v>
+        <v>31</v>
       </c>
       <c r="J13" t="n">
-        <v>61</v>
+        <v>60.9</v>
       </c>
       <c r="K13" t="n">
-        <v>60.1</v>
+        <v>64.2</v>
       </c>
       <c r="L13" t="n">
-        <v>50.1</v>
+        <v>53.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-11.65</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-20.7</v>
+        <v>-18.23</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.08</v>
+        <v>0.52</v>
       </c>
       <c r="U13" t="n">
-        <v>21.3</v>
+        <v>24.9</v>
       </c>
       <c r="V13" t="n">
-        <v>24.66</v>
+        <v>26.62</v>
       </c>
       <c r="W13" t="n">
-        <v>17.91</v>
+        <v>17.99</v>
       </c>
       <c r="X13" t="n">
         <v>-21.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>379.2068</v>
+        <v>378.5036</v>
       </c>
       <c r="AA13" t="n">
-        <v>362.8027</v>
+        <v>363.1672</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>25.1</v>
+        <v>31</v>
       </c>
       <c r="AF13" t="n">
-        <v>61</v>
+        <v>60.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>60.1</v>
+        <v>64.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI13" t="n">
         <v>340.82</v>
@@ -2553,22 +2553,22 @@
         <v>377.9</v>
       </c>
       <c r="AL13" t="n">
-        <v>417.5</v>
+        <v>407.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>-10.12</v>
+        <v>-7.39</v>
       </c>
       <c r="AN13" t="n">
-        <v>-6.06</v>
+        <v>-3.48</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 49.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.1%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 51.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 417.50 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 407.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.95</v>
+        <v>26.02</v>
       </c>
       <c r="F14" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="I14" t="n">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
       <c r="J14" t="n">
         <v>15.3</v>
       </c>
       <c r="K14" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="L14" t="n">
-        <v>33.1</v>
+        <v>32.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>12.78</v>
+        <v>10.14</v>
       </c>
       <c r="S14" t="n">
-        <v>6.79</v>
+        <v>6.62</v>
       </c>
       <c r="T14" t="n">
-        <v>-11.45</v>
+        <v>-12.8</v>
       </c>
       <c r="U14" t="n">
-        <v>-17.3</v>
+        <v>-16.21</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.47</v>
+        <v>-3.77</v>
       </c>
       <c r="W14" t="n">
-        <v>33.98</v>
+        <v>34</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.3892</v>
+        <v>24.4489</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9372</v>
+        <v>26.9215</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,19 +2694,19 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
       <c r="AF14" t="n">
         <v>20.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI14" t="n">
-        <v>24.07</v>
+        <v>24.705</v>
       </c>
       <c r="AJ14" t="n">
         <v>20.205</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>6.4</v>
+        <v>6.43</v>
       </c>
       <c r="AN14" t="n">
-        <v>-3.66</v>
+        <v>-3.35</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 38.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,30 +660,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.22</v>
+        <v>72.25</v>
       </c>
       <c r="F2" t="n">
-        <v>79.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.3</v>
+        <v>79</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="K2" t="n">
-        <v>55.9</v>
+        <v>51.7</v>
       </c>
       <c r="L2" t="n">
-        <v>68.5</v>
+        <v>65.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 10.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 11.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>5.64</v>
+        <v>9.25</v>
       </c>
       <c r="S2" t="n">
-        <v>26.93</v>
+        <v>28.28</v>
       </c>
       <c r="T2" t="n">
-        <v>37.44</v>
+        <v>39.61</v>
       </c>
       <c r="U2" t="n">
-        <v>60.57</v>
+        <v>63.26</v>
       </c>
       <c r="V2" t="n">
-        <v>25.63</v>
+        <v>26.16</v>
       </c>
       <c r="W2" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>64.3308</v>
+        <v>64.64360000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.2088</v>
+        <v>55.3358</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -753,10 +753,10 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>55.9</v>
+        <v>51.7</v>
       </c>
       <c r="AH2" t="n">
         <v>755</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>10.71</v>
+        <v>11.77</v>
       </c>
       <c r="AN2" t="n">
-        <v>29</v>
+        <v>30.57</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.7%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.8%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.86</v>
+        <v>49.13</v>
       </c>
       <c r="F3" t="n">
-        <v>79.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69.2</v>
+        <v>70.2</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>65.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="K3" t="n">
-        <v>76.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>79.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -869,38 +869,38 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>7.08</v>
       </c>
       <c r="S3" t="n">
-        <v>17.75</v>
+        <v>20.67</v>
       </c>
       <c r="T3" t="n">
-        <v>25.42</v>
+        <v>29.2</v>
       </c>
       <c r="U3" t="n">
-        <v>42.7</v>
+        <v>45.72</v>
       </c>
       <c r="V3" t="n">
-        <v>18.82</v>
+        <v>19.84</v>
       </c>
       <c r="W3" t="n">
-        <v>16.1</v>
+        <v>16.17</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>45.3446</v>
+        <v>45.5145</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.5402</v>
+        <v>40.6089</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
         <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>65.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>76.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="AH3" t="n">
         <v>755</v>
@@ -936,14 +936,14 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.55</v>
+        <v>7.94</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.06</v>
+        <v>20.98</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.5%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>162.46</v>
+        <v>164.6</v>
       </c>
       <c r="F4" t="n">
-        <v>76.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="I4" t="n">
-        <v>78.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1031,38 +1031,38 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.89</v>
+        <v>3.24</v>
       </c>
       <c r="S4" t="n">
-        <v>10.55</v>
+        <v>12.14</v>
       </c>
       <c r="T4" t="n">
-        <v>11.92</v>
+        <v>13.6</v>
       </c>
       <c r="U4" t="n">
-        <v>24.62</v>
+        <v>27.42</v>
       </c>
       <c r="V4" t="n">
-        <v>17.11</v>
+        <v>17.48</v>
       </c>
       <c r="W4" t="n">
-        <v>12.92</v>
+        <v>12.94</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>156.5144</v>
+        <v>156.9084</v>
       </c>
       <c r="AA4" t="n">
-        <v>147.1249</v>
+        <v>147.2667</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,13 +1074,13 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>78.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AH4" t="n">
         <v>758</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.42</v>
+        <v>11.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.9%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>122.82</v>
+        <v>124.26</v>
       </c>
       <c r="F5" t="n">
-        <v>75.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="I5" t="n">
-        <v>75</v>
+        <v>78.3</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>82.8</v>
+        <v>81.2</v>
       </c>
       <c r="L5" t="n">
-        <v>75.8</v>
+        <v>76.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1193,38 +1193,38 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.68</v>
+        <v>2.67</v>
       </c>
       <c r="S5" t="n">
-        <v>9.630000000000001</v>
+        <v>11.06</v>
       </c>
       <c r="T5" t="n">
-        <v>9.960000000000001</v>
+        <v>11.43</v>
       </c>
       <c r="U5" t="n">
-        <v>22.2</v>
+        <v>23.73</v>
       </c>
       <c r="V5" t="n">
-        <v>16.93</v>
+        <v>17.21</v>
       </c>
       <c r="W5" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>118.7594</v>
+        <v>119.0378</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.4454</v>
+        <v>112.5415</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,13 +1236,13 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>78.3</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>82.8</v>
+        <v>81.2</v>
       </c>
       <c r="AH5" t="n">
         <v>755</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.42</v>
+        <v>4.39</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.23</v>
+        <v>10.41</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63.0272</v>
+        <v>701.6</v>
       </c>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>75.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="I6" t="n">
-        <v>72</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="K6" t="n">
-        <v>82.8</v>
+        <v>79.5</v>
       </c>
       <c r="L6" t="n">
-        <v>76</v>
+        <v>75.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="S6" t="n">
-        <v>7.44</v>
+        <v>12.33</v>
       </c>
       <c r="T6" t="n">
-        <v>11.69</v>
+        <v>11.22</v>
       </c>
       <c r="U6" t="n">
-        <v>18.08</v>
+        <v>26.29</v>
       </c>
       <c r="V6" t="n">
-        <v>13.98</v>
+        <v>18.43</v>
       </c>
       <c r="W6" t="n">
-        <v>12.9</v>
+        <v>14.17</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>60.9692</v>
+        <v>669.422</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.0466</v>
+        <v>631.965</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>72</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>82.8</v>
+        <v>79.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AI6" t="n">
-        <v>60.5943</v>
+        <v>680.9400000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>56.0747</v>
+        <v>597.92</v>
       </c>
       <c r="AK6" t="n">
-        <v>63.2349</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.2349</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.38</v>
+        <v>4.81</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.58</v>
+        <v>11.02</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.8%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.23 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.07 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,14 +1466,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>691.86</v>
+        <v>63.08</v>
       </c>
       <c r="F7" t="n">
-        <v>74.7</v>
+        <v>75.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>76.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>75.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1517,38 +1517,38 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.1</v>
+        <v>4.89</v>
       </c>
       <c r="S7" t="n">
-        <v>10.75</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>9.42</v>
+        <v>11.91</v>
       </c>
       <c r="U7" t="n">
-        <v>23.25</v>
+        <v>19.3</v>
       </c>
       <c r="V7" t="n">
-        <v>18.05</v>
+        <v>13.81</v>
       </c>
       <c r="W7" t="n">
-        <v>14.15</v>
+        <v>12.9</v>
       </c>
       <c r="X7" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>667.596</v>
+        <v>61.0566</v>
       </c>
       <c r="AA7" t="n">
-        <v>631.4109</v>
+        <v>58.0921</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,48 +1560,48 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>76.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI7" t="n">
-        <v>680.9400000000001</v>
+        <v>60.6339</v>
       </c>
       <c r="AJ7" t="n">
-        <v>597.92</v>
+        <v>56.0747</v>
       </c>
       <c r="AK7" t="n">
-        <v>703.9400000000001</v>
+        <v>63.2349</v>
       </c>
       <c r="AL7" t="n">
-        <v>703.9400000000001</v>
+        <v>63.2349</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.57</v>
+        <v>8.59</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.23 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.07 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.27</v>
+        <v>75.89</v>
       </c>
       <c r="F8" t="n">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65</v>
+        <v>65.2</v>
       </c>
       <c r="I8" t="n">
-        <v>72.8</v>
+        <v>75.5</v>
       </c>
       <c r="J8" t="n">
-        <v>68.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="K8" t="n">
-        <v>82.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>74.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>3.56</v>
       </c>
       <c r="S8" t="n">
-        <v>8.470000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="T8" t="n">
-        <v>10.25</v>
+        <v>11.65</v>
       </c>
       <c r="U8" t="n">
-        <v>19.1</v>
+        <v>20.21</v>
       </c>
       <c r="V8" t="n">
-        <v>15.11</v>
+        <v>15.18</v>
       </c>
       <c r="W8" t="n">
         <v>12.89</v>
@@ -1704,13 +1704,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.36199999999999</v>
+        <v>72.51600000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.8582</v>
+        <v>68.9156</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,43 +1722,43 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>72.8</v>
+        <v>75.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>68.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="AG8" t="n">
-        <v>82.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AH8" t="n">
         <v>755</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.94</v>
+        <v>73.11</v>
       </c>
       <c r="AJ8" t="n">
         <v>66.58</v>
       </c>
       <c r="AK8" t="n">
-        <v>75.27</v>
+        <v>75.89</v>
       </c>
       <c r="AL8" t="n">
-        <v>75.27</v>
+        <v>75.89</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.02</v>
+        <v>4.65</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.31</v>
+        <v>10.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64.29000000000001</v>
+        <v>64.11</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>62.2</v>
+        <v>61.5</v>
       </c>
       <c r="I9" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="J9" t="n">
         <v>78.2</v>
@@ -1817,7 +1817,7 @@
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>71.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,34 +1845,34 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.03</v>
+        <v>-1.79</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>7.04</v>
+        <v>6.71</v>
       </c>
       <c r="W9" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="X9" t="n">
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.3706</v>
+        <v>63.3822</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1116</v>
+        <v>63.1178</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="AF9" t="n">
         <v>78.2</v>
@@ -1908,14 +1908,14 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.4%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,30 +1956,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.972</v>
+        <v>18.54</v>
       </c>
       <c r="F10" t="n">
-        <v>68.8</v>
+        <v>67.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>50.9</v>
+        <v>51.8</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="K10" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="L10" t="n">
-        <v>64.5</v>
+        <v>56.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2003,38 +2003,38 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 12.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3.56</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>29.69</v>
+        <v>35.01</v>
       </c>
       <c r="T10" t="n">
-        <v>26.21</v>
+        <v>30.75</v>
       </c>
       <c r="U10" t="n">
-        <v>40.98</v>
+        <v>45.39</v>
       </c>
       <c r="V10" t="n">
-        <v>17.57</v>
+        <v>18.79</v>
       </c>
       <c r="W10" t="n">
-        <v>21.47</v>
+        <v>21.54</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.4273</v>
+        <v>16.5267</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.5329</v>
+        <v>14.5605</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
         <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="AH10" t="n">
         <v>755</v>
@@ -2064,25 +2064,25 @@
         <v>12.936</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.17</v>
+        <v>18.54</v>
       </c>
       <c r="AL10" t="n">
-        <v>18.17</v>
+        <v>18.54</v>
       </c>
       <c r="AM10" t="n">
-        <v>9.4</v>
+        <v>12.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.66</v>
+        <v>27.33</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.54 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.4</v>
+        <v>10.384</v>
       </c>
       <c r="F11" t="n">
-        <v>63.7</v>
+        <v>64</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2132,16 +2132,16 @@
         <v>31</v>
       </c>
       <c r="I11" t="n">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="K11" t="n">
         <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>57.5</v>
+        <v>57.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2169,34 +2169,34 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-3.59</v>
+        <v>-3.16</v>
       </c>
       <c r="S11" t="n">
-        <v>12.29</v>
+        <v>12.61</v>
       </c>
       <c r="T11" t="n">
-        <v>25.6</v>
+        <v>26.85</v>
       </c>
       <c r="U11" t="n">
-        <v>59.54</v>
+        <v>58.57</v>
       </c>
       <c r="V11" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="W11" t="n">
         <v>23.42</v>
       </c>
       <c r="X11" t="n">
-        <v>-43.61</v>
+        <v>-43.51</v>
       </c>
       <c r="Y11" t="n">
         <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.2478</v>
+        <v>10.2735</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.801</v>
+        <v>8.817500000000001</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         <v>85</v>
       </c>
       <c r="AE11" t="n">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AF11" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="AG11" t="n">
         <v>82.8</v>
@@ -2232,14 +2232,14 @@
         <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.17</v>
+        <v>17.77</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 63.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.5%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>647.1</v>
+        <v>616</v>
       </c>
       <c r="F12" t="n">
-        <v>59.4</v>
+        <v>63.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>59.1</v>
+        <v>57.8</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>41.1</v>
       </c>
       <c r="L12" t="n">
-        <v>12.1</v>
+        <v>32.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 21.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 14.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>11.89</v>
+        <v>10.72</v>
       </c>
       <c r="S12" t="n">
-        <v>64.27</v>
+        <v>55.21</v>
       </c>
       <c r="T12" t="n">
-        <v>75.02</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>146.67</v>
+        <v>140.44</v>
       </c>
       <c r="V12" t="n">
-        <v>62.84</v>
+        <v>60.36</v>
       </c>
       <c r="W12" t="n">
-        <v>35.23</v>
+        <v>35.35</v>
       </c>
       <c r="X12" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Z12" t="n">
-        <v>533.9662</v>
+        <v>538.3665999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>405.6687</v>
+        <v>407.2589</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2373,10 +2373,10 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>41.1</v>
       </c>
       <c r="AH12" t="n">
         <v>751</v>
@@ -2394,14 +2394,14 @@
         <v>647.1</v>
       </c>
       <c r="AM12" t="n">
-        <v>21.19</v>
+        <v>14.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.51</v>
+        <v>51.26</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 59.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.2%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.4%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>350.52</v>
+        <v>361.04</v>
       </c>
       <c r="F13" t="n">
-        <v>51.7</v>
+        <v>54.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>67.7</v>
+        <v>68.7</v>
       </c>
       <c r="I13" t="n">
-        <v>31</v>
+        <v>38.6</v>
       </c>
       <c r="J13" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="K13" t="n">
-        <v>64.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>53.1</v>
+        <v>56.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 7.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 4.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-9.279999999999999</v>
+        <v>-4.01</v>
       </c>
       <c r="S13" t="n">
-        <v>-18.23</v>
+        <v>-14.96</v>
       </c>
       <c r="T13" t="n">
-        <v>0.52</v>
+        <v>3.91</v>
       </c>
       <c r="U13" t="n">
-        <v>24.9</v>
+        <v>28.99</v>
       </c>
       <c r="V13" t="n">
-        <v>26.62</v>
+        <v>27.8</v>
       </c>
       <c r="W13" t="n">
-        <v>17.99</v>
+        <v>18.06</v>
       </c>
       <c r="X13" t="n">
         <v>-21.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Z13" t="n">
-        <v>378.5036</v>
+        <v>377.802</v>
       </c>
       <c r="AA13" t="n">
-        <v>363.1672</v>
+        <v>363.5818</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>31</v>
+        <v>38.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>64.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AH13" t="n">
         <v>755</v>
@@ -2553,22 +2553,22 @@
         <v>377.9</v>
       </c>
       <c r="AL13" t="n">
-        <v>407.57</v>
+        <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-7.39</v>
+        <v>-4.44</v>
       </c>
       <c r="AN13" t="n">
-        <v>-3.48</v>
+        <v>-0.7</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 51.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.4%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 407.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.02</v>
+        <v>26.53</v>
       </c>
       <c r="F14" t="n">
-        <v>38.8</v>
+        <v>39.3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="I14" t="n">
-        <v>47.5</v>
+        <v>53.3</v>
       </c>
       <c r="J14" t="n">
         <v>15.3</v>
       </c>
       <c r="K14" t="n">
-        <v>68.5</v>
+        <v>61.3</v>
       </c>
       <c r="L14" t="n">
-        <v>32.8</v>
+        <v>29.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>10.14</v>
+        <v>10.22</v>
       </c>
       <c r="S14" t="n">
-        <v>6.62</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-12.8</v>
+        <v>-11.93</v>
       </c>
       <c r="U14" t="n">
-        <v>-16.21</v>
+        <v>-12.74</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.77</v>
+        <v>-3.11</v>
       </c>
       <c r="W14" t="n">
-        <v>34</v>
+        <v>34.02</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.4489</v>
+        <v>24.5113</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9215</v>
+        <v>26.9103</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,19 +2694,19 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>47.5</v>
+        <v>53.3</v>
       </c>
       <c r="AF14" t="n">
         <v>20.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>68.5</v>
+        <v>61.3</v>
       </c>
       <c r="AH14" t="n">
         <v>756</v>
       </c>
       <c r="AI14" t="n">
-        <v>24.705</v>
+        <v>24.93</v>
       </c>
       <c r="AJ14" t="n">
         <v>20.205</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>6.43</v>
+        <v>8.24</v>
       </c>
       <c r="AN14" t="n">
-        <v>-3.35</v>
+        <v>-1.41</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 38.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.2%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,18 +660,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72.25</v>
+        <v>71.7</v>
       </c>
       <c r="F2" t="n">
-        <v>79.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.2</v>
       </c>
       <c r="K2" t="n">
-        <v>51.7</v>
+        <v>57.2</v>
       </c>
       <c r="L2" t="n">
-        <v>65.3</v>
+        <v>69.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 11.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>9.25</v>
+        <v>9.48</v>
       </c>
       <c r="S2" t="n">
-        <v>28.28</v>
+        <v>26.25</v>
       </c>
       <c r="T2" t="n">
-        <v>39.61</v>
+        <v>38.02</v>
       </c>
       <c r="U2" t="n">
-        <v>63.26</v>
+        <v>63.23</v>
       </c>
       <c r="V2" t="n">
-        <v>26.16</v>
+        <v>26.04</v>
       </c>
       <c r="W2" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>64.64360000000001</v>
+        <v>64.94840000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.3358</v>
+        <v>55.4611</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -756,13 +756,13 @@
         <v>69.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>51.7</v>
+        <v>57.2</v>
       </c>
       <c r="AH2" t="n">
         <v>755</v>
       </c>
       <c r="AI2" t="n">
-        <v>65.27</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>54.81</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>11.77</v>
+        <v>10.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>30.57</v>
+        <v>29.28</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.8%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.4%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.13</v>
+        <v>48.575</v>
       </c>
       <c r="F3" t="n">
-        <v>78.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>70.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -842,10 +842,10 @@
         <v>65.3</v>
       </c>
       <c r="K3" t="n">
-        <v>67</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>75.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -869,38 +869,38 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>7.08</v>
+        <v>6.65</v>
       </c>
       <c r="S3" t="n">
-        <v>20.67</v>
+        <v>17.6</v>
       </c>
       <c r="T3" t="n">
-        <v>29.2</v>
+        <v>27.81</v>
       </c>
       <c r="U3" t="n">
-        <v>45.72</v>
+        <v>45.39</v>
       </c>
       <c r="V3" t="n">
-        <v>19.84</v>
+        <v>19.55</v>
       </c>
       <c r="W3" t="n">
-        <v>16.17</v>
+        <v>16.18</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>45.5145</v>
+        <v>45.6843</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.6089</v>
+        <v>40.6756</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -918,13 +918,13 @@
         <v>65.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>67</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AH3" t="n">
         <v>755</v>
       </c>
       <c r="AI3" t="n">
-        <v>44.985</v>
+        <v>45.845</v>
       </c>
       <c r="AJ3" t="n">
         <v>39.31</v>
@@ -936,14 +936,14 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>7.94</v>
+        <v>6.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.98</v>
+        <v>19.42</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.3%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>164.6</v>
+        <v>164.16</v>
       </c>
       <c r="F4" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="I4" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>79.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="L4" t="n">
-        <v>76.8</v>
+        <v>77.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3.24</v>
+        <v>3.61</v>
       </c>
       <c r="S4" t="n">
-        <v>12.14</v>
+        <v>11.39</v>
       </c>
       <c r="T4" t="n">
-        <v>13.6</v>
+        <v>13.23</v>
       </c>
       <c r="U4" t="n">
-        <v>27.42</v>
+        <v>27.67</v>
       </c>
       <c r="V4" t="n">
-        <v>17.48</v>
+        <v>17.59</v>
       </c>
       <c r="W4" t="n">
         <v>12.94</v>
@@ -1056,13 +1056,13 @@
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>156.9084</v>
+        <v>157.2968</v>
       </c>
       <c r="AA4" t="n">
-        <v>147.2667</v>
+        <v>147.4076</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>79.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="AH4" t="n">
         <v>758</v>
       </c>
       <c r="AI4" t="n">
-        <v>158.2</v>
+        <v>159.24</v>
       </c>
       <c r="AJ4" t="n">
         <v>140.98</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.9</v>
+        <v>4.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.77</v>
+        <v>11.36</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.9%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124.26</v>
+        <v>124.11</v>
       </c>
       <c r="F5" t="n">
-        <v>75.8</v>
+        <v>76</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>78.3</v>
+        <v>77.8</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>81.2</v>
+        <v>82.7</v>
       </c>
       <c r="L5" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.67</v>
+        <v>3.09</v>
       </c>
       <c r="S5" t="n">
-        <v>11.06</v>
+        <v>10.65</v>
       </c>
       <c r="T5" t="n">
-        <v>11.43</v>
+        <v>11.19</v>
       </c>
       <c r="U5" t="n">
-        <v>23.73</v>
+        <v>24.62</v>
       </c>
       <c r="V5" t="n">
-        <v>17.21</v>
+        <v>17.41</v>
       </c>
       <c r="W5" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>119.0378</v>
+        <v>119.3124</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.5415</v>
+        <v>112.638</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,19 +1236,19 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>78.3</v>
+        <v>77.8</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>81.2</v>
+        <v>82.7</v>
       </c>
       <c r="AH5" t="n">
         <v>755</v>
       </c>
       <c r="AI5" t="n">
-        <v>120.3</v>
+        <v>120.73</v>
       </c>
       <c r="AJ5" t="n">
         <v>107.5</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.39</v>
+        <v>4.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.41</v>
+        <v>10.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>701.6</v>
+        <v>699.6799999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>75.3</v>
+        <v>75.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.5</v>
+        <v>70.7</v>
       </c>
       <c r="I6" t="n">
-        <v>80.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="J6" t="n">
         <v>64.3</v>
       </c>
       <c r="K6" t="n">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="S6" t="n">
-        <v>12.33</v>
+        <v>11.88</v>
       </c>
       <c r="T6" t="n">
-        <v>11.22</v>
+        <v>10.79</v>
       </c>
       <c r="U6" t="n">
-        <v>26.29</v>
+        <v>26.31</v>
       </c>
       <c r="V6" t="n">
-        <v>18.43</v>
+        <v>18.52</v>
       </c>
       <c r="W6" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="X6" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>669.422</v>
+        <v>671.184</v>
       </c>
       <c r="AA6" t="n">
-        <v>631.965</v>
+        <v>632.5137</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,19 +1398,19 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>80.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="AF6" t="n">
         <v>64.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
       <c r="AH6" t="n">
         <v>758</v>
       </c>
       <c r="AI6" t="n">
-        <v>680.9400000000001</v>
+        <v>681.24</v>
       </c>
       <c r="AJ6" t="n">
         <v>597.92</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.81</v>
+        <v>4.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>11.02</v>
+        <v>10.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.08</v>
+        <v>63.25</v>
       </c>
       <c r="F7" t="n">
-        <v>75.3</v>
+        <v>75.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="I7" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4.89</v>
+        <v>4.38</v>
       </c>
       <c r="S7" t="n">
-        <v>8.130000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="T7" t="n">
-        <v>11.91</v>
+        <v>12.15</v>
       </c>
       <c r="U7" t="n">
-        <v>19.3</v>
+        <v>19.11</v>
       </c>
       <c r="V7" t="n">
-        <v>13.81</v>
+        <v>14.3</v>
       </c>
       <c r="W7" t="n">
-        <v>12.9</v>
+        <v>12.88</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.0566</v>
+        <v>61.1499</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.0921</v>
+        <v>58.1382</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1572,31 +1572,31 @@
         <v>759</v>
       </c>
       <c r="AI7" t="n">
-        <v>60.6339</v>
+        <v>61.4745</v>
       </c>
       <c r="AJ7" t="n">
         <v>56.0747</v>
       </c>
       <c r="AK7" t="n">
-        <v>63.2349</v>
+        <v>63.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>63.2349</v>
+        <v>63.25</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.31</v>
+        <v>3.43</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.59</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.23 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.25 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.89</v>
+        <v>75.77</v>
       </c>
       <c r="F8" t="n">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65.2</v>
+        <v>65.5</v>
       </c>
       <c r="I8" t="n">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>80.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="L8" t="n">
-        <v>74.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.56</v>
+        <v>3.88</v>
       </c>
       <c r="S8" t="n">
-        <v>9.59</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>11.65</v>
+        <v>11.57</v>
       </c>
       <c r="U8" t="n">
-        <v>20.21</v>
+        <v>21.21</v>
       </c>
       <c r="V8" t="n">
-        <v>15.18</v>
+        <v>15.41</v>
       </c>
       <c r="W8" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.51600000000001</v>
+        <v>72.667</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.9156</v>
+        <v>68.973</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,19 +1722,19 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AF8" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>80.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="AH8" t="n">
         <v>755</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.11</v>
+        <v>73.59</v>
       </c>
       <c r="AJ8" t="n">
         <v>66.58</v>
@@ -1746,14 +1746,14 @@
         <v>75.89</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.65</v>
+        <v>4.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.12</v>
+        <v>9.85</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64.11</v>
+        <v>63.98</v>
       </c>
       <c r="F9" t="n">
         <v>68.59999999999999</v>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="I9" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="J9" t="n">
         <v>78.2</v>
@@ -1841,23 +1841,23 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>0.52</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.79</v>
+        <v>-1.95</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>6.71</v>
+        <v>6.82</v>
       </c>
       <c r="W9" t="n">
         <v>9.56</v>
@@ -1866,13 +1866,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.3822</v>
+        <v>63.3816</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1178</v>
+        <v>63.1244</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="AF9" t="n">
         <v>78.2</v>
@@ -1908,14 +1908,14 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.1%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.9%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,18 +1956,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.54</v>
+        <v>18.274</v>
       </c>
       <c r="F10" t="n">
-        <v>67.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1976,10 +1976,10 @@
         <v>45.6</v>
       </c>
       <c r="K10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="L10" t="n">
-        <v>56.1</v>
+        <v>62.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2003,38 +2003,38 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 12.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>9.279999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="S10" t="n">
-        <v>35.01</v>
+        <v>31.75</v>
       </c>
       <c r="T10" t="n">
-        <v>30.75</v>
+        <v>28.44</v>
       </c>
       <c r="U10" t="n">
-        <v>45.39</v>
+        <v>45.01</v>
       </c>
       <c r="V10" t="n">
-        <v>18.79</v>
+        <v>18.48</v>
       </c>
       <c r="W10" t="n">
-        <v>21.54</v>
+        <v>21.56</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.5267</v>
+        <v>16.6226</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.5605</v>
+        <v>14.5869</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,13 +2052,13 @@
         <v>50.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="AH10" t="n">
         <v>755</v>
       </c>
       <c r="AI10" t="n">
-        <v>16.544</v>
+        <v>17.092</v>
       </c>
       <c r="AJ10" t="n">
         <v>12.936</v>
@@ -2070,14 +2070,14 @@
         <v>18.54</v>
       </c>
       <c r="AM10" t="n">
-        <v>12.18</v>
+        <v>9.93</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.33</v>
+        <v>25.28</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.384</v>
+        <v>10.466</v>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31</v>
+        <v>31.4</v>
       </c>
       <c r="I11" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
         <v>32.1</v>
@@ -2141,7 +2141,7 @@
         <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>57.8</v>
+        <v>58.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2169,34 +2169,34 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-3.16</v>
+        <v>-0.36</v>
       </c>
       <c r="S11" t="n">
-        <v>12.61</v>
+        <v>13.52</v>
       </c>
       <c r="T11" t="n">
-        <v>26.85</v>
+        <v>27.41</v>
       </c>
       <c r="U11" t="n">
-        <v>58.57</v>
+        <v>61.81</v>
       </c>
       <c r="V11" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="W11" t="n">
         <v>23.42</v>
       </c>
       <c r="X11" t="n">
-        <v>-43.51</v>
+        <v>-43.46</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.2735</v>
+        <v>10.3021</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.817500000000001</v>
+        <v>8.8345</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>85</v>
       </c>
       <c r="AE11" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
         <v>37.1</v>
@@ -2232,14 +2232,14 @@
         <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.08</v>
+        <v>1.59</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.77</v>
+        <v>18.47</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>616</v>
+        <v>623.97</v>
       </c>
       <c r="F12" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>57.8</v>
+        <v>58.2</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -2300,10 +2300,10 @@
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>41.1</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 14.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 14.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>10.72</v>
+        <v>14.25</v>
       </c>
       <c r="S12" t="n">
-        <v>55.21</v>
+        <v>58.5</v>
       </c>
       <c r="T12" t="n">
-        <v>74.48999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="U12" t="n">
-        <v>140.44</v>
+        <v>137.65</v>
       </c>
       <c r="V12" t="n">
-        <v>60.36</v>
+        <v>60.95</v>
       </c>
       <c r="W12" t="n">
-        <v>35.35</v>
+        <v>35.33</v>
       </c>
       <c r="X12" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>538.3665999999999</v>
+        <v>542.848</v>
       </c>
       <c r="AA12" t="n">
-        <v>407.2589</v>
+        <v>408.9318</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2376,13 +2376,13 @@
         <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>41.1</v>
+        <v>39</v>
       </c>
       <c r="AH12" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AI12" t="n">
-        <v>543.96</v>
+        <v>564.66</v>
       </c>
       <c r="AJ12" t="n">
         <v>362.53</v>
@@ -2394,14 +2394,14 @@
         <v>647.1</v>
       </c>
       <c r="AM12" t="n">
-        <v>14.42</v>
+        <v>14.94</v>
       </c>
       <c r="AN12" t="n">
-        <v>51.26</v>
+        <v>52.59</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 63.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.4%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 62.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.9%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>361.04</v>
+        <v>358.64</v>
       </c>
       <c r="F13" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="J13" t="n">
         <v>60.8</v>
       </c>
       <c r="K13" t="n">
-        <v>68.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 4.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-4.01</v>
+        <v>-4.43</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.96</v>
+        <v>-14</v>
       </c>
       <c r="T13" t="n">
-        <v>3.91</v>
+        <v>2.74</v>
       </c>
       <c r="U13" t="n">
-        <v>28.99</v>
+        <v>27.17</v>
       </c>
       <c r="V13" t="n">
-        <v>27.8</v>
+        <v>27.66</v>
       </c>
       <c r="W13" t="n">
-        <v>18.06</v>
+        <v>18.07</v>
       </c>
       <c r="X13" t="n">
         <v>-21.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
-        <v>377.802</v>
+        <v>377.1878</v>
       </c>
       <c r="AA13" t="n">
-        <v>363.5818</v>
+        <v>363.9777</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="AF13" t="n">
         <v>60.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>68.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AH13" t="n">
         <v>755</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-4.44</v>
+        <v>-4.92</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.7</v>
+        <v>-1.47</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.4%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.53</v>
+        <v>25.865</v>
       </c>
       <c r="F14" t="n">
         <v>39.3</v>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="I14" t="n">
-        <v>53.3</v>
+        <v>46.8</v>
       </c>
       <c r="J14" t="n">
         <v>15.3</v>
       </c>
       <c r="K14" t="n">
-        <v>61.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>29.8</v>
+        <v>34</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 8.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>10.22</v>
+        <v>4.7</v>
       </c>
       <c r="S14" t="n">
-        <v>9.720000000000001</v>
+        <v>6.44</v>
       </c>
       <c r="T14" t="n">
-        <v>-11.93</v>
+        <v>-14.81</v>
       </c>
       <c r="U14" t="n">
-        <v>-12.74</v>
+        <v>-13.31</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.11</v>
+        <v>-3.93</v>
       </c>
       <c r="W14" t="n">
-        <v>34.02</v>
+        <v>34.05</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.5113</v>
+        <v>24.5557</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9103</v>
+        <v>26.8912</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,13 +2694,13 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>53.3</v>
+        <v>46.8</v>
       </c>
       <c r="AF14" t="n">
         <v>20.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>61.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AH14" t="n">
         <v>756</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.24</v>
+        <v>5.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.41</v>
+        <v>-3.82</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.3%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.7</v>
+        <v>71.72</v>
       </c>
       <c r="F2" t="n">
-        <v>79.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -680,10 +680,10 @@
         <v>69.2</v>
       </c>
       <c r="K2" t="n">
-        <v>57.2</v>
+        <v>59.1</v>
       </c>
       <c r="L2" t="n">
-        <v>69.5</v>
+        <v>71</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -707,26 +707,26 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 10.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>9.48</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>26.25</v>
+        <v>25.74</v>
       </c>
       <c r="T2" t="n">
-        <v>38.02</v>
+        <v>37.82</v>
       </c>
       <c r="U2" t="n">
-        <v>63.23</v>
+        <v>63.26</v>
       </c>
       <c r="V2" t="n">
-        <v>26.04</v>
+        <v>26.02</v>
       </c>
       <c r="W2" t="n">
-        <v>13.78</v>
+        <v>13.77</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
@@ -735,10 +735,10 @@
         <v>1.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>64.94840000000001</v>
+        <v>65.258</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.4611</v>
+        <v>55.5858</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,13 +756,13 @@
         <v>69.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>57.2</v>
+        <v>59.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI2" t="n">
-        <v>66.59999999999999</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>54.81</v>
@@ -774,14 +774,14 @@
         <v>72.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.28</v>
+        <v>29.03</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.4%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.575</v>
+        <v>49.225</v>
       </c>
       <c r="F3" t="n">
-        <v>79.3</v>
+        <v>78.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>65.3</v>
+        <v>65.2</v>
       </c>
       <c r="K3" t="n">
-        <v>73.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="L3" t="n">
-        <v>78.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -869,23 +869,23 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>6.65</v>
+        <v>9.43</v>
       </c>
       <c r="S3" t="n">
-        <v>17.6</v>
+        <v>18.29</v>
       </c>
       <c r="T3" t="n">
-        <v>27.81</v>
+        <v>29.3</v>
       </c>
       <c r="U3" t="n">
-        <v>45.39</v>
+        <v>49.05</v>
       </c>
       <c r="V3" t="n">
-        <v>19.55</v>
+        <v>20.05</v>
       </c>
       <c r="W3" t="n">
         <v>16.18</v>
@@ -894,13 +894,13 @@
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>45.6843</v>
+        <v>45.8697</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.6756</v>
+        <v>40.7463</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
         <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>65.3</v>
+        <v>65.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>73.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI3" t="n">
-        <v>45.845</v>
+        <v>45.945</v>
       </c>
       <c r="AJ3" t="n">
         <v>39.31</v>
@@ -936,14 +936,14 @@
         <v>49.485</v>
       </c>
       <c r="AM3" t="n">
-        <v>6.33</v>
+        <v>7.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.42</v>
+        <v>20.81</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.3%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.3%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>164.16</v>
+        <v>164.64</v>
       </c>
       <c r="F4" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="L4" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3.61</v>
+        <v>4.07</v>
       </c>
       <c r="S4" t="n">
         <v>11.39</v>
       </c>
       <c r="T4" t="n">
-        <v>13.23</v>
+        <v>13.76</v>
       </c>
       <c r="U4" t="n">
-        <v>27.67</v>
+        <v>27.43</v>
       </c>
       <c r="V4" t="n">
-        <v>17.59</v>
+        <v>17.68</v>
       </c>
       <c r="W4" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>157.2968</v>
+        <v>157.7112</v>
       </c>
       <c r="AA4" t="n">
-        <v>147.4076</v>
+        <v>147.5467</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,16 +1074,16 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
@@ -1098,14 +1098,14 @@
         <v>164.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.36</v>
+        <v>11.59</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124.11</v>
+        <v>124.17</v>
       </c>
       <c r="F5" t="n">
         <v>76</v>
@@ -1166,7 +1166,7 @@
         <v>66.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="L5" t="n">
         <v>76.59999999999999</v>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="S5" t="n">
-        <v>10.65</v>
+        <v>10.46</v>
       </c>
       <c r="T5" t="n">
-        <v>11.19</v>
+        <v>11.49</v>
       </c>
       <c r="U5" t="n">
-        <v>24.62</v>
+        <v>25.15</v>
       </c>
       <c r="V5" t="n">
-        <v>17.41</v>
+        <v>17.4</v>
       </c>
       <c r="W5" t="n">
         <v>13.19</v>
@@ -1221,10 +1221,10 @@
         <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>119.3124</v>
+        <v>119.601</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.638</v>
+        <v>112.7309</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1242,10 +1242,10 @@
         <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
@@ -1260,14 +1260,14 @@
         <v>124.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.02</v>
+        <v>3.82</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.18</v>
+        <v>10.15</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>699.6799999999999</v>
+        <v>63.63</v>
       </c>
       <c r="F6" t="n">
-        <v>75.5</v>
+        <v>75.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.7</v>
+        <v>71.2</v>
       </c>
       <c r="I6" t="n">
-        <v>79.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>64.3</v>
+        <v>71.5</v>
       </c>
       <c r="K6" t="n">
-        <v>81.8</v>
+        <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.59</v>
+        <v>4.94</v>
       </c>
       <c r="S6" t="n">
-        <v>11.88</v>
+        <v>7.88</v>
       </c>
       <c r="T6" t="n">
-        <v>10.79</v>
+        <v>12.22</v>
       </c>
       <c r="U6" t="n">
-        <v>26.31</v>
+        <v>20.89</v>
       </c>
       <c r="V6" t="n">
-        <v>18.52</v>
+        <v>14.5</v>
       </c>
       <c r="W6" t="n">
-        <v>14.16</v>
+        <v>12.88</v>
       </c>
       <c r="X6" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>671.184</v>
+        <v>61.2626</v>
       </c>
       <c r="AA6" t="n">
-        <v>632.5137</v>
+        <v>58.1866</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>79.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.3</v>
+        <v>71.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.8</v>
+        <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AI6" t="n">
-        <v>681.24</v>
+        <v>61.4745</v>
       </c>
       <c r="AJ6" t="n">
-        <v>597.92</v>
+        <v>56.4209</v>
       </c>
       <c r="AK6" t="n">
-        <v>703.9400000000001</v>
+        <v>63.63</v>
       </c>
       <c r="AL6" t="n">
-        <v>703.9400000000001</v>
+        <v>63.63</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.62</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,14 +1466,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.25</v>
+        <v>698.02</v>
       </c>
       <c r="F7" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70.8</v>
+        <v>70.5</v>
       </c>
       <c r="I7" t="n">
-        <v>73.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>76.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4.38</v>
+        <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>7.96</v>
+        <v>11.47</v>
       </c>
       <c r="T7" t="n">
-        <v>12.15</v>
+        <v>10.82</v>
       </c>
       <c r="U7" t="n">
-        <v>19.11</v>
+        <v>25.56</v>
       </c>
       <c r="V7" t="n">
-        <v>14.3</v>
+        <v>18.4</v>
       </c>
       <c r="W7" t="n">
-        <v>12.88</v>
+        <v>14.16</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.1499</v>
+        <v>672.9712</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.1382</v>
+        <v>633.0239</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>73.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
@@ -1572,36 +1572,36 @@
         <v>759</v>
       </c>
       <c r="AI7" t="n">
-        <v>61.4745</v>
+        <v>681.24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>56.0747</v>
+        <v>597.92</v>
       </c>
       <c r="AK7" t="n">
-        <v>63.25</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AL7" t="n">
-        <v>63.25</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.43</v>
+        <v>3.72</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.789999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.25 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.07 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.77</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1646,16 +1646,16 @@
         <v>65.5</v>
       </c>
       <c r="I8" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>81.7</v>
+        <v>82.3</v>
       </c>
       <c r="L8" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,16 +1683,16 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="S8" t="n">
-        <v>9.210000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>11.57</v>
+        <v>11.88</v>
       </c>
       <c r="U8" t="n">
-        <v>21.21</v>
+        <v>22.13</v>
       </c>
       <c r="V8" t="n">
         <v>15.41</v>
@@ -1707,10 +1707,10 @@
         <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.667</v>
+        <v>72.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>68.973</v>
+        <v>69.0282</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,19 +1722,19 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>81.7</v>
+        <v>82.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.59</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>66.58</v>
@@ -1746,14 +1746,14 @@
         <v>75.89</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.27</v>
+        <v>4.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>63.98</v>
+        <v>63.85</v>
       </c>
       <c r="F9" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1808,16 +1808,16 @@
         <v>61.7</v>
       </c>
       <c r="I9" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="J9" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K9" t="n">
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,22 +1845,22 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.52</v>
+        <v>-1.04</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.95</v>
+        <v>-2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6.82</v>
+        <v>6.74</v>
       </c>
       <c r="W9" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="X9" t="n">
         <v>-12.85</v>
@@ -1869,10 +1869,10 @@
         <v>0.71</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.3816</v>
+        <v>63.3858</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1244</v>
+        <v>63.1282</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="AG9" t="n">
         <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI9" t="n">
         <v>63.51</v>
@@ -1908,14 +1908,14 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.9%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.274</v>
+        <v>18.422</v>
       </c>
       <c r="F10" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1976,10 +1976,10 @@
         <v>45.6</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>58.1</v>
       </c>
       <c r="L10" t="n">
-        <v>62.9</v>
+        <v>62.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2003,38 +2003,38 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 9.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>9.52</v>
+        <v>11.35</v>
       </c>
       <c r="S10" t="n">
-        <v>31.75</v>
+        <v>33.76</v>
       </c>
       <c r="T10" t="n">
-        <v>28.44</v>
+        <v>30.52</v>
       </c>
       <c r="U10" t="n">
-        <v>45.01</v>
+        <v>47.66</v>
       </c>
       <c r="V10" t="n">
-        <v>18.48</v>
+        <v>18.77</v>
       </c>
       <c r="W10" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.6226</v>
+        <v>16.7222</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.5869</v>
+        <v>14.6136</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
         <v>50.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>59</v>
+        <v>58.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI10" t="n">
         <v>17.092</v>
@@ -2070,14 +2070,14 @@
         <v>18.54</v>
       </c>
       <c r="AM10" t="n">
-        <v>9.93</v>
+        <v>10.16</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.28</v>
+        <v>26.06</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.2%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.466</v>
+        <v>10.342</v>
       </c>
       <c r="F11" t="n">
-        <v>64.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>32.1</v>
@@ -2141,7 +2141,7 @@
         <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>58.2</v>
+        <v>57.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-0.36</v>
+        <v>0.53</v>
       </c>
       <c r="S11" t="n">
-        <v>13.52</v>
+        <v>11.15</v>
       </c>
       <c r="T11" t="n">
-        <v>27.41</v>
+        <v>27.11</v>
       </c>
       <c r="U11" t="n">
-        <v>61.81</v>
+        <v>59.99</v>
       </c>
       <c r="V11" t="n">
-        <v>3.18</v>
+        <v>2.76</v>
       </c>
       <c r="W11" t="n">
         <v>23.42</v>
@@ -2190,13 +2190,13 @@
         <v>-43.46</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.3021</v>
+        <v>10.3337</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.8345</v>
+        <v>8.850899999999999</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>85</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AF11" t="n">
         <v>37.1</v>
@@ -2217,7 +2217,7 @@
         <v>82.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI11" t="n">
         <v>9.914999999999999</v>
@@ -2232,14 +2232,14 @@
         <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.59</v>
+        <v>0.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.47</v>
+        <v>16.85</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 63.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.1%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>623.97</v>
+        <v>659.88</v>
       </c>
       <c r="F12" t="n">
-        <v>62.9</v>
+        <v>59.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>58.2</v>
+        <v>59.4</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="K12" t="n">
-        <v>39</v>
+        <v>16.7</v>
       </c>
       <c r="L12" t="n">
-        <v>31.1</v>
+        <v>14.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 14.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 20.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>14.25</v>
+        <v>21.31</v>
       </c>
       <c r="S12" t="n">
-        <v>58.5</v>
+        <v>67.09</v>
       </c>
       <c r="T12" t="n">
-        <v>77.36</v>
+        <v>88.08</v>
       </c>
       <c r="U12" t="n">
-        <v>137.65</v>
+        <v>153.04</v>
       </c>
       <c r="V12" t="n">
-        <v>60.95</v>
+        <v>63.89</v>
       </c>
       <c r="W12" t="n">
-        <v>35.33</v>
+        <v>35.45</v>
       </c>
       <c r="X12" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>542.848</v>
+        <v>547.5872000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>408.9318</v>
+        <v>410.8032</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2373,40 +2373,40 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>39</v>
+        <v>16.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AI12" t="n">
-        <v>564.66</v>
+        <v>567.88</v>
       </c>
       <c r="AJ12" t="n">
         <v>362.53</v>
       </c>
       <c r="AK12" t="n">
-        <v>647.1</v>
+        <v>659.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>647.1</v>
+        <v>659.88</v>
       </c>
       <c r="AM12" t="n">
-        <v>14.94</v>
+        <v>20.51</v>
       </c>
       <c r="AN12" t="n">
-        <v>52.59</v>
+        <v>60.63</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 62.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.9%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 59.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.5%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 647.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 659.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>358.64</v>
+        <v>361.71</v>
       </c>
       <c r="F13" t="n">
-        <v>54.4</v>
+        <v>55.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="J13" t="n">
         <v>60.8</v>
       </c>
       <c r="K13" t="n">
-        <v>67.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="L13" t="n">
-        <v>56.4</v>
+        <v>57.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,43 +2484,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-4.43</v>
+        <v>-3.15</v>
       </c>
       <c r="S13" t="n">
-        <v>-14</v>
+        <v>-13.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.74</v>
+        <v>4.18</v>
       </c>
       <c r="U13" t="n">
-        <v>27.17</v>
+        <v>26.81</v>
       </c>
       <c r="V13" t="n">
-        <v>27.66</v>
+        <v>27.98</v>
       </c>
       <c r="W13" t="n">
-        <v>18.07</v>
+        <v>18.06</v>
       </c>
       <c r="X13" t="n">
         <v>-21.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>377.1878</v>
+        <v>376.6952</v>
       </c>
       <c r="AA13" t="n">
-        <v>363.9777</v>
+        <v>364.3808</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="AF13" t="n">
         <v>60.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AI13" t="n">
         <v>340.82</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-4.92</v>
+        <v>-3.98</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1.47</v>
+        <v>-0.73</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.9%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.0%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.865</v>
+        <v>25.88</v>
       </c>
       <c r="F14" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="I14" t="n">
-        <v>46.8</v>
+        <v>45.6</v>
       </c>
       <c r="J14" t="n">
         <v>15.3</v>
       </c>
       <c r="K14" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="L14" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4.7</v>
+        <v>2.31</v>
       </c>
       <c r="S14" t="n">
-        <v>6.44</v>
+        <v>5.76</v>
       </c>
       <c r="T14" t="n">
-        <v>-14.81</v>
+        <v>-14.98</v>
       </c>
       <c r="U14" t="n">
-        <v>-13.31</v>
+        <v>-13.81</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.93</v>
+        <v>-3.91</v>
       </c>
       <c r="W14" t="n">
-        <v>34.05</v>
+        <v>34.03</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.5557</v>
+        <v>24.6063</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.8912</v>
+        <v>26.87</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,16 +2694,16 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>46.8</v>
+        <v>45.6</v>
       </c>
       <c r="AF14" t="n">
         <v>20.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI14" t="n">
         <v>24.93</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.33</v>
+        <v>5.18</v>
       </c>
       <c r="AN14" t="n">
-        <v>-3.82</v>
+        <v>-3.68</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.3%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.72</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>80.2</v>
+        <v>80</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.2</v>
       </c>
       <c r="K2" t="n">
-        <v>59.1</v>
+        <v>56.9</v>
       </c>
       <c r="L2" t="n">
-        <v>71</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -707,23 +707,23 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 9.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>9.880000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>25.74</v>
+        <v>27</v>
       </c>
       <c r="T2" t="n">
-        <v>37.82</v>
+        <v>38.54</v>
       </c>
       <c r="U2" t="n">
-        <v>63.26</v>
+        <v>64.62</v>
       </c>
       <c r="V2" t="n">
-        <v>26.02</v>
+        <v>26.37</v>
       </c>
       <c r="W2" t="n">
         <v>13.77</v>
@@ -732,13 +732,13 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Z2" t="n">
-        <v>65.258</v>
+        <v>65.5444</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.5858</v>
+        <v>55.7142</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,37 +756,37 @@
         <v>69.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>59.1</v>
+        <v>56.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI2" t="n">
-        <v>66.84999999999999</v>
+        <v>68.45</v>
       </c>
       <c r="AJ2" t="n">
         <v>54.81</v>
       </c>
       <c r="AK2" t="n">
-        <v>72.27</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AL2" t="n">
-        <v>72.27</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>9.9</v>
+        <v>10.46</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.03</v>
+        <v>29.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.5%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.225</v>
+        <v>50.16</v>
       </c>
       <c r="F3" t="n">
-        <v>78.8</v>
+        <v>78</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>70.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -842,10 +842,10 @@
         <v>65.2</v>
       </c>
       <c r="K3" t="n">
-        <v>69.5</v>
+        <v>62.9</v>
       </c>
       <c r="L3" t="n">
-        <v>77.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -864,43 +864,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>9.43</v>
+        <v>9.41</v>
       </c>
       <c r="S3" t="n">
-        <v>18.29</v>
+        <v>21.38</v>
       </c>
       <c r="T3" t="n">
-        <v>29.3</v>
+        <v>32.73</v>
       </c>
       <c r="U3" t="n">
-        <v>49.05</v>
+        <v>50.25</v>
       </c>
       <c r="V3" t="n">
-        <v>20.05</v>
+        <v>20.78</v>
       </c>
       <c r="W3" t="n">
-        <v>16.18</v>
+        <v>16.21</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>45.8697</v>
+        <v>46.0295</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.7463</v>
+        <v>40.8219</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>65.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>69.5</v>
+        <v>62.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI3" t="n">
         <v>45.945</v>
@@ -930,25 +930,25 @@
         <v>39.31</v>
       </c>
       <c r="AK3" t="n">
-        <v>49.485</v>
+        <v>50.16</v>
       </c>
       <c r="AL3" t="n">
-        <v>49.485</v>
+        <v>50.16</v>
       </c>
       <c r="AM3" t="n">
-        <v>7.31</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.81</v>
+        <v>22.88</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.3%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>164.64</v>
+        <v>165.46</v>
       </c>
       <c r="F4" t="n">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="I4" t="n">
-        <v>81.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>81.2</v>
+        <v>80</v>
       </c>
       <c r="L4" t="n">
-        <v>77.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>4.07</v>
+        <v>3.57</v>
       </c>
       <c r="S4" t="n">
-        <v>11.39</v>
+        <v>12.71</v>
       </c>
       <c r="T4" t="n">
-        <v>13.76</v>
+        <v>14.84</v>
       </c>
       <c r="U4" t="n">
-        <v>27.43</v>
+        <v>28.4</v>
       </c>
       <c r="V4" t="n">
-        <v>17.68</v>
+        <v>17.85</v>
       </c>
       <c r="W4" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>157.7112</v>
+        <v>158.0588</v>
       </c>
       <c r="AA4" t="n">
-        <v>147.5467</v>
+        <v>147.6913</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,16 +1074,16 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>81.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>81.2</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
@@ -1092,25 +1092,25 @@
         <v>140.98</v>
       </c>
       <c r="AK4" t="n">
-        <v>164.88</v>
+        <v>165.46</v>
       </c>
       <c r="AL4" t="n">
-        <v>164.88</v>
+        <v>165.46</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.39</v>
+        <v>4.68</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.59</v>
+        <v>12.03</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 165.46 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124.17</v>
+        <v>124.67</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I5" t="n">
-        <v>77.8</v>
+        <v>80</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>76.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>3.22</v>
+        <v>2.74</v>
       </c>
       <c r="S5" t="n">
-        <v>10.46</v>
+        <v>11.61</v>
       </c>
       <c r="T5" t="n">
-        <v>11.49</v>
+        <v>12.36</v>
       </c>
       <c r="U5" t="n">
-        <v>25.15</v>
+        <v>25.17</v>
       </c>
       <c r="V5" t="n">
-        <v>17.4</v>
+        <v>17.54</v>
       </c>
       <c r="W5" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>119.601</v>
+        <v>119.8436</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.7309</v>
+        <v>112.8274</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,16 +1236,16 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>77.8</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
@@ -1254,25 +1254,25 @@
         <v>107.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>124.27</v>
+        <v>124.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>124.27</v>
+        <v>124.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.82</v>
+        <v>4.03</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.15</v>
+        <v>10.5</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.67 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63.63</v>
+        <v>701.66</v>
       </c>
       <c r="F6" t="n">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.2</v>
+        <v>70.7</v>
       </c>
       <c r="I6" t="n">
-        <v>73.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="J6" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="L6" t="n">
-        <v>76.5</v>
+        <v>76.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4.94</v>
+        <v>2.24</v>
       </c>
       <c r="S6" t="n">
-        <v>7.88</v>
+        <v>12.74</v>
       </c>
       <c r="T6" t="n">
-        <v>12.22</v>
+        <v>12.11</v>
       </c>
       <c r="U6" t="n">
-        <v>20.89</v>
+        <v>26.23</v>
       </c>
       <c r="V6" t="n">
-        <v>14.5</v>
+        <v>18.58</v>
       </c>
       <c r="W6" t="n">
-        <v>12.88</v>
+        <v>14.15</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>61.2626</v>
+        <v>674.5712</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.1866</v>
+        <v>633.5651</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>73.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="AH6" t="n">
         <v>760</v>
       </c>
       <c r="AI6" t="n">
-        <v>61.4745</v>
+        <v>681.24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>56.4209</v>
+        <v>597.92</v>
       </c>
       <c r="AK6" t="n">
-        <v>63.63</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.63</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.359999999999999</v>
+        <v>10.75</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,14 +1466,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>698.02</v>
+        <v>63.36</v>
       </c>
       <c r="F7" t="n">
-        <v>75.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70.5</v>
+        <v>70.8</v>
       </c>
       <c r="I7" t="n">
-        <v>78.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="J7" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>76.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.51</v>
+        <v>2.79</v>
       </c>
       <c r="S7" t="n">
-        <v>11.47</v>
+        <v>8.24</v>
       </c>
       <c r="T7" t="n">
-        <v>10.82</v>
+        <v>12.38</v>
       </c>
       <c r="U7" t="n">
-        <v>25.56</v>
+        <v>20.84</v>
       </c>
       <c r="V7" t="n">
-        <v>18.4</v>
+        <v>14.32</v>
       </c>
       <c r="W7" t="n">
-        <v>14.16</v>
+        <v>12.87</v>
       </c>
       <c r="X7" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>672.9712</v>
+        <v>61.3231</v>
       </c>
       <c r="AA7" t="n">
-        <v>633.0239</v>
+        <v>58.2354</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,48 +1560,48 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>78.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AI7" t="n">
-        <v>681.24</v>
+        <v>61.4745</v>
       </c>
       <c r="AJ7" t="n">
-        <v>597.92</v>
+        <v>56.4209</v>
       </c>
       <c r="AK7" t="n">
-        <v>703.9400000000001</v>
+        <v>63.63</v>
       </c>
       <c r="AL7" t="n">
-        <v>703.9400000000001</v>
+        <v>63.63</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.72</v>
+        <v>3.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.81999999999999</v>
+        <v>75.83</v>
       </c>
       <c r="F8" t="n">
-        <v>73.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1646,16 +1646,16 @@
         <v>65.5</v>
       </c>
       <c r="I8" t="n">
-        <v>75.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>82.3</v>
+        <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>75.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,22 +1683,22 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.71</v>
+        <v>3.04</v>
       </c>
       <c r="S8" t="n">
-        <v>9.119999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="T8" t="n">
-        <v>11.88</v>
+        <v>12.04</v>
       </c>
       <c r="U8" t="n">
-        <v>22.13</v>
+        <v>21.87</v>
       </c>
       <c r="V8" t="n">
-        <v>15.41</v>
+        <v>15.4</v>
       </c>
       <c r="W8" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
@@ -1707,10 +1707,10 @@
         <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.83</v>
+        <v>72.95780000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.0282</v>
+        <v>69.0853</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,19 +1722,19 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>75.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>82.3</v>
+        <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.73999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="AJ8" t="n">
         <v>66.58</v>
@@ -1746,14 +1746,14 @@
         <v>75.89</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.11</v>
+        <v>3.94</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.84</v>
+        <v>9.76</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>63.85</v>
+        <v>63.44</v>
       </c>
       <c r="F9" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>61.7</v>
+        <v>61.2</v>
       </c>
       <c r="I9" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="J9" t="n">
         <v>78.3</v>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-1.04</v>
+        <v>-1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.15</v>
+        <v>-1.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>6.74</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
         <v>9.550000000000001</v>
@@ -1866,13 +1866,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.3858</v>
+        <v>63.3808</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1282</v>
+        <v>63.1322</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="AF9" t="n">
         <v>78.3</v>
@@ -1893,10 +1893,10 @@
         <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.51</v>
+        <v>63.44</v>
       </c>
       <c r="AJ9" t="n">
         <v>62.06</v>
@@ -1908,14 +1908,14 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.73</v>
+        <v>0.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.14</v>
+        <v>0.49</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.1%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,18 +1956,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.422</v>
+        <v>18.786</v>
       </c>
       <c r="F10" t="n">
-        <v>68.5</v>
+        <v>67.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>51.7</v>
+        <v>52.5</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1976,10 +1976,10 @@
         <v>45.6</v>
       </c>
       <c r="K10" t="n">
-        <v>58.1</v>
+        <v>51.8</v>
       </c>
       <c r="L10" t="n">
-        <v>62.3</v>
+        <v>57.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2003,38 +2003,38 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 10.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>11.35</v>
+        <v>9.9</v>
       </c>
       <c r="S10" t="n">
-        <v>33.76</v>
+        <v>36.27</v>
       </c>
       <c r="T10" t="n">
-        <v>30.52</v>
+        <v>34.03</v>
       </c>
       <c r="U10" t="n">
-        <v>47.66</v>
+        <v>48.91</v>
       </c>
       <c r="V10" t="n">
-        <v>18.77</v>
+        <v>19.52</v>
       </c>
       <c r="W10" t="n">
-        <v>21.55</v>
+        <v>21.56</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.7222</v>
+        <v>16.8126</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.6136</v>
+        <v>14.6416</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
         <v>50.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>58.1</v>
+        <v>51.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI10" t="n">
         <v>17.092</v>
@@ -2064,25 +2064,25 @@
         <v>12.936</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.54</v>
+        <v>18.786</v>
       </c>
       <c r="AL10" t="n">
-        <v>18.54</v>
+        <v>18.786</v>
       </c>
       <c r="AM10" t="n">
-        <v>10.16</v>
+        <v>11.74</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.06</v>
+        <v>28.31</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.2%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.54 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.342</v>
+        <v>10.512</v>
       </c>
       <c r="F11" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="I11" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
         <v>32.1</v>
@@ -2141,7 +2141,7 @@
         <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>57.4</v>
+        <v>58.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0.53</v>
+        <v>-0.51</v>
       </c>
       <c r="S11" t="n">
-        <v>11.15</v>
+        <v>13.74</v>
       </c>
       <c r="T11" t="n">
-        <v>27.11</v>
+        <v>28.57</v>
       </c>
       <c r="U11" t="n">
-        <v>59.99</v>
+        <v>59.97</v>
       </c>
       <c r="V11" t="n">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="W11" t="n">
         <v>23.42</v>
@@ -2190,13 +2190,13 @@
         <v>-43.46</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.3337</v>
+        <v>10.3619</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.850899999999999</v>
+        <v>8.867800000000001</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>85</v>
       </c>
       <c r="AE11" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
         <v>37.1</v>
@@ -2217,7 +2217,7 @@
         <v>82.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI11" t="n">
         <v>9.914999999999999</v>
@@ -2232,14 +2232,14 @@
         <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.08</v>
+        <v>1.45</v>
       </c>
       <c r="AN11" t="n">
-        <v>16.85</v>
+        <v>18.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 63.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.1%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>361.71</v>
+        <v>354.79</v>
       </c>
       <c r="F13" t="n">
-        <v>55.2</v>
+        <v>54.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>68.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="I13" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
       <c r="J13" t="n">
         <v>60.8</v>
       </c>
       <c r="K13" t="n">
-        <v>69.3</v>
+        <v>66.8</v>
       </c>
       <c r="L13" t="n">
-        <v>57.4</v>
+        <v>56.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,43 +2484,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-3.15</v>
+        <v>-5.46</v>
       </c>
       <c r="S13" t="n">
-        <v>-13.36</v>
+        <v>-12.95</v>
       </c>
       <c r="T13" t="n">
-        <v>4.18</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>26.81</v>
+        <v>25.28</v>
       </c>
       <c r="V13" t="n">
-        <v>27.98</v>
+        <v>27.12</v>
       </c>
       <c r="W13" t="n">
-        <v>18.06</v>
+        <v>18.09</v>
       </c>
       <c r="X13" t="n">
         <v>-21.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>376.6952</v>
+        <v>375.9604</v>
       </c>
       <c r="AA13" t="n">
-        <v>364.3808</v>
+        <v>364.7486</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
       <c r="AF13" t="n">
         <v>60.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>69.3</v>
+        <v>66.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI13" t="n">
         <v>340.82</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-3.98</v>
+        <v>-5.63</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.73</v>
+        <v>-2.73</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.0%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.88</v>
+        <v>25.09</v>
       </c>
       <c r="F14" t="n">
-        <v>39.1</v>
+        <v>38.2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="I14" t="n">
-        <v>45.6</v>
+        <v>39.8</v>
       </c>
       <c r="J14" t="n">
         <v>15.3</v>
       </c>
       <c r="K14" t="n">
-        <v>73.5</v>
+        <v>78.2</v>
       </c>
       <c r="L14" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2.31</v>
+        <v>-0.32</v>
       </c>
       <c r="S14" t="n">
-        <v>5.76</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
-        <v>-14.98</v>
+        <v>-16.98</v>
       </c>
       <c r="U14" t="n">
-        <v>-13.81</v>
+        <v>-16.84</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.91</v>
+        <v>-4.89</v>
       </c>
       <c r="W14" t="n">
-        <v>34.03</v>
+        <v>34.05</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.6063</v>
+        <v>24.6398</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.87</v>
+        <v>26.8449</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,19 +2694,19 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>45.6</v>
+        <v>39.8</v>
       </c>
       <c r="AF14" t="n">
         <v>20.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>73.5</v>
+        <v>78.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI14" t="n">
-        <v>24.93</v>
+        <v>25.09</v>
       </c>
       <c r="AJ14" t="n">
         <v>20.205</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.18</v>
+        <v>1.83</v>
       </c>
       <c r="AN14" t="n">
-        <v>-3.68</v>
+        <v>-6.54</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 38.2, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.8%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72.40000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.2</v>
       </c>
       <c r="K2" t="n">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
       <c r="L2" t="n">
-        <v>69.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -707,38 +707,38 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 10.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>27</v>
+        <v>29.69</v>
       </c>
       <c r="T2" t="n">
-        <v>38.54</v>
+        <v>39.09</v>
       </c>
       <c r="U2" t="n">
-        <v>64.62</v>
+        <v>66.14</v>
       </c>
       <c r="V2" t="n">
-        <v>26.37</v>
+        <v>27.29</v>
       </c>
       <c r="W2" t="n">
-        <v>13.77</v>
+        <v>13.76</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Z2" t="n">
-        <v>65.5444</v>
+        <v>65.83459999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.7142</v>
+        <v>55.8445</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,37 +756,37 @@
         <v>69.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI2" t="n">
-        <v>68.45</v>
+        <v>68.89</v>
       </c>
       <c r="AJ2" t="n">
         <v>54.81</v>
       </c>
       <c r="AK2" t="n">
-        <v>72.40000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="AL2" t="n">
-        <v>72.40000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>10.46</v>
+        <v>10.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.95</v>
+        <v>29.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.5%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.51 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50.16</v>
+        <v>49.8</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>71.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -842,10 +842,10 @@
         <v>65.2</v>
       </c>
       <c r="K3" t="n">
-        <v>62.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>72.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -864,28 +864,28 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo 9.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>9.41</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>21.38</v>
+        <v>23.05</v>
       </c>
       <c r="T3" t="n">
-        <v>32.73</v>
+        <v>32.96</v>
       </c>
       <c r="U3" t="n">
-        <v>50.25</v>
+        <v>50.16</v>
       </c>
       <c r="V3" t="n">
-        <v>20.78</v>
+        <v>21.55</v>
       </c>
       <c r="W3" t="n">
         <v>16.21</v>
@@ -894,13 +894,13 @@
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>46.0295</v>
+        <v>46.1851</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.8219</v>
+        <v>40.8969</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>65.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>62.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI3" t="n">
         <v>45.945</v>
@@ -936,14 +936,14 @@
         <v>50.16</v>
       </c>
       <c r="AM3" t="n">
-        <v>8.970000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="AN3" t="n">
-        <v>22.88</v>
+        <v>21.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.8%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,30 +984,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>165.46</v>
+        <v>165.44</v>
       </c>
       <c r="F4" t="n">
-        <v>77.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>83.8</v>
+        <v>87</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L4" t="n">
-        <v>77.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,38 +1035,38 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="S4" t="n">
-        <v>12.71</v>
+        <v>14.67</v>
       </c>
       <c r="T4" t="n">
-        <v>14.84</v>
+        <v>15.55</v>
       </c>
       <c r="U4" t="n">
-        <v>28.4</v>
+        <v>28.49</v>
       </c>
       <c r="V4" t="n">
-        <v>17.85</v>
+        <v>18.44</v>
       </c>
       <c r="W4" t="n">
-        <v>12.92</v>
+        <v>12.93</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>158.0588</v>
+        <v>158.4044</v>
       </c>
       <c r="AA4" t="n">
-        <v>147.6913</v>
+        <v>147.8411</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1074,16 +1074,16 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>83.8</v>
+        <v>87</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
@@ -1098,14 +1098,14 @@
         <v>165.46</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.68</v>
+        <v>4.44</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.03</v>
+        <v>11.9</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.7%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124.67</v>
+        <v>124.82</v>
       </c>
       <c r="F5" t="n">
-        <v>76.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.3</v>
+        <v>73</v>
       </c>
       <c r="I5" t="n">
-        <v>80</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>77.2</v>
+        <v>78.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="S5" t="n">
-        <v>11.61</v>
+        <v>13.63</v>
       </c>
       <c r="T5" t="n">
-        <v>12.36</v>
+        <v>13.12</v>
       </c>
       <c r="U5" t="n">
-        <v>25.17</v>
+        <v>25.6</v>
       </c>
       <c r="V5" t="n">
-        <v>17.54</v>
+        <v>18.1</v>
       </c>
       <c r="W5" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>119.8436</v>
+        <v>120.086</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.8274</v>
+        <v>112.9285</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,16 +1236,16 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
@@ -1254,25 +1254,25 @@
         <v>107.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>124.67</v>
+        <v>124.82</v>
       </c>
       <c r="AL5" t="n">
-        <v>124.67</v>
+        <v>124.82</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.03</v>
+        <v>3.94</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.5</v>
+        <v>10.53</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.67 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.82 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>701.66</v>
+        <v>703.54</v>
       </c>
       <c r="F6" t="n">
-        <v>76.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>81.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>76.8</v>
+        <v>77.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="S6" t="n">
-        <v>12.74</v>
+        <v>14.71</v>
       </c>
       <c r="T6" t="n">
-        <v>12.11</v>
+        <v>13.13</v>
       </c>
       <c r="U6" t="n">
-        <v>26.23</v>
+        <v>26.63</v>
       </c>
       <c r="V6" t="n">
-        <v>18.58</v>
+        <v>19.16</v>
       </c>
       <c r="W6" t="n">
-        <v>14.15</v>
+        <v>14.16</v>
       </c>
       <c r="X6" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>674.5712</v>
+        <v>676.1572</v>
       </c>
       <c r="AA6" t="n">
-        <v>633.5651</v>
+        <v>634.1368</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,16 +1398,16 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>81.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AF6" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AH6" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AI6" t="n">
         <v>681.24</v>
@@ -1422,14 +1422,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.75</v>
+        <v>10.94</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.36</v>
+        <v>63.22</v>
       </c>
       <c r="F7" t="n">
-        <v>75.7</v>
+        <v>76.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>74.2</v>
+        <v>77.2</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>76.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="S7" t="n">
-        <v>8.24</v>
+        <v>10.75</v>
       </c>
       <c r="T7" t="n">
-        <v>12.38</v>
+        <v>11.25</v>
       </c>
       <c r="U7" t="n">
-        <v>20.84</v>
+        <v>21.57</v>
       </c>
       <c r="V7" t="n">
-        <v>14.32</v>
+        <v>14.87</v>
       </c>
       <c r="W7" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.3231</v>
+        <v>61.3819</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.2354</v>
+        <v>58.2829</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>74.2</v>
+        <v>77.2</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1569,7 +1569,7 @@
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AI7" t="n">
         <v>61.4745</v>
@@ -1584,14 +1584,14 @@
         <v>63.63</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.83</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>74.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>76.7</v>
+        <v>79</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="S8" t="n">
-        <v>9.99</v>
+        <v>11.59</v>
       </c>
       <c r="T8" t="n">
-        <v>12.04</v>
+        <v>12.05</v>
       </c>
       <c r="U8" t="n">
-        <v>21.87</v>
+        <v>22</v>
       </c>
       <c r="V8" t="n">
-        <v>15.4</v>
+        <v>15.86</v>
       </c>
       <c r="W8" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.95780000000001</v>
+        <v>73.0796</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.0853</v>
+        <v>69.1437</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>76.7</v>
+        <v>79</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1731,7 +1731,7 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI8" t="n">
         <v>73.8</v>
@@ -1746,14 +1746,14 @@
         <v>75.89</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.94</v>
+        <v>3.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.76</v>
+        <v>9.57</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>63.44</v>
+        <v>63.52</v>
       </c>
       <c r="F9" t="n">
-        <v>68.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>61.2</v>
+        <v>61.9</v>
       </c>
       <c r="I9" t="n">
-        <v>49.2</v>
+        <v>51</v>
       </c>
       <c r="J9" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K9" t="n">
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>70.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,34 +1845,34 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-1.21</v>
+        <v>-1.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.73</v>
+        <v>-0.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.87</v>
       </c>
       <c r="W9" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="X9" t="n">
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.3808</v>
+        <v>63.3784</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1322</v>
+        <v>63.1369</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>49.2</v>
+        <v>51</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="AG9" t="n">
         <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI9" t="n">
         <v>63.44</v>
@@ -1908,14 +1908,14 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.49</v>
+        <v>0.61</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.1%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.2%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.786</v>
+        <v>18.916</v>
       </c>
       <c r="F10" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1976,10 +1976,10 @@
         <v>45.6</v>
       </c>
       <c r="K10" t="n">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="L10" t="n">
-        <v>57.5</v>
+        <v>57.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2003,38 +2003,38 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>9.9</v>
+        <v>10.32</v>
       </c>
       <c r="S10" t="n">
-        <v>36.27</v>
+        <v>39.4</v>
       </c>
       <c r="T10" t="n">
-        <v>34.03</v>
+        <v>36.4</v>
       </c>
       <c r="U10" t="n">
-        <v>48.91</v>
+        <v>50.51</v>
       </c>
       <c r="V10" t="n">
-        <v>19.52</v>
+        <v>20.98</v>
       </c>
       <c r="W10" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.8126</v>
+        <v>16.9072</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.6416</v>
+        <v>14.671</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
         <v>50.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI10" t="n">
         <v>17.092</v>
@@ -2064,25 +2064,25 @@
         <v>12.936</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.786</v>
+        <v>18.916</v>
       </c>
       <c r="AL10" t="n">
-        <v>18.786</v>
+        <v>18.916</v>
       </c>
       <c r="AM10" t="n">
-        <v>11.74</v>
+        <v>11.88</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.31</v>
+        <v>28.93</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.92 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.512</v>
+        <v>10.684</v>
       </c>
       <c r="F11" t="n">
-        <v>64.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31.4</v>
+        <v>32.9</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="K11" t="n">
         <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2169,34 +2169,34 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-0.51</v>
+        <v>-1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>13.74</v>
+        <v>16.69</v>
       </c>
       <c r="T11" t="n">
-        <v>28.57</v>
+        <v>32.93</v>
       </c>
       <c r="U11" t="n">
-        <v>59.97</v>
+        <v>68.37</v>
       </c>
       <c r="V11" t="n">
-        <v>3.32</v>
+        <v>5.04</v>
       </c>
       <c r="W11" t="n">
-        <v>23.42</v>
+        <v>23.44</v>
       </c>
       <c r="X11" t="n">
-        <v>-43.46</v>
+        <v>-43.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.3619</v>
+        <v>10.3918</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.867800000000001</v>
+        <v>8.886100000000001</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,13 +2211,13 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="AG11" t="n">
         <v>82.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI11" t="n">
         <v>9.914999999999999</v>
@@ -2232,14 +2232,14 @@
         <v>11.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.54</v>
+        <v>20.23</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>659.88</v>
+        <v>668.91</v>
       </c>
       <c r="F12" t="n">
         <v>59.9</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>59.4</v>
+        <v>60.8</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -2300,10 +2300,10 @@
         <v>23.9</v>
       </c>
       <c r="K12" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="L12" t="n">
-        <v>14.1</v>
+        <v>12.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 20.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 21.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>21.31</v>
+        <v>18.46</v>
       </c>
       <c r="S12" t="n">
-        <v>67.09</v>
+        <v>73.86</v>
       </c>
       <c r="T12" t="n">
-        <v>88.08</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>153.04</v>
+        <v>155.53</v>
       </c>
       <c r="V12" t="n">
-        <v>63.89</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>35.45</v>
+        <v>35.46</v>
       </c>
       <c r="X12" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="Z12" t="n">
-        <v>547.5872000000001</v>
+        <v>552.3592</v>
       </c>
       <c r="AA12" t="n">
-        <v>410.8032</v>
+        <v>412.7201</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2376,37 +2376,37 @@
         <v>28.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AI12" t="n">
-        <v>567.88</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AJ12" t="n">
         <v>362.53</v>
       </c>
       <c r="AK12" t="n">
-        <v>659.88</v>
+        <v>668.91</v>
       </c>
       <c r="AL12" t="n">
-        <v>659.88</v>
+        <v>668.91</v>
       </c>
       <c r="AM12" t="n">
-        <v>20.51</v>
+        <v>21.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.63</v>
+        <v>62.07</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 59.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.5%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 59.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.1%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 659.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>354.79</v>
+        <v>348.23</v>
       </c>
       <c r="F13" t="n">
-        <v>54.2</v>
+        <v>54.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="I13" t="n">
-        <v>39.2</v>
+        <v>42.6</v>
       </c>
       <c r="J13" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="K13" t="n">
-        <v>66.8</v>
+        <v>64.5</v>
       </c>
       <c r="L13" t="n">
-        <v>56.1</v>
+        <v>56.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 5.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-5.46</v>
+        <v>-6.97</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.95</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>-0.86</v>
       </c>
       <c r="U13" t="n">
-        <v>25.28</v>
+        <v>23.18</v>
       </c>
       <c r="V13" t="n">
-        <v>27.12</v>
+        <v>27.39</v>
       </c>
       <c r="W13" t="n">
-        <v>18.09</v>
+        <v>18.12</v>
       </c>
       <c r="X13" t="n">
         <v>-21.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z13" t="n">
-        <v>375.9604</v>
+        <v>375.0458</v>
       </c>
       <c r="AA13" t="n">
-        <v>364.7486</v>
+        <v>365.0718</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>39.2</v>
+        <v>42.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>66.8</v>
+        <v>64.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AI13" t="n">
         <v>340.82</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.63</v>
+        <v>-7.15</v>
       </c>
       <c r="AN13" t="n">
-        <v>-2.73</v>
+        <v>-4.61</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.09</v>
+        <v>25.315</v>
       </c>
       <c r="F14" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="I14" t="n">
-        <v>39.8</v>
+        <v>44</v>
       </c>
       <c r="J14" t="n">
         <v>15.3</v>
@@ -2627,7 +2627,7 @@
         <v>78.2</v>
       </c>
       <c r="L14" t="n">
-        <v>33.8</v>
+        <v>35</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-0.32</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>3.02</v>
+        <v>5.04</v>
       </c>
       <c r="T14" t="n">
-        <v>-16.98</v>
+        <v>-15.22</v>
       </c>
       <c r="U14" t="n">
-        <v>-16.84</v>
+        <v>-15.71</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.89</v>
+        <v>-3.11</v>
       </c>
       <c r="W14" t="n">
-        <v>34.05</v>
+        <v>34.04</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.14</v>
+        <v>-0.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.6398</v>
+        <v>24.7195</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.8449</v>
+        <v>26.8206</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>39.8</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
         <v>20.3</v>
@@ -2703,7 +2703,7 @@
         <v>78.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI14" t="n">
         <v>25.09</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="AN14" t="n">
-        <v>-6.54</v>
+        <v>-5.61</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 38.2, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.8%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,18 +660,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72.51000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="F2" t="n">
-        <v>80.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>80.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.2</v>
       </c>
       <c r="K2" t="n">
-        <v>58.2</v>
+        <v>54.4</v>
       </c>
       <c r="L2" t="n">
-        <v>70.5</v>
+        <v>67.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>8.470000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="S2" t="n">
-        <v>29.69</v>
+        <v>33.05</v>
       </c>
       <c r="T2" t="n">
-        <v>39.09</v>
+        <v>40.88</v>
       </c>
       <c r="U2" t="n">
-        <v>66.14</v>
+        <v>68.09</v>
       </c>
       <c r="V2" t="n">
-        <v>27.29</v>
+        <v>28.13</v>
       </c>
       <c r="W2" t="n">
-        <v>13.76</v>
+        <v>13.78</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Z2" t="n">
-        <v>65.83459999999999</v>
+        <v>66.1416</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.8445</v>
+        <v>55.9789</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -756,7 +756,7 @@
         <v>69.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>58.2</v>
+        <v>54.4</v>
       </c>
       <c r="AH2" t="n">
         <v>755</v>
@@ -768,25 +768,25 @@
         <v>54.81</v>
       </c>
       <c r="AK2" t="n">
-        <v>72.51000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="AL2" t="n">
-        <v>72.51000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>10.14</v>
+        <v>11.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.84</v>
+        <v>31.25</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 80.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.1%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.51 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -818,14 +818,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.8</v>
+        <v>166.04</v>
       </c>
       <c r="F3" t="n">
-        <v>78.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>72</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>65.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>67.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>75.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>8.390000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="S3" t="n">
-        <v>23.05</v>
+        <v>16.4</v>
       </c>
       <c r="T3" t="n">
-        <v>32.96</v>
+        <v>15.74</v>
       </c>
       <c r="U3" t="n">
-        <v>50.16</v>
+        <v>30.1</v>
       </c>
       <c r="V3" t="n">
-        <v>21.55</v>
+        <v>18.66</v>
       </c>
       <c r="W3" t="n">
-        <v>16.21</v>
+        <v>12.93</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>46.1851</v>
+        <v>158.754</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.8969</v>
+        <v>147.9919</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,48 +912,48 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>65.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>67.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="AI3" t="n">
-        <v>45.945</v>
+        <v>159.24</v>
       </c>
       <c r="AJ3" t="n">
-        <v>39.31</v>
+        <v>140.98</v>
       </c>
       <c r="AK3" t="n">
-        <v>50.16</v>
+        <v>166.04</v>
       </c>
       <c r="AL3" t="n">
-        <v>50.16</v>
+        <v>166.04</v>
       </c>
       <c r="AM3" t="n">
-        <v>7.83</v>
+        <v>4.59</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.77</v>
+        <v>12.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.8%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 79.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.6%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>165.44</v>
+        <v>50.73</v>
       </c>
       <c r="F4" t="n">
-        <v>78.8</v>
+        <v>78.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>74.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="I4" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>67.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="K4" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="L4" t="n">
-        <v>78.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1026,43 +1026,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3.45</v>
+        <v>8.9</v>
       </c>
       <c r="S4" t="n">
-        <v>14.67</v>
+        <v>27.69</v>
       </c>
       <c r="T4" t="n">
-        <v>15.55</v>
+        <v>35.12</v>
       </c>
       <c r="U4" t="n">
-        <v>28.49</v>
+        <v>53.38</v>
       </c>
       <c r="V4" t="n">
-        <v>18.44</v>
+        <v>22.65</v>
       </c>
       <c r="W4" t="n">
-        <v>12.93</v>
+        <v>16.23</v>
       </c>
       <c r="X4" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>158.4044</v>
+        <v>46.3517</v>
       </c>
       <c r="AA4" t="n">
-        <v>147.8411</v>
+        <v>40.9763</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,48 +1074,48 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
-        <v>67.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="AH4" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AI4" t="n">
-        <v>159.24</v>
+        <v>45.945</v>
       </c>
       <c r="AJ4" t="n">
-        <v>140.98</v>
+        <v>39.31</v>
       </c>
       <c r="AK4" t="n">
-        <v>165.46</v>
+        <v>50.73</v>
       </c>
       <c r="AL4" t="n">
-        <v>165.46</v>
+        <v>50.73</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.44</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.9</v>
+        <v>23.8</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 165.46 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124.82</v>
+        <v>125.04</v>
       </c>
       <c r="F5" t="n">
-        <v>77.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="I5" t="n">
-        <v>83.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>78.2</v>
+        <v>78.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.72</v>
+        <v>1.81</v>
       </c>
       <c r="S5" t="n">
-        <v>13.63</v>
+        <v>14.99</v>
       </c>
       <c r="T5" t="n">
-        <v>13.12</v>
+        <v>13.18</v>
       </c>
       <c r="U5" t="n">
-        <v>25.6</v>
+        <v>25.88</v>
       </c>
       <c r="V5" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="W5" t="n">
         <v>13.19</v>
@@ -1218,17 +1218,17 @@
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>120.086</v>
+        <v>120.327</v>
       </c>
       <c r="AA5" t="n">
-        <v>112.9285</v>
+        <v>113.0294</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1254,25 +1254,25 @@
         <v>107.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>124.82</v>
+        <v>125.04</v>
       </c>
       <c r="AL5" t="n">
-        <v>124.82</v>
+        <v>125.04</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.53</v>
+        <v>10.63</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>SWDA.MI: scenario base Buy Watchlist, score 78.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.82 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>703.54</v>
+        <v>63.63</v>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>78</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I6" t="n">
-        <v>85.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="J6" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>77.8</v>
+        <v>78.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="S6" t="n">
-        <v>14.71</v>
+        <v>13.47</v>
       </c>
       <c r="T6" t="n">
-        <v>13.13</v>
+        <v>12.44</v>
       </c>
       <c r="U6" t="n">
-        <v>26.63</v>
+        <v>22.08</v>
       </c>
       <c r="V6" t="n">
-        <v>19.16</v>
+        <v>15.28</v>
       </c>
       <c r="W6" t="n">
-        <v>14.16</v>
+        <v>12.88</v>
       </c>
       <c r="X6" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>676.1572</v>
+        <v>61.4452</v>
       </c>
       <c r="AA6" t="n">
-        <v>634.1368</v>
+        <v>58.3367</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>85.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI6" t="n">
-        <v>681.24</v>
+        <v>61.4745</v>
       </c>
       <c r="AJ6" t="n">
-        <v>597.92</v>
+        <v>56.4209</v>
       </c>
       <c r="AK6" t="n">
-        <v>703.9400000000001</v>
+        <v>63.63</v>
       </c>
       <c r="AL6" t="n">
-        <v>703.9400000000001</v>
+        <v>63.63</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.94</v>
+        <v>9.07</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 78.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,14 +1466,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.22</v>
+        <v>703.6</v>
       </c>
       <c r="F7" t="n">
-        <v>76.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>77.2</v>
+        <v>86.7</v>
       </c>
       <c r="J7" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>77.5</v>
+        <v>78.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.56</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>10.75</v>
+        <v>15.62</v>
       </c>
       <c r="T7" t="n">
-        <v>11.25</v>
+        <v>13.16</v>
       </c>
       <c r="U7" t="n">
-        <v>21.57</v>
+        <v>27.73</v>
       </c>
       <c r="V7" t="n">
-        <v>14.87</v>
+        <v>19.08</v>
       </c>
       <c r="W7" t="n">
-        <v>12.88</v>
+        <v>14.16</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.3819</v>
+        <v>677.7148</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.2829</v>
+        <v>634.7016</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,48 +1560,48 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>77.2</v>
+        <v>86.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AI7" t="n">
-        <v>61.4745</v>
+        <v>681.24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>56.4209</v>
+        <v>597.92</v>
       </c>
       <c r="AK7" t="n">
-        <v>63.63</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AL7" t="n">
-        <v>63.63</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.99</v>
+        <v>3.82</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.470000000000001</v>
+        <v>10.86</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.76000000000001</v>
+        <v>75.94</v>
       </c>
       <c r="F8" t="n">
-        <v>75.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>66.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="I8" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>76.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="S8" t="n">
-        <v>11.59</v>
+        <v>12.82</v>
       </c>
       <c r="T8" t="n">
-        <v>12.05</v>
+        <v>12.22</v>
       </c>
       <c r="U8" t="n">
-        <v>22</v>
+        <v>22.74</v>
       </c>
       <c r="V8" t="n">
-        <v>15.86</v>
+        <v>15.95</v>
       </c>
       <c r="W8" t="n">
         <v>12.88</v>
@@ -1704,13 +1704,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.0796</v>
+        <v>73.2024</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.1437</v>
+        <v>69.2025</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1740,25 +1740,25 @@
         <v>66.58</v>
       </c>
       <c r="AK8" t="n">
-        <v>75.89</v>
+        <v>75.94</v>
       </c>
       <c r="AL8" t="n">
-        <v>75.89</v>
+        <v>75.94</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.57</v>
+        <v>9.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>63.52</v>
+        <v>63.57</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
       <c r="I9" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
       <c r="J9" t="n">
         <v>78.2</v>
@@ -1817,7 +1817,7 @@
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-1.03</v>
+        <v>-1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>6.87</v>
+        <v>6.76</v>
       </c>
       <c r="W9" t="n">
         <v>9.56</v>
@@ -1866,13 +1866,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.3784</v>
+        <v>63.3914</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1369</v>
+        <v>63.1403</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
       <c r="AF9" t="n">
         <v>78.2</v>
@@ -1902,20 +1902,20 @@
         <v>62.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>64.68000000000001</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="AL9" t="n">
         <v>64.68000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.2%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.3%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.916</v>
+        <v>19.164</v>
       </c>
       <c r="F10" t="n">
-        <v>67.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>53.5</v>
+        <v>54.3</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1976,10 +1976,10 @@
         <v>45.6</v>
       </c>
       <c r="K10" t="n">
-        <v>51.2</v>
+        <v>47.9</v>
       </c>
       <c r="L10" t="n">
-        <v>57.2</v>
+        <v>54.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2003,23 +2003,23 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 11.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 12.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>10.32</v>
+        <v>8.44</v>
       </c>
       <c r="S10" t="n">
-        <v>39.4</v>
+        <v>42.76</v>
       </c>
       <c r="T10" t="n">
-        <v>36.4</v>
+        <v>38.47</v>
       </c>
       <c r="U10" t="n">
-        <v>50.51</v>
+        <v>52.41</v>
       </c>
       <c r="V10" t="n">
-        <v>20.98</v>
+        <v>21.84</v>
       </c>
       <c r="W10" t="n">
         <v>21.57</v>
@@ -2028,13 +2028,13 @@
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.9072</v>
+        <v>17.0039</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.671</v>
+        <v>14.7015</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>50.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>51.2</v>
+        <v>47.9</v>
       </c>
       <c r="AH10" t="n">
         <v>755</v>
@@ -2064,25 +2064,25 @@
         <v>12.936</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.916</v>
+        <v>19.164</v>
       </c>
       <c r="AL10" t="n">
-        <v>18.916</v>
+        <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>11.88</v>
+        <v>12.7</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.93</v>
+        <v>30.35</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.7%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.92 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.684</v>
+        <v>622.05</v>
       </c>
       <c r="F11" t="n">
         <v>64.8</v>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>32.9</v>
+        <v>58.7</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>32.2</v>
+        <v>23.6</v>
       </c>
       <c r="K11" t="n">
-        <v>82.8</v>
+        <v>51.3</v>
       </c>
       <c r="L11" t="n">
-        <v>58.4</v>
+        <v>40.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 11.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-1.35</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>16.69</v>
+        <v>58.95</v>
       </c>
       <c r="T11" t="n">
-        <v>32.93</v>
+        <v>79.69</v>
       </c>
       <c r="U11" t="n">
-        <v>68.37</v>
+        <v>139.75</v>
       </c>
       <c r="V11" t="n">
-        <v>5.04</v>
+        <v>63.06</v>
       </c>
       <c r="W11" t="n">
-        <v>23.44</v>
+        <v>35.7</v>
       </c>
       <c r="X11" t="n">
-        <v>-43.36</v>
+        <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.22</v>
+        <v>1.77</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.3918</v>
+        <v>556.0626</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.886100000000001</v>
+        <v>414.3855</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,45 +2211,45 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>37.2</v>
+        <v>28.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>82.8</v>
+        <v>51.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="AI11" t="n">
-        <v>9.914999999999999</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8.7643</v>
+        <v>362.53</v>
       </c>
       <c r="AK11" t="n">
-        <v>11.61</v>
+        <v>668.91</v>
       </c>
       <c r="AL11" t="n">
-        <v>11.61</v>
+        <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.81</v>
+        <v>11.87</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.23</v>
+        <v>50.11</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.8%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>668.91</v>
+        <v>10.872</v>
       </c>
       <c r="F12" t="n">
-        <v>59.9</v>
+        <v>64.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>60.8</v>
+        <v>33.6</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>23.9</v>
+        <v>32.2</v>
       </c>
       <c r="K12" t="n">
-        <v>14.3</v>
+        <v>81.5</v>
       </c>
       <c r="L12" t="n">
-        <v>12.5</v>
+        <v>58.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 21.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>18.46</v>
+        <v>-2.05</v>
       </c>
       <c r="S12" t="n">
-        <v>73.86</v>
+        <v>19.01</v>
       </c>
       <c r="T12" t="n">
-        <v>97.79000000000001</v>
+        <v>34.35</v>
       </c>
       <c r="U12" t="n">
-        <v>155.53</v>
+        <v>71.66</v>
       </c>
       <c r="V12" t="n">
-        <v>66.81999999999999</v>
+        <v>6.06</v>
       </c>
       <c r="W12" t="n">
-        <v>35.46</v>
+        <v>23.45</v>
       </c>
       <c r="X12" t="n">
-        <v>-35.74</v>
+        <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.88</v>
+        <v>0.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>552.3592</v>
+        <v>10.4235</v>
       </c>
       <c r="AA12" t="n">
-        <v>412.7201</v>
+        <v>8.9054</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2373,45 +2373,45 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>28.9</v>
+        <v>37.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.3</v>
+        <v>81.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AI12" t="n">
-        <v>569.6900000000001</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>362.53</v>
+        <v>8.7643</v>
       </c>
       <c r="AK12" t="n">
-        <v>668.91</v>
+        <v>11.61</v>
       </c>
       <c r="AL12" t="n">
-        <v>668.91</v>
+        <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>21.1</v>
+        <v>4.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>62.07</v>
+        <v>22.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 59.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.1%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>348.23</v>
+        <v>352.3</v>
       </c>
       <c r="F13" t="n">
-        <v>54.8</v>
+        <v>55.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>68.2</v>
       </c>
       <c r="I13" t="n">
-        <v>42.6</v>
+        <v>45.5</v>
       </c>
       <c r="J13" t="n">
         <v>60.7</v>
       </c>
       <c r="K13" t="n">
-        <v>64.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>56.3</v>
+        <v>57.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,28 +2484,28 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.97</v>
+        <v>-6</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.029999999999999</v>
+        <v>-7.69</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.86</v>
+        <v>0.21</v>
       </c>
       <c r="U13" t="n">
-        <v>23.18</v>
+        <v>24.36</v>
       </c>
       <c r="V13" t="n">
-        <v>27.39</v>
+        <v>27.41</v>
       </c>
       <c r="W13" t="n">
         <v>18.12</v>
@@ -2517,10 +2517,10 @@
         <v>1.51</v>
       </c>
       <c r="Z13" t="n">
-        <v>375.0458</v>
+        <v>374.2578</v>
       </c>
       <c r="AA13" t="n">
-        <v>365.0718</v>
+        <v>365.4025</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>42.6</v>
+        <v>45.5</v>
       </c>
       <c r="AF13" t="n">
         <v>60.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>64.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AH13" t="n">
         <v>755</v>
@@ -2550,20 +2550,20 @@
         <v>340.82</v>
       </c>
       <c r="AK13" t="n">
-        <v>377.9</v>
+        <v>377.2</v>
       </c>
       <c r="AL13" t="n">
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-7.15</v>
+        <v>-5.87</v>
       </c>
       <c r="AN13" t="n">
-        <v>-4.61</v>
+        <v>-3.59</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.9%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.315</v>
+        <v>24.785</v>
       </c>
       <c r="F14" t="n">
-        <v>39.5</v>
+        <v>35.2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,28 +2615,28 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="I14" t="n">
-        <v>44</v>
+        <v>41.1</v>
       </c>
       <c r="J14" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="K14" t="n">
-        <v>78.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>31.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1.54</v>
+        <v>-2.65</v>
       </c>
       <c r="S14" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>-15.22</v>
+        <v>-15.55</v>
       </c>
       <c r="U14" t="n">
-        <v>-15.71</v>
+        <v>-16.31</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.11</v>
+        <v>-3.6</v>
       </c>
       <c r="W14" t="n">
-        <v>34.04</v>
+        <v>34.06</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.7195</v>
+        <v>24.8111</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.8206</v>
+        <v>26.7978</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2691,22 +2691,22 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AE14" t="n">
-        <v>44</v>
+        <v>41.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>78.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AH14" t="n">
         <v>756</v>
       </c>
       <c r="AI14" t="n">
-        <v>25.09</v>
+        <v>24.785</v>
       </c>
       <c r="AJ14" t="n">
         <v>20.205</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.41</v>
+        <v>-0.11</v>
       </c>
       <c r="AN14" t="n">
-        <v>-5.61</v>
+        <v>-7.51</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 35.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.1%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,18 +660,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73.47</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>80.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>81.5</v>
+        <v>80.2</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.2</v>
       </c>
       <c r="K2" t="n">
-        <v>54.4</v>
+        <v>65.2</v>
       </c>
       <c r="L2" t="n">
-        <v>67.7</v>
+        <v>75.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -702,47 +702,47 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 11.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>7.33</v>
+        <v>3.75</v>
       </c>
       <c r="S2" t="n">
-        <v>33.05</v>
+        <v>30.93</v>
       </c>
       <c r="T2" t="n">
-        <v>40.88</v>
+        <v>39.13</v>
       </c>
       <c r="U2" t="n">
-        <v>68.09</v>
+        <v>65.92</v>
       </c>
       <c r="V2" t="n">
-        <v>28.13</v>
+        <v>27.29</v>
       </c>
       <c r="W2" t="n">
-        <v>13.78</v>
+        <v>13.83</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Z2" t="n">
-        <v>66.1416</v>
+        <v>66.42359999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.9789</v>
+        <v>56.108</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -756,7 +756,7 @@
         <v>69.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>54.4</v>
+        <v>65.2</v>
       </c>
       <c r="AH2" t="n">
         <v>755</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>11.08</v>
+        <v>8.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.25</v>
+        <v>28.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 80.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.1%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 81.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.4%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -818,14 +818,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>166.04</v>
+        <v>48.45</v>
       </c>
       <c r="F3" t="n">
-        <v>79.5</v>
+        <v>80.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>74.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="I3" t="n">
-        <v>89.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>67.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>80.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="L3" t="n">
-        <v>79.5</v>
+        <v>81.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -869,38 +869,38 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="S3" t="n">
-        <v>16.4</v>
+        <v>20.73</v>
       </c>
       <c r="T3" t="n">
-        <v>15.74</v>
+        <v>30.88</v>
       </c>
       <c r="U3" t="n">
-        <v>30.1</v>
+        <v>48.17</v>
       </c>
       <c r="V3" t="n">
-        <v>18.66</v>
+        <v>20.7</v>
       </c>
       <c r="W3" t="n">
-        <v>12.93</v>
+        <v>16.44</v>
       </c>
       <c r="X3" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>158.754</v>
+        <v>46.4756</v>
       </c>
       <c r="AA3" t="n">
-        <v>147.9919</v>
+        <v>41.0446</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,48 +912,48 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>89.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>67.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>80.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AI3" t="n">
-        <v>159.24</v>
+        <v>45.945</v>
       </c>
       <c r="AJ3" t="n">
-        <v>140.98</v>
+        <v>39.31</v>
       </c>
       <c r="AK3" t="n">
-        <v>166.04</v>
+        <v>50.73</v>
       </c>
       <c r="AL3" t="n">
-        <v>166.04</v>
+        <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.59</v>
+        <v>4.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.2</v>
+        <v>18.04</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 79.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.6%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50.73</v>
+        <v>163.92</v>
       </c>
       <c r="F4" t="n">
-        <v>78.3</v>
+        <v>78.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="J4" t="n">
-        <v>65.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>61</v>
+        <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>70.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1026,43 +1026,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>8.9</v>
+        <v>0.7</v>
       </c>
       <c r="S4" t="n">
-        <v>27.69</v>
+        <v>14.36</v>
       </c>
       <c r="T4" t="n">
-        <v>35.12</v>
+        <v>15.08</v>
       </c>
       <c r="U4" t="n">
-        <v>53.38</v>
+        <v>28.02</v>
       </c>
       <c r="V4" t="n">
-        <v>22.65</v>
+        <v>18.23</v>
       </c>
       <c r="W4" t="n">
-        <v>16.23</v>
+        <v>12.95</v>
       </c>
       <c r="X4" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>46.3517</v>
+        <v>159.0628</v>
       </c>
       <c r="AA4" t="n">
-        <v>40.9763</v>
+        <v>148.1395</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,48 +1074,48 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>65.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>61</v>
+        <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="AI4" t="n">
-        <v>45.945</v>
+        <v>159.24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>39.31</v>
+        <v>140.98</v>
       </c>
       <c r="AK4" t="n">
-        <v>50.73</v>
+        <v>166.04</v>
       </c>
       <c r="AL4" t="n">
-        <v>50.73</v>
+        <v>166.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>9.449999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.8</v>
+        <v>10.65</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>125.04</v>
+        <v>123.92</v>
       </c>
       <c r="F5" t="n">
-        <v>78.2</v>
+        <v>77.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="I5" t="n">
-        <v>85.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.81</v>
+        <v>0.31</v>
       </c>
       <c r="S5" t="n">
-        <v>14.99</v>
+        <v>13.53</v>
       </c>
       <c r="T5" t="n">
-        <v>13.18</v>
+        <v>12.92</v>
       </c>
       <c r="U5" t="n">
-        <v>25.88</v>
+        <v>25.72</v>
       </c>
       <c r="V5" t="n">
-        <v>18.2</v>
+        <v>17.93</v>
       </c>
       <c r="W5" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>120.327</v>
+        <v>120.5462</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.0294</v>
+        <v>113.1305</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>85.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1260,14 +1260,14 @@
         <v>125.04</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.63</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Buy Watchlist, score 78.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63.63</v>
+        <v>63.18</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>72.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>81.8</v>
+        <v>79</v>
       </c>
       <c r="J6" t="n">
         <v>71.5</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>78.8</v>
+        <v>78</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>-0.09</v>
       </c>
       <c r="S6" t="n">
-        <v>13.47</v>
+        <v>11.8</v>
       </c>
       <c r="T6" t="n">
-        <v>12.44</v>
+        <v>11.78</v>
       </c>
       <c r="U6" t="n">
-        <v>22.08</v>
+        <v>21.68</v>
       </c>
       <c r="V6" t="n">
-        <v>15.28</v>
+        <v>15.02</v>
       </c>
       <c r="W6" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="X6" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>61.4452</v>
+        <v>61.5015</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.3367</v>
+        <v>58.3864</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>81.8</v>
+        <v>79</v>
       </c>
       <c r="AF6" t="n">
         <v>71.5</v>
@@ -1422,14 +1422,14 @@
         <v>63.63</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.56</v>
+        <v>2.73</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.07</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 78.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>703.6</v>
+        <v>698.0599999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>77.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="J7" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>78.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>0.22</v>
       </c>
       <c r="S7" t="n">
-        <v>15.62</v>
+        <v>14.41</v>
       </c>
       <c r="T7" t="n">
-        <v>13.16</v>
+        <v>13.01</v>
       </c>
       <c r="U7" t="n">
-        <v>27.73</v>
+        <v>26.14</v>
       </c>
       <c r="V7" t="n">
-        <v>19.08</v>
+        <v>18.9</v>
       </c>
       <c r="W7" t="n">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="X7" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>677.7148</v>
+        <v>679.1627999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>634.7016</v>
+        <v>635.2736</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
@@ -1584,14 +1584,14 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.82</v>
+        <v>2.78</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.86</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.94</v>
+        <v>75.3</v>
       </c>
       <c r="F8" t="n">
-        <v>75.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>66.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>81</v>
+        <v>78.7</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>77.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1.93</v>
+        <v>0.45</v>
       </c>
       <c r="S8" t="n">
-        <v>12.82</v>
+        <v>11.26</v>
       </c>
       <c r="T8" t="n">
-        <v>12.22</v>
+        <v>12.12</v>
       </c>
       <c r="U8" t="n">
-        <v>22.74</v>
+        <v>22.72</v>
       </c>
       <c r="V8" t="n">
-        <v>15.95</v>
+        <v>15.77</v>
       </c>
       <c r="W8" t="n">
         <v>12.88</v>
@@ -1704,13 +1704,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.2024</v>
+        <v>73.31440000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.2025</v>
+        <v>69.2615</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>81</v>
+        <v>78.7</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1746,14 +1746,14 @@
         <v>75.94</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.74</v>
+        <v>2.71</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.74</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>63.57</v>
+        <v>64.06</v>
       </c>
       <c r="F9" t="n">
-        <v>69.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>61.7</v>
+        <v>62.6</v>
       </c>
       <c r="I9" t="n">
-        <v>52.5</v>
+        <v>54.9</v>
       </c>
       <c r="J9" t="n">
         <v>78.2</v>
@@ -1817,7 +1817,7 @@
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>71.5</v>
+        <v>72.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,23 +1841,23 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-1.38</v>
+        <v>-0.96</v>
       </c>
       <c r="S9" t="n">
-        <v>0.55</v>
+        <v>1.52</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>3.39</v>
       </c>
       <c r="U9" t="n">
-        <v>1.79</v>
+        <v>2.76</v>
       </c>
       <c r="V9" t="n">
-        <v>6.76</v>
+        <v>7.26</v>
       </c>
       <c r="W9" t="n">
         <v>9.56</v>
@@ -1866,13 +1866,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.3914</v>
+        <v>63.4182</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1403</v>
+        <v>63.1468</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>52.5</v>
+        <v>54.9</v>
       </c>
       <c r="AF9" t="n">
         <v>78.2</v>
@@ -1908,14 +1908,14 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.28</v>
+        <v>1.01</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.68</v>
+        <v>1.45</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.3%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.0%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,30 +1956,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19.164</v>
+        <v>18.45</v>
       </c>
       <c r="F10" t="n">
-        <v>67.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>54.3</v>
+        <v>52.8</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="K10" t="n">
-        <v>47.9</v>
+        <v>66.8</v>
       </c>
       <c r="L10" t="n">
-        <v>54.7</v>
+        <v>69</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2003,38 +2003,38 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 12.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>8.44</v>
+        <v>2.43</v>
       </c>
       <c r="S10" t="n">
-        <v>42.76</v>
+        <v>35.5</v>
       </c>
       <c r="T10" t="n">
-        <v>38.47</v>
+        <v>34.95</v>
       </c>
       <c r="U10" t="n">
-        <v>52.41</v>
+        <v>48.67</v>
       </c>
       <c r="V10" t="n">
-        <v>21.84</v>
+        <v>20.21</v>
       </c>
       <c r="W10" t="n">
-        <v>21.57</v>
+        <v>21.69</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.01</v>
+        <v>0.93</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.0039</v>
+        <v>17.0849</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.7015</v>
+        <v>14.7297</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
         <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>47.9</v>
+        <v>66.8</v>
       </c>
       <c r="AH10" t="n">
         <v>755</v>
@@ -2070,14 +2070,14 @@
         <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>12.7</v>
+        <v>7.99</v>
       </c>
       <c r="AN10" t="n">
-        <v>30.35</v>
+        <v>25.26</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.7%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>622.05</v>
+        <v>618.92</v>
       </c>
       <c r="F11" t="n">
-        <v>64.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>58.7</v>
+        <v>58.5</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -2138,10 +2138,10 @@
         <v>23.6</v>
       </c>
       <c r="K11" t="n">
-        <v>51.3</v>
+        <v>56.3</v>
       </c>
       <c r="L11" t="n">
-        <v>40.5</v>
+        <v>44.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 11.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>9.539999999999999</v>
+        <v>7.39</v>
       </c>
       <c r="S11" t="n">
-        <v>58.95</v>
+        <v>56.85</v>
       </c>
       <c r="T11" t="n">
-        <v>79.69</v>
+        <v>74.28</v>
       </c>
       <c r="U11" t="n">
-        <v>139.75</v>
+        <v>137.04</v>
       </c>
       <c r="V11" t="n">
-        <v>63.06</v>
+        <v>62.68</v>
       </c>
       <c r="W11" t="n">
-        <v>35.7</v>
+        <v>35.68</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Z11" t="n">
-        <v>556.0626</v>
+        <v>559.5742</v>
       </c>
       <c r="AA11" t="n">
-        <v>414.3855</v>
+        <v>416.0183</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         <v>28.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>51.3</v>
+        <v>56.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AI11" t="n">
         <v>569.6900000000001</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>11.87</v>
+        <v>10.61</v>
       </c>
       <c r="AN11" t="n">
-        <v>50.11</v>
+        <v>48.77</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 65.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.6%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.872</v>
+        <v>10.53</v>
       </c>
       <c r="F12" t="n">
         <v>64.8</v>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>33.6</v>
+        <v>32.7</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="K12" t="n">
-        <v>81.5</v>
+        <v>82.8</v>
       </c>
       <c r="L12" t="n">
-        <v>58.1</v>
+        <v>58.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2331,34 +2331,34 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-2.05</v>
+        <v>-6.17</v>
       </c>
       <c r="S12" t="n">
-        <v>19.01</v>
+        <v>17.81</v>
       </c>
       <c r="T12" t="n">
-        <v>34.35</v>
+        <v>32.64</v>
       </c>
       <c r="U12" t="n">
-        <v>71.66</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>6.06</v>
+        <v>4.83</v>
       </c>
       <c r="W12" t="n">
-        <v>23.45</v>
+        <v>23.52</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.4235</v>
+        <v>10.4492</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.9054</v>
+        <v>8.923400000000001</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2373,10 +2373,10 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>81.5</v>
+        <v>82.8</v>
       </c>
       <c r="AH12" t="n">
         <v>755</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.3</v>
+        <v>0.77</v>
       </c>
       <c r="AN12" t="n">
-        <v>22.08</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>352.3</v>
+        <v>349.36</v>
       </c>
       <c r="F13" t="n">
-        <v>55.8</v>
+        <v>56.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="I13" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J13" t="n">
         <v>60.7</v>
       </c>
       <c r="K13" t="n">
-        <v>66.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>57.6</v>
+        <v>58.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 5.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6</v>
+        <v>-7.55</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.69</v>
+        <v>-3.89</v>
       </c>
       <c r="T13" t="n">
-        <v>0.21</v>
+        <v>-0.7</v>
       </c>
       <c r="U13" t="n">
-        <v>24.36</v>
+        <v>23.49</v>
       </c>
       <c r="V13" t="n">
-        <v>27.41</v>
+        <v>27.04</v>
       </c>
       <c r="W13" t="n">
-        <v>18.12</v>
+        <v>18.13</v>
       </c>
       <c r="X13" t="n">
         <v>-21.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>374.2578</v>
+        <v>373.4988</v>
       </c>
       <c r="AA13" t="n">
-        <v>365.4025</v>
+        <v>365.6973</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="AF13" t="n">
         <v>60.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>66.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AH13" t="n">
         <v>755</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.87</v>
+        <v>-6.46</v>
       </c>
       <c r="AN13" t="n">
-        <v>-3.59</v>
+        <v>-4.47</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.9%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 56.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>24.785</v>
+        <v>25.305</v>
       </c>
       <c r="F14" t="n">
-        <v>35.2</v>
+        <v>40</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,28 +2615,28 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="I14" t="n">
-        <v>41.1</v>
+        <v>46.1</v>
       </c>
       <c r="J14" t="n">
         <v>15.2</v>
       </c>
       <c r="K14" t="n">
-        <v>75.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="L14" t="n">
-        <v>31.8</v>
+        <v>35.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-2.65</v>
+        <v>-1.06</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>5.61</v>
       </c>
       <c r="T14" t="n">
-        <v>-15.55</v>
+        <v>-13.31</v>
       </c>
       <c r="U14" t="n">
-        <v>-16.31</v>
+        <v>-15.14</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.6</v>
+        <v>-3.03</v>
       </c>
       <c r="W14" t="n">
-        <v>34.06</v>
+        <v>34.08</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.8111</v>
+        <v>24.8966</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.7978</v>
+        <v>26.778</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2691,16 +2691,16 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>41.1</v>
+        <v>46.1</v>
       </c>
       <c r="AF14" t="n">
         <v>20.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>75.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="AH14" t="n">
         <v>756</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.11</v>
+        <v>1.64</v>
       </c>
       <c r="AN14" t="n">
-        <v>-7.51</v>
+        <v>-5.5</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 35.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.1%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 40.0, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>81.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>80.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>65.2</v>
+        <v>61.4</v>
       </c>
       <c r="L2" t="n">
-        <v>75.8</v>
+        <v>73</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -702,43 +702,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 8.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>3.75</v>
+        <v>4.78</v>
       </c>
       <c r="S2" t="n">
-        <v>30.93</v>
+        <v>30.41</v>
       </c>
       <c r="T2" t="n">
-        <v>39.13</v>
+        <v>40.63</v>
       </c>
       <c r="U2" t="n">
-        <v>65.92</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>27.29</v>
+        <v>27.93</v>
       </c>
       <c r="W2" t="n">
-        <v>13.83</v>
+        <v>13.87</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="Z2" t="n">
-        <v>66.42359999999999</v>
+        <v>66.9888</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.108</v>
+        <v>56.3684</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -753,13 +753,13 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>65.2</v>
+        <v>61.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AI2" t="n">
         <v>68.89</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.4</v>
+        <v>9.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.32</v>
+        <v>29.93</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 81.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.4%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 81.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.3%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.45</v>
+        <v>48.725</v>
       </c>
       <c r="F3" t="n">
         <v>80.7</v>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="S3" t="n">
-        <v>20.73</v>
+        <v>19.75</v>
       </c>
       <c r="T3" t="n">
-        <v>30.88</v>
+        <v>30.02</v>
       </c>
       <c r="U3" t="n">
-        <v>48.17</v>
+        <v>48.37</v>
       </c>
       <c r="V3" t="n">
-        <v>20.7</v>
+        <v>20.87</v>
       </c>
       <c r="W3" t="n">
-        <v>16.44</v>
+        <v>16.42</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>46.4756</v>
+        <v>46.6981</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.0446</v>
+        <v>41.1816</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
         <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="AG3" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AI3" t="n">
         <v>45.945</v>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.04</v>
+        <v>18.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>163.92</v>
+        <v>164.2</v>
       </c>
       <c r="F4" t="n">
-        <v>78.8</v>
+        <v>78.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>74.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>86.2</v>
+        <v>84.3</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>79.2</v>
+        <v>78.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,22 +1035,22 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.7</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>14.36</v>
+        <v>13.49</v>
       </c>
       <c r="T4" t="n">
-        <v>15.08</v>
+        <v>14.41</v>
       </c>
       <c r="U4" t="n">
-        <v>28.02</v>
+        <v>27.13</v>
       </c>
       <c r="V4" t="n">
-        <v>18.23</v>
+        <v>18.24</v>
       </c>
       <c r="W4" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
@@ -1059,10 +1059,10 @@
         <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>159.0628</v>
+        <v>159.6216</v>
       </c>
       <c r="AA4" t="n">
-        <v>148.1395</v>
+        <v>148.4266</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>86.2</v>
+        <v>84.3</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1083,13 +1083,13 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>140.98</v>
+        <v>141.82</v>
       </c>
       <c r="AK4" t="n">
         <v>166.04</v>
@@ -1098,14 +1098,14 @@
         <v>166.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.65</v>
+        <v>10.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 141.82 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>123.92</v>
+        <v>124.08</v>
       </c>
       <c r="F5" t="n">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>72.8</v>
       </c>
       <c r="I5" t="n">
-        <v>83.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>78.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.31</v>
+        <v>0.99</v>
       </c>
       <c r="S5" t="n">
-        <v>13.53</v>
+        <v>12.65</v>
       </c>
       <c r="T5" t="n">
-        <v>12.92</v>
+        <v>12.36</v>
       </c>
       <c r="U5" t="n">
-        <v>25.72</v>
+        <v>25.78</v>
       </c>
       <c r="V5" t="n">
         <v>17.93</v>
       </c>
       <c r="W5" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
@@ -1221,10 +1221,10 @@
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>120.5462</v>
+        <v>120.9462</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.1305</v>
+        <v>113.3263</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,13 +1245,13 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>107.5</v>
+        <v>108.12</v>
       </c>
       <c r="AK5" t="n">
         <v>125.04</v>
@@ -1260,14 +1260,14 @@
         <v>125.04</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.539999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 108.12 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63.18</v>
+        <v>63.79</v>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I6" t="n">
-        <v>79</v>
+        <v>77.3</v>
       </c>
       <c r="J6" t="n">
         <v>71.5</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>78</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>-0.09</v>
+        <v>2.17</v>
       </c>
       <c r="S6" t="n">
-        <v>11.8</v>
+        <v>10.66</v>
       </c>
       <c r="T6" t="n">
-        <v>11.78</v>
+        <v>11.29</v>
       </c>
       <c r="U6" t="n">
-        <v>21.68</v>
+        <v>22.39</v>
       </c>
       <c r="V6" t="n">
-        <v>15.02</v>
+        <v>15.34</v>
       </c>
       <c r="W6" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="X6" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>61.5015</v>
+        <v>61.6106</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.3864</v>
+        <v>58.4865</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>79</v>
+        <v>77.3</v>
       </c>
       <c r="AF6" t="n">
         <v>71.5</v>
@@ -1407,39 +1407,39 @@
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AI6" t="n">
         <v>61.4745</v>
       </c>
       <c r="AJ6" t="n">
-        <v>56.4209</v>
+        <v>57.2813</v>
       </c>
       <c r="AK6" t="n">
-        <v>63.63</v>
+        <v>63.79</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.63</v>
+        <v>63.79</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.73</v>
+        <v>3.54</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.210000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 57.28 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>698.0599999999999</v>
+        <v>697.5599999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>76.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>71.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>84.5</v>
+        <v>82.8</v>
       </c>
       <c r="J7" t="n">
         <v>64.3</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>77.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="S7" t="n">
-        <v>14.41</v>
+        <v>13.75</v>
       </c>
       <c r="T7" t="n">
-        <v>13.01</v>
+        <v>12.12</v>
       </c>
       <c r="U7" t="n">
-        <v>26.14</v>
+        <v>25.01</v>
       </c>
       <c r="V7" t="n">
-        <v>18.9</v>
+        <v>18.82</v>
       </c>
       <c r="W7" t="n">
         <v>14.17</v>
@@ -1545,10 +1545,10 @@
         <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>679.1627999999999</v>
+        <v>681.798</v>
       </c>
       <c r="AA7" t="n">
-        <v>635.2736</v>
+        <v>636.3686</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>84.5</v>
+        <v>82.8</v>
       </c>
       <c r="AF7" t="n">
         <v>64.3</v>
@@ -1569,39 +1569,39 @@
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AI7" t="n">
         <v>681.24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>597.92</v>
+        <v>600.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>703.9400000000001</v>
+        <v>703.98</v>
       </c>
       <c r="AL7" t="n">
-        <v>703.9400000000001</v>
+        <v>703.98</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.880000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 600.12 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.3</v>
+        <v>75.66</v>
       </c>
       <c r="F8" t="n">
         <v>74.90000000000001</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="I8" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0.45</v>
+        <v>1.73</v>
       </c>
       <c r="S8" t="n">
-        <v>11.26</v>
+        <v>10.92</v>
       </c>
       <c r="T8" t="n">
-        <v>12.12</v>
+        <v>11.82</v>
       </c>
       <c r="U8" t="n">
-        <v>22.72</v>
+        <v>23.26</v>
       </c>
       <c r="V8" t="n">
-        <v>15.77</v>
+        <v>15.91</v>
       </c>
       <c r="W8" t="n">
         <v>12.88</v>
@@ -1704,13 +1704,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.31440000000001</v>
+        <v>73.5318</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.2615</v>
+        <v>69.3764</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1731,13 +1731,13 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AI8" t="n">
         <v>73.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>66.58</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="AK8" t="n">
         <v>75.94</v>
@@ -1746,14 +1746,14 @@
         <v>75.94</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.720000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 66.93 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64.06</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>70.2</v>
+        <v>70.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>62.6</v>
+        <v>63.1</v>
       </c>
       <c r="I9" t="n">
-        <v>54.9</v>
+        <v>55.7</v>
       </c>
       <c r="J9" t="n">
         <v>78.2</v>
@@ -1817,7 +1817,7 @@
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,34 +1845,34 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-0.96</v>
+        <v>0.99</v>
       </c>
       <c r="S9" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="T9" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="U9" t="n">
-        <v>2.76</v>
+        <v>3.53</v>
       </c>
       <c r="V9" t="n">
-        <v>7.26</v>
+        <v>7.51</v>
       </c>
       <c r="W9" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="X9" t="n">
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.4182</v>
+        <v>63.495</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1468</v>
+        <v>63.1648</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>54.9</v>
+        <v>55.7</v>
       </c>
       <c r="AF9" t="n">
         <v>78.2</v>
@@ -1893,7 +1893,7 @@
         <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AI9" t="n">
         <v>63.44</v>
@@ -1902,25 +1902,25 @@
         <v>62.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>64.51000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="AL9" t="n">
-        <v>64.68000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.0%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.70 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.45</v>
+        <v>18.592</v>
       </c>
       <c r="F10" t="n">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1976,10 +1976,10 @@
         <v>45.5</v>
       </c>
       <c r="K10" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="L10" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.43</v>
+        <v>4.86</v>
       </c>
       <c r="S10" t="n">
-        <v>35.5</v>
+        <v>35.85</v>
       </c>
       <c r="T10" t="n">
-        <v>34.95</v>
+        <v>35.95</v>
       </c>
       <c r="U10" t="n">
-        <v>48.67</v>
+        <v>49.45</v>
       </c>
       <c r="V10" t="n">
-        <v>20.21</v>
+        <v>20.46</v>
       </c>
       <c r="W10" t="n">
-        <v>21.69</v>
+        <v>21.66</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.0849</v>
+        <v>17.2374</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.7297</v>
+        <v>14.7864</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
         <v>50.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AI10" t="n">
         <v>17.092</v>
@@ -2070,14 +2070,14 @@
         <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>7.99</v>
+        <v>7.86</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.26</v>
+        <v>25.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>618.92</v>
+        <v>636.88</v>
       </c>
       <c r="F11" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>58.5</v>
+        <v>59.3</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -2138,10 +2138,10 @@
         <v>23.6</v>
       </c>
       <c r="K11" t="n">
-        <v>56.3</v>
+        <v>46.5</v>
       </c>
       <c r="L11" t="n">
-        <v>44.4</v>
+        <v>36.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 10.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 13.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>7.39</v>
+        <v>5.77</v>
       </c>
       <c r="S11" t="n">
-        <v>56.85</v>
+        <v>59.61</v>
       </c>
       <c r="T11" t="n">
-        <v>74.28</v>
+        <v>77.06</v>
       </c>
       <c r="U11" t="n">
-        <v>137.04</v>
+        <v>135.27</v>
       </c>
       <c r="V11" t="n">
-        <v>62.68</v>
+        <v>64.14</v>
       </c>
       <c r="W11" t="n">
-        <v>35.68</v>
+        <v>35.69</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>559.5742</v>
+        <v>563.2718</v>
       </c>
       <c r="AA11" t="n">
-        <v>416.0183</v>
+        <v>417.7247</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2214,16 +2214,16 @@
         <v>28.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>56.3</v>
+        <v>46.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AI11" t="n">
         <v>569.6900000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>362.53</v>
+        <v>383.4</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>10.61</v>
+        <v>13.07</v>
       </c>
       <c r="AN11" t="n">
-        <v>48.77</v>
+        <v>52.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 65.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.6%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.1%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 383.40 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.53</v>
+        <v>10.19</v>
       </c>
       <c r="F12" t="n">
-        <v>64.8</v>
+        <v>59.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,23 +2291,23 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>32.7</v>
+        <v>31.8</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="J12" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>82.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>58.4</v>
+        <v>53.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2331,34 +2331,34 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-6.17</v>
+        <v>-10.66</v>
       </c>
       <c r="S12" t="n">
-        <v>17.81</v>
+        <v>9.19</v>
       </c>
       <c r="T12" t="n">
-        <v>32.64</v>
+        <v>27.93</v>
       </c>
       <c r="U12" t="n">
-        <v>67.45999999999999</v>
+        <v>62.26</v>
       </c>
       <c r="V12" t="n">
-        <v>4.83</v>
+        <v>3.68</v>
       </c>
       <c r="W12" t="n">
-        <v>23.52</v>
+        <v>23.56</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.4492</v>
+        <v>10.4803</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.923400000000001</v>
+        <v>8.9572</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2367,19 +2367,19 @@
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="AG12" t="n">
-        <v>82.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AH12" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AI12" t="n">
         <v>9.914999999999999</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.77</v>
+        <v>-2.77</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>13.76</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 59.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>349.36</v>
+        <v>339.98</v>
       </c>
       <c r="F13" t="n">
-        <v>56.7</v>
+        <v>52.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>67.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="J13" t="n">
-        <v>60.7</v>
+        <v>60.4</v>
       </c>
       <c r="K13" t="n">
-        <v>65.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="L13" t="n">
-        <v>58.5</v>
+        <v>54.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,43 +2484,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-7.55</v>
+        <v>-7.38</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.89</v>
+        <v>-10.18</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7</v>
+        <v>-5.11</v>
       </c>
       <c r="U13" t="n">
-        <v>23.49</v>
+        <v>20.32</v>
       </c>
       <c r="V13" t="n">
-        <v>27.04</v>
+        <v>25.82</v>
       </c>
       <c r="W13" t="n">
-        <v>18.13</v>
+        <v>18.18</v>
       </c>
       <c r="X13" t="n">
-        <v>-21.9</v>
+        <v>-22.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>373.4988</v>
+        <v>371.4308</v>
       </c>
       <c r="AA13" t="n">
-        <v>365.6973</v>
+        <v>366.1597</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,22 +2532,22 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.7</v>
+        <v>60.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>65.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AI13" t="n">
-        <v>340.82</v>
+        <v>339.65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>340.82</v>
+        <v>339.65</v>
       </c>
       <c r="AK13" t="n">
         <v>377.2</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-6.46</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>-4.47</v>
+        <v>-7.15</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 56.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 52.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.5%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 340.82 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 339.65 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.305</v>
+        <v>25.22</v>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>40.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>21.8</v>
       </c>
       <c r="I14" t="n">
-        <v>46.1</v>
+        <v>49.8</v>
       </c>
       <c r="J14" t="n">
         <v>15.2</v>
@@ -2627,7 +2627,7 @@
         <v>78.2</v>
       </c>
       <c r="L14" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2655,22 +2655,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-1.06</v>
+        <v>-1.79</v>
       </c>
       <c r="S14" t="n">
-        <v>5.61</v>
+        <v>8.85</v>
       </c>
       <c r="T14" t="n">
-        <v>-13.31</v>
+        <v>-14.45</v>
       </c>
       <c r="U14" t="n">
-        <v>-15.14</v>
+        <v>-15.65</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.03</v>
+        <v>-3.13</v>
       </c>
       <c r="W14" t="n">
-        <v>34.08</v>
+        <v>34.06</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
@@ -2679,10 +2679,10 @@
         <v>-0.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.8966</v>
+        <v>24.9784</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.778</v>
+        <v>26.7573</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>46.1</v>
+        <v>49.8</v>
       </c>
       <c r="AF14" t="n">
         <v>20.2</v>
@@ -2703,7 +2703,7 @@
         <v>78.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI14" t="n">
         <v>24.785</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.64</v>
+        <v>0.97</v>
       </c>
       <c r="AN14" t="n">
-        <v>-5.5</v>
+        <v>-5.75</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 40.0, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 40.9, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.0%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73.23999999999999</v>
+        <v>72.83</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>61.4</v>
+        <v>65.7</v>
       </c>
       <c r="L2" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -702,28 +702,28 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 9.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>4.78</v>
+        <v>3.28</v>
       </c>
       <c r="S2" t="n">
-        <v>30.41</v>
+        <v>30.87</v>
       </c>
       <c r="T2" t="n">
-        <v>40.63</v>
+        <v>38.94</v>
       </c>
       <c r="U2" t="n">
-        <v>69.15000000000001</v>
+        <v>66.22</v>
       </c>
       <c r="V2" t="n">
-        <v>27.93</v>
+        <v>27.65</v>
       </c>
       <c r="W2" t="n">
         <v>13.87</v>
@@ -732,13 +732,13 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="Z2" t="n">
-        <v>66.9888</v>
+        <v>67.2694</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.3684</v>
+        <v>56.499</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,16 +756,16 @@
         <v>69.09999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>61.4</v>
+        <v>65.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI2" t="n">
         <v>68.89</v>
       </c>
       <c r="AJ2" t="n">
-        <v>54.81</v>
+        <v>56.24</v>
       </c>
       <c r="AK2" t="n">
         <v>73.47</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>9.33</v>
+        <v>8.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.93</v>
+        <v>28.9</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 81.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.3%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 81.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.3%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.24 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.725</v>
+        <v>48.16</v>
       </c>
       <c r="F3" t="n">
         <v>80.7</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>70.8</v>
+        <v>70.3</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -842,10 +842,10 @@
         <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>81.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>81.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1.85</v>
+        <v>0.43</v>
       </c>
       <c r="S3" t="n">
-        <v>19.75</v>
+        <v>21.2</v>
       </c>
       <c r="T3" t="n">
-        <v>30.02</v>
+        <v>27.44</v>
       </c>
       <c r="U3" t="n">
-        <v>48.37</v>
+        <v>43.55</v>
       </c>
       <c r="V3" t="n">
-        <v>20.87</v>
+        <v>20.37</v>
       </c>
       <c r="W3" t="n">
-        <v>16.42</v>
+        <v>16.43</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>46.6981</v>
+        <v>46.792</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.1816</v>
+        <v>41.2472</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -918,16 +918,16 @@
         <v>65</v>
       </c>
       <c r="AG3" t="n">
-        <v>81.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI3" t="n">
         <v>45.945</v>
       </c>
       <c r="AJ3" t="n">
-        <v>39.31</v>
+        <v>39.955</v>
       </c>
       <c r="AK3" t="n">
         <v>50.73</v>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.34</v>
+        <v>2.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.32</v>
+        <v>16.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.95 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>164.2</v>
+        <v>163.7</v>
       </c>
       <c r="F4" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>74.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>84.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>0.54</v>
       </c>
       <c r="S4" t="n">
-        <v>13.49</v>
+        <v>14.51</v>
       </c>
       <c r="T4" t="n">
-        <v>14.41</v>
+        <v>13.54</v>
       </c>
       <c r="U4" t="n">
-        <v>27.13</v>
+        <v>26.82</v>
       </c>
       <c r="V4" t="n">
-        <v>18.24</v>
+        <v>18.1</v>
       </c>
       <c r="W4" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>159.6216</v>
+        <v>159.8616</v>
       </c>
       <c r="AA4" t="n">
-        <v>148.4266</v>
+        <v>148.5673</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>84.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1083,13 +1083,13 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>141.82</v>
+        <v>143.92</v>
       </c>
       <c r="AK4" t="n">
         <v>166.04</v>
@@ -1098,14 +1098,14 @@
         <v>166.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.63</v>
+        <v>10.19</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 141.82 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 143.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124.08</v>
+        <v>123.73</v>
       </c>
       <c r="F5" t="n">
         <v>77.2</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1193,38 +1193,38 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.99</v>
+        <v>0.46</v>
       </c>
       <c r="S5" t="n">
-        <v>12.65</v>
+        <v>13.52</v>
       </c>
       <c r="T5" t="n">
-        <v>12.36</v>
+        <v>11.52</v>
       </c>
       <c r="U5" t="n">
-        <v>25.78</v>
+        <v>24.26</v>
       </c>
       <c r="V5" t="n">
-        <v>17.93</v>
+        <v>17.8</v>
       </c>
       <c r="W5" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>120.9462</v>
+        <v>121.1144</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.3263</v>
+        <v>113.4222</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,13 +1245,13 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>108.12</v>
+        <v>109.74</v>
       </c>
       <c r="AK5" t="n">
         <v>125.04</v>
@@ -1260,14 +1260,14 @@
         <v>125.04</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.59</v>
+        <v>2.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.49</v>
+        <v>9.09</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 108.12 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 109.74 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63.79</v>
+        <v>63.33</v>
       </c>
       <c r="F6" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>72.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="J6" t="n">
         <v>71.5</v>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.17</v>
+        <v>1.82</v>
       </c>
       <c r="S6" t="n">
-        <v>10.66</v>
+        <v>11.23</v>
       </c>
       <c r="T6" t="n">
-        <v>11.29</v>
+        <v>10.69</v>
       </c>
       <c r="U6" t="n">
-        <v>22.39</v>
+        <v>21.44</v>
       </c>
       <c r="V6" t="n">
-        <v>15.34</v>
+        <v>15.05</v>
       </c>
       <c r="W6" t="n">
         <v>12.88</v>
@@ -1380,13 +1380,13 @@
         <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>61.6106</v>
+        <v>61.6633</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.4865</v>
+        <v>58.5344</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="AF6" t="n">
         <v>71.5</v>
@@ -1407,13 +1407,13 @@
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AI6" t="n">
         <v>61.4745</v>
       </c>
       <c r="AJ6" t="n">
-        <v>57.2813</v>
+        <v>57.9933</v>
       </c>
       <c r="AK6" t="n">
         <v>63.79</v>
@@ -1422,14 +1422,14 @@
         <v>63.79</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.54</v>
+        <v>2.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.07</v>
+        <v>8.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 57.28 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 57.99 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>697.5599999999999</v>
+        <v>696.42</v>
       </c>
       <c r="F7" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>82.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>77.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1517,38 +1517,38 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.44</v>
+        <v>-0.18</v>
       </c>
       <c r="S7" t="n">
-        <v>13.75</v>
+        <v>14.69</v>
       </c>
       <c r="T7" t="n">
-        <v>12.12</v>
+        <v>11.52</v>
       </c>
       <c r="U7" t="n">
-        <v>25.01</v>
+        <v>24.65</v>
       </c>
       <c r="V7" t="n">
-        <v>18.82</v>
+        <v>18.73</v>
       </c>
       <c r="W7" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="X7" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>681.798</v>
+        <v>682.8828</v>
       </c>
       <c r="AA7" t="n">
-        <v>636.3686</v>
+        <v>636.9071</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,22 +1560,22 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>82.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AF7" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI7" t="n">
         <v>681.24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>600.12</v>
+        <v>608.66</v>
       </c>
       <c r="AK7" t="n">
         <v>703.98</v>
@@ -1584,14 +1584,14 @@
         <v>703.98</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 600.12 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 608.66 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.66</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>74.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>66.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>78.2</v>
+        <v>79.3</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>76.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>10.92</v>
+        <v>12.1</v>
       </c>
       <c r="T8" t="n">
-        <v>11.82</v>
+        <v>11.37</v>
       </c>
       <c r="U8" t="n">
-        <v>23.26</v>
+        <v>22.25</v>
       </c>
       <c r="V8" t="n">
-        <v>15.91</v>
+        <v>15.86</v>
       </c>
       <c r="W8" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.5318</v>
+        <v>73.62820000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.3764</v>
+        <v>69.4346</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>78.2</v>
+        <v>79.3</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1731,13 +1731,13 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI8" t="n">
         <v>73.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>66.93000000000001</v>
+        <v>67.67</v>
       </c>
       <c r="AK8" t="n">
         <v>75.94</v>
@@ -1746,14 +1746,14 @@
         <v>75.94</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.06</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.93 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 67.67 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64.54000000000001</v>
+        <v>18.288</v>
       </c>
       <c r="F9" t="n">
-        <v>70.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>63.1</v>
+        <v>52.4</v>
       </c>
       <c r="I9" t="n">
-        <v>55.7</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>78.2</v>
+        <v>45.5</v>
       </c>
       <c r="K9" t="n">
-        <v>82.8</v>
+        <v>76</v>
       </c>
       <c r="L9" t="n">
-        <v>72.5</v>
+        <v>73.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.99</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.98</v>
+        <v>36.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.36</v>
+        <v>32.62</v>
       </c>
       <c r="U9" t="n">
-        <v>3.53</v>
+        <v>44.5</v>
       </c>
       <c r="V9" t="n">
-        <v>7.51</v>
+        <v>19.77</v>
       </c>
       <c r="W9" t="n">
-        <v>9.57</v>
+        <v>21.67</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.85</v>
+        <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.495</v>
+        <v>17.3019</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1648</v>
+        <v>14.8131</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,48 +1884,48 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>55.7</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.2</v>
+        <v>50.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>82.8</v>
+        <v>76</v>
       </c>
       <c r="AH9" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.44</v>
+        <v>17.092</v>
       </c>
       <c r="AJ9" t="n">
-        <v>62.06</v>
+        <v>13.44</v>
       </c>
       <c r="AK9" t="n">
-        <v>64.7</v>
+        <v>19.164</v>
       </c>
       <c r="AL9" t="n">
-        <v>64.7</v>
+        <v>19.164</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.65</v>
+        <v>5.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.18</v>
+        <v>23.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.7%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.70 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 13.44 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,29 +1937,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.592</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>70.2</v>
+        <v>70.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>53</v>
+        <v>63.3</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="J10" t="n">
-        <v>45.5</v>
+        <v>78.2</v>
       </c>
       <c r="K10" t="n">
-        <v>67.3</v>
+        <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>69.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,57 +1988,57 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>4.86</v>
+        <v>1.84</v>
       </c>
       <c r="S10" t="n">
-        <v>35.85</v>
+        <v>2.29</v>
       </c>
       <c r="T10" t="n">
-        <v>35.95</v>
+        <v>3.81</v>
       </c>
       <c r="U10" t="n">
-        <v>49.45</v>
+        <v>3.96</v>
       </c>
       <c r="V10" t="n">
-        <v>20.46</v>
+        <v>7.67</v>
       </c>
       <c r="W10" t="n">
-        <v>21.66</v>
+        <v>9.56</v>
       </c>
       <c r="X10" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.2374</v>
+        <v>63.5298</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.7864</v>
+        <v>63.1763</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2046,48 +2046,48 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>50.5</v>
+        <v>78.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>67.3</v>
+        <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI10" t="n">
-        <v>17.092</v>
+        <v>63.44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12.936</v>
+        <v>62.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>19.164</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>19.164</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AM10" t="n">
-        <v>7.86</v>
+        <v>2.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.74</v>
+        <v>2.65</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>636.88</v>
+        <v>611.61</v>
       </c>
       <c r="F11" t="n">
-        <v>64.3</v>
+        <v>66.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>59.3</v>
+        <v>57.3</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="K11" t="n">
-        <v>46.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>52.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 13.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>5.77</v>
+        <v>2.71</v>
       </c>
       <c r="S11" t="n">
-        <v>59.61</v>
+        <v>60.59</v>
       </c>
       <c r="T11" t="n">
-        <v>77.06</v>
+        <v>68.41</v>
       </c>
       <c r="U11" t="n">
-        <v>135.27</v>
+        <v>122.93</v>
       </c>
       <c r="V11" t="n">
-        <v>64.14</v>
+        <v>60.24</v>
       </c>
       <c r="W11" t="n">
-        <v>35.69</v>
+        <v>35.73</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="Z11" t="n">
-        <v>563.2718</v>
+        <v>566.444</v>
       </c>
       <c r="AA11" t="n">
-        <v>417.7247</v>
+        <v>419.2983</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,10 +2211,10 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>46.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AH11" t="n">
         <v>753</v>
@@ -2223,7 +2223,7 @@
         <v>569.6900000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>383.4</v>
+        <v>391.97</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>13.07</v>
+        <v>7.97</v>
       </c>
       <c r="AN11" t="n">
-        <v>52.46</v>
+        <v>45.87</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.1%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 383.40 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 391.97 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.19</v>
+        <v>9.98</v>
       </c>
       <c r="F12" t="n">
-        <v>59.2</v>
+        <v>57.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
       <c r="I12" t="n">
-        <v>95.2</v>
+        <v>92.3</v>
       </c>
       <c r="J12" t="n">
         <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>75.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>53.4</v>
+        <v>51.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-10.66</v>
+        <v>-13.19</v>
       </c>
       <c r="S12" t="n">
-        <v>9.19</v>
+        <v>9.91</v>
       </c>
       <c r="T12" t="n">
-        <v>27.93</v>
+        <v>23.33</v>
       </c>
       <c r="U12" t="n">
-        <v>62.26</v>
+        <v>57.5</v>
       </c>
       <c r="V12" t="n">
-        <v>3.68</v>
+        <v>2.96</v>
       </c>
       <c r="W12" t="n">
-        <v>23.56</v>
+        <v>23.58</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.4803</v>
+        <v>10.491</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.9572</v>
+        <v>8.9716</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>95.2</v>
+        <v>92.3</v>
       </c>
       <c r="AF12" t="n">
         <v>37</v>
       </c>
       <c r="AG12" t="n">
-        <v>75.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI12" t="n">
         <v>9.914999999999999</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-2.77</v>
+        <v>-4.87</v>
       </c>
       <c r="AN12" t="n">
-        <v>13.76</v>
+        <v>11.24</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 59.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 57.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>339.98</v>
+        <v>344.28</v>
       </c>
       <c r="F13" t="n">
-        <v>52.8</v>
+        <v>55.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>37.8</v>
+        <v>45.7</v>
       </c>
       <c r="J13" t="n">
         <v>60.4</v>
       </c>
       <c r="K13" t="n">
-        <v>62.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>54.1</v>
+        <v>56.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,28 +2484,28 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 8.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-7.38</v>
+        <v>-6.94</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.18</v>
+        <v>-6.06</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.11</v>
+        <v>-3.59</v>
       </c>
       <c r="U13" t="n">
-        <v>20.32</v>
+        <v>25.33</v>
       </c>
       <c r="V13" t="n">
-        <v>25.82</v>
+        <v>26.3</v>
       </c>
       <c r="W13" t="n">
         <v>18.18</v>
@@ -2514,13 +2514,13 @@
         <v>-22.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>371.4308</v>
+        <v>370.4684</v>
       </c>
       <c r="AA13" t="n">
-        <v>366.1597</v>
+        <v>366.4099</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>37.8</v>
+        <v>45.7</v>
       </c>
       <c r="AF13" t="n">
         <v>60.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>62.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AH13" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI13" t="n">
         <v>339.65</v>
@@ -2550,20 +2550,20 @@
         <v>339.65</v>
       </c>
       <c r="AK13" t="n">
-        <v>377.2</v>
+        <v>372.59</v>
       </c>
       <c r="AL13" t="n">
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-8.470000000000001</v>
+        <v>-7.07</v>
       </c>
       <c r="AN13" t="n">
-        <v>-7.15</v>
+        <v>-6.04</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 52.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.5%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.22</v>
+        <v>26.055</v>
       </c>
       <c r="F14" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="I14" t="n">
-        <v>49.8</v>
+        <v>55</v>
       </c>
       <c r="J14" t="n">
-        <v>15.2</v>
+        <v>13.1</v>
       </c>
       <c r="K14" t="n">
         <v>78.2</v>
       </c>
       <c r="L14" t="n">
-        <v>36.5</v>
+        <v>37.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-1.79</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>8.85</v>
+        <v>11.27</v>
       </c>
       <c r="T14" t="n">
-        <v>-14.45</v>
+        <v>-12.39</v>
       </c>
       <c r="U14" t="n">
-        <v>-15.65</v>
+        <v>-13.41</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.13</v>
+        <v>-2.07</v>
       </c>
       <c r="W14" t="n">
-        <v>34.06</v>
+        <v>35.89</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.9784</v>
+        <v>25.1883</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.7573</v>
+        <v>26.7331</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,16 +2694,16 @@
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>49.8</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>20.2</v>
+        <v>18.1</v>
       </c>
       <c r="AG14" t="n">
         <v>78.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AI14" t="n">
         <v>24.785</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.97</v>
+        <v>3.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>-5.75</v>
+        <v>-2.54</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 40.9, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.0%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 41.7, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72.83</v>
+        <v>71.39</v>
       </c>
       <c r="F2" t="n">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>80.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>65.7</v>
+        <v>75.7</v>
       </c>
       <c r="L2" t="n">
-        <v>76.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -707,38 +707,38 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prezzo 8.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>3.28</v>
+        <v>0.61</v>
       </c>
       <c r="S2" t="n">
-        <v>30.87</v>
+        <v>29.64</v>
       </c>
       <c r="T2" t="n">
-        <v>38.94</v>
+        <v>36.42</v>
       </c>
       <c r="U2" t="n">
-        <v>66.22</v>
+        <v>63.95</v>
       </c>
       <c r="V2" t="n">
-        <v>27.65</v>
+        <v>26.3</v>
       </c>
       <c r="W2" t="n">
-        <v>13.87</v>
+        <v>13.93</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>67.2694</v>
+        <v>67.505</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.499</v>
+        <v>56.6218</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -753,13 +753,13 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="AG2" t="n">
-        <v>65.7</v>
+        <v>75.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI2" t="n">
         <v>68.89</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.27</v>
+        <v>5.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.9</v>
+        <v>26.08</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 81.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.3%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 82.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.16</v>
+        <v>47.74</v>
       </c>
       <c r="F3" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>70.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.43</v>
+        <v>-0.5</v>
       </c>
       <c r="S3" t="n">
-        <v>21.2</v>
+        <v>21.32</v>
       </c>
       <c r="T3" t="n">
-        <v>27.44</v>
+        <v>26.26</v>
       </c>
       <c r="U3" t="n">
-        <v>43.55</v>
+        <v>42.02</v>
       </c>
       <c r="V3" t="n">
-        <v>20.37</v>
+        <v>20.03</v>
       </c>
       <c r="W3" t="n">
-        <v>16.43</v>
+        <v>16.46</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>46.792</v>
+        <v>46.8593</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.2472</v>
+        <v>41.3092</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
         <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI3" t="n">
         <v>45.945</v>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.76</v>
+        <v>15.57</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>163.7</v>
+        <v>163.44</v>
       </c>
       <c r="F4" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I4" t="n">
-        <v>85.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>78.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.54</v>
+        <v>0.17</v>
       </c>
       <c r="S4" t="n">
-        <v>14.51</v>
+        <v>15.93</v>
       </c>
       <c r="T4" t="n">
-        <v>13.54</v>
+        <v>13.19</v>
       </c>
       <c r="U4" t="n">
-        <v>26.82</v>
+        <v>26.54</v>
       </c>
       <c r="V4" t="n">
-        <v>18.1</v>
+        <v>17.65</v>
       </c>
       <c r="W4" t="n">
-        <v>12.93</v>
+        <v>12.94</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>159.8616</v>
+        <v>160.0572</v>
       </c>
       <c r="AA4" t="n">
-        <v>148.5673</v>
+        <v>148.7023</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>85.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1083,7 +1083,7 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
@@ -1098,14 +1098,14 @@
         <v>166.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.19</v>
+        <v>9.91</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>123.73</v>
+        <v>123.88</v>
       </c>
       <c r="F5" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>81.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>77.8</v>
+        <v>78.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1193,38 +1193,38 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="S5" t="n">
-        <v>13.52</v>
+        <v>15.24</v>
       </c>
       <c r="T5" t="n">
-        <v>11.52</v>
+        <v>11.42</v>
       </c>
       <c r="U5" t="n">
-        <v>24.26</v>
+        <v>24.55</v>
       </c>
       <c r="V5" t="n">
-        <v>17.8</v>
+        <v>17.41</v>
       </c>
       <c r="W5" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.1144</v>
+        <v>121.2584</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.4222</v>
+        <v>113.5156</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>81.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,7 +1245,7 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
@@ -1263,11 +1263,11 @@
         <v>2.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.09</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63.33</v>
+        <v>697.76</v>
       </c>
       <c r="F6" t="n">
-        <v>76.8</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>77.5</v>
+        <v>86.5</v>
       </c>
       <c r="J6" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="K6" t="n">
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>77.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>1.82</v>
+        <v>-0.16</v>
       </c>
       <c r="S6" t="n">
-        <v>11.23</v>
+        <v>16.7</v>
       </c>
       <c r="T6" t="n">
-        <v>10.69</v>
+        <v>11.4</v>
       </c>
       <c r="U6" t="n">
-        <v>21.44</v>
+        <v>24.97</v>
       </c>
       <c r="V6" t="n">
-        <v>15.05</v>
+        <v>18.33</v>
       </c>
       <c r="W6" t="n">
-        <v>12.88</v>
+        <v>14.16</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>61.6633</v>
+        <v>683.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.5344</v>
+        <v>637.4372</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>77.5</v>
+        <v>86.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="AG6" t="n">
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="AI6" t="n">
-        <v>61.4745</v>
+        <v>681.24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>57.9933</v>
+        <v>608.66</v>
       </c>
       <c r="AK6" t="n">
-        <v>63.79</v>
+        <v>703.98</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.79</v>
+        <v>703.98</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.19</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 57.99 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 608.66 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,14 +1466,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>696.42</v>
+        <v>63.36</v>
       </c>
       <c r="F7" t="n">
-        <v>76.7</v>
+        <v>77</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>83.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>77.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1517,38 +1517,38 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>-0.18</v>
+        <v>1.84</v>
       </c>
       <c r="S7" t="n">
-        <v>14.69</v>
+        <v>12.3</v>
       </c>
       <c r="T7" t="n">
-        <v>11.52</v>
+        <v>10.33</v>
       </c>
       <c r="U7" t="n">
-        <v>24.65</v>
+        <v>20</v>
       </c>
       <c r="V7" t="n">
-        <v>18.73</v>
+        <v>14.77</v>
       </c>
       <c r="W7" t="n">
-        <v>14.16</v>
+        <v>12.89</v>
       </c>
       <c r="X7" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>682.8828</v>
+        <v>61.6973</v>
       </c>
       <c r="AA7" t="n">
-        <v>636.9071</v>
+        <v>58.5823</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,48 +1560,48 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>83.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AI7" t="n">
-        <v>681.24</v>
+        <v>61.4745</v>
       </c>
       <c r="AJ7" t="n">
-        <v>608.66</v>
+        <v>57.9933</v>
       </c>
       <c r="AK7" t="n">
-        <v>703.98</v>
+        <v>63.79</v>
       </c>
       <c r="AL7" t="n">
-        <v>703.98</v>
+        <v>63.79</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.34</v>
+        <v>8.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 608.66 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 57.99 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.59999999999999</v>
+        <v>76.14</v>
       </c>
       <c r="F8" t="n">
-        <v>75.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>66.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="I8" t="n">
-        <v>79.3</v>
+        <v>83</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>76.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>2.59</v>
       </c>
       <c r="S8" t="n">
-        <v>12.1</v>
+        <v>14.36</v>
       </c>
       <c r="T8" t="n">
-        <v>11.37</v>
+        <v>11.95</v>
       </c>
       <c r="U8" t="n">
-        <v>22.25</v>
+        <v>23.04</v>
       </c>
       <c r="V8" t="n">
-        <v>15.86</v>
+        <v>15.64</v>
       </c>
       <c r="W8" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.62820000000001</v>
+        <v>73.721</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.4346</v>
+        <v>69.4943</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>79.3</v>
+        <v>83</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
@@ -1731,7 +1731,7 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI8" t="n">
         <v>73.8</v>
@@ -1740,25 +1740,25 @@
         <v>67.67</v>
       </c>
       <c r="AK8" t="n">
-        <v>75.94</v>
+        <v>76.14</v>
       </c>
       <c r="AL8" t="n">
-        <v>75.94</v>
+        <v>76.14</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.68</v>
+        <v>3.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 76.14 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.288</v>
+        <v>18.444</v>
       </c>
       <c r="F9" t="n">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>52.4</v>
+        <v>52</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1814,10 +1814,10 @@
         <v>45.5</v>
       </c>
       <c r="K9" t="n">
-        <v>76</v>
+        <v>73.8</v>
       </c>
       <c r="L9" t="n">
-        <v>73.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,34 +1845,34 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="S9" t="n">
-        <v>36.5</v>
+        <v>41.53</v>
       </c>
       <c r="T9" t="n">
-        <v>32.62</v>
+        <v>32.73</v>
       </c>
       <c r="U9" t="n">
-        <v>44.5</v>
+        <v>45.64</v>
       </c>
       <c r="V9" t="n">
-        <v>19.77</v>
+        <v>19.37</v>
       </c>
       <c r="W9" t="n">
-        <v>21.67</v>
+        <v>21.68</v>
       </c>
       <c r="X9" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.3019</v>
+        <v>17.3626</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.8131</v>
+        <v>14.8396</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         <v>50.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>76</v>
+        <v>73.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI9" t="n">
         <v>17.092</v>
@@ -1908,14 +1908,14 @@
         <v>19.164</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.7</v>
+        <v>6.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.46</v>
+        <v>24.29</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.7%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.2%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64.84999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="F10" t="n">
         <v>70.8</v>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>63.3</v>
+        <v>62.8</v>
       </c>
       <c r="I10" t="n">
-        <v>56.5</v>
+        <v>57.2</v>
       </c>
       <c r="J10" t="n">
         <v>78.2</v>
@@ -1979,7 +1979,7 @@
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="S10" t="n">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="T10" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>3.96</v>
+        <v>4.44</v>
       </c>
       <c r="V10" t="n">
-        <v>7.67</v>
+        <v>7.33</v>
       </c>
       <c r="W10" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="X10" t="n">
         <v>-12.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.5298</v>
+        <v>63.5588</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.1763</v>
+        <v>63.1877</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>56.5</v>
+        <v>57.2</v>
       </c>
       <c r="AF10" t="n">
         <v>78.2</v>
@@ -2055,7 +2055,7 @@
         <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI10" t="n">
         <v>63.44</v>
@@ -2070,14 +2070,14 @@
         <v>64.84999999999999</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.8%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>611.61</v>
+        <v>631.98</v>
       </c>
       <c r="F11" t="n">
-        <v>66.8</v>
+        <v>65.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>57.3</v>
+        <v>57.9</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="K11" t="n">
-        <v>66.90000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="L11" t="n">
-        <v>52.3</v>
+        <v>43.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 10.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>2.71</v>
+        <v>5.36</v>
       </c>
       <c r="S11" t="n">
-        <v>60.59</v>
+        <v>68.87</v>
       </c>
       <c r="T11" t="n">
-        <v>68.41</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>122.93</v>
+        <v>128.7</v>
       </c>
       <c r="V11" t="n">
-        <v>60.24</v>
+        <v>61.95</v>
       </c>
       <c r="W11" t="n">
-        <v>35.73</v>
+        <v>35.81</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Z11" t="n">
-        <v>566.444</v>
+        <v>569.9876</v>
       </c>
       <c r="AA11" t="n">
-        <v>419.2983</v>
+        <v>420.9587</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>66.90000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AI11" t="n">
         <v>569.6900000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>391.97</v>
+        <v>392.32</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>7.97</v>
+        <v>10.88</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.87</v>
+        <v>50.13</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 65.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.9%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 391.97 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 392.32 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.98</v>
+        <v>9.863</v>
       </c>
       <c r="F12" t="n">
-        <v>57.9</v>
+        <v>57.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>31.2</v>
+        <v>30.7</v>
       </c>
       <c r="I12" t="n">
-        <v>92.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>72.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="L12" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-13.19</v>
+        <v>-14.61</v>
       </c>
       <c r="S12" t="n">
-        <v>9.91</v>
+        <v>10.1</v>
       </c>
       <c r="T12" t="n">
-        <v>23.33</v>
+        <v>21.4</v>
       </c>
       <c r="U12" t="n">
-        <v>57.5</v>
+        <v>55.77</v>
       </c>
       <c r="V12" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="W12" t="n">
-        <v>23.58</v>
+        <v>23.59</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.491</v>
+        <v>10.4994</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.9716</v>
+        <v>8.9855</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,19 +2370,19 @@
         <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>92.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AF12" t="n">
         <v>37</v>
       </c>
       <c r="AG12" t="n">
-        <v>72.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.914999999999999</v>
+        <v>9.863</v>
       </c>
       <c r="AJ12" t="n">
         <v>8.7643</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-4.87</v>
+        <v>-6.06</v>
       </c>
       <c r="AN12" t="n">
-        <v>11.24</v>
+        <v>9.77</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 57.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 57.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.1%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>344.28</v>
+        <v>338.68</v>
       </c>
       <c r="F13" t="n">
-        <v>55.2</v>
+        <v>52.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="I13" t="n">
-        <v>45.7</v>
+        <v>37.3</v>
       </c>
       <c r="J13" t="n">
-        <v>60.4</v>
+        <v>60.2</v>
       </c>
       <c r="K13" t="n">
-        <v>64.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="L13" t="n">
-        <v>56.9</v>
+        <v>54</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,43 +2484,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 7.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.94</v>
+        <v>-10.21</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.06</v>
+        <v>-10.28</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.59</v>
+        <v>-6.78</v>
       </c>
       <c r="U13" t="n">
-        <v>25.33</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>26.3</v>
+        <v>25.96</v>
       </c>
       <c r="W13" t="n">
-        <v>18.18</v>
+        <v>18.22</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.17</v>
+        <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>370.4684</v>
+        <v>369.3078</v>
       </c>
       <c r="AA13" t="n">
-        <v>366.4099</v>
+        <v>366.6128</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,22 +2532,22 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>45.7</v>
+        <v>37.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.4</v>
+        <v>60.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>64.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>339.65</v>
+        <v>338.68</v>
       </c>
       <c r="AJ13" t="n">
-        <v>339.65</v>
+        <v>338.68</v>
       </c>
       <c r="AK13" t="n">
         <v>372.59</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-7.07</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="AN13" t="n">
-        <v>-6.04</v>
+        <v>-7.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.1%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 52.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.3%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 339.65 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.055</v>
+        <v>27.145</v>
       </c>
       <c r="F14" t="n">
-        <v>41.7</v>
+        <v>49.2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,23 +2615,23 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I14" t="n">
-        <v>55</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
       <c r="K14" t="n">
-        <v>78.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>37.3</v>
+        <v>39.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>11.27</v>
+        <v>20.54</v>
       </c>
       <c r="T14" t="n">
-        <v>-12.39</v>
+        <v>-10.03</v>
       </c>
       <c r="U14" t="n">
-        <v>-13.41</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.07</v>
+        <v>-1.69</v>
       </c>
       <c r="W14" t="n">
-        <v>35.89</v>
+        <v>34.2</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.1883</v>
+        <v>25.214</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.7331</v>
+        <v>26.7012</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2691,19 +2691,19 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>78.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AH14" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AI14" t="n">
         <v>24.785</v>
@@ -2712,20 +2712,20 @@
         <v>20.205</v>
       </c>
       <c r="AK14" t="n">
-        <v>30.11</v>
+        <v>29.005</v>
       </c>
       <c r="AL14" t="n">
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.44</v>
+        <v>7.66</v>
       </c>
       <c r="AN14" t="n">
-        <v>-2.54</v>
+        <v>1.66</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 41.7, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.4%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 49.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.7%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.39</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>82.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>75.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>81.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="S2" t="n">
-        <v>29.64</v>
+        <v>30.66</v>
       </c>
       <c r="T2" t="n">
-        <v>36.42</v>
+        <v>37.7</v>
       </c>
       <c r="U2" t="n">
-        <v>63.95</v>
+        <v>65.44</v>
       </c>
       <c r="V2" t="n">
-        <v>26.3</v>
+        <v>26.46</v>
       </c>
       <c r="W2" t="n">
-        <v>13.93</v>
+        <v>13.94</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>67.505</v>
+        <v>67.7608</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.6218</v>
+        <v>56.7477</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>69</v>
       </c>
       <c r="AG2" t="n">
-        <v>75.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AH2" t="n">
         <v>756</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.76</v>
+        <v>6.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>26.08</v>
+        <v>27.05</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 82.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 82.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.4%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.74</v>
+        <v>48.825</v>
       </c>
       <c r="F3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-0.5</v>
+        <v>-0.27</v>
       </c>
       <c r="S3" t="n">
-        <v>21.32</v>
+        <v>23.55</v>
       </c>
       <c r="T3" t="n">
-        <v>26.26</v>
+        <v>29.08</v>
       </c>
       <c r="U3" t="n">
-        <v>42.02</v>
+        <v>45.16</v>
       </c>
       <c r="V3" t="n">
-        <v>20.03</v>
+        <v>20.68</v>
       </c>
       <c r="W3" t="n">
-        <v>16.46</v>
+        <v>16.5</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>46.8593</v>
+        <v>46.9587</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.3092</v>
+        <v>41.3751</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.88</v>
+        <v>3.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.57</v>
+        <v>18.01</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>163.44</v>
+        <v>165.22</v>
       </c>
       <c r="F4" t="n">
-        <v>78.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>86.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1031,38 +1031,38 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.17</v>
+        <v>0.79</v>
       </c>
       <c r="S4" t="n">
-        <v>15.93</v>
+        <v>16.43</v>
       </c>
       <c r="T4" t="n">
-        <v>13.19</v>
+        <v>14.18</v>
       </c>
       <c r="U4" t="n">
-        <v>26.54</v>
+        <v>26.99</v>
       </c>
       <c r="V4" t="n">
-        <v>17.65</v>
+        <v>17.76</v>
       </c>
       <c r="W4" t="n">
-        <v>12.94</v>
+        <v>12.95</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>160.0572</v>
+        <v>160.304</v>
       </c>
       <c r="AA4" t="n">
-        <v>148.7023</v>
+        <v>148.8455</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>86.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1098,14 +1098,14 @@
         <v>166.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.11</v>
+        <v>3.07</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.91</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 79.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>123.88</v>
+        <v>125.09</v>
       </c>
       <c r="F5" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>84.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>78.3</v>
+        <v>78.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.36</v>
+        <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>15.24</v>
+        <v>15.58</v>
       </c>
       <c r="T5" t="n">
-        <v>11.42</v>
+        <v>12.29</v>
       </c>
       <c r="U5" t="n">
-        <v>24.55</v>
+        <v>25.69</v>
       </c>
       <c r="V5" t="n">
-        <v>17.41</v>
+        <v>17.46</v>
       </c>
       <c r="W5" t="n">
         <v>13.19</v>
@@ -1221,10 +1221,10 @@
         <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.2584</v>
+        <v>121.436</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.5156</v>
+        <v>113.6149</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>84.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1254,25 +1254,25 @@
         <v>109.74</v>
       </c>
       <c r="AK5" t="n">
-        <v>125.04</v>
+        <v>125.09</v>
       </c>
       <c r="AL5" t="n">
-        <v>125.04</v>
+        <v>125.09</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.16</v>
+        <v>3.01</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.130000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 78.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 125.09 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>697.76</v>
+        <v>704.98</v>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>77.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="I6" t="n">
-        <v>86.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>64.3</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>78.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>-0.16</v>
+        <v>0.36</v>
       </c>
       <c r="S6" t="n">
-        <v>16.7</v>
+        <v>17.41</v>
       </c>
       <c r="T6" t="n">
-        <v>11.4</v>
+        <v>12.36</v>
       </c>
       <c r="U6" t="n">
-        <v>24.97</v>
+        <v>25.33</v>
       </c>
       <c r="V6" t="n">
-        <v>18.33</v>
+        <v>18.4</v>
       </c>
       <c r="W6" t="n">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="X6" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>683.85</v>
+        <v>685.0016000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>637.4372</v>
+        <v>638.0015</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>86.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AF6" t="n">
         <v>64.3</v>
@@ -1416,25 +1416,25 @@
         <v>608.66</v>
       </c>
       <c r="AK6" t="n">
-        <v>703.98</v>
+        <v>704.98</v>
       </c>
       <c r="AL6" t="n">
-        <v>703.98</v>
+        <v>704.98</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.03</v>
+        <v>2.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.460000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 704.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.36</v>
+        <v>63.94</v>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>77.8</v>
+        <v>78</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="S7" t="n">
-        <v>12.3</v>
+        <v>12.17</v>
       </c>
       <c r="T7" t="n">
-        <v>10.33</v>
+        <v>11.19</v>
       </c>
       <c r="U7" t="n">
-        <v>20</v>
+        <v>21.75</v>
       </c>
       <c r="V7" t="n">
-        <v>14.77</v>
+        <v>14.67</v>
       </c>
       <c r="W7" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.6973</v>
+        <v>61.7533</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.5823</v>
+        <v>58.6332</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1578,25 +1578,25 @@
         <v>57.9933</v>
       </c>
       <c r="AK7" t="n">
-        <v>63.79</v>
+        <v>63.94</v>
       </c>
       <c r="AL7" t="n">
-        <v>63.79</v>
+        <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.69</v>
+        <v>3.54</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.16</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>76.14</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>76.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>82.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.59</v>
+        <v>3.82</v>
       </c>
       <c r="S8" t="n">
-        <v>14.36</v>
+        <v>14.86</v>
       </c>
       <c r="T8" t="n">
-        <v>11.95</v>
+        <v>12.91</v>
       </c>
       <c r="U8" t="n">
-        <v>23.04</v>
+        <v>24.66</v>
       </c>
       <c r="V8" t="n">
-        <v>15.64</v>
+        <v>15.72</v>
       </c>
       <c r="W8" t="n">
         <v>12.88</v>
@@ -1704,13 +1704,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.721</v>
+        <v>73.8302</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.4943</v>
+        <v>69.5578</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,13 +1722,13 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>82.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AH8" t="n">
         <v>756</v>
@@ -1740,25 +1740,25 @@
         <v>67.67</v>
       </c>
       <c r="AK8" t="n">
-        <v>76.14</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AL8" t="n">
-        <v>76.14</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.28</v>
+        <v>4.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.56</v>
+        <v>10.56</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 76.14 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 76.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.444</v>
+        <v>64.73</v>
       </c>
       <c r="F9" t="n">
-        <v>70.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>52</v>
+        <v>62.4</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="J9" t="n">
-        <v>45.5</v>
+        <v>78.2</v>
       </c>
       <c r="K9" t="n">
-        <v>73.8</v>
+        <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>72.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>3.25</v>
+        <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>41.53</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>32.73</v>
+        <v>3.83</v>
       </c>
       <c r="U9" t="n">
-        <v>45.64</v>
+        <v>5.01</v>
       </c>
       <c r="V9" t="n">
-        <v>19.37</v>
+        <v>7.16</v>
       </c>
       <c r="W9" t="n">
-        <v>21.68</v>
+        <v>9.57</v>
       </c>
       <c r="X9" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.3626</v>
+        <v>63.5848</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.8396</v>
+        <v>63.1983</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,48 +1884,48 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>50.5</v>
+        <v>78.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>73.8</v>
+        <v>82.8</v>
       </c>
       <c r="AH9" t="n">
         <v>756</v>
       </c>
       <c r="AI9" t="n">
-        <v>17.092</v>
+        <v>63.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13.44</v>
+        <v>62.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.164</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AL9" t="n">
-        <v>19.164</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AM9" t="n">
-        <v>6.23</v>
+        <v>1.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.29</v>
+        <v>2.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.2%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.8%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 13.44 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,29 +1937,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64.7</v>
+        <v>19.158</v>
       </c>
       <c r="F10" t="n">
-        <v>70.8</v>
+        <v>69</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62.8</v>
+        <v>52.9</v>
       </c>
       <c r="I10" t="n">
-        <v>57.2</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>78.2</v>
+        <v>45.4</v>
       </c>
       <c r="K10" t="n">
-        <v>82.8</v>
+        <v>59.4</v>
       </c>
       <c r="L10" t="n">
-        <v>72.90000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,57 +1988,57 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>1.87</v>
+        <v>6.28</v>
       </c>
       <c r="S10" t="n">
-        <v>2.67</v>
+        <v>47.51</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>38.54</v>
       </c>
       <c r="U10" t="n">
-        <v>4.44</v>
+        <v>50.16</v>
       </c>
       <c r="V10" t="n">
-        <v>7.33</v>
+        <v>20.48</v>
       </c>
       <c r="W10" t="n">
-        <v>9.57</v>
+        <v>21.78</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.85</v>
+        <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.5588</v>
+        <v>17.4402</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.1877</v>
+        <v>14.8699</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2046,48 +2046,48 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>57.2</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>78.2</v>
+        <v>50.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>82.8</v>
+        <v>59.4</v>
       </c>
       <c r="AH10" t="n">
         <v>756</v>
       </c>
       <c r="AI10" t="n">
-        <v>63.44</v>
+        <v>17.092</v>
       </c>
       <c r="AJ10" t="n">
-        <v>62.06</v>
+        <v>13.44</v>
       </c>
       <c r="AK10" t="n">
-        <v>64.84999999999999</v>
+        <v>19.164</v>
       </c>
       <c r="AL10" t="n">
-        <v>64.84999999999999</v>
+        <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.8</v>
+        <v>9.85</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.39</v>
+        <v>28.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.8%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.8%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 13.44 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>631.98</v>
+        <v>655.89</v>
       </c>
       <c r="F11" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>57.9</v>
+        <v>58.6</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -2138,10 +2138,10 @@
         <v>23.4</v>
       </c>
       <c r="K11" t="n">
-        <v>55.2</v>
+        <v>41.5</v>
       </c>
       <c r="L11" t="n">
-        <v>43.4</v>
+        <v>33</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 10.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 14.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>5.36</v>
+        <v>9.51</v>
       </c>
       <c r="S11" t="n">
-        <v>68.87</v>
+        <v>80.92</v>
       </c>
       <c r="T11" t="n">
-        <v>73.54000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="U11" t="n">
-        <v>128.7</v>
+        <v>136.31</v>
       </c>
       <c r="V11" t="n">
-        <v>61.95</v>
+        <v>63.5</v>
       </c>
       <c r="W11" t="n">
-        <v>35.81</v>
+        <v>35.87</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Z11" t="n">
-        <v>569.9876</v>
+        <v>573.8222</v>
       </c>
       <c r="AA11" t="n">
-        <v>420.9587</v>
+        <v>422.7232</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>28.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>55.2</v>
+        <v>41.5</v>
       </c>
       <c r="AH11" t="n">
         <v>751</v>
@@ -2223,7 +2223,7 @@
         <v>569.6900000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>392.32</v>
+        <v>395.98</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>10.88</v>
+        <v>14.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>50.13</v>
+        <v>55.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 65.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.9%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.3%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 392.32 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 395.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.863</v>
+        <v>10.282</v>
       </c>
       <c r="F12" t="n">
-        <v>57.1</v>
+        <v>60.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30.7</v>
+        <v>31.3</v>
       </c>
       <c r="I12" t="n">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="K12" t="n">
-        <v>70.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>50.6</v>
+        <v>54.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 6.1% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-14.61</v>
+        <v>-9.35</v>
       </c>
       <c r="S12" t="n">
-        <v>10.1</v>
+        <v>16.06</v>
       </c>
       <c r="T12" t="n">
-        <v>21.4</v>
+        <v>27.96</v>
       </c>
       <c r="U12" t="n">
-        <v>55.77</v>
+        <v>60.68</v>
       </c>
       <c r="V12" t="n">
-        <v>2.46</v>
+        <v>3.39</v>
       </c>
       <c r="W12" t="n">
-        <v>23.59</v>
+        <v>23.7</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.4994</v>
+        <v>10.5145</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.9855</v>
+        <v>9.001799999999999</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,13 +2370,13 @@
         <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>70.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AH12" t="n">
         <v>756</v>
@@ -2388,20 +2388,20 @@
         <v>8.7643</v>
       </c>
       <c r="AK12" t="n">
-        <v>11.61</v>
+        <v>11.494</v>
       </c>
       <c r="AL12" t="n">
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-6.06</v>
+        <v>-2.21</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.77</v>
+        <v>14.22</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 57.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.1%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 60.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.2%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>338.68</v>
+        <v>339.49</v>
       </c>
       <c r="F13" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,16 +2453,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.3</v>
+        <v>66.5</v>
       </c>
       <c r="I13" t="n">
-        <v>37.3</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
         <v>60.2</v>
       </c>
       <c r="K13" t="n">
-        <v>62.8</v>
+        <v>63.5</v>
       </c>
       <c r="L13" t="n">
         <v>54</v>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 8.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-10.21</v>
+        <v>-8.25</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.28</v>
+        <v>-11.07</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.78</v>
+        <v>-6.89</v>
       </c>
       <c r="U13" t="n">
-        <v>23</v>
+        <v>24.2</v>
       </c>
       <c r="V13" t="n">
-        <v>25.96</v>
+        <v>26.02</v>
       </c>
       <c r="W13" t="n">
         <v>18.22</v>
@@ -2514,13 +2514,13 @@
         <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>369.3078</v>
+        <v>368.2504</v>
       </c>
       <c r="AA13" t="n">
-        <v>366.6128</v>
+        <v>366.8157</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>37.3</v>
+        <v>36.4</v>
       </c>
       <c r="AF13" t="n">
         <v>60.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>62.8</v>
+        <v>63.5</v>
       </c>
       <c r="AH13" t="n">
         <v>756</v>
@@ -2550,20 +2550,20 @@
         <v>338.68</v>
       </c>
       <c r="AK13" t="n">
-        <v>372.59</v>
+        <v>370.15</v>
       </c>
       <c r="AL13" t="n">
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-8.289999999999999</v>
+        <v>-7.81</v>
       </c>
       <c r="AN13" t="n">
-        <v>-7.62</v>
+        <v>-7.45</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 52.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.3%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 52.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.8%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27.145</v>
+        <v>27.32</v>
       </c>
       <c r="F14" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2618,16 +2618,16 @@
         <v>22.5</v>
       </c>
       <c r="I14" t="n">
-        <v>70.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>15.1</v>
       </c>
       <c r="K14" t="n">
-        <v>68.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>39.6</v>
+        <v>38.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2655,19 +2655,19 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-9.27</v>
       </c>
       <c r="S14" t="n">
-        <v>20.54</v>
+        <v>18.47</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.03</v>
+        <v>-7.45</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.470000000000001</v>
+        <v>-9.15</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.69</v>
+        <v>-1.59</v>
       </c>
       <c r="W14" t="n">
         <v>34.2</v>
@@ -2679,10 +2679,10 @@
         <v>-0.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.214</v>
+        <v>25.303</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.7012</v>
+        <v>26.6877</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,13 +2694,13 @@
         <v>85</v>
       </c>
       <c r="AE14" t="n">
-        <v>70.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AF14" t="n">
         <v>20.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>68.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AH14" t="n">
         <v>757</v>
@@ -2712,20 +2712,20 @@
         <v>20.205</v>
       </c>
       <c r="AK14" t="n">
-        <v>29.005</v>
+        <v>28.58</v>
       </c>
       <c r="AL14" t="n">
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>7.66</v>
+        <v>7.97</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 49.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.7%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 48.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>82.2</v>
+        <v>82.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>73.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>80.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.85</v>
+        <v>-0.91</v>
       </c>
       <c r="S2" t="n">
-        <v>30.66</v>
+        <v>30.63</v>
       </c>
       <c r="T2" t="n">
-        <v>37.7</v>
+        <v>36.17</v>
       </c>
       <c r="U2" t="n">
-        <v>65.44</v>
+        <v>62.51</v>
       </c>
       <c r="V2" t="n">
-        <v>26.46</v>
+        <v>25.86</v>
       </c>
       <c r="W2" t="n">
         <v>13.94</v>
@@ -732,13 +732,13 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Z2" t="n">
-        <v>67.7608</v>
+        <v>68.0108</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.7477</v>
+        <v>56.8705</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>69</v>
       </c>
       <c r="AG2" t="n">
-        <v>73.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AH2" t="n">
         <v>756</v>
@@ -765,7 +765,7 @@
         <v>68.89</v>
       </c>
       <c r="AJ2" t="n">
-        <v>56.24</v>
+        <v>57.9</v>
       </c>
       <c r="AK2" t="n">
         <v>73.47</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.4</v>
+        <v>5.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>27.05</v>
+        <v>25.9</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 82.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.4%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 82.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.3%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.24 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 57.90 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.825</v>
+        <v>48.27</v>
       </c>
       <c r="F3" t="n">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>70.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-0.27</v>
+        <v>-2.46</v>
       </c>
       <c r="S3" t="n">
-        <v>23.55</v>
+        <v>22.79</v>
       </c>
       <c r="T3" t="n">
-        <v>29.08</v>
+        <v>26.61</v>
       </c>
       <c r="U3" t="n">
-        <v>45.16</v>
+        <v>43.72</v>
       </c>
       <c r="V3" t="n">
-        <v>20.68</v>
+        <v>19.76</v>
       </c>
       <c r="W3" t="n">
         <v>16.5</v>
@@ -894,13 +894,13 @@
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>46.9587</v>
+        <v>47.0489</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.3751</v>
+        <v>41.4365</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>45.945</v>
       </c>
       <c r="AJ3" t="n">
-        <v>39.955</v>
+        <v>42.02</v>
       </c>
       <c r="AK3" t="n">
         <v>50.73</v>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.97</v>
+        <v>2.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.01</v>
+        <v>16.49</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.95 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 42.02 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>165.22</v>
+        <v>165.94</v>
       </c>
       <c r="F4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>88.3</v>
+        <v>89.5</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>79.7</v>
+        <v>80</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.79</v>
+        <v>0.64</v>
       </c>
       <c r="S4" t="n">
-        <v>16.43</v>
+        <v>17.01</v>
       </c>
       <c r="T4" t="n">
-        <v>14.18</v>
+        <v>14.46</v>
       </c>
       <c r="U4" t="n">
-        <v>26.99</v>
+        <v>27.86</v>
       </c>
       <c r="V4" t="n">
-        <v>17.76</v>
+        <v>17.81</v>
       </c>
       <c r="W4" t="n">
         <v>12.95</v>
@@ -1059,10 +1059,10 @@
         <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>160.304</v>
+        <v>160.5716</v>
       </c>
       <c r="AA4" t="n">
-        <v>148.8455</v>
+        <v>148.9883</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>88.3</v>
+        <v>89.5</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1089,7 +1089,7 @@
         <v>159.24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>143.92</v>
+        <v>148.08</v>
       </c>
       <c r="AK4" t="n">
         <v>166.04</v>
@@ -1098,14 +1098,14 @@
         <v>166.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.07</v>
+        <v>3.34</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>11.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 79.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 79.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 143.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 148.08 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>125.09</v>
+        <v>125.89</v>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I5" t="n">
-        <v>85.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>78.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>15.58</v>
+        <v>16.44</v>
       </c>
       <c r="T5" t="n">
-        <v>12.29</v>
+        <v>12.87</v>
       </c>
       <c r="U5" t="n">
-        <v>25.69</v>
+        <v>25.43</v>
       </c>
       <c r="V5" t="n">
-        <v>17.46</v>
+        <v>17.6</v>
       </c>
       <c r="W5" t="n">
         <v>13.19</v>
@@ -1218,17 +1218,17 @@
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.436</v>
+        <v>121.6318</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.6149</v>
+        <v>113.7154</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>85.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1251,33 +1251,33 @@
         <v>120.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>109.74</v>
+        <v>112.54</v>
       </c>
       <c r="AK5" t="n">
-        <v>125.09</v>
+        <v>125.89</v>
       </c>
       <c r="AL5" t="n">
-        <v>125.09</v>
+        <v>125.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.1</v>
+        <v>10.71</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 78.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>SWDA.MI: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 125.09 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 125.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 109.74 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 112.54 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>704.98</v>
+        <v>710.42</v>
       </c>
       <c r="F6" t="n">
-        <v>77.7</v>
+        <v>78.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.5</v>
+        <v>70.7</v>
       </c>
       <c r="I6" t="n">
-        <v>88.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="J6" t="n">
         <v>64.3</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>78.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.36</v>
+        <v>0.92</v>
       </c>
       <c r="S6" t="n">
-        <v>17.41</v>
+        <v>18.38</v>
       </c>
       <c r="T6" t="n">
-        <v>12.36</v>
+        <v>13</v>
       </c>
       <c r="U6" t="n">
-        <v>25.33</v>
+        <v>26.49</v>
       </c>
       <c r="V6" t="n">
-        <v>18.4</v>
+        <v>18.59</v>
       </c>
       <c r="W6" t="n">
         <v>14.17</v>
@@ -1380,17 +1380,17 @@
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>685.0016000000001</v>
+        <v>686.2408</v>
       </c>
       <c r="AA6" t="n">
-        <v>638.0015</v>
+        <v>638.5756</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>88.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="AF6" t="n">
         <v>64.3</v>
@@ -1413,33 +1413,33 @@
         <v>681.24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>608.66</v>
+        <v>621.66</v>
       </c>
       <c r="AK6" t="n">
-        <v>704.98</v>
+        <v>710.42</v>
       </c>
       <c r="AL6" t="n">
-        <v>704.98</v>
+        <v>710.42</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.92</v>
+        <v>3.52</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.5</v>
+        <v>11.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
+          <t>SXR8.DE: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 704.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 710.42 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 608.66 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 621.66 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.94</v>
+        <v>63.74</v>
       </c>
       <c r="F7" t="n">
-        <v>77.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>79.2</v>
+        <v>77.3</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="S7" t="n">
-        <v>12.17</v>
+        <v>11.28</v>
       </c>
       <c r="T7" t="n">
-        <v>11.19</v>
+        <v>10.25</v>
       </c>
       <c r="U7" t="n">
-        <v>21.75</v>
+        <v>21.59</v>
       </c>
       <c r="V7" t="n">
-        <v>14.67</v>
+        <v>14.63</v>
       </c>
       <c r="W7" t="n">
         <v>12.88</v>
@@ -1545,10 +1545,10 @@
         <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.7533</v>
+        <v>61.8153</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.6332</v>
+        <v>58.6814</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>79.2</v>
+        <v>77.3</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1575,7 +1575,7 @@
         <v>61.4745</v>
       </c>
       <c r="AJ7" t="n">
-        <v>57.9933</v>
+        <v>59.5065</v>
       </c>
       <c r="AK7" t="n">
         <v>63.94</v>
@@ -1584,14 +1584,14 @@
         <v>63.94</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.54</v>
+        <v>3.11</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.050000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 57.99 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>76.90000000000001</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>84.7</v>
+        <v>85.8</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>82.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="L8" t="n">
-        <v>77.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.82</v>
+        <v>4.11</v>
       </c>
       <c r="S8" t="n">
-        <v>14.86</v>
+        <v>15.52</v>
       </c>
       <c r="T8" t="n">
-        <v>12.91</v>
+        <v>13.41</v>
       </c>
       <c r="U8" t="n">
-        <v>24.66</v>
+        <v>24.15</v>
       </c>
       <c r="V8" t="n">
-        <v>15.72</v>
+        <v>15.91</v>
       </c>
       <c r="W8" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.8302</v>
+        <v>73.9504</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.5578</v>
+        <v>69.6233</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,13 +1722,13 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>84.7</v>
+        <v>85.8</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>82.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="AH8" t="n">
         <v>756</v>
@@ -1737,33 +1737,33 @@
         <v>73.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>67.67</v>
+        <v>69.44</v>
       </c>
       <c r="AK8" t="n">
-        <v>76.90000000000001</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="AL8" t="n">
-        <v>76.90000000000001</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.16</v>
+        <v>4.56</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.56</v>
+        <v>11.05</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.6%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 76.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 77.32 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 67.67 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 69.44 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64.73</v>
+        <v>65.2</v>
       </c>
       <c r="F9" t="n">
-        <v>70.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>62.4</v>
+        <v>62.8</v>
       </c>
       <c r="I9" t="n">
-        <v>55.6</v>
+        <v>57.6</v>
       </c>
       <c r="J9" t="n">
         <v>78.2</v>
@@ -1817,7 +1817,7 @@
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>72.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,38 +1841,38 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1.51</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>2.76</v>
       </c>
       <c r="T9" t="n">
-        <v>3.83</v>
+        <v>4.07</v>
       </c>
       <c r="U9" t="n">
-        <v>5.01</v>
+        <v>5.13</v>
       </c>
       <c r="V9" t="n">
-        <v>7.16</v>
+        <v>7.35</v>
       </c>
       <c r="W9" t="n">
-        <v>9.57</v>
+        <v>9.58</v>
       </c>
       <c r="X9" t="n">
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.5848</v>
+        <v>63.628</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.1983</v>
+        <v>63.2124</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>55.6</v>
+        <v>57.6</v>
       </c>
       <c r="AF9" t="n">
         <v>78.2</v>
@@ -1902,25 +1902,25 @@
         <v>62.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>64.84999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>64.84999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.8</v>
+        <v>2.47</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.42</v>
+        <v>3.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.8%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19.158</v>
+        <v>19.102</v>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         <v>45.4</v>
       </c>
       <c r="K10" t="n">
-        <v>59.4</v>
+        <v>62.5</v>
       </c>
       <c r="L10" t="n">
-        <v>63.3</v>
+        <v>65.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2003,23 +2003,23 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 9.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>6.28</v>
+        <v>6.19</v>
       </c>
       <c r="S10" t="n">
-        <v>47.51</v>
+        <v>47.67</v>
       </c>
       <c r="T10" t="n">
-        <v>38.54</v>
+        <v>37.76</v>
       </c>
       <c r="U10" t="n">
-        <v>50.16</v>
+        <v>47.94</v>
       </c>
       <c r="V10" t="n">
-        <v>20.48</v>
+        <v>20.47</v>
       </c>
       <c r="W10" t="n">
         <v>21.78</v>
@@ -2031,10 +2031,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.4402</v>
+        <v>17.5136</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.8699</v>
+        <v>14.8996</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>50.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>59.4</v>
+        <v>62.5</v>
       </c>
       <c r="AH10" t="n">
         <v>756</v>
@@ -2061,7 +2061,7 @@
         <v>17.092</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13.44</v>
+        <v>14.19</v>
       </c>
       <c r="AK10" t="n">
         <v>19.164</v>
@@ -2070,14 +2070,14 @@
         <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>9.85</v>
+        <v>9.07</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.84</v>
+        <v>28.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.8%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.1%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 13.44 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 14.19 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>655.89</v>
+        <v>620.46</v>
       </c>
       <c r="F11" t="n">
-        <v>63.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>58.6</v>
+        <v>57</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="K11" t="n">
-        <v>41.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>33</v>
+        <v>53.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 14.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>9.51</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
-        <v>80.92</v>
+        <v>61.83</v>
       </c>
       <c r="T11" t="n">
-        <v>79.27</v>
+        <v>70.36</v>
       </c>
       <c r="U11" t="n">
-        <v>136.31</v>
+        <v>123.18</v>
       </c>
       <c r="V11" t="n">
-        <v>63.5</v>
+        <v>60.38</v>
       </c>
       <c r="W11" t="n">
-        <v>35.87</v>
+        <v>35.99</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Z11" t="n">
-        <v>573.8222</v>
+        <v>576.9521999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>422.7232</v>
+        <v>424.3086</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>41.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AH11" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AI11" t="n">
         <v>569.6900000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>395.98</v>
+        <v>399.9</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>14.3</v>
+        <v>7.54</v>
       </c>
       <c r="AN11" t="n">
-        <v>55.16</v>
+        <v>46.23</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.3%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 66.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.5%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 395.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 399.90 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.282</v>
+        <v>10.444</v>
       </c>
       <c r="F12" t="n">
-        <v>60.4</v>
+        <v>60.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -2300,10 +2300,10 @@
         <v>31.9</v>
       </c>
       <c r="K12" t="n">
-        <v>76.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="L12" t="n">
-        <v>54.8</v>
+        <v>55.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2331,34 +2331,34 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-9.35</v>
+        <v>-10.04</v>
       </c>
       <c r="S12" t="n">
-        <v>16.06</v>
+        <v>17.51</v>
       </c>
       <c r="T12" t="n">
-        <v>27.96</v>
+        <v>28.7</v>
       </c>
       <c r="U12" t="n">
-        <v>60.68</v>
+        <v>63.82</v>
       </c>
       <c r="V12" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="W12" t="n">
-        <v>23.7</v>
+        <v>23.71</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5145</v>
+        <v>10.5313</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.001799999999999</v>
+        <v>9.0183</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>36.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>76.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="AH12" t="n">
         <v>756</v>
@@ -2385,23 +2385,23 @@
         <v>9.863</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8.7643</v>
+        <v>9.0997</v>
       </c>
       <c r="AK12" t="n">
-        <v>11.494</v>
+        <v>11.252</v>
       </c>
       <c r="AL12" t="n">
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-2.21</v>
+        <v>-0.83</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.22</v>
+        <v>15.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 60.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.2%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 60.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 9.10 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>339.49</v>
+        <v>344.75</v>
       </c>
       <c r="F13" t="n">
-        <v>52.5</v>
+        <v>54</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.5</v>
+        <v>66.8</v>
       </c>
       <c r="I13" t="n">
-        <v>36.4</v>
+        <v>40.4</v>
       </c>
       <c r="J13" t="n">
         <v>60.2</v>
       </c>
       <c r="K13" t="n">
-        <v>63.5</v>
+        <v>66</v>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>55.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 7.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-8.25</v>
+        <v>-7.47</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.07</v>
+        <v>-10.61</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.89</v>
+        <v>-2.94</v>
       </c>
       <c r="U13" t="n">
-        <v>24.2</v>
+        <v>28.17</v>
       </c>
       <c r="V13" t="n">
-        <v>26.02</v>
+        <v>26.45</v>
       </c>
       <c r="W13" t="n">
-        <v>18.22</v>
+        <v>18.24</v>
       </c>
       <c r="X13" t="n">
         <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>368.2504</v>
+        <v>367.3744</v>
       </c>
       <c r="AA13" t="n">
-        <v>366.8157</v>
+        <v>367.0419</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>36.4</v>
+        <v>40.4</v>
       </c>
       <c r="AF13" t="n">
         <v>60.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>63.5</v>
+        <v>66</v>
       </c>
       <c r="AH13" t="n">
         <v>756</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-7.81</v>
+        <v>-6.16</v>
       </c>
       <c r="AN13" t="n">
-        <v>-7.45</v>
+        <v>-6.07</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 52.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.8%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27.32</v>
+        <v>28.915</v>
       </c>
       <c r="F14" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="I14" t="n">
-        <v>69.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J14" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="K14" t="n">
-        <v>66.90000000000001</v>
+        <v>43.5</v>
       </c>
       <c r="L14" t="n">
-        <v>38.3</v>
+        <v>24.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 13.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-9.27</v>
+        <v>-0.31</v>
       </c>
       <c r="S14" t="n">
-        <v>18.47</v>
+        <v>25.53</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.45</v>
+        <v>-2.51</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.15</v>
+        <v>-4.18</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.59</v>
+        <v>0.43</v>
       </c>
       <c r="W14" t="n">
-        <v>34.2</v>
+        <v>34.36</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.303</v>
+        <v>25.4077</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.6877</v>
+        <v>26.6815</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,13 +2694,13 @@
         <v>85</v>
       </c>
       <c r="AE14" t="n">
-        <v>69.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>66.90000000000001</v>
+        <v>43.5</v>
       </c>
       <c r="AH14" t="n">
         <v>757</v>
@@ -2712,20 +2712,20 @@
         <v>20.205</v>
       </c>
       <c r="AK14" t="n">
-        <v>28.58</v>
+        <v>28.915</v>
       </c>
       <c r="AL14" t="n">
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>7.97</v>
+        <v>13.8</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.37</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 48.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 48.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.8%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.59999999999999</v>
+        <v>70.81</v>
       </c>
       <c r="F2" t="n">
-        <v>82.7</v>
+        <v>83.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.2</v>
+        <v>77.5</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>77.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L2" t="n">
-        <v>82</v>
+        <v>83.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-0.91</v>
+        <v>-2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>30.63</v>
+        <v>25.08</v>
       </c>
       <c r="T2" t="n">
-        <v>36.17</v>
+        <v>33.96</v>
       </c>
       <c r="U2" t="n">
-        <v>62.51</v>
+        <v>61</v>
       </c>
       <c r="V2" t="n">
-        <v>25.86</v>
+        <v>25.36</v>
       </c>
       <c r="W2" t="n">
-        <v>13.94</v>
+        <v>13.95</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Z2" t="n">
-        <v>68.0108</v>
+        <v>68.24160000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.8705</v>
+        <v>56.987</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         <v>69</v>
       </c>
       <c r="AG2" t="n">
-        <v>77.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI2" t="n">
         <v>68.89</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.28</v>
+        <v>3.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.9</v>
+        <v>24.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 82.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.3%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.27</v>
+        <v>47.31</v>
       </c>
       <c r="F3" t="n">
-        <v>80.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="J3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="K3" t="n">
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>81.7</v>
+        <v>80.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-2.46</v>
+        <v>-3.29</v>
       </c>
       <c r="S3" t="n">
-        <v>22.79</v>
+        <v>16.43</v>
       </c>
       <c r="T3" t="n">
-        <v>26.61</v>
+        <v>23.17</v>
       </c>
       <c r="U3" t="n">
-        <v>43.72</v>
+        <v>41.43</v>
       </c>
       <c r="V3" t="n">
-        <v>19.76</v>
+        <v>18.94</v>
       </c>
       <c r="W3" t="n">
-        <v>16.5</v>
+        <v>16.54</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.0489</v>
+        <v>47.1074</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.4365</v>
+        <v>41.4918</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,16 +912,16 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AG3" t="n">
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI3" t="n">
         <v>45.945</v>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.6</v>
+        <v>0.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.49</v>
+        <v>14.02</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>165.94</v>
+        <v>164.98</v>
       </c>
       <c r="F4" t="n">
-        <v>79.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I4" t="n">
-        <v>89.5</v>
+        <v>84.3</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="S4" t="n">
-        <v>17.01</v>
+        <v>13.86</v>
       </c>
       <c r="T4" t="n">
-        <v>14.46</v>
+        <v>13.45</v>
       </c>
       <c r="U4" t="n">
-        <v>27.86</v>
+        <v>27.32</v>
       </c>
       <c r="V4" t="n">
-        <v>17.81</v>
+        <v>17.55</v>
       </c>
       <c r="W4" t="n">
         <v>12.95</v>
@@ -1056,13 +1056,13 @@
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>160.5716</v>
+        <v>160.8036</v>
       </c>
       <c r="AA4" t="n">
-        <v>148.9883</v>
+        <v>149.1217</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>89.5</v>
+        <v>84.3</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1083,13 +1083,13 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>148.08</v>
+        <v>148.16</v>
       </c>
       <c r="AK4" t="n">
         <v>166.04</v>
@@ -1098,14 +1098,14 @@
         <v>166.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.38</v>
+        <v>10.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 79.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 148.08 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 148.16 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>125.89</v>
+        <v>125.23</v>
       </c>
       <c r="F5" t="n">
-        <v>78.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>87.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>79.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>16.44</v>
+        <v>13.49</v>
       </c>
       <c r="T5" t="n">
-        <v>12.87</v>
+        <v>12</v>
       </c>
       <c r="U5" t="n">
-        <v>25.43</v>
+        <v>25.04</v>
       </c>
       <c r="V5" t="n">
-        <v>17.6</v>
+        <v>17.37</v>
       </c>
       <c r="W5" t="n">
         <v>13.19</v>
@@ -1218,17 +1218,17 @@
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.6318</v>
+        <v>121.8052</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.7154</v>
+        <v>113.8092</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>87.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,13 +1245,13 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>112.54</v>
+        <v>112.7</v>
       </c>
       <c r="AK5" t="n">
         <v>125.89</v>
@@ -1260,14 +1260,14 @@
         <v>125.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.71</v>
+        <v>10.04</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 112.54 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 112.70 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>710.42</v>
+        <v>704.54</v>
       </c>
       <c r="F6" t="n">
-        <v>78.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.7</v>
+        <v>70.3</v>
       </c>
       <c r="I6" t="n">
-        <v>90.2</v>
+        <v>85.2</v>
       </c>
       <c r="J6" t="n">
         <v>64.3</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>79.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.92</v>
+        <v>0.4</v>
       </c>
       <c r="S6" t="n">
-        <v>18.38</v>
+        <v>15.44</v>
       </c>
       <c r="T6" t="n">
-        <v>13</v>
+        <v>11.97</v>
       </c>
       <c r="U6" t="n">
-        <v>26.49</v>
+        <v>25.59</v>
       </c>
       <c r="V6" t="n">
-        <v>18.59</v>
+        <v>18.24</v>
       </c>
       <c r="W6" t="n">
         <v>14.17</v>
@@ -1380,17 +1380,17 @@
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>686.2408</v>
+        <v>687.2723999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>638.5756</v>
+        <v>639.101</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>90.2</v>
+        <v>85.2</v>
       </c>
       <c r="AF6" t="n">
         <v>64.3</v>
@@ -1407,13 +1407,13 @@
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AI6" t="n">
         <v>681.24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>621.66</v>
+        <v>624.24</v>
       </c>
       <c r="AK6" t="n">
         <v>710.42</v>
@@ -1422,14 +1422,14 @@
         <v>710.42</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.52</v>
+        <v>2.51</v>
       </c>
       <c r="AN6" t="n">
-        <v>11.25</v>
+        <v>10.24</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 621.66 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 624.24 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1470,30 +1470,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.74</v>
+        <v>64.66</v>
       </c>
       <c r="F7" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I7" t="n">
         <v>76.59999999999999</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Accumulate Carefully</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>77.3</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
       </c>
       <c r="K7" t="n">
-        <v>82.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>77.5</v>
+        <v>76.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2.37</v>
+        <v>4.59</v>
       </c>
       <c r="S7" t="n">
-        <v>11.28</v>
+        <v>10.14</v>
       </c>
       <c r="T7" t="n">
-        <v>10.25</v>
+        <v>11.03</v>
       </c>
       <c r="U7" t="n">
-        <v>21.59</v>
+        <v>23.09</v>
       </c>
       <c r="V7" t="n">
-        <v>14.63</v>
+        <v>15.15</v>
       </c>
       <c r="W7" t="n">
-        <v>12.88</v>
+        <v>12.9</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.8153</v>
+        <v>61.8987</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.6814</v>
+        <v>58.7346</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,16 +1560,16 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>77.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>82.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI7" t="n">
         <v>61.4745</v>
@@ -1578,25 +1578,25 @@
         <v>59.5065</v>
       </c>
       <c r="AK7" t="n">
-        <v>63.94</v>
+        <v>64.66</v>
       </c>
       <c r="AL7" t="n">
-        <v>63.94</v>
+        <v>64.66</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.11</v>
+        <v>4.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.619999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.66 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77.31999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>76.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>66.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>85.8</v>
+        <v>81.3</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>80.5</v>
+        <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>77.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>4.11</v>
+        <v>3.6</v>
       </c>
       <c r="S8" t="n">
-        <v>15.52</v>
+        <v>12.77</v>
       </c>
       <c r="T8" t="n">
-        <v>13.41</v>
+        <v>12.53</v>
       </c>
       <c r="U8" t="n">
-        <v>24.15</v>
+        <v>23.75</v>
       </c>
       <c r="V8" t="n">
-        <v>15.91</v>
+        <v>15.68</v>
       </c>
       <c r="W8" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.9504</v>
+        <v>74.0564</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.6233</v>
+        <v>69.6842</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,22 +1722,22 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>85.8</v>
+        <v>81.3</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>80.5</v>
+        <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI8" t="n">
         <v>73.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>69.44</v>
+        <v>69.67</v>
       </c>
       <c r="AK8" t="n">
         <v>77.31999999999999</v>
@@ -1746,14 +1746,14 @@
         <v>77.31999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.56</v>
+        <v>3.84</v>
       </c>
       <c r="AN8" t="n">
-        <v>11.05</v>
+        <v>10.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.6%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 69.44 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 69.67 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65.2</v>
+        <v>18.49</v>
       </c>
       <c r="F9" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>62.8</v>
+        <v>51.8</v>
       </c>
       <c r="I9" t="n">
-        <v>57.6</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>78.2</v>
+        <v>45.3</v>
       </c>
       <c r="K9" t="n">
-        <v>82.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>73</v>
+        <v>74.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="S9" t="n">
-        <v>2.76</v>
+        <v>36.28</v>
       </c>
       <c r="T9" t="n">
-        <v>4.07</v>
+        <v>32.72</v>
       </c>
       <c r="U9" t="n">
-        <v>5.13</v>
+        <v>43.98</v>
       </c>
       <c r="V9" t="n">
-        <v>7.35</v>
+        <v>19.14</v>
       </c>
       <c r="W9" t="n">
-        <v>9.58</v>
+        <v>21.85</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.85</v>
+        <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.628</v>
+        <v>17.5723</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.2124</v>
+        <v>14.9259</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,48 +1884,48 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>57.6</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.2</v>
+        <v>50.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>82.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AH9" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.44</v>
+        <v>17.092</v>
       </c>
       <c r="AJ9" t="n">
-        <v>62.06</v>
+        <v>14.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>65.2</v>
+        <v>19.164</v>
       </c>
       <c r="AL9" t="n">
-        <v>65.2</v>
+        <v>19.164</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.47</v>
+        <v>5.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.14</v>
+        <v>23.88</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 14.19 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,29 +1937,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19.102</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>69.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>52.9</v>
+        <v>63.1</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>58.7</v>
       </c>
       <c r="J10" t="n">
-        <v>45.4</v>
+        <v>78.2</v>
       </c>
       <c r="K10" t="n">
-        <v>62.5</v>
+        <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>65.7</v>
+        <v>73.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,57 +1988,57 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>6.19</v>
+        <v>2.85</v>
       </c>
       <c r="S10" t="n">
-        <v>47.67</v>
+        <v>3.21</v>
       </c>
       <c r="T10" t="n">
-        <v>37.76</v>
+        <v>4.66</v>
       </c>
       <c r="U10" t="n">
-        <v>47.94</v>
+        <v>5.66</v>
       </c>
       <c r="V10" t="n">
-        <v>20.47</v>
+        <v>7.54</v>
       </c>
       <c r="W10" t="n">
-        <v>21.78</v>
+        <v>9.58</v>
       </c>
       <c r="X10" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.5136</v>
+        <v>63.6818</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.8996</v>
+        <v>63.2256</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2046,48 +2046,48 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>100</v>
+        <v>58.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>50.4</v>
+        <v>78.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>62.5</v>
+        <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI10" t="n">
-        <v>17.092</v>
+        <v>63.44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14.19</v>
+        <v>62.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>19.164</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>19.164</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="AM10" t="n">
-        <v>9.07</v>
+        <v>2.97</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.2</v>
+        <v>3.71</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.1%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 14.19 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2118,30 +2118,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>620.46</v>
+        <v>591.48</v>
       </c>
       <c r="F11" t="n">
-        <v>66.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>57</v>
+        <v>55.5</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="K11" t="n">
-        <v>68.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>53.5</v>
+        <v>58.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2169,34 +2169,34 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>-6.44</v>
       </c>
       <c r="S11" t="n">
-        <v>61.83</v>
+        <v>50.9</v>
       </c>
       <c r="T11" t="n">
-        <v>70.36</v>
+        <v>62.8</v>
       </c>
       <c r="U11" t="n">
-        <v>123.18</v>
+        <v>115.1</v>
       </c>
       <c r="V11" t="n">
-        <v>60.38</v>
+        <v>57.74</v>
       </c>
       <c r="W11" t="n">
-        <v>35.99</v>
+        <v>36.08</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>576.9521999999999</v>
+        <v>579.4886</v>
       </c>
       <c r="AA11" t="n">
-        <v>424.3086</v>
+        <v>425.735</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>68.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AI11" t="n">
         <v>569.6900000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>399.9</v>
+        <v>422.92</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>7.54</v>
+        <v>2.07</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.23</v>
+        <v>38.93</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 66.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.5%.</t>
+          <t>SMH: scenario base Accumulate Carefully, score 68.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 399.90 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 422.92 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.444</v>
+        <v>10.01</v>
       </c>
       <c r="F12" t="n">
-        <v>60.8</v>
+        <v>57.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>31.5</v>
+        <v>30.4</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="J12" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="K12" t="n">
-        <v>78.5</v>
+        <v>72.2</v>
       </c>
       <c r="L12" t="n">
-        <v>55.5</v>
+        <v>51.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-10.04</v>
+        <v>-12.91</v>
       </c>
       <c r="S12" t="n">
-        <v>17.51</v>
+        <v>10.03</v>
       </c>
       <c r="T12" t="n">
-        <v>28.7</v>
+        <v>23.51</v>
       </c>
       <c r="U12" t="n">
-        <v>63.82</v>
+        <v>57.48</v>
       </c>
       <c r="V12" t="n">
-        <v>3.55</v>
+        <v>2.09</v>
       </c>
       <c r="W12" t="n">
-        <v>23.71</v>
+        <v>23.82</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5313</v>
+        <v>10.5372</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.0183</v>
+        <v>9.032400000000001</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,38 +2370,38 @@
         <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>78.5</v>
+        <v>72.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI12" t="n">
         <v>9.863</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.0997</v>
+        <v>9.1906</v>
       </c>
       <c r="AK12" t="n">
-        <v>11.252</v>
+        <v>10.872</v>
       </c>
       <c r="AL12" t="n">
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.83</v>
+        <v>-5</v>
       </c>
       <c r="AN12" t="n">
-        <v>15.81</v>
+        <v>10.82</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 60.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 57.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 9.10 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 9.19 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>344.75</v>
+        <v>347.04</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>53.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.8</v>
+        <v>67</v>
       </c>
       <c r="I13" t="n">
-        <v>40.4</v>
+        <v>38.1</v>
       </c>
       <c r="J13" t="n">
         <v>60.2</v>
       </c>
       <c r="K13" t="n">
-        <v>66</v>
+        <v>67.3</v>
       </c>
       <c r="L13" t="n">
-        <v>55.9</v>
+        <v>55.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 6.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-7.47</v>
+        <v>-5.74</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.61</v>
+        <v>-12.39</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.94</v>
+        <v>-2.87</v>
       </c>
       <c r="U13" t="n">
-        <v>28.17</v>
+        <v>28.73</v>
       </c>
       <c r="V13" t="n">
-        <v>26.45</v>
+        <v>26.69</v>
       </c>
       <c r="W13" t="n">
-        <v>18.24</v>
+        <v>18.23</v>
       </c>
       <c r="X13" t="n">
         <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z13" t="n">
-        <v>367.3744</v>
+        <v>366.5446</v>
       </c>
       <c r="AA13" t="n">
-        <v>367.0419</v>
+        <v>367.2858</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>40.4</v>
+        <v>38.1</v>
       </c>
       <c r="AF13" t="n">
         <v>60.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>66</v>
+        <v>67.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI13" t="n">
         <v>338.68</v>
@@ -2550,20 +2550,20 @@
         <v>338.68</v>
       </c>
       <c r="AK13" t="n">
-        <v>370.15</v>
+        <v>362.44</v>
       </c>
       <c r="AL13" t="n">
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-6.16</v>
+        <v>-5.32</v>
       </c>
       <c r="AN13" t="n">
-        <v>-6.07</v>
+        <v>-5.51</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 53.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28.915</v>
+        <v>28.685</v>
       </c>
       <c r="F14" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="I14" t="n">
-        <v>83.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>14.9</v>
       </c>
       <c r="K14" t="n">
-        <v>43.5</v>
+        <v>49.1</v>
       </c>
       <c r="L14" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 13.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 12.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-0.31</v>
+        <v>1.99</v>
       </c>
       <c r="S14" t="n">
-        <v>25.53</v>
+        <v>22.53</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.51</v>
+        <v>-3.76</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.18</v>
+        <v>-3.53</v>
       </c>
       <c r="V14" t="n">
-        <v>0.43</v>
+        <v>0.16</v>
       </c>
       <c r="W14" t="n">
-        <v>34.36</v>
+        <v>34.34</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.4077</v>
+        <v>25.5156</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.6815</v>
+        <v>26.6747</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,16 +2694,16 @@
         <v>85</v>
       </c>
       <c r="AE14" t="n">
-        <v>83.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AF14" t="n">
         <v>19.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>43.5</v>
+        <v>49.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI14" t="n">
         <v>24.785</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>13.8</v>
+        <v>12.42</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.369999999999999</v>
+        <v>7.54</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 48.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.8%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 48.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.4%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70.81</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77.5</v>
+        <v>78</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>82.8</v>
+        <v>80.7</v>
       </c>
       <c r="L2" t="n">
-        <v>83.5</v>
+        <v>83</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-2.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>25.08</v>
+        <v>26.76</v>
       </c>
       <c r="T2" t="n">
-        <v>33.96</v>
+        <v>34.66</v>
       </c>
       <c r="U2" t="n">
-        <v>61</v>
+        <v>62.46</v>
       </c>
       <c r="V2" t="n">
-        <v>25.36</v>
+        <v>25.77</v>
       </c>
       <c r="W2" t="n">
         <v>13.95</v>
@@ -732,13 +732,13 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>68.24160000000001</v>
+        <v>68.47839999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.987</v>
+        <v>57.1085</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         <v>69</v>
       </c>
       <c r="AG2" t="n">
-        <v>82.8</v>
+        <v>80.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI2" t="n">
         <v>68.89</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.76</v>
+        <v>4.51</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.26</v>
+        <v>25.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.31</v>
+        <v>48.36</v>
       </c>
       <c r="F3" t="n">
-        <v>79.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I3" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
         <v>64.8</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>80.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-3.29</v>
+        <v>0.23</v>
       </c>
       <c r="S3" t="n">
-        <v>16.43</v>
+        <v>20.64</v>
       </c>
       <c r="T3" t="n">
-        <v>23.17</v>
+        <v>23.59</v>
       </c>
       <c r="U3" t="n">
-        <v>41.43</v>
+        <v>44.21</v>
       </c>
       <c r="V3" t="n">
-        <v>18.94</v>
+        <v>19.78</v>
       </c>
       <c r="W3" t="n">
-        <v>16.54</v>
+        <v>16.57</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.1074</v>
+        <v>47.1934</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.4918</v>
+        <v>41.552</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
         <v>64.8</v>
@@ -921,13 +921,13 @@
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI3" t="n">
         <v>45.945</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42.02</v>
+        <v>42.255</v>
       </c>
       <c r="AK3" t="n">
         <v>50.73</v>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.43</v>
+        <v>2.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.02</v>
+        <v>16.38</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.4%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 42.02 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 42.26 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>164.98</v>
+        <v>165.88</v>
       </c>
       <c r="F4" t="n">
-        <v>78.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>84.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>78.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.51</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>13.86</v>
+        <v>14.61</v>
       </c>
       <c r="T4" t="n">
-        <v>13.45</v>
+        <v>14.29</v>
       </c>
       <c r="U4" t="n">
-        <v>27.32</v>
+        <v>27.68</v>
       </c>
       <c r="V4" t="n">
-        <v>17.55</v>
+        <v>17.74</v>
       </c>
       <c r="W4" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>160.8036</v>
+        <v>161.0456</v>
       </c>
       <c r="AA4" t="n">
-        <v>149.1217</v>
+        <v>149.2594</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>84.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1083,13 +1083,13 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>148.16</v>
+        <v>148.48</v>
       </c>
       <c r="AK4" t="n">
         <v>166.04</v>
@@ -1098,14 +1098,14 @@
         <v>166.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.63</v>
+        <v>11.14</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 148.16 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 148.48 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>125.23</v>
+        <v>125.72</v>
       </c>
       <c r="F5" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I5" t="n">
-        <v>82.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>77.8</v>
+        <v>78.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>13.49</v>
+        <v>13.9</v>
       </c>
       <c r="T5" t="n">
-        <v>12</v>
+        <v>12.91</v>
       </c>
       <c r="U5" t="n">
-        <v>25.04</v>
+        <v>25.72</v>
       </c>
       <c r="V5" t="n">
-        <v>17.37</v>
+        <v>17.49</v>
       </c>
       <c r="W5" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.8052</v>
+        <v>121.98</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.8092</v>
+        <v>113.9053</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>82.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,13 +1245,13 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>112.7</v>
+        <v>112.96</v>
       </c>
       <c r="AK5" t="n">
         <v>125.89</v>
@@ -1260,14 +1260,14 @@
         <v>125.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.81</v>
+        <v>3.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.04</v>
+        <v>10.37</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 112.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 112.96 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>704.54</v>
+        <v>706.12</v>
       </c>
       <c r="F6" t="n">
-        <v>76.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>85.2</v>
+        <v>85.8</v>
       </c>
       <c r="J6" t="n">
         <v>64.3</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,22 +1359,22 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="S6" t="n">
-        <v>15.44</v>
+        <v>15.46</v>
       </c>
       <c r="T6" t="n">
-        <v>11.97</v>
+        <v>13.03</v>
       </c>
       <c r="U6" t="n">
-        <v>25.59</v>
+        <v>25.53</v>
       </c>
       <c r="V6" t="n">
-        <v>18.24</v>
+        <v>18.3</v>
       </c>
       <c r="W6" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="X6" t="n">
         <v>-23.32</v>
@@ -1383,10 +1383,10 @@
         <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>687.2723999999999</v>
+        <v>688.2796</v>
       </c>
       <c r="AA6" t="n">
-        <v>639.101</v>
+        <v>639.6289</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>85.2</v>
+        <v>85.8</v>
       </c>
       <c r="AF6" t="n">
         <v>64.3</v>
@@ -1407,13 +1407,13 @@
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI6" t="n">
         <v>681.24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>624.24</v>
+        <v>625.66</v>
       </c>
       <c r="AK6" t="n">
         <v>710.42</v>
@@ -1422,14 +1422,14 @@
         <v>710.42</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.24</v>
+        <v>10.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 624.24 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 625.66 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64.66</v>
+        <v>65.06</v>
       </c>
       <c r="F7" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I7" t="n">
-        <v>76.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
       </c>
       <c r="K7" t="n">
-        <v>80.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>76.8</v>
+        <v>76.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="S7" t="n">
-        <v>10.14</v>
+        <v>11.05</v>
       </c>
       <c r="T7" t="n">
-        <v>11.03</v>
+        <v>10.72</v>
       </c>
       <c r="U7" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="V7" t="n">
-        <v>15.15</v>
+        <v>15.36</v>
       </c>
       <c r="W7" t="n">
-        <v>12.9</v>
+        <v>12.89</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.8987</v>
+        <v>61.9896</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.7346</v>
+        <v>58.7885</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,16 +1560,16 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>76.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>80.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AI7" t="n">
         <v>61.4745</v>
@@ -1578,25 +1578,25 @@
         <v>59.5065</v>
       </c>
       <c r="AK7" t="n">
-        <v>64.66</v>
+        <v>65.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>64.66</v>
+        <v>65.06</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.46</v>
+        <v>4.95</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.09</v>
+        <v>10.67</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.0%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.66 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>76.90000000000001</v>
+        <v>77.39</v>
       </c>
       <c r="F8" t="n">
-        <v>75.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>81.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>82.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="S8" t="n">
-        <v>12.77</v>
+        <v>13.44</v>
       </c>
       <c r="T8" t="n">
-        <v>12.53</v>
+        <v>13.71</v>
       </c>
       <c r="U8" t="n">
-        <v>23.75</v>
+        <v>24.1</v>
       </c>
       <c r="V8" t="n">
-        <v>15.68</v>
+        <v>15.9</v>
       </c>
       <c r="W8" t="n">
         <v>12.88</v>
@@ -1704,13 +1704,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>74.0564</v>
+        <v>74.1674</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.6842</v>
+        <v>69.74760000000001</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,48 +1722,48 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>81.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>82.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AH8" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI8" t="n">
         <v>73.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>69.67</v>
+        <v>69.7</v>
       </c>
       <c r="AK8" t="n">
-        <v>77.31999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="AL8" t="n">
-        <v>77.31999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.84</v>
+        <v>4.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.36</v>
+        <v>10.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 77.32 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 77.39 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 69.67 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 69.70 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.49</v>
+        <v>65.63</v>
       </c>
       <c r="F9" t="n">
-        <v>71.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51.8</v>
+        <v>63.1</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>58.2</v>
       </c>
       <c r="J9" t="n">
-        <v>45.3</v>
+        <v>78.2</v>
       </c>
       <c r="K9" t="n">
-        <v>77.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>74.2</v>
+        <v>73.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1.76</v>
+        <v>3.03</v>
       </c>
       <c r="S9" t="n">
-        <v>36.28</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
-        <v>32.72</v>
+        <v>5.62</v>
       </c>
       <c r="U9" t="n">
-        <v>43.98</v>
+        <v>5.18</v>
       </c>
       <c r="V9" t="n">
-        <v>19.14</v>
+        <v>7.57</v>
       </c>
       <c r="W9" t="n">
-        <v>21.85</v>
+        <v>9.57</v>
       </c>
       <c r="X9" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.5723</v>
+        <v>63.7334</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.9259</v>
+        <v>63.2397</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,48 +1884,48 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>58.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>50.3</v>
+        <v>78.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI9" t="n">
-        <v>17.092</v>
+        <v>63.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14.19</v>
+        <v>62.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.164</v>
+        <v>65.63</v>
       </c>
       <c r="AL9" t="n">
-        <v>19.164</v>
+        <v>65.63</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.22</v>
+        <v>2.98</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.88</v>
+        <v>3.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.2%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 14.19 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,29 +1937,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65.56999999999999</v>
+        <v>18.66</v>
       </c>
       <c r="F10" t="n">
-        <v>71.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>63.1</v>
+        <v>52</v>
       </c>
       <c r="I10" t="n">
-        <v>58.7</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>78.2</v>
+        <v>45.3</v>
       </c>
       <c r="K10" t="n">
-        <v>82.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>73.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1993,52 +1993,52 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.21</v>
+        <v>38.43</v>
       </c>
       <c r="T10" t="n">
-        <v>4.66</v>
+        <v>34.28</v>
       </c>
       <c r="U10" t="n">
-        <v>5.66</v>
+        <v>46.49</v>
       </c>
       <c r="V10" t="n">
-        <v>7.54</v>
+        <v>19.48</v>
       </c>
       <c r="W10" t="n">
-        <v>9.58</v>
+        <v>21.84</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.85</v>
+        <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.6818</v>
+        <v>17.6327</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.2256</v>
+        <v>14.9532</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2046,48 +2046,48 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>58.7</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>78.2</v>
+        <v>50.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>82.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AH10" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI10" t="n">
-        <v>63.44</v>
+        <v>17.092</v>
       </c>
       <c r="AJ10" t="n">
-        <v>62.06</v>
+        <v>14.326</v>
       </c>
       <c r="AK10" t="n">
-        <v>65.56999999999999</v>
+        <v>19.164</v>
       </c>
       <c r="AL10" t="n">
-        <v>65.56999999999999</v>
+        <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.97</v>
+        <v>5.83</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.71</v>
+        <v>24.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 14.33 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>591.48</v>
+        <v>592.29</v>
       </c>
       <c r="F11" t="n">
         <v>68.7</v>
@@ -2169,22 +2169,22 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-6.44</v>
+        <v>-6.31</v>
       </c>
       <c r="S11" t="n">
-        <v>50.9</v>
+        <v>51.11</v>
       </c>
       <c r="T11" t="n">
-        <v>62.8</v>
+        <v>63.03</v>
       </c>
       <c r="U11" t="n">
-        <v>115.1</v>
+        <v>115.39</v>
       </c>
       <c r="V11" t="n">
-        <v>57.74</v>
+        <v>57.81</v>
       </c>
       <c r="W11" t="n">
-        <v>36.08</v>
+        <v>36.07</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
@@ -2193,10 +2193,10 @@
         <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>579.4886</v>
+        <v>579.5048</v>
       </c>
       <c r="AA11" t="n">
-        <v>425.735</v>
+        <v>425.739</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="AN11" t="n">
-        <v>38.93</v>
+        <v>39.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Accumulate Carefully, score 68.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.1%.</t>
+          <t>SMH: scenario base Accumulate Carefully, score 68.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.01</v>
+        <v>10.054</v>
       </c>
       <c r="F12" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
         <v>31.7</v>
       </c>
       <c r="K12" t="n">
-        <v>72.2</v>
+        <v>72.8</v>
       </c>
       <c r="L12" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,26 +2327,26 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-12.91</v>
+        <v>-10.65</v>
       </c>
       <c r="S12" t="n">
-        <v>10.03</v>
+        <v>11.28</v>
       </c>
       <c r="T12" t="n">
-        <v>23.51</v>
+        <v>20.45</v>
       </c>
       <c r="U12" t="n">
-        <v>57.48</v>
+        <v>57.63</v>
       </c>
       <c r="V12" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="W12" t="n">
-        <v>23.82</v>
+        <v>23.8</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
@@ -2355,10 +2355,10 @@
         <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5372</v>
+        <v>10.5404</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.032400000000001</v>
+        <v>9.0471</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2376,16 +2376,16 @@
         <v>36.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>72.2</v>
+        <v>72.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI12" t="n">
         <v>9.863</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.1906</v>
+        <v>9.243499999999999</v>
       </c>
       <c r="AK12" t="n">
         <v>10.872</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-5</v>
+        <v>-4.61</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.82</v>
+        <v>11.13</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 57.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 57.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.6%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 9.19 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 9.24 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>347.04</v>
+        <v>350.47</v>
       </c>
       <c r="F13" t="n">
-        <v>53.7</v>
+        <v>55.1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>67</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>38.1</v>
+        <v>42.5</v>
       </c>
       <c r="J13" t="n">
         <v>60.2</v>
       </c>
       <c r="K13" t="n">
-        <v>67.3</v>
+        <v>69</v>
       </c>
       <c r="L13" t="n">
-        <v>55.7</v>
+        <v>57.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,28 +2484,28 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 5.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 4.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-5.74</v>
+        <v>-5.32</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.39</v>
+        <v>-9.99</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.87</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>28.73</v>
+        <v>28.21</v>
       </c>
       <c r="V13" t="n">
-        <v>26.69</v>
+        <v>27.07</v>
       </c>
       <c r="W13" t="n">
         <v>18.23</v>
@@ -2514,13 +2514,13 @@
         <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>366.5446</v>
+        <v>365.7756</v>
       </c>
       <c r="AA13" t="n">
-        <v>367.2858</v>
+        <v>367.5404</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>38.1</v>
+        <v>42.5</v>
       </c>
       <c r="AF13" t="n">
         <v>60.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.3</v>
+        <v>69</v>
       </c>
       <c r="AH13" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI13" t="n">
         <v>338.68</v>
@@ -2550,20 +2550,20 @@
         <v>338.68</v>
       </c>
       <c r="AK13" t="n">
-        <v>362.44</v>
+        <v>361.71</v>
       </c>
       <c r="AL13" t="n">
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.32</v>
+        <v>-4.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>-5.51</v>
+        <v>-4.64</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 53.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.2%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28.685</v>
+        <v>28.55</v>
       </c>
       <c r="F14" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2618,16 +2618,16 @@
         <v>23.3</v>
       </c>
       <c r="I14" t="n">
-        <v>78.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>14.9</v>
       </c>
       <c r="K14" t="n">
-        <v>49.1</v>
+        <v>53.4</v>
       </c>
       <c r="L14" t="n">
-        <v>27.1</v>
+        <v>30.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,26 +2651,26 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 12.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1.99</v>
+        <v>-0.1</v>
       </c>
       <c r="S14" t="n">
-        <v>22.53</v>
+        <v>20.74</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.76</v>
+        <v>-0.28</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.53</v>
+        <v>-4.05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="W14" t="n">
-        <v>34.34</v>
+        <v>34.32</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
@@ -2679,10 +2679,10 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.5156</v>
+        <v>25.6421</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.6747</v>
+        <v>26.6666</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,16 +2694,16 @@
         <v>85</v>
       </c>
       <c r="AE14" t="n">
-        <v>78.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AF14" t="n">
         <v>19.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>49.1</v>
+        <v>53.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI14" t="n">
         <v>24.785</v>
@@ -2718,14 +2718,14 @@
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>12.42</v>
+        <v>11.34</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.54</v>
+        <v>7.06</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 48.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.4%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 49.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.3%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.56999999999999</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>83.2</v>
+        <v>83.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>79.3</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>80.7</v>
+        <v>82.7</v>
       </c>
       <c r="L2" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>26.76</v>
+        <v>27.06</v>
       </c>
       <c r="T2" t="n">
-        <v>34.66</v>
+        <v>33.3</v>
       </c>
       <c r="U2" t="n">
-        <v>62.46</v>
+        <v>61.64</v>
       </c>
       <c r="V2" t="n">
-        <v>25.77</v>
+        <v>26.71</v>
       </c>
       <c r="W2" t="n">
-        <v>13.95</v>
+        <v>13.91</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Z2" t="n">
-        <v>68.47839999999999</v>
+        <v>68.71040000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.1085</v>
+        <v>57.2293</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -753,13 +753,13 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>80.7</v>
+        <v>82.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI2" t="n">
         <v>68.89</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.51</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.32</v>
+        <v>24.87</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.36</v>
+        <v>48.51</v>
       </c>
       <c r="F3" t="n">
-        <v>80.5</v>
+        <v>80.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69.3</v>
+        <v>70.8</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.23</v>
+        <v>4.21</v>
       </c>
       <c r="S3" t="n">
-        <v>20.64</v>
+        <v>21.41</v>
       </c>
       <c r="T3" t="n">
-        <v>23.59</v>
+        <v>22.01</v>
       </c>
       <c r="U3" t="n">
-        <v>44.21</v>
+        <v>44.53</v>
       </c>
       <c r="V3" t="n">
-        <v>19.78</v>
+        <v>20.92</v>
       </c>
       <c r="W3" t="n">
-        <v>16.57</v>
+        <v>16.53</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.1934</v>
+        <v>47.2758</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.552</v>
+        <v>41.6124</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI3" t="n">
         <v>45.945</v>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.38</v>
+        <v>16.58</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>165.88</v>
+        <v>166.6</v>
       </c>
       <c r="F4" t="n">
-        <v>78.5</v>
+        <v>79</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>2.61</v>
       </c>
       <c r="S4" t="n">
-        <v>14.61</v>
+        <v>15.76</v>
       </c>
       <c r="T4" t="n">
-        <v>14.29</v>
+        <v>13.27</v>
       </c>
       <c r="U4" t="n">
-        <v>27.68</v>
+        <v>26.96</v>
       </c>
       <c r="V4" t="n">
-        <v>17.74</v>
+        <v>18.62</v>
       </c>
       <c r="W4" t="n">
-        <v>12.94</v>
+        <v>12.92</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>161.0456</v>
+        <v>161.3056</v>
       </c>
       <c r="AA4" t="n">
-        <v>149.2594</v>
+        <v>149.3995</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1083,7 +1083,7 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AI4" t="n">
         <v>159.24</v>
@@ -1092,25 +1092,25 @@
         <v>148.48</v>
       </c>
       <c r="AK4" t="n">
-        <v>166.04</v>
+        <v>166.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>166.04</v>
+        <v>166.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.14</v>
+        <v>11.51</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 79.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>125.72</v>
+        <v>126.34</v>
       </c>
       <c r="F5" t="n">
-        <v>77.5</v>
+        <v>78.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.3</v>
+        <v>73.5</v>
       </c>
       <c r="I5" t="n">
-        <v>83.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>78.2</v>
+        <v>78.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
-        <v>13.9</v>
+        <v>15.13</v>
       </c>
       <c r="T5" t="n">
-        <v>12.91</v>
+        <v>12.09</v>
       </c>
       <c r="U5" t="n">
-        <v>25.72</v>
+        <v>26.05</v>
       </c>
       <c r="V5" t="n">
-        <v>17.49</v>
+        <v>18.37</v>
       </c>
       <c r="W5" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.98</v>
+        <v>122.1718</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.9053</v>
+        <v>114.0038</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,7 +1245,7 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI5" t="n">
         <v>120.73</v>
@@ -1254,25 +1254,25 @@
         <v>112.96</v>
       </c>
       <c r="AK5" t="n">
-        <v>125.89</v>
+        <v>126.34</v>
       </c>
       <c r="AL5" t="n">
-        <v>125.89</v>
+        <v>126.34</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.37</v>
+        <v>10.82</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
+          <t>SWDA.MI: scenario base Buy Watchlist, score 78.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 125.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>706.12</v>
+        <v>710.36</v>
       </c>
       <c r="F6" t="n">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="I6" t="n">
-        <v>85.8</v>
+        <v>87</v>
       </c>
       <c r="J6" t="n">
         <v>64.3</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>77.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.77</v>
+        <v>1.73</v>
       </c>
       <c r="S6" t="n">
-        <v>15.46</v>
+        <v>16.71</v>
       </c>
       <c r="T6" t="n">
-        <v>13.03</v>
+        <v>12.37</v>
       </c>
       <c r="U6" t="n">
-        <v>25.53</v>
+        <v>24.8</v>
       </c>
       <c r="V6" t="n">
-        <v>18.3</v>
+        <v>18.97</v>
       </c>
       <c r="W6" t="n">
         <v>14.16</v>
@@ -1380,13 +1380,13 @@
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>688.2796</v>
+        <v>689.3724</v>
       </c>
       <c r="AA6" t="n">
-        <v>639.6289</v>
+        <v>640.1772</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>85.8</v>
+        <v>87</v>
       </c>
       <c r="AF6" t="n">
         <v>64.3</v>
@@ -1407,7 +1407,7 @@
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AI6" t="n">
         <v>681.24</v>
@@ -1422,14 +1422,14 @@
         <v>710.42</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.4</v>
+        <v>10.96</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65.06</v>
+        <v>64.86</v>
       </c>
       <c r="F7" t="n">
-        <v>76.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>72.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>77.7</v>
+        <v>78.3</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
       </c>
       <c r="K7" t="n">
-        <v>78.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>76.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="S7" t="n">
-        <v>11.05</v>
+        <v>11.84</v>
       </c>
       <c r="T7" t="n">
-        <v>10.72</v>
+        <v>9.77</v>
       </c>
       <c r="U7" t="n">
-        <v>23.1</v>
+        <v>23.36</v>
       </c>
       <c r="V7" t="n">
-        <v>15.36</v>
+        <v>16.47</v>
       </c>
       <c r="W7" t="n">
-        <v>12.89</v>
+        <v>12.83</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.9896</v>
+        <v>62.0831</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.7885</v>
+        <v>58.8445</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,16 +1560,16 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>77.7</v>
+        <v>78.3</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>78.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="AI7" t="n">
         <v>61.4745</v>
@@ -1584,14 +1584,14 @@
         <v>65.06</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.95</v>
+        <v>4.47</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.67</v>
+        <v>10.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.0%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77.39</v>
+        <v>77.17</v>
       </c>
       <c r="F8" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>66.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="I8" t="n">
-        <v>83.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="J8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>81.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="S8" t="n">
-        <v>13.44</v>
+        <v>14.04</v>
       </c>
       <c r="T8" t="n">
-        <v>13.71</v>
+        <v>11.5</v>
       </c>
       <c r="U8" t="n">
-        <v>24.1</v>
+        <v>23.93</v>
       </c>
       <c r="V8" t="n">
-        <v>15.9</v>
+        <v>16.4</v>
       </c>
       <c r="W8" t="n">
-        <v>12.88</v>
+        <v>12.86</v>
       </c>
       <c r="X8" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>74.1674</v>
+        <v>74.2754</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.74760000000001</v>
+        <v>69.81010000000001</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>83.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="AF8" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>81.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI8" t="n">
         <v>73.8</v>
@@ -1746,14 +1746,14 @@
         <v>77.39</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.96</v>
+        <v>10.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1797,7 +1797,7 @@
         <v>65.63</v>
       </c>
       <c r="F9" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>63.1</v>
+        <v>63.7</v>
       </c>
       <c r="I9" t="n">
-        <v>58.2</v>
+        <v>59.2</v>
       </c>
       <c r="J9" t="n">
         <v>78.2</v>
@@ -1817,7 +1817,7 @@
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>3.03</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>2.53</v>
+        <v>3.13</v>
       </c>
       <c r="T9" t="n">
-        <v>5.62</v>
+        <v>5.45</v>
       </c>
       <c r="U9" t="n">
-        <v>5.18</v>
+        <v>6.18</v>
       </c>
       <c r="V9" t="n">
-        <v>7.57</v>
+        <v>7.85</v>
       </c>
       <c r="W9" t="n">
         <v>9.57</v>
@@ -1866,13 +1866,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.7334</v>
+        <v>63.7932</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.2397</v>
+        <v>63.2561</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>58.2</v>
+        <v>59.2</v>
       </c>
       <c r="AF9" t="n">
         <v>78.2</v>
@@ -1893,7 +1893,7 @@
         <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI9" t="n">
         <v>63.44</v>
@@ -1908,14 +1908,14 @@
         <v>65.63</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.66</v>
+        <v>18.828</v>
       </c>
       <c r="F10" t="n">
         <v>71.09999999999999</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>52</v>
+        <v>53.4</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1976,10 +1976,10 @@
         <v>45.3</v>
       </c>
       <c r="K10" t="n">
-        <v>75.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="L10" t="n">
-        <v>73.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3.24</v>
+        <v>7.54</v>
       </c>
       <c r="S10" t="n">
-        <v>38.43</v>
+        <v>40.09</v>
       </c>
       <c r="T10" t="n">
-        <v>34.28</v>
+        <v>31.94</v>
       </c>
       <c r="U10" t="n">
-        <v>46.49</v>
+        <v>47.12</v>
       </c>
       <c r="V10" t="n">
-        <v>19.48</v>
+        <v>21.08</v>
       </c>
       <c r="W10" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.6327</v>
+        <v>17.6878</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.9532</v>
+        <v>14.9815</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,16 +2052,16 @@
         <v>50.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>75.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="AH10" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI10" t="n">
         <v>17.092</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14.326</v>
+        <v>14.4</v>
       </c>
       <c r="AK10" t="n">
         <v>19.164</v>
@@ -2070,14 +2070,14 @@
         <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>5.83</v>
+        <v>6.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>24.79</v>
+        <v>25.67</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.5%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 14.33 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 14.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>592.29</v>
+        <v>604.3</v>
       </c>
       <c r="F11" t="n">
-        <v>68.7</v>
+        <v>69</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>55.5</v>
+        <v>56.9</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -2141,7 +2141,7 @@
         <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2169,34 +2169,34 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-6.31</v>
+        <v>-5.27</v>
       </c>
       <c r="S11" t="n">
-        <v>51.11</v>
+        <v>54.03</v>
       </c>
       <c r="T11" t="n">
-        <v>63.03</v>
+        <v>67.8</v>
       </c>
       <c r="U11" t="n">
-        <v>115.39</v>
+        <v>115.53</v>
       </c>
       <c r="V11" t="n">
-        <v>57.81</v>
+        <v>60.68</v>
       </c>
       <c r="W11" t="n">
-        <v>36.07</v>
+        <v>36.11</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z11" t="n">
-        <v>579.5048</v>
+        <v>582.0542</v>
       </c>
       <c r="AA11" t="n">
-        <v>425.739</v>
+        <v>427.2292</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         <v>82.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AI11" t="n">
         <v>569.6900000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>422.92</v>
+        <v>430.31</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.21</v>
+        <v>3.82</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.12</v>
+        <v>41.45</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Accumulate Carefully, score 68.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.2%.</t>
+          <t>SMH: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 422.92 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 430.31 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.054</v>
+        <v>10.236</v>
       </c>
       <c r="F12" t="n">
-        <v>57.7</v>
+        <v>60.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30.4</v>
+        <v>32</v>
       </c>
       <c r="I12" t="n">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="K12" t="n">
-        <v>72.8</v>
+        <v>75.3</v>
       </c>
       <c r="L12" t="n">
-        <v>51.5</v>
+        <v>54.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-10.65</v>
+        <v>-5.4</v>
       </c>
       <c r="S12" t="n">
-        <v>11.28</v>
+        <v>16.79</v>
       </c>
       <c r="T12" t="n">
-        <v>20.45</v>
+        <v>23.03</v>
       </c>
       <c r="U12" t="n">
-        <v>57.63</v>
+        <v>57.26</v>
       </c>
       <c r="V12" t="n">
-        <v>2.24</v>
+        <v>4.24</v>
       </c>
       <c r="W12" t="n">
-        <v>23.8</v>
+        <v>23.79</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5404</v>
+        <v>10.5487</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.0471</v>
+        <v>9.0624</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>72.8</v>
+        <v>75.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI12" t="n">
         <v>9.863</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-4.61</v>
+        <v>-2.96</v>
       </c>
       <c r="AN12" t="n">
-        <v>11.13</v>
+        <v>12.95</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 57.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.6%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 60.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.0%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>350.47</v>
+        <v>349.69</v>
       </c>
       <c r="F13" t="n">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>67.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="I13" t="n">
-        <v>42.5</v>
+        <v>41.2</v>
       </c>
       <c r="J13" t="n">
         <v>60.2</v>
@@ -2465,7 +2465,7 @@
         <v>69</v>
       </c>
       <c r="L13" t="n">
-        <v>57.5</v>
+        <v>57.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2493,34 +2493,34 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-5.32</v>
+        <v>-3.52</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.99</v>
+        <v>-9.49</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-4.23</v>
       </c>
       <c r="U13" t="n">
-        <v>28.21</v>
+        <v>27.97</v>
       </c>
       <c r="V13" t="n">
-        <v>27.07</v>
+        <v>27.28</v>
       </c>
       <c r="W13" t="n">
-        <v>18.23</v>
+        <v>18.25</v>
       </c>
       <c r="X13" t="n">
         <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>365.7756</v>
+        <v>365.0114</v>
       </c>
       <c r="AA13" t="n">
-        <v>367.5404</v>
+        <v>367.7884</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>42.5</v>
+        <v>41.2</v>
       </c>
       <c r="AF13" t="n">
         <v>60.2</v>
@@ -2541,7 +2541,7 @@
         <v>69</v>
       </c>
       <c r="AH13" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI13" t="n">
         <v>338.68</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-4.18</v>
+        <v>-4.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>-4.64</v>
+        <v>-4.92</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.2%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.2%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28.55</v>
+        <v>29.385</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>49.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="I14" t="n">
-        <v>77.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="J14" t="n">
         <v>14.9</v>
       </c>
       <c r="K14" t="n">
-        <v>53.4</v>
+        <v>42.9</v>
       </c>
       <c r="L14" t="n">
-        <v>30.3</v>
+        <v>24.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 11.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 14.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-0.1</v>
+        <v>7.22</v>
       </c>
       <c r="S14" t="n">
-        <v>20.74</v>
+        <v>25.85</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.28</v>
+        <v>1.54</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.05</v>
+        <v>-4.47</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01</v>
+        <v>2.04</v>
       </c>
       <c r="W14" t="n">
-        <v>34.32</v>
+        <v>34.38</v>
       </c>
       <c r="X14" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.6421</v>
+        <v>25.7838</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.6666</v>
+        <v>26.6651</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,38 +2694,38 @@
         <v>85</v>
       </c>
       <c r="AE14" t="n">
-        <v>77.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="AF14" t="n">
         <v>19.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>53.4</v>
+        <v>42.9</v>
       </c>
       <c r="AH14" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AI14" t="n">
         <v>24.785</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20.205</v>
+        <v>21.03</v>
       </c>
       <c r="AK14" t="n">
-        <v>28.915</v>
+        <v>29.385</v>
       </c>
       <c r="AL14" t="n">
         <v>30.11</v>
       </c>
       <c r="AM14" t="n">
-        <v>11.34</v>
+        <v>13.97</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.06</v>
+        <v>10.2</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 49.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.3%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 49.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.0%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 21.03 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.45999999999999</v>
+        <v>70.27</v>
       </c>
       <c r="F2" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>79.3</v>
+        <v>78</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="L2" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>-0.3</v>
       </c>
       <c r="S2" t="n">
-        <v>27.06</v>
+        <v>20.99</v>
       </c>
       <c r="T2" t="n">
-        <v>33.3</v>
+        <v>29.91</v>
       </c>
       <c r="U2" t="n">
-        <v>61.64</v>
+        <v>58.07</v>
       </c>
       <c r="V2" t="n">
-        <v>26.71</v>
+        <v>25.79</v>
       </c>
       <c r="W2" t="n">
-        <v>13.91</v>
+        <v>13.95</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>68.71040000000001</v>
+        <v>68.9152</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.2293</v>
+        <v>57.3462</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -753,10 +753,10 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="AG2" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="AH2" t="n">
         <v>756</v>
@@ -765,7 +765,7 @@
         <v>68.89</v>
       </c>
       <c r="AJ2" t="n">
-        <v>57.9</v>
+        <v>58.27</v>
       </c>
       <c r="AK2" t="n">
         <v>73.47</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>1.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.87</v>
+        <v>22.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 57.90 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 58.27 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -818,34 +818,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.51</v>
+        <v>125.4</v>
       </c>
       <c r="F3" t="n">
-        <v>80.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>70.8</v>
+        <v>73</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>78.5</v>
       </c>
       <c r="J3" t="n">
-        <v>64.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>81.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -869,42 +869,42 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>4.21</v>
+        <v>2.23</v>
       </c>
       <c r="S3" t="n">
-        <v>21.41</v>
+        <v>11.43</v>
       </c>
       <c r="T3" t="n">
-        <v>22.01</v>
+        <v>10.86</v>
       </c>
       <c r="U3" t="n">
-        <v>44.53</v>
+        <v>23.88</v>
       </c>
       <c r="V3" t="n">
-        <v>20.92</v>
+        <v>18.08</v>
       </c>
       <c r="W3" t="n">
-        <v>16.53</v>
+        <v>13.17</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.17</v>
+        <v>-21.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.2758</v>
+        <v>122.3474</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.6124</v>
+        <v>114.102</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -912,10 +912,10 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>78.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>64.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>82.8</v>
@@ -924,36 +924,36 @@
         <v>756</v>
       </c>
       <c r="AI3" t="n">
-        <v>45.945</v>
+        <v>120.73</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42.255</v>
+        <v>114.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>50.73</v>
+        <v>126.34</v>
       </c>
       <c r="AL3" t="n">
-        <v>50.73</v>
+        <v>126.34</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.58</v>
+        <v>9.9</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 42.26 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 114.16 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -980,34 +980,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>166.6</v>
+        <v>705.4400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>76.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>74.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>86.8</v>
+        <v>81.8</v>
       </c>
       <c r="J4" t="n">
-        <v>67.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="K4" t="n">
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>79.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,38 +1035,38 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2.61</v>
+        <v>1.76</v>
       </c>
       <c r="S4" t="n">
-        <v>15.76</v>
+        <v>13.48</v>
       </c>
       <c r="T4" t="n">
-        <v>13.27</v>
+        <v>11.23</v>
       </c>
       <c r="U4" t="n">
-        <v>26.96</v>
+        <v>24.84</v>
       </c>
       <c r="V4" t="n">
-        <v>18.62</v>
+        <v>18.77</v>
       </c>
       <c r="W4" t="n">
-        <v>12.92</v>
+        <v>14.17</v>
       </c>
       <c r="X4" t="n">
-        <v>-21.07</v>
+        <v>-23.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>161.3056</v>
+        <v>690.3784000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>149.3995</v>
+        <v>640.7239</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1074,10 +1074,10 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>86.8</v>
+        <v>81.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>67.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="AG4" t="n">
         <v>82.8</v>
@@ -1086,36 +1086,36 @@
         <v>759</v>
       </c>
       <c r="AI4" t="n">
-        <v>159.24</v>
+        <v>681.24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>148.48</v>
+        <v>632.8</v>
       </c>
       <c r="AK4" t="n">
-        <v>166.6</v>
+        <v>710.42</v>
       </c>
       <c r="AL4" t="n">
-        <v>166.6</v>
+        <v>710.42</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.28</v>
+        <v>2.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.51</v>
+        <v>10.1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 79.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 166.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 710.42 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 148.48 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 632.80 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1127,12 +1127,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1142,34 +1142,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>126.34</v>
+        <v>64.45</v>
       </c>
       <c r="F5" t="n">
-        <v>78.2</v>
+        <v>75.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>73.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>84.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="J5" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K5" t="n">
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>78.7</v>
+        <v>76</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>4.19</v>
       </c>
       <c r="S5" t="n">
-        <v>15.13</v>
+        <v>6.82</v>
       </c>
       <c r="T5" t="n">
-        <v>12.09</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>26.05</v>
+        <v>21.99</v>
       </c>
       <c r="V5" t="n">
-        <v>18.37</v>
+        <v>16.15</v>
       </c>
       <c r="W5" t="n">
-        <v>13.17</v>
+        <v>12.83</v>
       </c>
       <c r="X5" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>122.1718</v>
+        <v>62.1713</v>
       </c>
       <c r="AA5" t="n">
-        <v>114.0038</v>
+        <v>58.8985</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1236,48 +1236,48 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>84.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AG5" t="n">
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="AI5" t="n">
-        <v>120.73</v>
+        <v>61.4745</v>
       </c>
       <c r="AJ5" t="n">
-        <v>112.96</v>
+        <v>59.5065</v>
       </c>
       <c r="AK5" t="n">
-        <v>126.34</v>
+        <v>65.06</v>
       </c>
       <c r="AL5" t="n">
-        <v>126.34</v>
+        <v>65.06</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.41</v>
+        <v>3.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.82</v>
+        <v>9.43</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Buy Watchlist, score 78.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 112.96 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1289,29 +1289,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>710.36</v>
+        <v>76.66</v>
       </c>
       <c r="F6" t="n">
-        <v>77.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>87</v>
+        <v>76.2</v>
       </c>
       <c r="J6" t="n">
-        <v>64.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>78.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>1.73</v>
+        <v>2.95</v>
       </c>
       <c r="S6" t="n">
-        <v>16.71</v>
+        <v>10.4</v>
       </c>
       <c r="T6" t="n">
-        <v>12.37</v>
+        <v>10.29</v>
       </c>
       <c r="U6" t="n">
-        <v>24.8</v>
+        <v>21.95</v>
       </c>
       <c r="V6" t="n">
-        <v>18.97</v>
+        <v>16.26</v>
       </c>
       <c r="W6" t="n">
-        <v>14.16</v>
+        <v>12.87</v>
       </c>
       <c r="X6" t="n">
-        <v>-23.32</v>
+        <v>-20.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>689.3724</v>
+        <v>74.3772</v>
       </c>
       <c r="AA6" t="n">
-        <v>640.1772</v>
+        <v>69.87220000000001</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>87</v>
+        <v>76.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AG6" t="n">
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="AI6" t="n">
-        <v>681.24</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>625.66</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>710.42</v>
+        <v>77.39</v>
       </c>
       <c r="AL6" t="n">
-        <v>710.42</v>
+        <v>77.39</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.96</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 710.42 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 77.39 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 625.66 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 70.29 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,14 +1466,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64.86</v>
+        <v>46.795</v>
       </c>
       <c r="F7" t="n">
-        <v>77.2</v>
+        <v>72.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,23 +1481,23 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>73.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>78.3</v>
+        <v>84.7</v>
       </c>
       <c r="J7" t="n">
-        <v>71.5</v>
+        <v>64.7</v>
       </c>
       <c r="K7" t="n">
-        <v>80.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>77.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1512,43 +1512,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4.7</v>
+        <v>0.72</v>
       </c>
       <c r="S7" t="n">
-        <v>11.84</v>
+        <v>10.97</v>
       </c>
       <c r="T7" t="n">
-        <v>9.77</v>
+        <v>16.42</v>
       </c>
       <c r="U7" t="n">
-        <v>23.36</v>
+        <v>38.04</v>
       </c>
       <c r="V7" t="n">
-        <v>16.47</v>
+        <v>19.21</v>
       </c>
       <c r="W7" t="n">
-        <v>12.83</v>
+        <v>16.66</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.33</v>
+        <v>-19.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>62.0831</v>
+        <v>47.3241</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.8445</v>
+        <v>41.6646</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1557,51 +1557,51 @@
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE7" t="n">
-        <v>78.3</v>
+        <v>84.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>71.5</v>
+        <v>64.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>80.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AH7" t="n">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="AI7" t="n">
-        <v>61.4745</v>
+        <v>45.945</v>
       </c>
       <c r="AJ7" t="n">
-        <v>59.5065</v>
+        <v>43.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>65.06</v>
+        <v>50.73</v>
       </c>
       <c r="AL7" t="n">
-        <v>65.06</v>
+        <v>50.73</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.47</v>
+        <v>-1.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.22</v>
+        <v>12.31</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 72.7, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.1%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 43.02 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1613,29 +1613,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77.17</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>76.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>66.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>82.5</v>
+        <v>60.9</v>
       </c>
       <c r="J8" t="n">
-        <v>68.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K8" t="n">
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>77.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1683,38 +1683,38 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="S8" t="n">
-        <v>14.04</v>
+        <v>3.96</v>
       </c>
       <c r="T8" t="n">
-        <v>11.5</v>
+        <v>6.28</v>
       </c>
       <c r="U8" t="n">
-        <v>23.93</v>
+        <v>6.43</v>
       </c>
       <c r="V8" t="n">
-        <v>16.4</v>
+        <v>8.48</v>
       </c>
       <c r="W8" t="n">
-        <v>12.86</v>
+        <v>9.57</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.6</v>
+        <v>-12.85</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>0.89</v>
       </c>
       <c r="Z8" t="n">
-        <v>74.2754</v>
+        <v>63.8662</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.81010000000001</v>
+        <v>63.2788</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>82.5</v>
+        <v>60.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>68.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="AG8" t="n">
         <v>82.8</v>
@@ -1734,36 +1734,36 @@
         <v>756</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.8</v>
+        <v>63.44</v>
       </c>
       <c r="AJ8" t="n">
-        <v>69.7</v>
+        <v>62.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>77.39</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AL8" t="n">
-        <v>77.39</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.9</v>
+        <v>3.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.54</v>
+        <v>4.63</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 77.39 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 69.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65.63</v>
+        <v>17.904</v>
       </c>
       <c r="F9" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>63.7</v>
+        <v>51.2</v>
       </c>
       <c r="I9" t="n">
-        <v>59.2</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>78.2</v>
+        <v>45.1</v>
       </c>
       <c r="K9" t="n">
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>73.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>3.13</v>
+        <v>25.5</v>
       </c>
       <c r="T9" t="n">
-        <v>5.45</v>
+        <v>24.98</v>
       </c>
       <c r="U9" t="n">
-        <v>6.18</v>
+        <v>37.51</v>
       </c>
       <c r="V9" t="n">
-        <v>7.85</v>
+        <v>18.73</v>
       </c>
       <c r="W9" t="n">
-        <v>9.57</v>
+        <v>22.02</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.85</v>
+        <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.7932</v>
+        <v>17.7236</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.2561</v>
+        <v>15.006</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>59.2</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.2</v>
+        <v>50.1</v>
       </c>
       <c r="AG9" t="n">
         <v>82.8</v>
@@ -1896,36 +1896,36 @@
         <v>756</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.44</v>
+        <v>17.092</v>
       </c>
       <c r="AJ9" t="n">
-        <v>62.06</v>
+        <v>14.74</v>
       </c>
       <c r="AK9" t="n">
-        <v>65.63</v>
+        <v>19.164</v>
       </c>
       <c r="AL9" t="n">
-        <v>65.63</v>
+        <v>19.164</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.88</v>
+        <v>1.02</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.75</v>
+        <v>19.31</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 72.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.0%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 14.74 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1952,48 +1952,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.828</v>
+        <v>581.45</v>
       </c>
       <c r="F10" t="n">
-        <v>71.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>53.4</v>
+        <v>55.4</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>45.3</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>73</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>72.8</v>
+        <v>56.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2007,87 +2007,87 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>7.54</v>
+        <v>-7.34</v>
       </c>
       <c r="S10" t="n">
-        <v>40.09</v>
+        <v>46.84</v>
       </c>
       <c r="T10" t="n">
-        <v>31.94</v>
+        <v>55.76</v>
       </c>
       <c r="U10" t="n">
-        <v>47.12</v>
+        <v>105.65</v>
       </c>
       <c r="V10" t="n">
-        <v>21.08</v>
+        <v>57.87</v>
       </c>
       <c r="W10" t="n">
-        <v>21.83</v>
+        <v>36.18</v>
       </c>
       <c r="X10" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.6878</v>
+        <v>584.0462</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.9815</v>
+        <v>428.615</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE10" t="n">
         <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>50.3</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>73</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AH10" t="n">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="AI10" t="n">
-        <v>17.092</v>
+        <v>570.91</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14.4</v>
+        <v>436.88</v>
       </c>
       <c r="AK10" t="n">
-        <v>19.164</v>
+        <v>668.91</v>
       </c>
       <c r="AL10" t="n">
-        <v>19.164</v>
+        <v>668.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>6.45</v>
+        <v>-0.44</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.67</v>
+        <v>35.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.5%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 65.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.4%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 14.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 436.88 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2099,157 +2099,157 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Oro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>604.3</v>
+        <v>348.83</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>54.1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>56.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>38.4</v>
       </c>
       <c r="J11" t="n">
-        <v>23.1</v>
+        <v>60.2</v>
       </c>
       <c r="K11" t="n">
-        <v>82.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>59</v>
+        <v>56.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-5.27</v>
+        <v>-3.48</v>
       </c>
       <c r="S11" t="n">
-        <v>54.03</v>
+        <v>-10.91</v>
       </c>
       <c r="T11" t="n">
-        <v>67.8</v>
+        <v>-5.59</v>
       </c>
       <c r="U11" t="n">
-        <v>115.53</v>
+        <v>27.95</v>
       </c>
       <c r="V11" t="n">
-        <v>60.68</v>
+        <v>27.03</v>
       </c>
       <c r="W11" t="n">
-        <v>36.11</v>
+        <v>18.25</v>
       </c>
       <c r="X11" t="n">
-        <v>-35.74</v>
+        <v>-22.39</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>582.0542</v>
+        <v>364.3138</v>
       </c>
       <c r="AA11" t="n">
-        <v>427.2292</v>
+        <v>368.0359</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>38.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>28.1</v>
+        <v>60.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>82.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AI11" t="n">
-        <v>569.6900000000001</v>
+        <v>338.68</v>
       </c>
       <c r="AJ11" t="n">
-        <v>430.31</v>
+        <v>338.68</v>
       </c>
       <c r="AK11" t="n">
-        <v>668.91</v>
+        <v>361.71</v>
       </c>
       <c r="AL11" t="n">
-        <v>668.91</v>
+        <v>396.71</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.82</v>
+        <v>-4.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.45</v>
+        <v>-5.22</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.2%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 430.31 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,30 +2280,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.236</v>
+        <v>9.673</v>
       </c>
       <c r="F12" t="n">
-        <v>60.4</v>
+        <v>53.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>30.1</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="J12" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="K12" t="n">
-        <v>75.3</v>
+        <v>67.3</v>
       </c>
       <c r="L12" t="n">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-5.4</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>16.79</v>
+        <v>6.3</v>
       </c>
       <c r="T12" t="n">
-        <v>23.03</v>
+        <v>15.29</v>
       </c>
       <c r="U12" t="n">
-        <v>57.26</v>
+        <v>44.21</v>
       </c>
       <c r="V12" t="n">
-        <v>4.24</v>
+        <v>1.84</v>
       </c>
       <c r="W12" t="n">
-        <v>23.79</v>
+        <v>23.99</v>
       </c>
       <c r="X12" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5487</v>
+        <v>10.5466</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.0624</v>
+        <v>9.0748</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,22 +2370,22 @@
         <v>65</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AF12" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>75.3</v>
+        <v>67.3</v>
       </c>
       <c r="AH12" t="n">
         <v>756</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.863</v>
+        <v>9.673</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.243499999999999</v>
+        <v>9.4422</v>
       </c>
       <c r="AK12" t="n">
         <v>10.872</v>
@@ -2394,14 +2394,14 @@
         <v>11.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>-2.96</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.95</v>
+        <v>6.59</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 60.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.0%.</t>
+          <t>INRG.MI: scenario base High Risk, score 53.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.3%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 9.24 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 9.44 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2423,157 +2423,157 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oro</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>349.69</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>54.8</v>
+        <v>49.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>67.5</v>
+        <v>24.4</v>
       </c>
       <c r="I13" t="n">
-        <v>41.2</v>
+        <v>90.7</v>
       </c>
       <c r="J13" t="n">
-        <v>60.2</v>
+        <v>14.8</v>
       </c>
       <c r="K13" t="n">
-        <v>69</v>
+        <v>35.8</v>
       </c>
       <c r="L13" t="n">
-        <v>57.1</v>
+        <v>20.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 4.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 15.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-3.52</v>
+        <v>10.58</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.49</v>
+        <v>28.12</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.23</v>
+        <v>3.16</v>
       </c>
       <c r="U13" t="n">
-        <v>27.97</v>
+        <v>-2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>27.28</v>
+        <v>2.23</v>
       </c>
       <c r="W13" t="n">
-        <v>18.25</v>
+        <v>34.39</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.39</v>
+        <v>-48.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>0.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>365.0114</v>
+        <v>25.9234</v>
       </c>
       <c r="AA13" t="n">
-        <v>367.7884</v>
+        <v>26.6654</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AE13" t="n">
-        <v>41.2</v>
+        <v>90.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.2</v>
+        <v>19.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>69</v>
+        <v>35.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI13" t="n">
-        <v>338.68</v>
+        <v>24.785</v>
       </c>
       <c r="AJ13" t="n">
-        <v>338.68</v>
+        <v>21.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>361.71</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>396.71</v>
+        <v>30.11</v>
       </c>
       <c r="AM13" t="n">
-        <v>-4.2</v>
+        <v>15.73</v>
       </c>
       <c r="AN13" t="n">
-        <v>-4.92</v>
+        <v>12.51</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 49.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.7%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 21.13 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2585,157 +2585,127 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>Vanguard FTSE All-World</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29.385</v>
-      </c>
+          <t>Azionario globale</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>49.8</v>
+        <v>29.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>24.4</v>
+        <v>39.2</v>
       </c>
       <c r="I14" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>14.9</v>
+        <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>24.5</v>
+        <v>28.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 14.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25.85</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-4.47</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="W14" t="n">
-        <v>34.38</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-48.6</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>25.7838</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>26.6651</v>
-      </c>
+          <t>Dati prezzo insufficienti.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
       <c r="AD14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.9</v>
+        <v>100</v>
       </c>
       <c r="AG14" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>757</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>24.785</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>21.03</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>29.385</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>10.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 49.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.0%.</t>
+          <t>VWCE.DE: scenario base Avoid for Now, score 29.8, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 21.03 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70.27</v>
+        <v>69.73</v>
       </c>
       <c r="F2" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>77.7</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-0.3</v>
+        <v>0.93</v>
       </c>
       <c r="S2" t="n">
-        <v>20.99</v>
+        <v>20.22</v>
       </c>
       <c r="T2" t="n">
-        <v>29.91</v>
+        <v>29.01</v>
       </c>
       <c r="U2" t="n">
-        <v>58.07</v>
+        <v>58.1</v>
       </c>
       <c r="V2" t="n">
-        <v>25.79</v>
+        <v>25.58</v>
       </c>
       <c r="W2" t="n">
         <v>13.95</v>
@@ -732,13 +732,13 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z2" t="n">
-        <v>68.9152</v>
+        <v>69.1142</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.3462</v>
+        <v>57.4593</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>756</v>
       </c>
       <c r="AI2" t="n">
-        <v>68.89</v>
+        <v>69.23</v>
       </c>
       <c r="AJ2" t="n">
         <v>58.27</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.97</v>
+        <v>0.89</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.54</v>
+        <v>21.36</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.9%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -818,14 +818,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>125.4</v>
+        <v>163.78</v>
       </c>
       <c r="F3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>73</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>78.5</v>
+        <v>77.5</v>
       </c>
       <c r="J3" t="n">
-        <v>66.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>82.8</v>
@@ -869,38 +869,38 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2.23</v>
+        <v>2.68</v>
       </c>
       <c r="S3" t="n">
-        <v>11.43</v>
+        <v>10.54</v>
       </c>
       <c r="T3" t="n">
-        <v>10.86</v>
+        <v>10.66</v>
       </c>
       <c r="U3" t="n">
-        <v>23.88</v>
+        <v>25.31</v>
       </c>
       <c r="V3" t="n">
         <v>18.08</v>
       </c>
       <c r="W3" t="n">
-        <v>13.17</v>
+        <v>12.94</v>
       </c>
       <c r="X3" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>122.3474</v>
+        <v>161.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>114.102</v>
+        <v>149.6666</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,48 +912,48 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>78.5</v>
+        <v>77.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>66.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="AI3" t="n">
-        <v>120.73</v>
+        <v>159.56</v>
       </c>
       <c r="AJ3" t="n">
-        <v>114.16</v>
+        <v>150.78</v>
       </c>
       <c r="AK3" t="n">
-        <v>126.34</v>
+        <v>166.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>126.34</v>
+        <v>166.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.9</v>
+        <v>9.43</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.3%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 114.16 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 150.78 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>705.4400000000001</v>
+        <v>124.48</v>
       </c>
       <c r="F4" t="n">
-        <v>76.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>70.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="I4" t="n">
-        <v>81.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1031,38 +1031,38 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.76</v>
+        <v>2.98</v>
       </c>
       <c r="S4" t="n">
-        <v>13.48</v>
+        <v>10.45</v>
       </c>
       <c r="T4" t="n">
-        <v>11.23</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>24.84</v>
+        <v>23.77</v>
       </c>
       <c r="V4" t="n">
-        <v>18.77</v>
+        <v>17.96</v>
       </c>
       <c r="W4" t="n">
-        <v>14.17</v>
+        <v>13.18</v>
       </c>
       <c r="X4" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>690.3784000000001</v>
+        <v>122.5116</v>
       </c>
       <c r="AA4" t="n">
-        <v>640.7239</v>
+        <v>114.196</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,48 +1074,48 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>81.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AF4" t="n">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="AI4" t="n">
-        <v>681.24</v>
+        <v>120.89</v>
       </c>
       <c r="AJ4" t="n">
-        <v>632.8</v>
+        <v>114.65</v>
       </c>
       <c r="AK4" t="n">
-        <v>710.42</v>
+        <v>126.34</v>
       </c>
       <c r="AL4" t="n">
-        <v>710.42</v>
+        <v>126.34</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.18</v>
+        <v>1.61</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.1</v>
+        <v>9.01</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 710.42 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 632.80 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 114.65 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1127,12 +1127,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>64.45</v>
+        <v>702.24</v>
       </c>
       <c r="F5" t="n">
-        <v>75.5</v>
+        <v>75.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>73.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
       <c r="J5" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="K5" t="n">
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>76.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1193,38 +1193,38 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>4.19</v>
+        <v>2.89</v>
       </c>
       <c r="S5" t="n">
-        <v>6.82</v>
+        <v>12.5</v>
       </c>
       <c r="T5" t="n">
-        <v>9.109999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="U5" t="n">
-        <v>21.99</v>
+        <v>23.81</v>
       </c>
       <c r="V5" t="n">
-        <v>16.15</v>
+        <v>18.8</v>
       </c>
       <c r="W5" t="n">
-        <v>12.83</v>
+        <v>14.17</v>
       </c>
       <c r="X5" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>62.1713</v>
+        <v>691.3556</v>
       </c>
       <c r="AA5" t="n">
-        <v>58.8985</v>
+        <v>641.259</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,48 +1236,48 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="AG5" t="n">
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AI5" t="n">
-        <v>61.4745</v>
+        <v>681.24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>59.5065</v>
+        <v>636.98</v>
       </c>
       <c r="AK5" t="n">
-        <v>65.06</v>
+        <v>710.42</v>
       </c>
       <c r="AL5" t="n">
-        <v>65.06</v>
+        <v>710.42</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.67</v>
+        <v>1.57</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.43</v>
+        <v>9.51</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 710.42 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 636.98 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1289,29 +1289,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76.66</v>
+        <v>63.45</v>
       </c>
       <c r="F6" t="n">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>66.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I6" t="n">
-        <v>76.2</v>
+        <v>66.8</v>
       </c>
       <c r="J6" t="n">
-        <v>68.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="K6" t="n">
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1350,43 +1350,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="S6" t="n">
-        <v>10.4</v>
+        <v>5.26</v>
       </c>
       <c r="T6" t="n">
-        <v>10.29</v>
+        <v>7.64</v>
       </c>
       <c r="U6" t="n">
-        <v>21.95</v>
+        <v>19.57</v>
       </c>
       <c r="V6" t="n">
-        <v>16.26</v>
+        <v>15.45</v>
       </c>
       <c r="W6" t="n">
         <v>12.87</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.6</v>
+        <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.3772</v>
+        <v>62.244</v>
       </c>
       <c r="AA6" t="n">
-        <v>69.87220000000001</v>
+        <v>58.9454</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>76.2</v>
+        <v>66.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>68.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AG6" t="n">
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="AI6" t="n">
-        <v>74.01000000000001</v>
+        <v>61.8701</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70.29000000000001</v>
+        <v>59.5065</v>
       </c>
       <c r="AK6" t="n">
-        <v>77.39</v>
+        <v>65.06</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.39</v>
+        <v>65.06</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.07</v>
+        <v>1.94</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.710000000000001</v>
+        <v>7.64</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 77.39 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 70.29 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,29 +1451,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>46.795</v>
+        <v>76.27</v>
       </c>
       <c r="F7" t="n">
-        <v>72.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,23 +1481,23 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>68.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>84.7</v>
+        <v>74.5</v>
       </c>
       <c r="J7" t="n">
-        <v>64.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>78.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>74.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.72</v>
+        <v>3.35</v>
       </c>
       <c r="S7" t="n">
-        <v>10.97</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>16.42</v>
+        <v>9.49</v>
       </c>
       <c r="U7" t="n">
-        <v>38.04</v>
+        <v>22.05</v>
       </c>
       <c r="V7" t="n">
-        <v>19.21</v>
+        <v>16.18</v>
       </c>
       <c r="W7" t="n">
-        <v>16.66</v>
+        <v>12.87</v>
       </c>
       <c r="X7" t="n">
-        <v>-19.17</v>
+        <v>-20.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>47.3241</v>
+        <v>74.4774</v>
       </c>
       <c r="AA7" t="n">
-        <v>41.6646</v>
+        <v>69.932</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1557,51 +1557,51 @@
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>84.7</v>
+        <v>74.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>64.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>78.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH7" t="n">
         <v>756</v>
       </c>
       <c r="AI7" t="n">
-        <v>45.945</v>
+        <v>74.36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.02</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>50.73</v>
+        <v>77.39</v>
       </c>
       <c r="AL7" t="n">
-        <v>50.73</v>
+        <v>77.39</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1.12</v>
+        <v>2.41</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.31</v>
+        <v>9.06</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 72.7, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.1%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 77.39 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 43.02 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 70.29 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1613,29 +1613,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>66.20999999999999</v>
+        <v>46.73</v>
       </c>
       <c r="F8" t="n">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,23 +1643,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>64.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="I8" t="n">
-        <v>60.9</v>
+        <v>85.5</v>
       </c>
       <c r="J8" t="n">
-        <v>78.2</v>
+        <v>64.7</v>
       </c>
       <c r="K8" t="n">
-        <v>82.8</v>
+        <v>77.7</v>
       </c>
       <c r="L8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1679,91 +1679,91 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.47</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.96</v>
+        <v>11.21</v>
       </c>
       <c r="T8" t="n">
-        <v>6.28</v>
+        <v>16.71</v>
       </c>
       <c r="U8" t="n">
-        <v>6.43</v>
+        <v>39.26</v>
       </c>
       <c r="V8" t="n">
-        <v>8.48</v>
+        <v>19.31</v>
       </c>
       <c r="W8" t="n">
-        <v>9.57</v>
+        <v>16.66</v>
       </c>
       <c r="X8" t="n">
-        <v>-12.85</v>
+        <v>-19.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.89</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>63.8662</v>
+        <v>47.3822</v>
       </c>
       <c r="AA8" t="n">
-        <v>63.2788</v>
+        <v>41.715</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE8" t="n">
-        <v>60.9</v>
+        <v>85.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>78.2</v>
+        <v>64.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>82.8</v>
+        <v>77.7</v>
       </c>
       <c r="AH8" t="n">
         <v>756</v>
       </c>
       <c r="AI8" t="n">
-        <v>63.44</v>
+        <v>46.425</v>
       </c>
       <c r="AJ8" t="n">
-        <v>62.06</v>
+        <v>43.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>66.20999999999999</v>
+        <v>50.73</v>
       </c>
       <c r="AL8" t="n">
-        <v>66.20999999999999</v>
+        <v>50.73</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.67</v>
+        <v>-1.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.63</v>
+        <v>12.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 72.9, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.4%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 43.12 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.904</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51.2</v>
+        <v>64.8</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="J9" t="n">
-        <v>45.1</v>
+        <v>78.2</v>
       </c>
       <c r="K9" t="n">
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>75.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1.63</v>
+        <v>3.48</v>
       </c>
       <c r="S9" t="n">
-        <v>25.5</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>24.98</v>
+        <v>5.3</v>
       </c>
       <c r="U9" t="n">
-        <v>37.51</v>
+        <v>6.3</v>
       </c>
       <c r="V9" t="n">
-        <v>18.73</v>
+        <v>8.41</v>
       </c>
       <c r="W9" t="n">
-        <v>22.02</v>
+        <v>9.57</v>
       </c>
       <c r="X9" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.7236</v>
+        <v>63.931</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.006</v>
+        <v>63.299</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>50.1</v>
+        <v>78.2</v>
       </c>
       <c r="AG9" t="n">
         <v>82.8</v>
@@ -1896,36 +1896,36 @@
         <v>756</v>
       </c>
       <c r="AI9" t="n">
-        <v>17.092</v>
+        <v>63.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14.74</v>
+        <v>62.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.164</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AL9" t="n">
-        <v>19.164</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.02</v>
+        <v>3.13</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.31</v>
+        <v>4.16</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 72.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.0%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 14.74 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1956,18 +1956,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>581.45</v>
+        <v>593.4299999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>65.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>55.4</v>
+        <v>56</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1976,14 +1976,14 @@
         <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>79.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>56.3</v>
+        <v>58.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>-7.34</v>
+        <v>4.17</v>
       </c>
       <c r="S10" t="n">
-        <v>46.84</v>
+        <v>48.39</v>
       </c>
       <c r="T10" t="n">
-        <v>55.76</v>
+        <v>57.16</v>
       </c>
       <c r="U10" t="n">
-        <v>105.65</v>
+        <v>112.78</v>
       </c>
       <c r="V10" t="n">
-        <v>57.87</v>
+        <v>58.86</v>
       </c>
       <c r="W10" t="n">
-        <v>36.18</v>
+        <v>36.17</v>
       </c>
       <c r="X10" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>584.0462</v>
+        <v>585.7859999999999</v>
       </c>
       <c r="AA10" t="n">
-        <v>428.615</v>
+        <v>430.0022</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AE10" t="n">
         <v>100</v>
@@ -2052,16 +2052,16 @@
         <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>79.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AI10" t="n">
         <v>570.91</v>
       </c>
       <c r="AJ10" t="n">
-        <v>436.88</v>
+        <v>443.34</v>
       </c>
       <c r="AK10" t="n">
         <v>668.91</v>
@@ -2070,14 +2070,14 @@
         <v>668.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.44</v>
+        <v>1.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.66</v>
+        <v>38.01</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 65.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.4%.</t>
+          <t>SMH: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.3%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 436.88 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 443.34 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2099,157 +2099,157 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Oro</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>348.83</v>
+        <v>17.63</v>
       </c>
       <c r="F11" t="n">
-        <v>54.1</v>
+        <v>68.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>67.40000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="I11" t="n">
-        <v>38.4</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>60.2</v>
+        <v>45.1</v>
       </c>
       <c r="K11" t="n">
-        <v>68.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>56.4</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 4.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-3.48</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.91</v>
+        <v>24.24</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.59</v>
+        <v>21.86</v>
       </c>
       <c r="U11" t="n">
-        <v>27.95</v>
+        <v>36.94</v>
       </c>
       <c r="V11" t="n">
-        <v>27.03</v>
+        <v>18.01</v>
       </c>
       <c r="W11" t="n">
-        <v>18.25</v>
+        <v>22.04</v>
       </c>
       <c r="X11" t="n">
-        <v>-22.39</v>
+        <v>-29.37</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="Z11" t="n">
-        <v>364.3138</v>
+        <v>17.7612</v>
       </c>
       <c r="AA11" t="n">
-        <v>368.0359</v>
+        <v>15.0288</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AE11" t="n">
-        <v>38.4</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>60.2</v>
+        <v>50.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>68.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AH11" t="n">
         <v>756</v>
       </c>
       <c r="AI11" t="n">
-        <v>338.68</v>
+        <v>17.272</v>
       </c>
       <c r="AJ11" t="n">
-        <v>338.68</v>
+        <v>14.784</v>
       </c>
       <c r="AK11" t="n">
-        <v>361.71</v>
+        <v>19.164</v>
       </c>
       <c r="AL11" t="n">
-        <v>396.71</v>
+        <v>19.164</v>
       </c>
       <c r="AM11" t="n">
-        <v>-4.25</v>
+        <v>-0.74</v>
       </c>
       <c r="AN11" t="n">
-        <v>-5.22</v>
+        <v>17.31</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.2%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.2, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 14.78 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.673</v>
+        <v>28.935</v>
       </c>
       <c r="F12" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,28 +2291,28 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30.1</v>
+        <v>23.6</v>
       </c>
       <c r="I12" t="n">
-        <v>79</v>
+        <v>96.7</v>
       </c>
       <c r="J12" t="n">
-        <v>31.5</v>
+        <v>14.8</v>
       </c>
       <c r="K12" t="n">
-        <v>67.3</v>
+        <v>54.4</v>
       </c>
       <c r="L12" t="n">
-        <v>46.2</v>
+        <v>35.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 8.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 11.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-8.609999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="S12" t="n">
-        <v>6.3</v>
+        <v>35.65</v>
       </c>
       <c r="T12" t="n">
-        <v>15.29</v>
+        <v>-3.07</v>
       </c>
       <c r="U12" t="n">
-        <v>44.21</v>
+        <v>-5.47</v>
       </c>
       <c r="V12" t="n">
-        <v>1.84</v>
+        <v>0.72</v>
       </c>
       <c r="W12" t="n">
-        <v>23.99</v>
+        <v>34.45</v>
       </c>
       <c r="X12" t="n">
-        <v>-43.36</v>
+        <v>-48.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5466</v>
+        <v>26.0452</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.0748</v>
+        <v>26.6565</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2367,51 +2367,51 @@
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AE12" t="n">
-        <v>79</v>
+        <v>96.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>36.5</v>
+        <v>19.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>67.3</v>
+        <v>54.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.673</v>
+        <v>24.785</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.4422</v>
+        <v>21.98</v>
       </c>
       <c r="AK12" t="n">
-        <v>10.872</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>11.61</v>
+        <v>30.11</v>
       </c>
       <c r="AM12" t="n">
-        <v>-8.279999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.59</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base High Risk, score 53.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.3%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 53.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.1%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 9.44 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 21.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2423,157 +2423,157 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Oro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>339.78</v>
       </c>
       <c r="F13" t="n">
-        <v>49.8</v>
+        <v>51.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>90.7</v>
+        <v>32.4</v>
       </c>
       <c r="J13" t="n">
-        <v>14.8</v>
+        <v>60.1</v>
       </c>
       <c r="K13" t="n">
-        <v>35.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>20.2</v>
+        <v>53.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 15.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>10.58</v>
+        <v>-4.5</v>
       </c>
       <c r="S13" t="n">
-        <v>28.12</v>
+        <v>-13.75</v>
       </c>
       <c r="T13" t="n">
-        <v>3.16</v>
+        <v>-7.59</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.41</v>
+        <v>24.72</v>
       </c>
       <c r="V13" t="n">
-        <v>2.23</v>
+        <v>26.2</v>
       </c>
       <c r="W13" t="n">
-        <v>34.39</v>
+        <v>18.31</v>
       </c>
       <c r="X13" t="n">
-        <v>-48.6</v>
+        <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.06</v>
+        <v>1.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>25.9234</v>
+        <v>363.5948</v>
       </c>
       <c r="AA13" t="n">
-        <v>26.6654</v>
+        <v>368.2369</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>90.7</v>
+        <v>32.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>19.8</v>
+        <v>60.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>35.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>24.785</v>
+        <v>338.68</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21.13</v>
+        <v>338.68</v>
       </c>
       <c r="AK13" t="n">
-        <v>30</v>
+        <v>361.71</v>
       </c>
       <c r="AL13" t="n">
-        <v>30.11</v>
+        <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>15.73</v>
+        <v>-6.55</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.51</v>
+        <v>-7.73</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 49.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.7%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 51.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 21.13 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2585,127 +2585,157 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Energia pulita</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>9.483000000000001</v>
+      </c>
       <c r="F14" t="n">
-        <v>29.8</v>
+        <v>51.4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>39.2</v>
+        <v>29.6</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>100</v>
+        <v>31.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>64.7</v>
       </c>
       <c r="L14" t="n">
-        <v>28.4</v>
+        <v>43.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+          <t>prezzo 10.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-6.87</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T14" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="U14" t="n">
+        <v>42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-43.36</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>10.5423</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>9.085900000000001</v>
+      </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>100</v>
+        <v>36.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>64.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
+        <v>756</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>9.483000000000001</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>9.4422</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>10.872</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-10.05</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>4.37</v>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Avoid for Now, score 29.8, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>INRG.MI: scenario base High Risk, score 51.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -10.1%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 9.44 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.73</v>
+        <v>71.45</v>
       </c>
       <c r="F2" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>82.8</v>
       </c>
       <c r="L2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.93</v>
+        <v>3.72</v>
       </c>
       <c r="S2" t="n">
-        <v>20.22</v>
+        <v>22.94</v>
       </c>
       <c r="T2" t="n">
-        <v>29.01</v>
+        <v>32.56</v>
       </c>
       <c r="U2" t="n">
-        <v>58.1</v>
+        <v>62.2</v>
       </c>
       <c r="V2" t="n">
-        <v>25.58</v>
+        <v>26.56</v>
       </c>
       <c r="W2" t="n">
-        <v>13.95</v>
+        <v>14.01</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>69.1142</v>
+        <v>69.331</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.4593</v>
+        <v>57.578</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>82.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI2" t="n">
-        <v>69.23</v>
+        <v>69.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>58.27</v>
+        <v>58.8</v>
       </c>
       <c r="AK2" t="n">
         <v>73.47</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.89</v>
+        <v>3.06</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.36</v>
+        <v>24.09</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 58.27 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 58.80 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -818,14 +818,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>163.78</v>
+        <v>47.73</v>
       </c>
       <c r="F3" t="n">
-        <v>76.5</v>
+        <v>78</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>73.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>77.5</v>
+        <v>89.8</v>
       </c>
       <c r="J3" t="n">
-        <v>67.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>76.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2.68</v>
+        <v>3.89</v>
       </c>
       <c r="S3" t="n">
-        <v>10.54</v>
+        <v>12.57</v>
       </c>
       <c r="T3" t="n">
-        <v>10.66</v>
+        <v>19.59</v>
       </c>
       <c r="U3" t="n">
-        <v>25.31</v>
+        <v>41.84</v>
       </c>
       <c r="V3" t="n">
-        <v>18.08</v>
+        <v>20.13</v>
       </c>
       <c r="W3" t="n">
-        <v>12.94</v>
+        <v>16.69</v>
       </c>
       <c r="X3" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>161.75</v>
+        <v>47.4564</v>
       </c>
       <c r="AA3" t="n">
-        <v>149.6666</v>
+        <v>41.7702</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,48 +912,48 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>77.5</v>
+        <v>89.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>67.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AI3" t="n">
-        <v>159.56</v>
+        <v>46.73</v>
       </c>
       <c r="AJ3" t="n">
-        <v>150.78</v>
+        <v>43.465</v>
       </c>
       <c r="AK3" t="n">
-        <v>166.6</v>
+        <v>50.73</v>
       </c>
       <c r="AL3" t="n">
-        <v>166.6</v>
+        <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.26</v>
+        <v>0.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.43</v>
+        <v>14.27</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.3%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 78.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 166.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 150.78 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 43.47 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>124.48</v>
+        <v>165.56</v>
       </c>
       <c r="F4" t="n">
-        <v>75.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>72.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>76.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>66.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>76.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1031,38 +1031,38 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2.98</v>
+        <v>3.97</v>
       </c>
       <c r="S4" t="n">
-        <v>10.45</v>
+        <v>11.44</v>
       </c>
       <c r="T4" t="n">
-        <v>9.710000000000001</v>
+        <v>12.08</v>
       </c>
       <c r="U4" t="n">
-        <v>23.77</v>
+        <v>26.63</v>
       </c>
       <c r="V4" t="n">
-        <v>17.96</v>
+        <v>18.48</v>
       </c>
       <c r="W4" t="n">
-        <v>13.18</v>
+        <v>12.95</v>
       </c>
       <c r="X4" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>122.5116</v>
+        <v>161.9988</v>
       </c>
       <c r="AA4" t="n">
-        <v>114.196</v>
+        <v>149.7996</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,48 +1074,48 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>76.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AF4" t="n">
-        <v>66.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AG4" t="n">
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="AI4" t="n">
-        <v>120.89</v>
+        <v>162.46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>114.65</v>
+        <v>151.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>126.34</v>
+        <v>166.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>126.34</v>
+        <v>166.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.01</v>
+        <v>10.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 114.65 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 151.70 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1127,12 +1127,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>702.24</v>
+        <v>125.72</v>
       </c>
       <c r="F5" t="n">
-        <v>75.7</v>
+        <v>76.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>79.5</v>
+        <v>78.5</v>
       </c>
       <c r="J5" t="n">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>76.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1193,38 +1193,38 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2.89</v>
+        <v>4.13</v>
       </c>
       <c r="S5" t="n">
-        <v>12.5</v>
+        <v>11.27</v>
       </c>
       <c r="T5" t="n">
-        <v>10.17</v>
+        <v>10.98</v>
       </c>
       <c r="U5" t="n">
-        <v>23.81</v>
+        <v>24.62</v>
       </c>
       <c r="V5" t="n">
-        <v>18.8</v>
+        <v>18.32</v>
       </c>
       <c r="W5" t="n">
-        <v>14.17</v>
+        <v>13.18</v>
       </c>
       <c r="X5" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>691.3556</v>
+        <v>122.6992</v>
       </c>
       <c r="AA5" t="n">
-        <v>641.259</v>
+        <v>114.2903</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,48 +1236,48 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>79.5</v>
+        <v>78.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AI5" t="n">
-        <v>681.24</v>
+        <v>122.82</v>
       </c>
       <c r="AJ5" t="n">
-        <v>636.98</v>
+        <v>115.32</v>
       </c>
       <c r="AK5" t="n">
-        <v>710.42</v>
+        <v>126.34</v>
       </c>
       <c r="AL5" t="n">
-        <v>710.42</v>
+        <v>126.34</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.51</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 710.42 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 636.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 115.32 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63.45</v>
+        <v>708.8</v>
       </c>
       <c r="F6" t="n">
-        <v>74.3</v>
+        <v>76.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>72.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>66.8</v>
+        <v>81.7</v>
       </c>
       <c r="J6" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="K6" t="n">
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>74.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1350,43 +1350,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>3.11</v>
+        <v>3.98</v>
       </c>
       <c r="S6" t="n">
-        <v>5.26</v>
+        <v>13.28</v>
       </c>
       <c r="T6" t="n">
-        <v>7.64</v>
+        <v>11.45</v>
       </c>
       <c r="U6" t="n">
-        <v>19.57</v>
+        <v>24.99</v>
       </c>
       <c r="V6" t="n">
-        <v>15.45</v>
+        <v>19.14</v>
       </c>
       <c r="W6" t="n">
-        <v>12.87</v>
+        <v>14.17</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>62.244</v>
+        <v>692.424</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.9454</v>
+        <v>641.7882</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>66.8</v>
+        <v>81.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="AG6" t="n">
         <v>82.8</v>
@@ -1410,36 +1410,36 @@
         <v>760</v>
       </c>
       <c r="AI6" t="n">
-        <v>61.8701</v>
+        <v>691.86</v>
       </c>
       <c r="AJ6" t="n">
-        <v>59.5065</v>
+        <v>642.1799999999999</v>
       </c>
       <c r="AK6" t="n">
-        <v>65.06</v>
+        <v>710.42</v>
       </c>
       <c r="AL6" t="n">
-        <v>65.06</v>
+        <v>710.42</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.64</v>
+        <v>10.44</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 710.42 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 642.18 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76.27</v>
+        <v>76.88</v>
       </c>
       <c r="F7" t="n">
-        <v>74.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="I7" t="n">
-        <v>74.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J7" t="n">
         <v>68.09999999999999</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>75.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1517,23 +1517,23 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
       <c r="S7" t="n">
-        <v>9.470000000000001</v>
+        <v>10.14</v>
       </c>
       <c r="T7" t="n">
-        <v>9.49</v>
+        <v>10.4</v>
       </c>
       <c r="U7" t="n">
-        <v>22.05</v>
+        <v>22.77</v>
       </c>
       <c r="V7" t="n">
-        <v>16.18</v>
+        <v>16.47</v>
       </c>
       <c r="W7" t="n">
         <v>12.87</v>
@@ -1542,13 +1542,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>74.4774</v>
+        <v>74.5904</v>
       </c>
       <c r="AA7" t="n">
-        <v>69.932</v>
+        <v>69.9907</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>74.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AF7" t="n">
         <v>68.09999999999999</v>
@@ -1569,13 +1569,13 @@
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI7" t="n">
-        <v>74.36</v>
+        <v>75.27</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70.29000000000001</v>
+        <v>70.78</v>
       </c>
       <c r="AK7" t="n">
         <v>77.39</v>
@@ -1584,14 +1584,14 @@
         <v>77.39</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.41</v>
+        <v>3.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.06</v>
+        <v>9.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 70.29 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 70.78 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1628,14 +1628,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>46.73</v>
+        <v>63.92</v>
       </c>
       <c r="F8" t="n">
-        <v>72.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,23 +1643,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68.8</v>
+        <v>72.8</v>
       </c>
       <c r="I8" t="n">
-        <v>85.5</v>
+        <v>67.2</v>
       </c>
       <c r="J8" t="n">
-        <v>64.7</v>
+        <v>71.5</v>
       </c>
       <c r="K8" t="n">
-        <v>77.7</v>
+        <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>74.8</v>
+        <v>75</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>3.98</v>
       </c>
       <c r="S8" t="n">
-        <v>11.21</v>
+        <v>5.71</v>
       </c>
       <c r="T8" t="n">
-        <v>16.71</v>
+        <v>7.27</v>
       </c>
       <c r="U8" t="n">
-        <v>39.26</v>
+        <v>19.54</v>
       </c>
       <c r="V8" t="n">
-        <v>19.31</v>
+        <v>15.71</v>
       </c>
       <c r="W8" t="n">
-        <v>16.66</v>
+        <v>12.86</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.17</v>
+        <v>-16.33</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>47.3822</v>
+        <v>62.3323</v>
       </c>
       <c r="AA8" t="n">
-        <v>41.715</v>
+        <v>58.995</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1719,51 +1719,51 @@
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>85.5</v>
+        <v>67.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>64.7</v>
+        <v>71.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.7</v>
+        <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="AI8" t="n">
-        <v>46.425</v>
+        <v>63.0272</v>
       </c>
       <c r="AJ8" t="n">
-        <v>43.12</v>
+        <v>59.5065</v>
       </c>
       <c r="AK8" t="n">
-        <v>50.73</v>
+        <v>65.06</v>
       </c>
       <c r="AL8" t="n">
-        <v>50.73</v>
+        <v>65.06</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1.38</v>
+        <v>2.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.02</v>
+        <v>8.35</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 72.9, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.4%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 43.12 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65.93000000000001</v>
+        <v>18.344</v>
       </c>
       <c r="F9" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>64.8</v>
+        <v>51.7</v>
       </c>
       <c r="I9" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>78.2</v>
+        <v>44.9</v>
       </c>
       <c r="K9" t="n">
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>73.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>3.48</v>
+        <v>7.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>28.05</v>
       </c>
       <c r="T9" t="n">
-        <v>5.3</v>
+        <v>28.55</v>
       </c>
       <c r="U9" t="n">
-        <v>6.3</v>
+        <v>42.18</v>
       </c>
       <c r="V9" t="n">
-        <v>8.41</v>
+        <v>19.55</v>
       </c>
       <c r="W9" t="n">
-        <v>9.57</v>
+        <v>22.14</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.85</v>
+        <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
         <v>0.88</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.931</v>
+        <v>17.812</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.299</v>
+        <v>15.0531</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,48 +1884,48 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.2</v>
+        <v>49.9</v>
       </c>
       <c r="AG9" t="n">
         <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.44</v>
+        <v>17.63</v>
       </c>
       <c r="AJ9" t="n">
-        <v>62.06</v>
+        <v>15.062</v>
       </c>
       <c r="AK9" t="n">
-        <v>66.20999999999999</v>
+        <v>19.164</v>
       </c>
       <c r="AL9" t="n">
-        <v>66.20999999999999</v>
+        <v>19.164</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.16</v>
+        <v>21.86</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 72.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 15.06 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,29 +1937,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>593.4299999999999</v>
+        <v>65.64</v>
       </c>
       <c r="F10" t="n">
-        <v>68.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>56</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>59.9</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>78.2</v>
       </c>
       <c r="K10" t="n">
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>58.9</v>
+        <v>73.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,57 +1988,57 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>4.17</v>
+        <v>2.27</v>
       </c>
       <c r="S10" t="n">
-        <v>48.39</v>
+        <v>4.32</v>
       </c>
       <c r="T10" t="n">
-        <v>57.16</v>
+        <v>4.24</v>
       </c>
       <c r="U10" t="n">
-        <v>112.78</v>
+        <v>5.41</v>
       </c>
       <c r="V10" t="n">
-        <v>58.86</v>
+        <v>8.24</v>
       </c>
       <c r="W10" t="n">
-        <v>36.17</v>
+        <v>9.57</v>
       </c>
       <c r="X10" t="n">
-        <v>-35.74</v>
+        <v>-12.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63</v>
+        <v>0.86</v>
       </c>
       <c r="Z10" t="n">
-        <v>585.7859999999999</v>
+        <v>63.9944</v>
       </c>
       <c r="AA10" t="n">
-        <v>430.0022</v>
+        <v>63.3168</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2046,48 +2046,48 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>100</v>
+        <v>59.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>78.2</v>
       </c>
       <c r="AG10" t="n">
         <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="AI10" t="n">
-        <v>570.91</v>
+        <v>63.44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>443.34</v>
+        <v>62.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>668.91</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>668.91</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.3</v>
+        <v>2.57</v>
       </c>
       <c r="AN10" t="n">
-        <v>38.01</v>
+        <v>3.67</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>SMH: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.3%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 443.34 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,14 +2114,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.63</v>
+        <v>607.73</v>
       </c>
       <c r="F11" t="n">
-        <v>68.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,33 +2129,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>50.6</v>
+        <v>56.5</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>45.1</v>
+        <v>23</v>
       </c>
       <c r="K11" t="n">
-        <v>78.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>72.90000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2169,87 +2169,87 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>24.24</v>
+        <v>43.7</v>
       </c>
       <c r="T11" t="n">
-        <v>21.86</v>
+        <v>56.78</v>
       </c>
       <c r="U11" t="n">
-        <v>36.94</v>
+        <v>115.05</v>
       </c>
       <c r="V11" t="n">
-        <v>18.01</v>
+        <v>60.03</v>
       </c>
       <c r="W11" t="n">
-        <v>22.04</v>
+        <v>36.17</v>
       </c>
       <c r="X11" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.82</v>
+        <v>1.66</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.7612</v>
+        <v>587.8068</v>
       </c>
       <c r="AA11" t="n">
-        <v>15.0288</v>
+        <v>431.465</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AE11" t="n">
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>50.1</v>
+        <v>28</v>
       </c>
       <c r="AG11" t="n">
-        <v>78.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="AI11" t="n">
-        <v>17.272</v>
+        <v>570.91</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14.784</v>
+        <v>452</v>
       </c>
       <c r="AK11" t="n">
-        <v>19.164</v>
+        <v>668.91</v>
       </c>
       <c r="AL11" t="n">
-        <v>19.164</v>
+        <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.74</v>
+        <v>3.39</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.31</v>
+        <v>40.85</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.2, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -0.7%.</t>
+          <t>SMH: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 14.78 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 452.00 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>28.935</v>
+        <v>29.43</v>
       </c>
       <c r="F12" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="I12" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
         <v>14.8</v>
       </c>
       <c r="K12" t="n">
-        <v>54.4</v>
+        <v>49.1</v>
       </c>
       <c r="L12" t="n">
-        <v>35.9</v>
+        <v>32.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 11.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 12.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>10.35</v>
+        <v>10.97</v>
       </c>
       <c r="S12" t="n">
-        <v>35.65</v>
+        <v>45.66</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.07</v>
+        <v>0.27</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.47</v>
+        <v>-3.93</v>
       </c>
       <c r="V12" t="n">
-        <v>0.72</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>34.45</v>
+        <v>34.44</v>
       </c>
       <c r="X12" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.0452</v>
+        <v>26.1776</v>
       </c>
       <c r="AA12" t="n">
-        <v>26.6565</v>
+        <v>26.651</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,22 +2370,22 @@
         <v>85</v>
       </c>
       <c r="AE12" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
         <v>19.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>54.4</v>
+        <v>49.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI12" t="n">
         <v>24.785</v>
       </c>
       <c r="AJ12" t="n">
-        <v>21.98</v>
+        <v>22.225</v>
       </c>
       <c r="AK12" t="n">
         <v>30</v>
@@ -2394,14 +2394,14 @@
         <v>30.11</v>
       </c>
       <c r="AM12" t="n">
-        <v>11.1</v>
+        <v>12.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>8.550000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 53.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.1%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 54.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.4%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 21.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 22.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>339.78</v>
+        <v>347.31</v>
       </c>
       <c r="F13" t="n">
-        <v>51.8</v>
+        <v>53.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="I13" t="n">
-        <v>32.4</v>
+        <v>37.5</v>
       </c>
       <c r="J13" t="n">
         <v>60.1</v>
       </c>
       <c r="K13" t="n">
-        <v>65.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="L13" t="n">
-        <v>53.5</v>
+        <v>56</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 4.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-4.5</v>
+        <v>1.05</v>
       </c>
       <c r="S13" t="n">
-        <v>-13.75</v>
+        <v>-11.33</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.59</v>
+        <v>-5.73</v>
       </c>
       <c r="U13" t="n">
-        <v>24.72</v>
+        <v>27.42</v>
       </c>
       <c r="V13" t="n">
-        <v>26.2</v>
+        <v>27.09</v>
       </c>
       <c r="W13" t="n">
-        <v>18.31</v>
+        <v>18.34</v>
       </c>
       <c r="X13" t="n">
         <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>363.5948</v>
+        <v>363.0602</v>
       </c>
       <c r="AA13" t="n">
-        <v>368.2369</v>
+        <v>368.4859</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>32.4</v>
+        <v>37.5</v>
       </c>
       <c r="AF13" t="n">
         <v>60.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>65.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI13" t="n">
         <v>338.68</v>
@@ -2556,14 +2556,14 @@
         <v>396.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-6.55</v>
+        <v>-4.34</v>
       </c>
       <c r="AN13" t="n">
-        <v>-7.73</v>
+        <v>-5.75</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 51.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 53.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.3%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.483000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="F14" t="n">
-        <v>51.4</v>
+        <v>53.4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>29.6</v>
+        <v>30.3</v>
       </c>
       <c r="I14" t="n">
-        <v>72.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="J14" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="K14" t="n">
-        <v>64.7</v>
+        <v>68.7</v>
       </c>
       <c r="L14" t="n">
-        <v>43.7</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 10.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-6.87</v>
+        <v>-1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>3.18</v>
+        <v>5.1</v>
       </c>
       <c r="T14" t="n">
-        <v>13.29</v>
+        <v>15.11</v>
       </c>
       <c r="U14" t="n">
-        <v>42</v>
+        <v>47.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="W14" t="n">
-        <v>24.01</v>
+        <v>24.06</v>
       </c>
       <c r="X14" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.5423</v>
+        <v>10.5393</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.085900000000001</v>
+        <v>9.0982</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,16 +2694,16 @@
         <v>65</v>
       </c>
       <c r="AE14" t="n">
-        <v>72.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="AF14" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>64.7</v>
+        <v>68.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI14" t="n">
         <v>9.483000000000001</v>
@@ -2718,14 +2718,14 @@
         <v>11.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>-10.05</v>
+        <v>-7.39</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.37</v>
+        <v>7.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base High Risk, score 51.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -10.1%.</t>
+          <t>INRG.MI: scenario base High Risk, score 53.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.4%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.45</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,13 +671,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="K2" t="n">
         <v>82.8</v>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>3.72</v>
+        <v>3.22</v>
       </c>
       <c r="S2" t="n">
-        <v>22.94</v>
+        <v>23.42</v>
       </c>
       <c r="T2" t="n">
-        <v>32.56</v>
+        <v>30.98</v>
       </c>
       <c r="U2" t="n">
-        <v>62.2</v>
+        <v>61.4</v>
       </c>
       <c r="V2" t="n">
-        <v>26.56</v>
+        <v>26.53</v>
       </c>
       <c r="W2" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>69.331</v>
+        <v>69.53019999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.578</v>
+        <v>57.6978</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="AG2" t="n">
         <v>82.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI2" t="n">
         <v>69.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>58.8</v>
+        <v>59.1</v>
       </c>
       <c r="AK2" t="n">
         <v>73.47</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.06</v>
+        <v>2.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.09</v>
+        <v>23.85</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 58.80 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.10 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -822,30 +822,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.73</v>
+        <v>47.87</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>89.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="K3" t="n">
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>3.89</v>
+        <v>3.11</v>
       </c>
       <c r="S3" t="n">
-        <v>12.57</v>
+        <v>13.29</v>
       </c>
       <c r="T3" t="n">
-        <v>19.59</v>
+        <v>18.86</v>
       </c>
       <c r="U3" t="n">
-        <v>41.84</v>
+        <v>41.9</v>
       </c>
       <c r="V3" t="n">
-        <v>20.13</v>
+        <v>20.21</v>
       </c>
       <c r="W3" t="n">
-        <v>16.69</v>
+        <v>16.68</v>
       </c>
       <c r="X3" t="n">
         <v>-19.17</v>
@@ -897,14 +897,14 @@
         <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.4564</v>
+        <v>47.5279</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.7702</v>
+        <v>41.8259</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -912,22 +912,22 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>89.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="AG3" t="n">
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI3" t="n">
         <v>46.73</v>
       </c>
       <c r="AJ3" t="n">
-        <v>43.465</v>
+        <v>43.76</v>
       </c>
       <c r="AK3" t="n">
         <v>50.73</v>
@@ -936,14 +936,14 @@
         <v>50.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.27</v>
+        <v>14.45</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 78.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.6%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 43.47 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 43.76 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>165.56</v>
+        <v>166.14</v>
       </c>
       <c r="F4" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>79.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="J4" t="n">
         <v>67.59999999999999</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3.97</v>
+        <v>4.12</v>
       </c>
       <c r="S4" t="n">
-        <v>11.44</v>
+        <v>11.89</v>
       </c>
       <c r="T4" t="n">
-        <v>12.08</v>
+        <v>11.58</v>
       </c>
       <c r="U4" t="n">
-        <v>26.63</v>
+        <v>26.73</v>
       </c>
       <c r="V4" t="n">
-        <v>18.48</v>
+        <v>18.59</v>
       </c>
       <c r="W4" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="X4" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>161.9988</v>
+        <v>162.2424</v>
       </c>
       <c r="AA4" t="n">
-        <v>149.7996</v>
+        <v>149.9351</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>79.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="AF4" t="n">
         <v>67.59999999999999</v>
@@ -1083,13 +1083,13 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI4" t="n">
-        <v>162.46</v>
+        <v>163.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>151.7</v>
+        <v>152.56</v>
       </c>
       <c r="AK4" t="n">
         <v>166.6</v>
@@ -1098,14 +1098,14 @@
         <v>166.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.52</v>
+        <v>10.81</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 151.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 152.56 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>125.72</v>
+        <v>126.16</v>
       </c>
       <c r="F5" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="I5" t="n">
-        <v>78.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>66.90000000000001</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>76.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>4.13</v>
+        <v>4.36</v>
       </c>
       <c r="S5" t="n">
-        <v>11.27</v>
+        <v>11.69</v>
       </c>
       <c r="T5" t="n">
-        <v>10.98</v>
+        <v>10.47</v>
       </c>
       <c r="U5" t="n">
-        <v>24.62</v>
+        <v>25.06</v>
       </c>
       <c r="V5" t="n">
-        <v>18.32</v>
+        <v>18.44</v>
       </c>
       <c r="W5" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="X5" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>122.6992</v>
+        <v>122.881</v>
       </c>
       <c r="AA5" t="n">
-        <v>114.2903</v>
+        <v>114.3864</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>78.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>66.90000000000001</v>
@@ -1245,13 +1245,13 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI5" t="n">
-        <v>122.82</v>
+        <v>123.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>115.32</v>
+        <v>116.1</v>
       </c>
       <c r="AK5" t="n">
         <v>126.34</v>
@@ -1260,14 +1260,14 @@
         <v>126.34</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>10.29</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 115.32 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 116.10 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>708.8</v>
+        <v>711.48</v>
       </c>
       <c r="F6" t="n">
-        <v>76.3</v>
+        <v>76.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>81.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>76.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>3.98</v>
+        <v>4.44</v>
       </c>
       <c r="S6" t="n">
-        <v>13.28</v>
+        <v>13.72</v>
       </c>
       <c r="T6" t="n">
-        <v>11.45</v>
+        <v>11.07</v>
       </c>
       <c r="U6" t="n">
-        <v>24.99</v>
+        <v>25.08</v>
       </c>
       <c r="V6" t="n">
-        <v>19.14</v>
+        <v>19.27</v>
       </c>
       <c r="W6" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="X6" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>692.424</v>
+        <v>693.522</v>
       </c>
       <c r="AA6" t="n">
-        <v>641.7882</v>
+        <v>642.3258</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>81.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AG6" t="n">
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI6" t="n">
-        <v>691.86</v>
+        <v>696.42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>642.1799999999999</v>
+        <v>647.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>710.42</v>
+        <v>711.48</v>
       </c>
       <c r="AL6" t="n">
-        <v>710.42</v>
+        <v>711.48</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.37</v>
+        <v>2.59</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.44</v>
+        <v>10.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 710.42 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 711.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 642.18 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 647.40 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76.88</v>
+        <v>77.2</v>
       </c>
       <c r="F7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>67</v>
+        <v>67.2</v>
       </c>
       <c r="I7" t="n">
-        <v>76.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="J7" t="n">
         <v>68.09999999999999</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="S7" t="n">
-        <v>10.14</v>
+        <v>10.76</v>
       </c>
       <c r="T7" t="n">
-        <v>10.4</v>
+        <v>9.82</v>
       </c>
       <c r="U7" t="n">
-        <v>22.77</v>
+        <v>23.11</v>
       </c>
       <c r="V7" t="n">
-        <v>16.47</v>
+        <v>16.6</v>
       </c>
       <c r="W7" t="n">
-        <v>12.87</v>
+        <v>12.86</v>
       </c>
       <c r="X7" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>74.5904</v>
+        <v>74.7034</v>
       </c>
       <c r="AA7" t="n">
-        <v>69.9907</v>
+        <v>70.0514</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>76.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="AF7" t="n">
         <v>68.09999999999999</v>
@@ -1569,13 +1569,13 @@
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI7" t="n">
-        <v>75.27</v>
+        <v>75.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70.78</v>
+        <v>71.23</v>
       </c>
       <c r="AK7" t="n">
         <v>77.39</v>
@@ -1584,14 +1584,14 @@
         <v>77.39</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.07</v>
+        <v>3.34</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.84</v>
+        <v>10.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 70.78 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 71.23 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1613,29 +1613,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63.92</v>
+        <v>18.27</v>
       </c>
       <c r="F8" t="n">
-        <v>74.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>72.8</v>
+        <v>51.7</v>
       </c>
       <c r="I8" t="n">
-        <v>67.2</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>71.5</v>
+        <v>44.9</v>
       </c>
       <c r="K8" t="n">
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3.98</v>
+        <v>5.78</v>
       </c>
       <c r="S8" t="n">
-        <v>5.71</v>
+        <v>26.88</v>
       </c>
       <c r="T8" t="n">
-        <v>7.27</v>
+        <v>25.62</v>
       </c>
       <c r="U8" t="n">
-        <v>19.54</v>
+        <v>40.82</v>
       </c>
       <c r="V8" t="n">
-        <v>15.71</v>
+        <v>19.36</v>
       </c>
       <c r="W8" t="n">
-        <v>12.86</v>
+        <v>22.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-16.33</v>
+        <v>-29.37</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0.88</v>
       </c>
       <c r="Z8" t="n">
-        <v>62.3323</v>
+        <v>17.856</v>
       </c>
       <c r="AA8" t="n">
-        <v>58.995</v>
+        <v>15.0772</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,48 +1722,48 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>67.2</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>71.5</v>
+        <v>49.9</v>
       </c>
       <c r="AG8" t="n">
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AI8" t="n">
-        <v>63.0272</v>
+        <v>17.63</v>
       </c>
       <c r="AJ8" t="n">
-        <v>59.5065</v>
+        <v>15.276</v>
       </c>
       <c r="AK8" t="n">
-        <v>65.06</v>
+        <v>19.164</v>
       </c>
       <c r="AL8" t="n">
-        <v>65.06</v>
+        <v>19.164</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.35</v>
+        <v>21.18</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 72.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 15.28 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.344</v>
+        <v>65.67</v>
       </c>
       <c r="F9" t="n">
-        <v>72.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>60.4</v>
       </c>
       <c r="J9" t="n">
-        <v>44.9</v>
+        <v>78.2</v>
       </c>
       <c r="K9" t="n">
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>75.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>7.33</v>
+        <v>2.11</v>
       </c>
       <c r="S9" t="n">
-        <v>28.05</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>28.55</v>
+        <v>4.01</v>
       </c>
       <c r="U9" t="n">
-        <v>42.18</v>
+        <v>5.7</v>
       </c>
       <c r="V9" t="n">
-        <v>19.55</v>
+        <v>8.24</v>
       </c>
       <c r="W9" t="n">
-        <v>22.14</v>
+        <v>9.56</v>
       </c>
       <c r="X9" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.812</v>
+        <v>64.05200000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.0531</v>
+        <v>63.3348</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,48 +1884,48 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>60.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>49.9</v>
+        <v>78.2</v>
       </c>
       <c r="AG9" t="n">
         <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI9" t="n">
-        <v>17.63</v>
+        <v>63.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.062</v>
+        <v>62.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.164</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AL9" t="n">
-        <v>19.164</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.86</v>
+        <v>3.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 72.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 15.06 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,29 +1937,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65.64</v>
+        <v>611.625</v>
       </c>
       <c r="F10" t="n">
-        <v>71.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>64.40000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="I10" t="n">
-        <v>59.9</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>78.2</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
         <v>82.8</v>
       </c>
       <c r="L10" t="n">
-        <v>73.8</v>
+        <v>58.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,57 +1988,57 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2.27</v>
+        <v>3.49</v>
       </c>
       <c r="S10" t="n">
-        <v>4.32</v>
+        <v>42.14</v>
       </c>
       <c r="T10" t="n">
-        <v>4.24</v>
+        <v>58.86</v>
       </c>
       <c r="U10" t="n">
-        <v>5.41</v>
+        <v>114.96</v>
       </c>
       <c r="V10" t="n">
-        <v>8.24</v>
+        <v>60.27</v>
       </c>
       <c r="W10" t="n">
-        <v>9.57</v>
+        <v>36.14</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.85</v>
+        <v>-35.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.86</v>
+        <v>1.67</v>
       </c>
       <c r="Z10" t="n">
-        <v>63.9944</v>
+        <v>590.2151</v>
       </c>
       <c r="AA10" t="n">
-        <v>63.3168</v>
+        <v>432.9173</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2046,48 +2046,48 @@
         <v>85</v>
       </c>
       <c r="AE10" t="n">
-        <v>59.9</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>78.2</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
         <v>82.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="AI10" t="n">
-        <v>63.44</v>
+        <v>581.45</v>
       </c>
       <c r="AJ10" t="n">
-        <v>62.06</v>
+        <v>453</v>
       </c>
       <c r="AK10" t="n">
-        <v>66.20999999999999</v>
+        <v>668.91</v>
       </c>
       <c r="AL10" t="n">
-        <v>66.20999999999999</v>
+        <v>668.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.57</v>
+        <v>3.63</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.67</v>
+        <v>41.28</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>SMH: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 453.00 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,34 +2114,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>607.73</v>
+        <v>29.19</v>
       </c>
       <c r="F11" t="n">
-        <v>68.90000000000001</v>
+        <v>54.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>56.5</v>
+        <v>23.8</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>23</v>
+        <v>14.8</v>
       </c>
       <c r="K11" t="n">
-        <v>82.8</v>
+        <v>55</v>
       </c>
       <c r="L11" t="n">
-        <v>58.9</v>
+        <v>37.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 10.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>12.49</v>
       </c>
       <c r="S11" t="n">
-        <v>43.7</v>
+        <v>38.8</v>
       </c>
       <c r="T11" t="n">
-        <v>56.78</v>
+        <v>-0.65</v>
       </c>
       <c r="U11" t="n">
-        <v>115.05</v>
+        <v>-5.06</v>
       </c>
       <c r="V11" t="n">
-        <v>60.03</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>36.17</v>
+        <v>34.42</v>
       </c>
       <c r="X11" t="n">
-        <v>-35.74</v>
+        <v>-48.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.66</v>
+        <v>0.03</v>
       </c>
       <c r="Z11" t="n">
-        <v>587.8068</v>
+        <v>26.3094</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.465</v>
+        <v>26.644</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,45 +2211,45 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>28</v>
+        <v>19.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>82.8</v>
+        <v>55</v>
       </c>
       <c r="AH11" t="n">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="AI11" t="n">
-        <v>570.91</v>
+        <v>24.785</v>
       </c>
       <c r="AJ11" t="n">
-        <v>452</v>
+        <v>22.225</v>
       </c>
       <c r="AK11" t="n">
-        <v>668.91</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>668.91</v>
+        <v>30.11</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.39</v>
+        <v>10.95</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.85</v>
+        <v>9.56</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.4%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 54.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.9%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 452.00 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 22.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2261,157 +2261,157 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Oro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>29.43</v>
+        <v>345.19</v>
       </c>
       <c r="F12" t="n">
-        <v>54.1</v>
+        <v>53.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>37.2</v>
       </c>
       <c r="J12" t="n">
-        <v>14.8</v>
+        <v>60.1</v>
       </c>
       <c r="K12" t="n">
-        <v>49.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>32.8</v>
+        <v>55.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 12.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 4.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>10.97</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>45.66</v>
+        <v>-10.88</v>
       </c>
       <c r="T12" t="n">
-        <v>0.27</v>
+        <v>-7.35</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.93</v>
+        <v>27.29</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>26.79</v>
       </c>
       <c r="W12" t="n">
-        <v>34.44</v>
+        <v>18.33</v>
       </c>
       <c r="X12" t="n">
-        <v>-48.6</v>
+        <v>-22.39</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.04</v>
+        <v>1.46</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.1776</v>
+        <v>362.3772</v>
       </c>
       <c r="AA12" t="n">
-        <v>26.651</v>
+        <v>368.707</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>37.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.8</v>
+        <v>60.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>49.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AH12" t="n">
         <v>758</v>
       </c>
       <c r="AI12" t="n">
-        <v>24.785</v>
+        <v>338.68</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22.225</v>
+        <v>338.68</v>
       </c>
       <c r="AK12" t="n">
-        <v>30</v>
+        <v>361.71</v>
       </c>
       <c r="AL12" t="n">
-        <v>30.11</v>
+        <v>396.71</v>
       </c>
       <c r="AM12" t="n">
-        <v>12.42</v>
+        <v>-4.74</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.43</v>
+        <v>-6.38</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 54.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.4%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 53.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.7%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 22.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2423,157 +2423,157 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oro</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>347.31</v>
+        <v>9.657999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>53.8</v>
+        <v>52.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="H13" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K13" t="n">
         <v>67.3</v>
       </c>
-      <c r="I13" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>68.7</v>
-      </c>
       <c r="L13" t="n">
-        <v>56</v>
+        <v>45.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 4.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1.05</v>
+        <v>-4.21</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.33</v>
+        <v>4.48</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.73</v>
+        <v>13.36</v>
       </c>
       <c r="U13" t="n">
-        <v>27.42</v>
+        <v>47.11</v>
       </c>
       <c r="V13" t="n">
-        <v>27.09</v>
+        <v>1.92</v>
       </c>
       <c r="W13" t="n">
-        <v>18.34</v>
+        <v>24.05</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.39</v>
+        <v>-43.36</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>363.0602</v>
+        <v>10.5317</v>
       </c>
       <c r="AA13" t="n">
-        <v>368.4859</v>
+        <v>9.1097</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AE13" t="n">
-        <v>37.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.1</v>
+        <v>36.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>68.7</v>
+        <v>67.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI13" t="n">
-        <v>338.68</v>
+        <v>9.483000000000001</v>
       </c>
       <c r="AJ13" t="n">
-        <v>338.68</v>
+        <v>9.4422</v>
       </c>
       <c r="AK13" t="n">
-        <v>361.71</v>
+        <v>10.872</v>
       </c>
       <c r="AL13" t="n">
-        <v>396.71</v>
+        <v>11.61</v>
       </c>
       <c r="AM13" t="n">
-        <v>-4.34</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>-5.75</v>
+        <v>6.02</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 53.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.3%.</t>
+          <t>INRG.MI: scenario base High Risk, score 52.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.3%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 9.44 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2585,29 +2585,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.76</v>
+        <v>63.99</v>
       </c>
       <c r="F14" t="n">
-        <v>53.4</v>
+        <v>46.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,23 +2615,23 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>30.3</v>
+        <v>39.2</v>
       </c>
       <c r="I14" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>31.4</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>68.7</v>
+        <v>76.8</v>
       </c>
       <c r="L14" t="n">
-        <v>46.4</v>
+        <v>40.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Insufficient History</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2651,39 +2651,19 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 7.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="U14" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="W14" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-43.36</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>10.5393</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>9.0982</v>
-      </c>
+          <t>vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
           <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
@@ -2691,51 +2671,47 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AE14" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="AF14" t="n">
-        <v>36.4</v>
+        <v>30</v>
       </c>
       <c r="AG14" t="n">
-        <v>68.7</v>
+        <v>76.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>757</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>9.483000000000001</v>
+        <v>63.99</v>
       </c>
       <c r="AJ14" t="n">
-        <v>9.4422</v>
+        <v>63.99</v>
       </c>
       <c r="AK14" t="n">
-        <v>10.872</v>
+        <v>63.99</v>
       </c>
       <c r="AL14" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-7.39</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>7.27</v>
-      </c>
+        <v>63.99</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base High Risk, score 53.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.4%.</t>
+          <t>EXSA.DE: scenario base High Risk, score 46.6, trend Insufficient History. Entry zone: Monitor / partial entry only. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 9.44 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 63.99 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.45999999999999</v>
+        <v>71.05</v>
       </c>
       <c r="F2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.7</v>
+        <v>78</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>82.8</v>
       </c>
       <c r="L2" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>3.22</v>
+        <v>-0.24</v>
       </c>
       <c r="S2" t="n">
-        <v>23.42</v>
+        <v>21.81</v>
       </c>
       <c r="T2" t="n">
-        <v>30.98</v>
+        <v>30.2</v>
       </c>
       <c r="U2" t="n">
-        <v>61.4</v>
+        <v>59.66</v>
       </c>
       <c r="V2" t="n">
-        <v>26.53</v>
+        <v>25.94</v>
       </c>
       <c r="W2" t="n">
-        <v>14</v>
+        <v>14.02</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>69.53019999999999</v>
+        <v>69.71080000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.6978</v>
+        <v>57.8152</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -753,13 +753,13 @@
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>82.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI2" t="n">
         <v>69.73</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.78</v>
+        <v>1.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.85</v>
+        <v>22.89</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -818,34 +818,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.87</v>
+        <v>165.78</v>
       </c>
       <c r="F3" t="n">
-        <v>78.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>90.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>64.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>79.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -869,42 +869,42 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>3.11</v>
+        <v>2.04</v>
       </c>
       <c r="S3" t="n">
-        <v>13.29</v>
+        <v>10.31</v>
       </c>
       <c r="T3" t="n">
-        <v>18.86</v>
+        <v>11.26</v>
       </c>
       <c r="U3" t="n">
-        <v>41.9</v>
+        <v>25.59</v>
       </c>
       <c r="V3" t="n">
-        <v>20.21</v>
+        <v>18.15</v>
       </c>
       <c r="W3" t="n">
-        <v>16.68</v>
+        <v>12.95</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.5279</v>
+        <v>162.4668</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.8259</v>
+        <v>150.0676</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -912,48 +912,48 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>90.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>64.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI3" t="n">
-        <v>46.73</v>
+        <v>163.44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>43.76</v>
+        <v>152.56</v>
       </c>
       <c r="AK3" t="n">
-        <v>50.73</v>
+        <v>166.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>50.73</v>
+        <v>166.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.72</v>
+        <v>2.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.45</v>
+        <v>10.47</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 43.76 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 152.56 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>166.14</v>
+        <v>126.33</v>
       </c>
       <c r="F4" t="n">
-        <v>77.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>74.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="I4" t="n">
-        <v>80.3</v>
+        <v>77.5</v>
       </c>
       <c r="J4" t="n">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>77.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>4.12</v>
+        <v>2.86</v>
       </c>
       <c r="S4" t="n">
-        <v>11.89</v>
+        <v>10.66</v>
       </c>
       <c r="T4" t="n">
-        <v>11.58</v>
+        <v>10.64</v>
       </c>
       <c r="U4" t="n">
-        <v>26.73</v>
+        <v>24.81</v>
       </c>
       <c r="V4" t="n">
-        <v>18.59</v>
+        <v>18.18</v>
       </c>
       <c r="W4" t="n">
-        <v>12.94</v>
+        <v>13.19</v>
       </c>
       <c r="X4" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>162.2424</v>
+        <v>123.0586</v>
       </c>
       <c r="AA4" t="n">
-        <v>149.9351</v>
+        <v>114.4821</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,48 +1074,48 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>80.3</v>
+        <v>77.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="AI4" t="n">
-        <v>163.44</v>
+        <v>123.73</v>
       </c>
       <c r="AJ4" t="n">
-        <v>152.56</v>
+        <v>116.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>166.6</v>
+        <v>126.34</v>
       </c>
       <c r="AL4" t="n">
-        <v>166.6</v>
+        <v>126.34</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.81</v>
+        <v>10.35</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 166.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 152.56 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 116.10 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1127,12 +1127,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>126.16</v>
+        <v>712.88</v>
       </c>
       <c r="F5" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>73.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>78.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="J5" t="n">
-        <v>66.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="K5" t="n">
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>77.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>4.36</v>
+        <v>3.04</v>
       </c>
       <c r="S5" t="n">
-        <v>11.69</v>
+        <v>12.65</v>
       </c>
       <c r="T5" t="n">
-        <v>10.47</v>
+        <v>11.45</v>
       </c>
       <c r="U5" t="n">
-        <v>25.06</v>
+        <v>24.29</v>
       </c>
       <c r="V5" t="n">
-        <v>18.44</v>
+        <v>19.34</v>
       </c>
       <c r="W5" t="n">
-        <v>13.17</v>
+        <v>14.18</v>
       </c>
       <c r="X5" t="n">
-        <v>-21.63</v>
+        <v>-23.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>122.881</v>
+        <v>694.5508</v>
       </c>
       <c r="AA5" t="n">
-        <v>114.3864</v>
+        <v>642.8613</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,48 +1236,48 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>78.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>66.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="AG5" t="n">
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI5" t="n">
-        <v>123.73</v>
+        <v>696.42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>116.1</v>
+        <v>647.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>126.34</v>
+        <v>712.88</v>
       </c>
       <c r="AL5" t="n">
-        <v>126.34</v>
+        <v>712.88</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.29</v>
+        <v>10.89</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 126.34 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 712.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 116.10 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 647.40 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1289,29 +1289,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>711.48</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>76.5</v>
+        <v>74.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="I6" t="n">
-        <v>82.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="J6" t="n">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>77.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4.44</v>
+        <v>2.91</v>
       </c>
       <c r="S6" t="n">
-        <v>13.72</v>
+        <v>10.08</v>
       </c>
       <c r="T6" t="n">
-        <v>11.07</v>
+        <v>10.4</v>
       </c>
       <c r="U6" t="n">
-        <v>25.08</v>
+        <v>23.25</v>
       </c>
       <c r="V6" t="n">
-        <v>19.27</v>
+        <v>16.35</v>
       </c>
       <c r="W6" t="n">
-        <v>14.16</v>
+        <v>12.87</v>
       </c>
       <c r="X6" t="n">
-        <v>-23.32</v>
+        <v>-20.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>693.522</v>
+        <v>74.825</v>
       </c>
       <c r="AA6" t="n">
-        <v>642.3258</v>
+        <v>70.1123</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>82.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AG6" t="n">
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="AI6" t="n">
-        <v>696.42</v>
+        <v>75.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>647.4</v>
+        <v>71.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>711.48</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="AL6" t="n">
-        <v>711.48</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.59</v>
+        <v>3.52</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.77</v>
+        <v>10.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 711.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 77.46 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 647.40 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 71.23 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,29 +1451,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>77.2</v>
+        <v>63.99</v>
       </c>
       <c r="F7" t="n">
-        <v>74.8</v>
+        <v>74</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>67.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>76.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>68.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>76.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1512,43 +1512,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>3.82</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>10.76</v>
+        <v>5.06</v>
       </c>
       <c r="T7" t="n">
-        <v>9.82</v>
+        <v>7.31</v>
       </c>
       <c r="U7" t="n">
-        <v>23.11</v>
+        <v>20.37</v>
       </c>
       <c r="V7" t="n">
-        <v>16.6</v>
+        <v>14.7</v>
       </c>
       <c r="W7" t="n">
-        <v>12.86</v>
+        <v>12.83</v>
       </c>
       <c r="X7" t="n">
-        <v>-20.6</v>
+        <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>74.7034</v>
+        <v>62.4906</v>
       </c>
       <c r="AA7" t="n">
-        <v>70.0514</v>
+        <v>59.0953</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,48 +1560,48 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>76.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AF7" t="n">
-        <v>68.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AI7" t="n">
-        <v>75.3</v>
+        <v>63.18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>71.23</v>
+        <v>59.5065</v>
       </c>
       <c r="AK7" t="n">
-        <v>77.39</v>
+        <v>65.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>77.39</v>
+        <v>65.06</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.2</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 77.39 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 71.23 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1613,29 +1613,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18.27</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>51.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>62.1</v>
       </c>
       <c r="J8" t="n">
-        <v>44.9</v>
+        <v>78.2</v>
       </c>
       <c r="K8" t="n">
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>75.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1669,52 +1669,52 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>5.78</v>
+        <v>2.82</v>
       </c>
       <c r="S8" t="n">
-        <v>26.88</v>
+        <v>5.42</v>
       </c>
       <c r="T8" t="n">
-        <v>25.62</v>
+        <v>4.82</v>
       </c>
       <c r="U8" t="n">
-        <v>40.82</v>
+        <v>6.53</v>
       </c>
       <c r="V8" t="n">
-        <v>19.36</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>22.13</v>
+        <v>9.58</v>
       </c>
       <c r="X8" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.856</v>
+        <v>64.11620000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.0772</v>
+        <v>63.3562</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1722,48 +1722,48 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>100</v>
+        <v>62.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>49.9</v>
+        <v>78.2</v>
       </c>
       <c r="AG8" t="n">
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI8" t="n">
-        <v>17.63</v>
+        <v>63.44</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.276</v>
+        <v>62.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>19.164</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AL8" t="n">
-        <v>19.164</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.18</v>
+        <v>4.33</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 72.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 15.28 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65.67</v>
+        <v>18.13</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>71.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>64.40000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="I9" t="n">
-        <v>60.4</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>78.2</v>
+        <v>44.9</v>
       </c>
       <c r="K9" t="n">
         <v>82.8</v>
       </c>
       <c r="L9" t="n">
-        <v>73.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,52 +1831,52 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2.11</v>
+        <v>0.88</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="T9" t="n">
-        <v>4.01</v>
+        <v>24.5</v>
       </c>
       <c r="U9" t="n">
-        <v>5.7</v>
+        <v>39.46</v>
       </c>
       <c r="V9" t="n">
-        <v>8.24</v>
+        <v>18.28</v>
       </c>
       <c r="W9" t="n">
-        <v>9.56</v>
+        <v>22.15</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.85</v>
+        <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="Z9" t="n">
-        <v>64.05200000000001</v>
+        <v>17.8944</v>
       </c>
       <c r="AA9" t="n">
-        <v>63.3348</v>
+        <v>15.1002</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1884,48 +1884,48 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>60.4</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.2</v>
+        <v>49.9</v>
       </c>
       <c r="AG9" t="n">
         <v>82.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.44</v>
+        <v>17.63</v>
       </c>
       <c r="AJ9" t="n">
-        <v>62.06</v>
+        <v>15.276</v>
       </c>
       <c r="AK9" t="n">
-        <v>66.20999999999999</v>
+        <v>19.164</v>
       </c>
       <c r="AL9" t="n">
-        <v>66.20999999999999</v>
+        <v>19.164</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.53</v>
+        <v>1.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.69</v>
+        <v>20.06</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.3%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 66.21 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 15.28 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,29 +1937,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>611.625</v>
+        <v>46.77</v>
       </c>
       <c r="F10" t="n">
-        <v>68.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,38 +1967,38 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>56.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>81.2</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>82.8</v>
+        <v>77.2</v>
       </c>
       <c r="L10" t="n">
-        <v>58.9</v>
+        <v>73.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2007,87 +2007,87 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3.49</v>
+        <v>-2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>42.14</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>58.86</v>
+        <v>15.51</v>
       </c>
       <c r="U10" t="n">
-        <v>114.96</v>
+        <v>38.87</v>
       </c>
       <c r="V10" t="n">
-        <v>60.27</v>
+        <v>18.44</v>
       </c>
       <c r="W10" t="n">
-        <v>36.14</v>
+        <v>16.74</v>
       </c>
       <c r="X10" t="n">
-        <v>-35.74</v>
+        <v>-19.17</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>590.2151</v>
+        <v>47.5645</v>
       </c>
       <c r="AA10" t="n">
-        <v>432.9173</v>
+        <v>41.8762</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE10" t="n">
-        <v>100</v>
+        <v>81.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>82.8</v>
+        <v>77.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="AI10" t="n">
-        <v>581.45</v>
+        <v>46.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>453</v>
+        <v>43.76</v>
       </c>
       <c r="AK10" t="n">
-        <v>668.91</v>
+        <v>50.73</v>
       </c>
       <c r="AL10" t="n">
-        <v>668.91</v>
+        <v>50.73</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.63</v>
+        <v>-1.67</v>
       </c>
       <c r="AN10" t="n">
-        <v>41.28</v>
+        <v>11.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>SMH: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 71.5, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.7%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 453.00 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 43.76 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,38 +2114,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29.19</v>
+        <v>586.66</v>
       </c>
       <c r="F11" t="n">
-        <v>54.9</v>
+        <v>64.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>23.8</v>
+        <v>54.3</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>14.8</v>
+        <v>22.9</v>
       </c>
       <c r="K11" t="n">
-        <v>55</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>37.3</v>
+        <v>55.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 10.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>12.49</v>
+        <v>2.76</v>
       </c>
       <c r="S11" t="n">
-        <v>38.8</v>
+        <v>34.28</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.65</v>
+        <v>54.8</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.06</v>
+        <v>104.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>55.85</v>
       </c>
       <c r="W11" t="n">
-        <v>34.42</v>
+        <v>36.23</v>
       </c>
       <c r="X11" t="n">
-        <v>-48.6</v>
+        <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.03</v>
+        <v>1.54</v>
       </c>
       <c r="Z11" t="n">
-        <v>26.3094</v>
+        <v>591.9448</v>
       </c>
       <c r="AA11" t="n">
-        <v>26.644</v>
+        <v>434.2441</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2205,51 +2205,51 @@
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE11" t="n">
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.8</v>
+        <v>27.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>55</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="AI11" t="n">
-        <v>24.785</v>
+        <v>581.45</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22.225</v>
+        <v>454.8</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>668.91</v>
       </c>
       <c r="AL11" t="n">
-        <v>30.11</v>
+        <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>10.95</v>
+        <v>-0.89</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.56</v>
+        <v>35.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 54.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.9%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 64.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.9%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 22.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 454.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2261,157 +2261,157 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Oro</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>345.19</v>
+        <v>30.085</v>
       </c>
       <c r="F12" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>67</v>
+        <v>23.6</v>
       </c>
       <c r="I12" t="n">
-        <v>37.2</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>60.1</v>
+        <v>14.7</v>
       </c>
       <c r="K12" t="n">
-        <v>68.09999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="L12" t="n">
-        <v>55.7</v>
+        <v>28.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 4.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 13.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>15.62</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.88</v>
+        <v>42.38</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.35</v>
+        <v>2.78</v>
       </c>
       <c r="U12" t="n">
-        <v>27.29</v>
+        <v>-0.78</v>
       </c>
       <c r="V12" t="n">
-        <v>26.79</v>
+        <v>0.71</v>
       </c>
       <c r="W12" t="n">
-        <v>18.33</v>
+        <v>34.48</v>
       </c>
       <c r="X12" t="n">
-        <v>-22.39</v>
+        <v>-48.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.46</v>
+        <v>0.02</v>
       </c>
       <c r="Z12" t="n">
-        <v>362.3772</v>
+        <v>26.4152</v>
       </c>
       <c r="AA12" t="n">
-        <v>368.707</v>
+        <v>26.6407</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AE12" t="n">
-        <v>37.2</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>60.1</v>
+        <v>19.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>68.09999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AI12" t="n">
-        <v>338.68</v>
+        <v>24.785</v>
       </c>
       <c r="AJ12" t="n">
-        <v>338.68</v>
+        <v>22.225</v>
       </c>
       <c r="AK12" t="n">
-        <v>361.71</v>
+        <v>30.085</v>
       </c>
       <c r="AL12" t="n">
-        <v>396.71</v>
+        <v>30.11</v>
       </c>
       <c r="AM12" t="n">
-        <v>-4.74</v>
+        <v>13.89</v>
       </c>
       <c r="AN12" t="n">
-        <v>-6.38</v>
+        <v>12.93</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 53.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.7%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 53.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.9%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 22.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2423,157 +2423,157 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Oro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.657999999999999</v>
+        <v>339.05</v>
       </c>
       <c r="F13" t="n">
-        <v>52.7</v>
+        <v>51.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>30.1</v>
+        <v>66.2</v>
       </c>
       <c r="I13" t="n">
-        <v>76.09999999999999</v>
+        <v>30.7</v>
       </c>
       <c r="J13" t="n">
-        <v>31.5</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>67.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>45.4</v>
+        <v>53.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 8.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-4.21</v>
+        <v>-3.27</v>
       </c>
       <c r="S13" t="n">
-        <v>4.48</v>
+        <v>-13.46</v>
       </c>
       <c r="T13" t="n">
-        <v>13.36</v>
+        <v>-10.97</v>
       </c>
       <c r="U13" t="n">
-        <v>47.11</v>
+        <v>24.52</v>
       </c>
       <c r="V13" t="n">
-        <v>1.92</v>
+        <v>26.08</v>
       </c>
       <c r="W13" t="n">
-        <v>24.05</v>
+        <v>18.38</v>
       </c>
       <c r="X13" t="n">
-        <v>-43.36</v>
+        <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.08</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.5317</v>
+        <v>361.7042</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.1097</v>
+        <v>368.8763</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>76.09999999999999</v>
+        <v>30.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>36.5</v>
+        <v>60</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI13" t="n">
-        <v>9.483000000000001</v>
+        <v>338.68</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.4422</v>
+        <v>338.68</v>
       </c>
       <c r="AK13" t="n">
-        <v>10.872</v>
+        <v>361.71</v>
       </c>
       <c r="AL13" t="n">
-        <v>11.61</v>
+        <v>392.36</v>
       </c>
       <c r="AM13" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.26</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.02</v>
+        <v>-8.09</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base High Risk, score 52.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.3%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 51.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.3%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 392.36 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 9.44 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2585,29 +2585,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>63.99</v>
+        <v>9.538</v>
       </c>
       <c r="F14" t="n">
-        <v>46.6</v>
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,23 +2615,23 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>39.2</v>
+        <v>29</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>67.3</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>31.4</v>
       </c>
       <c r="K14" t="n">
-        <v>76.8</v>
+        <v>65.7</v>
       </c>
       <c r="L14" t="n">
-        <v>40.2</v>
+        <v>42.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Insufficient History</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2651,19 +2651,39 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+          <t>prezzo 9.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="U14" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="W14" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-43.36</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>10.5205</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>9.1205</v>
+      </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
@@ -2671,47 +2691,51 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="AE14" t="n">
-        <v>50</v>
+        <v>67.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>30</v>
+        <v>36.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>76.8</v>
+        <v>65.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>756</v>
       </c>
       <c r="AI14" t="n">
-        <v>63.99</v>
+        <v>9.483000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>63.99</v>
+        <v>9.483000000000001</v>
       </c>
       <c r="AK14" t="n">
-        <v>63.99</v>
+        <v>10.872</v>
       </c>
       <c r="AL14" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
+        <v>11.61</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-9.34</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>4.58</v>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base High Risk, score 46.6, trend Insufficient History. Entry zone: Monitor / partial entry only. Distanza da MA50: n/d.</t>
+          <t>INRG.MI: scenario base High Risk, score 50.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -9.3%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 63.99 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 9.48 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.05</v>
+        <v>71.47</v>
       </c>
       <c r="F2" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -683,7 +683,7 @@
         <v>82.8</v>
       </c>
       <c r="L2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-0.24</v>
+        <v>-1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>21.81</v>
+        <v>22.65</v>
       </c>
       <c r="T2" t="n">
-        <v>30.2</v>
+        <v>30.8</v>
       </c>
       <c r="U2" t="n">
-        <v>59.66</v>
+        <v>59.82</v>
       </c>
       <c r="V2" t="n">
-        <v>25.94</v>
+        <v>26.63</v>
       </c>
       <c r="W2" t="n">
-        <v>14.02</v>
+        <v>14.01</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>69.71080000000001</v>
+        <v>69.8758</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.8152</v>
+        <v>57.9339</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.89</v>
+        <v>23.36</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>165.78</v>
+        <v>165.66</v>
       </c>
       <c r="F3" t="n">
-        <v>76.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>73.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>77.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="J3" t="n">
         <v>67.59999999999999</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>77</v>
+        <v>76.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2.04</v>
+        <v>0.64</v>
       </c>
       <c r="S3" t="n">
-        <v>10.31</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>11.26</v>
+        <v>10.99</v>
       </c>
       <c r="U3" t="n">
-        <v>25.59</v>
+        <v>26.19</v>
       </c>
       <c r="V3" t="n">
         <v>18.15</v>
@@ -897,10 +897,10 @@
         <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>162.4668</v>
+        <v>162.6604</v>
       </c>
       <c r="AA3" t="n">
-        <v>150.0676</v>
+        <v>150.1983</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>77.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="AF3" t="n">
         <v>67.59999999999999</v>
@@ -936,14 +936,14 @@
         <v>166.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.47</v>
+        <v>10.29</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.8%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>126.33</v>
+        <v>126.09</v>
       </c>
       <c r="F4" t="n">
-        <v>76.2</v>
+        <v>75.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="I4" t="n">
-        <v>77.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>66.90000000000001</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>76.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2.86</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>10.66</v>
+        <v>9.98</v>
       </c>
       <c r="T4" t="n">
-        <v>10.64</v>
+        <v>10.3</v>
       </c>
       <c r="U4" t="n">
-        <v>24.81</v>
+        <v>23.67</v>
       </c>
       <c r="V4" t="n">
-        <v>18.18</v>
+        <v>18.11</v>
       </c>
       <c r="W4" t="n">
         <v>13.19</v>
@@ -1056,13 +1056,13 @@
         <v>-21.63</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>123.0586</v>
+        <v>123.2162</v>
       </c>
       <c r="AA4" t="n">
-        <v>114.4821</v>
+        <v>114.5762</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>77.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AF4" t="n">
         <v>66.90000000000001</v>
@@ -1098,14 +1098,14 @@
         <v>126.34</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.35</v>
+        <v>10.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>712.88</v>
+        <v>710</v>
       </c>
       <c r="F5" t="n">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>80.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>64.3</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>3.04</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>12.65</v>
+        <v>11.46</v>
       </c>
       <c r="T5" t="n">
-        <v>11.45</v>
+        <v>10.71</v>
       </c>
       <c r="U5" t="n">
-        <v>24.29</v>
+        <v>24.42</v>
       </c>
       <c r="V5" t="n">
-        <v>19.34</v>
+        <v>19.13</v>
       </c>
       <c r="W5" t="n">
         <v>14.18</v>
@@ -1218,13 +1218,13 @@
         <v>-23.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>694.5508</v>
+        <v>695.4308</v>
       </c>
       <c r="AA5" t="n">
-        <v>642.8613</v>
+        <v>643.3801</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>80.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>64.3</v>
@@ -1251,7 +1251,7 @@
         <v>696.42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>647.4</v>
+        <v>648.46</v>
       </c>
       <c r="AK5" t="n">
         <v>712.88</v>
@@ -1260,14 +1260,14 @@
         <v>712.88</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.64</v>
+        <v>2.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.89</v>
+        <v>10.35</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 647.40 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 648.46 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>77.45999999999999</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>74.5</v>
+        <v>74.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>66.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>76.2</v>
+        <v>75.3</v>
       </c>
       <c r="J6" t="n">
         <v>68.09999999999999</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.91</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>10.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>10.4</v>
+        <v>10.24</v>
       </c>
       <c r="U6" t="n">
-        <v>23.25</v>
+        <v>21.81</v>
       </c>
       <c r="V6" t="n">
-        <v>16.35</v>
+        <v>16.11</v>
       </c>
       <c r="W6" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="X6" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.825</v>
+        <v>74.93340000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>70.1123</v>
+        <v>70.17140000000001</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>76.2</v>
+        <v>75.3</v>
       </c>
       <c r="AF6" t="n">
         <v>68.09999999999999</v>
@@ -1422,14 +1422,14 @@
         <v>77.45999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.48</v>
+        <v>9.99</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.99</v>
+        <v>63.97</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>74.7</v>
+        <v>74.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>5.06</v>
+        <v>5.35</v>
       </c>
       <c r="T7" t="n">
-        <v>7.31</v>
+        <v>7.14</v>
       </c>
       <c r="U7" t="n">
-        <v>20.37</v>
+        <v>20.35</v>
       </c>
       <c r="V7" t="n">
-        <v>14.7</v>
+        <v>14.72</v>
       </c>
       <c r="W7" t="n">
         <v>12.83</v>
@@ -1545,10 +1545,10 @@
         <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>62.4906</v>
+        <v>62.5641</v>
       </c>
       <c r="AA7" t="n">
-        <v>59.0953</v>
+        <v>59.1455</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1584,14 +1584,14 @@
         <v>65.06</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.279999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>66.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="F8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>62.1</v>
+        <v>60.8</v>
       </c>
       <c r="J8" t="n">
         <v>78.2</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>74.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="S8" t="n">
-        <v>5.42</v>
+        <v>4.78</v>
       </c>
       <c r="T8" t="n">
-        <v>4.82</v>
+        <v>4.52</v>
       </c>
       <c r="U8" t="n">
-        <v>6.53</v>
+        <v>5.49</v>
       </c>
       <c r="V8" t="n">
-        <v>8.640000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>9.58</v>
@@ -1704,13 +1704,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="Z8" t="n">
-        <v>64.11620000000001</v>
+        <v>64.1754</v>
       </c>
       <c r="AA8" t="n">
-        <v>63.3562</v>
+        <v>63.3756</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>62.1</v>
+        <v>60.8</v>
       </c>
       <c r="AF8" t="n">
         <v>78.2</v>
@@ -1746,14 +1746,14 @@
         <v>66.20999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.09</v>
+        <v>2.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.33</v>
+        <v>3.67</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.1%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.13</v>
+        <v>18.004</v>
       </c>
       <c r="F9" t="n">
         <v>71.8</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1845,34 +1845,34 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.88</v>
+        <v>-2.89</v>
       </c>
       <c r="S9" t="n">
-        <v>23</v>
+        <v>21.78</v>
       </c>
       <c r="T9" t="n">
-        <v>24.5</v>
+        <v>22.68</v>
       </c>
       <c r="U9" t="n">
-        <v>39.46</v>
+        <v>37.31</v>
       </c>
       <c r="V9" t="n">
-        <v>18.28</v>
+        <v>18.07</v>
       </c>
       <c r="W9" t="n">
-        <v>22.15</v>
+        <v>22.16</v>
       </c>
       <c r="X9" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.8944</v>
+        <v>17.9212</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.1002</v>
+        <v>15.1224</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>17.63</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.276</v>
+        <v>15.43</v>
       </c>
       <c r="AK9" t="n">
         <v>19.164</v>
@@ -1908,14 +1908,14 @@
         <v>19.164</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.32</v>
+        <v>0.46</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.06</v>
+        <v>19.06</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.3%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.5%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 15.28 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 15.43 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.77</v>
+        <v>46.89</v>
       </c>
       <c r="F10" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="I10" t="n">
         <v>81.2</v>
@@ -1976,10 +1976,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,19 +2007,19 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>-2.28</v>
+        <v>-4.56</v>
       </c>
       <c r="S10" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="T10" t="n">
-        <v>15.51</v>
+        <v>15.59</v>
       </c>
       <c r="U10" t="n">
-        <v>38.87</v>
+        <v>38.46</v>
       </c>
       <c r="V10" t="n">
-        <v>18.44</v>
+        <v>18.67</v>
       </c>
       <c r="W10" t="n">
         <v>16.74</v>
@@ -2028,13 +2028,13 @@
         <v>-19.17</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>47.5645</v>
+        <v>47.586</v>
       </c>
       <c r="AA10" t="n">
-        <v>41.8762</v>
+        <v>41.9261</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AH10" t="n">
         <v>756</v>
@@ -2070,14 +2070,14 @@
         <v>50.73</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.67</v>
+        <v>-1.46</v>
       </c>
       <c r="AN10" t="n">
-        <v>11.69</v>
+        <v>11.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 71.5, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.7%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 71.6, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2118,18 +2118,18 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>586.66</v>
+        <v>600.5599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>54.3</v>
+        <v>55.2</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -2138,14 +2138,14 @@
         <v>22.9</v>
       </c>
       <c r="K11" t="n">
-        <v>78.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="L11" t="n">
-        <v>55.9</v>
+        <v>58.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2169,34 +2169,34 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>2.76</v>
+        <v>-1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>34.28</v>
+        <v>35.46</v>
       </c>
       <c r="T11" t="n">
-        <v>54.8</v>
+        <v>54.3</v>
       </c>
       <c r="U11" t="n">
-        <v>104.68</v>
+        <v>109.55</v>
       </c>
       <c r="V11" t="n">
-        <v>55.85</v>
+        <v>57.51</v>
       </c>
       <c r="W11" t="n">
-        <v>36.23</v>
+        <v>36.26</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>591.9448</v>
+        <v>593.8008</v>
       </c>
       <c r="AA11" t="n">
-        <v>434.2441</v>
+        <v>435.6411</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AE11" t="n">
         <v>100</v>
@@ -2214,7 +2214,7 @@
         <v>27.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>78.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AH11" t="n">
         <v>752</v>
@@ -2223,7 +2223,7 @@
         <v>581.45</v>
       </c>
       <c r="AJ11" t="n">
-        <v>454.8</v>
+        <v>463.96</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>35.1</v>
+        <v>37.86</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 64.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.9%.</t>
+          <t>SMH: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 454.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 463.96 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30.085</v>
+        <v>30.08</v>
       </c>
       <c r="F12" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -2300,10 +2300,10 @@
         <v>14.7</v>
       </c>
       <c r="K12" t="n">
-        <v>43.2</v>
+        <v>45</v>
       </c>
       <c r="L12" t="n">
-        <v>28.2</v>
+        <v>29.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,23 +2327,23 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 13.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 13.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>15.62</v>
+        <v>13.38</v>
       </c>
       <c r="S12" t="n">
-        <v>42.38</v>
+        <v>36.85</v>
       </c>
       <c r="T12" t="n">
-        <v>2.78</v>
+        <v>4.9</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.78</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="W12" t="n">
         <v>34.48</v>
@@ -2352,13 +2352,13 @@
         <v>-48.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.4152</v>
+        <v>26.5169</v>
       </c>
       <c r="AA12" t="n">
-        <v>26.6407</v>
+        <v>26.6392</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>19.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>43.2</v>
+        <v>45</v>
       </c>
       <c r="AH12" t="n">
         <v>757</v>
@@ -2394,14 +2394,14 @@
         <v>30.11</v>
       </c>
       <c r="AM12" t="n">
-        <v>13.89</v>
+        <v>13.44</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 53.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.9%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 53.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.4%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>339.05</v>
+        <v>343.28</v>
       </c>
       <c r="F13" t="n">
-        <v>51.4</v>
+        <v>52.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>30.7</v>
+        <v>33.3</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>65.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>53.2</v>
+        <v>54.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 6.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-3.27</v>
+        <v>-4.92</v>
       </c>
       <c r="S13" t="n">
-        <v>-13.46</v>
+        <v>-12.26</v>
       </c>
       <c r="T13" t="n">
-        <v>-10.97</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>24.52</v>
+        <v>25.39</v>
       </c>
       <c r="V13" t="n">
-        <v>26.08</v>
+        <v>26.85</v>
       </c>
       <c r="W13" t="n">
-        <v>18.38</v>
+        <v>18.39</v>
       </c>
       <c r="X13" t="n">
         <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z13" t="n">
-        <v>361.7042</v>
+        <v>361.0416</v>
       </c>
       <c r="AA13" t="n">
-        <v>368.8763</v>
+        <v>369.0488</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>30.7</v>
+        <v>33.3</v>
       </c>
       <c r="AF13" t="n">
         <v>60</v>
       </c>
       <c r="AG13" t="n">
-        <v>65.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AH13" t="n">
         <v>756</v>
@@ -2553,22 +2553,22 @@
         <v>361.71</v>
       </c>
       <c r="AL13" t="n">
-        <v>392.36</v>
+        <v>388.92</v>
       </c>
       <c r="AM13" t="n">
-        <v>-6.26</v>
+        <v>-4.92</v>
       </c>
       <c r="AN13" t="n">
-        <v>-8.09</v>
+        <v>-6.98</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 51.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.3%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 52.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 392.36 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 388.92 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.538</v>
+        <v>9.617000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="I14" t="n">
-        <v>67.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>31.4</v>
       </c>
       <c r="K14" t="n">
-        <v>65.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>42.5</v>
+        <v>43.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,23 +2651,23 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 9.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-8.289999999999999</v>
+        <v>-7.39</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.28</v>
+        <v>0.17</v>
       </c>
       <c r="T14" t="n">
-        <v>10.89</v>
+        <v>10.41</v>
       </c>
       <c r="U14" t="n">
-        <v>44.48</v>
+        <v>45.54</v>
       </c>
       <c r="V14" t="n">
-        <v>0.58</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
         <v>24.07</v>
@@ -2676,13 +2676,13 @@
         <v>-43.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.5205</v>
+        <v>10.5045</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.1205</v>
+        <v>9.131600000000001</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,13 +2694,13 @@
         <v>65</v>
       </c>
       <c r="AE14" t="n">
-        <v>67.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AF14" t="n">
         <v>36.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>65.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AH14" t="n">
         <v>756</v>
@@ -2718,14 +2718,14 @@
         <v>11.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>-9.34</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.58</v>
+        <v>5.32</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base High Risk, score 50.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -9.3%.</t>
+          <t>INRG.MI: scenario base High Risk, score 50.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.4%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.47</v>
+        <v>70.27</v>
       </c>
       <c r="F2" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -683,7 +683,7 @@
         <v>82.8</v>
       </c>
       <c r="L2" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,34 +711,34 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-1.08</v>
+        <v>-1.99</v>
       </c>
       <c r="S2" t="n">
-        <v>22.65</v>
+        <v>19.51</v>
       </c>
       <c r="T2" t="n">
-        <v>30.8</v>
+        <v>27.69</v>
       </c>
       <c r="U2" t="n">
-        <v>59.82</v>
+        <v>58.75</v>
       </c>
       <c r="V2" t="n">
-        <v>26.63</v>
+        <v>26.02</v>
       </c>
       <c r="W2" t="n">
-        <v>14.01</v>
+        <v>14.04</v>
       </c>
       <c r="X2" t="n">
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>69.8758</v>
+        <v>69.995</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.9339</v>
+        <v>58.0467</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>69.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>59.1</v>
+        <v>59.27</v>
       </c>
       <c r="AK2" t="n">
         <v>73.47</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.28</v>
+        <v>0.39</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.36</v>
+        <v>21.06</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 83.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 59.10 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.27 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>165.66</v>
+        <v>165.8</v>
       </c>
       <c r="F3" t="n">
         <v>76.40000000000001</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>73.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>77</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>67.59999999999999</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>9.869999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>10.99</v>
+        <v>11.73</v>
       </c>
       <c r="U3" t="n">
-        <v>26.19</v>
+        <v>26.14</v>
       </c>
       <c r="V3" t="n">
-        <v>18.15</v>
+        <v>18.23</v>
       </c>
       <c r="W3" t="n">
         <v>12.95</v>
@@ -894,13 +894,13 @@
         <v>-21.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>162.6604</v>
+        <v>162.8152</v>
       </c>
       <c r="AA3" t="n">
-        <v>150.1983</v>
+        <v>150.3306</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>77</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AF3" t="n">
         <v>67.59999999999999</v>
@@ -927,7 +927,7 @@
         <v>163.44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>152.56</v>
+        <v>152.88</v>
       </c>
       <c r="AK3" t="n">
         <v>166.6</v>
@@ -936,7 +936,7 @@
         <v>166.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AN3" t="n">
         <v>10.29</v>
@@ -953,7 +953,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 152.56 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 152.88 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>126.09</v>
+        <v>126.29</v>
       </c>
       <c r="F4" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="I4" t="n">
         <v>76.09999999999999</v>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="S4" t="n">
-        <v>9.98</v>
+        <v>9.51</v>
       </c>
       <c r="T4" t="n">
-        <v>10.3</v>
+        <v>11.09</v>
       </c>
       <c r="U4" t="n">
-        <v>23.67</v>
+        <v>24.64</v>
       </c>
       <c r="V4" t="n">
-        <v>18.11</v>
+        <v>18.23</v>
       </c>
       <c r="W4" t="n">
         <v>13.19</v>
@@ -1056,13 +1056,13 @@
         <v>-21.63</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>123.2162</v>
+        <v>123.3504</v>
       </c>
       <c r="AA4" t="n">
-        <v>114.5762</v>
+        <v>114.6722</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>123.73</v>
       </c>
       <c r="AJ4" t="n">
-        <v>116.1</v>
+        <v>116.27</v>
       </c>
       <c r="AK4" t="n">
         <v>126.34</v>
@@ -1098,14 +1098,14 @@
         <v>126.34</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.05</v>
+        <v>10.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 116.10 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 116.27 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>710</v>
+        <v>711.62</v>
       </c>
       <c r="F5" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="J5" t="n">
         <v>64.3</v>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="S5" t="n">
-        <v>11.46</v>
+        <v>10.81</v>
       </c>
       <c r="T5" t="n">
-        <v>10.71</v>
+        <v>12.05</v>
       </c>
       <c r="U5" t="n">
-        <v>24.42</v>
+        <v>24.57</v>
       </c>
       <c r="V5" t="n">
-        <v>19.13</v>
+        <v>19.22</v>
       </c>
       <c r="W5" t="n">
         <v>14.18</v>
@@ -1218,13 +1218,13 @@
         <v>-23.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>695.4308</v>
+        <v>696.234</v>
       </c>
       <c r="AA5" t="n">
-        <v>643.3801</v>
+        <v>643.9117</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="AF5" t="n">
         <v>64.3</v>
@@ -1251,7 +1251,7 @@
         <v>696.42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>648.46</v>
+        <v>652.96</v>
       </c>
       <c r="AK5" t="n">
         <v>712.88</v>
@@ -1260,14 +1260,14 @@
         <v>712.88</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.35</v>
+        <v>10.52</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 648.46 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 652.96 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>77.18000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="F6" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="I6" t="n">
-        <v>75.3</v>
+        <v>75.8</v>
       </c>
       <c r="J6" t="n">
         <v>68.09999999999999</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="S6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>10.24</v>
+        <v>10.99</v>
       </c>
       <c r="U6" t="n">
-        <v>21.81</v>
+        <v>23.3</v>
       </c>
       <c r="V6" t="n">
-        <v>16.11</v>
+        <v>16.34</v>
       </c>
       <c r="W6" t="n">
         <v>12.88</v>
@@ -1380,13 +1380,13 @@
         <v>-20.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.93340000000001</v>
+        <v>75.0324</v>
       </c>
       <c r="AA6" t="n">
-        <v>70.17140000000001</v>
+        <v>70.2328</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>75.3</v>
+        <v>75.8</v>
       </c>
       <c r="AF6" t="n">
         <v>68.09999999999999</v>
@@ -1416,25 +1416,25 @@
         <v>71.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>77.45999999999999</v>
+        <v>77.53</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.45999999999999</v>
+        <v>77.53</v>
       </c>
       <c r="AM6" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.99</v>
+        <v>10.39</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 77.46 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 77.53 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.97</v>
+        <v>64.11</v>
       </c>
       <c r="F7" t="n">
-        <v>74.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>66.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="J7" t="n">
         <v>71.5</v>
@@ -1493,7 +1493,7 @@
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>74.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,19 +1521,19 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>5.35</v>
+        <v>5.63</v>
       </c>
       <c r="T7" t="n">
-        <v>7.14</v>
+        <v>6.76</v>
       </c>
       <c r="U7" t="n">
-        <v>20.35</v>
+        <v>21.13</v>
       </c>
       <c r="V7" t="n">
-        <v>14.72</v>
+        <v>15.05</v>
       </c>
       <c r="W7" t="n">
         <v>12.83</v>
@@ -1542,13 +1542,13 @@
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>62.5641</v>
+        <v>62.6136</v>
       </c>
       <c r="AA7" t="n">
-        <v>59.1455</v>
+        <v>59.1981</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>66.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="AF7" t="n">
         <v>71.5</v>
@@ -1584,14 +1584,14 @@
         <v>65.06</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.16</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65.7</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>72.2</v>
+        <v>71.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>60.8</v>
+        <v>58.4</v>
       </c>
       <c r="J8" t="n">
         <v>78.2</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,38 +1679,38 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>4.78</v>
+        <v>3.41</v>
       </c>
       <c r="T8" t="n">
-        <v>4.52</v>
+        <v>3.55</v>
       </c>
       <c r="U8" t="n">
-        <v>5.49</v>
+        <v>5.82</v>
       </c>
       <c r="V8" t="n">
-        <v>8.539999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="W8" t="n">
-        <v>9.58</v>
+        <v>9.59</v>
       </c>
       <c r="X8" t="n">
         <v>-12.85</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="Z8" t="n">
-        <v>64.1754</v>
+        <v>64.22880000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>63.3756</v>
+        <v>63.3911</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>60.8</v>
+        <v>58.4</v>
       </c>
       <c r="AF8" t="n">
         <v>78.2</v>
@@ -1746,14 +1746,14 @@
         <v>66.20999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.67</v>
+        <v>2.95</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1775,29 +1775,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.004</v>
+        <v>46.8</v>
       </c>
       <c r="F9" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,23 +1805,23 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>50.6</v>
+        <v>68</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>79.7</v>
       </c>
       <c r="J9" t="n">
-        <v>44.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>82.8</v>
+        <v>77.3</v>
       </c>
       <c r="L9" t="n">
-        <v>75.5</v>
+        <v>73</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1845,34 +1845,34 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-2.89</v>
+        <v>-3.65</v>
       </c>
       <c r="S9" t="n">
-        <v>21.78</v>
+        <v>7.67</v>
       </c>
       <c r="T9" t="n">
-        <v>22.68</v>
+        <v>15.43</v>
       </c>
       <c r="U9" t="n">
-        <v>37.31</v>
+        <v>38.65</v>
       </c>
       <c r="V9" t="n">
-        <v>18.07</v>
+        <v>18.74</v>
       </c>
       <c r="W9" t="n">
-        <v>22.16</v>
+        <v>16.74</v>
       </c>
       <c r="X9" t="n">
-        <v>-29.37</v>
+        <v>-19.17</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.82</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.9212</v>
+        <v>47.5861</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.1224</v>
+        <v>41.9759</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1881,51 +1881,51 @@
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>79.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>49.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>82.8</v>
+        <v>77.3</v>
       </c>
       <c r="AH9" t="n">
         <v>756</v>
       </c>
       <c r="AI9" t="n">
-        <v>17.63</v>
+        <v>46.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.43</v>
+        <v>43.825</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.164</v>
+        <v>50.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>19.164</v>
+        <v>50.73</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.46</v>
+        <v>-1.65</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.06</v>
+        <v>11.49</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.5%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 71.2, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.6%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 15.43 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 43.83 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -1937,49 +1937,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.89</v>
+        <v>17.728</v>
       </c>
       <c r="F10" t="n">
-        <v>71.59999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>81.2</v>
+        <v>96.7</v>
       </c>
       <c r="J10" t="n">
-        <v>64.59999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="K10" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="L10" t="n">
-        <v>73.5</v>
+        <v>71.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>-4.56</v>
+        <v>-2.99</v>
       </c>
       <c r="S10" t="n">
-        <v>8.74</v>
+        <v>17.7</v>
       </c>
       <c r="T10" t="n">
-        <v>15.59</v>
+        <v>21.36</v>
       </c>
       <c r="U10" t="n">
-        <v>38.46</v>
+        <v>36.33</v>
       </c>
       <c r="V10" t="n">
-        <v>18.67</v>
+        <v>17.47</v>
       </c>
       <c r="W10" t="n">
-        <v>16.74</v>
+        <v>22.18</v>
       </c>
       <c r="X10" t="n">
-        <v>-19.17</v>
+        <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="Z10" t="n">
-        <v>47.586</v>
+        <v>17.9344</v>
       </c>
       <c r="AA10" t="n">
-        <v>41.9261</v>
+        <v>15.1436</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,48 +2046,48 @@
         <v>65</v>
       </c>
       <c r="AE10" t="n">
-        <v>81.2</v>
+        <v>96.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>64.59999999999999</v>
+        <v>49.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="n">
         <v>756</v>
       </c>
       <c r="AI10" t="n">
-        <v>46.73</v>
+        <v>17.63</v>
       </c>
       <c r="AJ10" t="n">
-        <v>43.76</v>
+        <v>15.558</v>
       </c>
       <c r="AK10" t="n">
-        <v>50.73</v>
+        <v>19.164</v>
       </c>
       <c r="AL10" t="n">
-        <v>50.73</v>
+        <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.46</v>
+        <v>-1.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>11.84</v>
+        <v>17.07</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 71.6, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.5%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.1, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.1%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 43.76 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 15.56 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2118,18 +2118,18 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>600.5599999999999</v>
+        <v>590.65</v>
       </c>
       <c r="F11" t="n">
-        <v>68.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>55.2</v>
+        <v>54.3</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -2138,14 +2138,14 @@
         <v>22.9</v>
       </c>
       <c r="K11" t="n">
-        <v>82.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>58.8</v>
+        <v>56</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2169,19 +2169,19 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-1.46</v>
+        <v>-4.73</v>
       </c>
       <c r="S11" t="n">
-        <v>35.46</v>
+        <v>30.67</v>
       </c>
       <c r="T11" t="n">
-        <v>54.3</v>
+        <v>51.19</v>
       </c>
       <c r="U11" t="n">
-        <v>109.55</v>
+        <v>107.66</v>
       </c>
       <c r="V11" t="n">
-        <v>57.51</v>
+        <v>55.67</v>
       </c>
       <c r="W11" t="n">
         <v>36.26</v>
@@ -2190,13 +2190,13 @@
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="Z11" t="n">
-        <v>593.8008</v>
+        <v>595.4124</v>
       </c>
       <c r="AA11" t="n">
-        <v>435.6411</v>
+        <v>436.9928</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE11" t="n">
         <v>100</v>
@@ -2214,7 +2214,7 @@
         <v>27.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>82.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AH11" t="n">
         <v>752</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.14</v>
+        <v>-0.8</v>
       </c>
       <c r="AN11" t="n">
-        <v>37.86</v>
+        <v>35.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 64.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30.08</v>
+        <v>30.045</v>
       </c>
       <c r="F12" t="n">
-        <v>53.4</v>
+        <v>53.7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="K12" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="L12" t="n">
-        <v>29.6</v>
+        <v>31.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 13.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 12.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>13.38</v>
+        <v>16.16</v>
       </c>
       <c r="S12" t="n">
-        <v>36.85</v>
+        <v>33.06</v>
       </c>
       <c r="T12" t="n">
-        <v>4.9</v>
+        <v>6.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0.96</v>
+        <v>0.55</v>
       </c>
       <c r="W12" t="n">
-        <v>34.48</v>
+        <v>34.47</v>
       </c>
       <c r="X12" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.5169</v>
+        <v>26.6348</v>
       </c>
       <c r="AA12" t="n">
-        <v>26.6392</v>
+        <v>26.6394</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2373,10 +2373,10 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="AH12" t="n">
         <v>757</v>
@@ -2394,14 +2394,14 @@
         <v>30.11</v>
       </c>
       <c r="AM12" t="n">
-        <v>13.44</v>
+        <v>12.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.92</v>
+        <v>12.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 53.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.4%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 53.7, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.8%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>343.28</v>
+        <v>340.43</v>
       </c>
       <c r="F13" t="n">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="I13" t="n">
-        <v>33.3</v>
+        <v>30.7</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>67.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="L13" t="n">
-        <v>54.6</v>
+        <v>53.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-4.92</v>
+        <v>-5.08</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.26</v>
+        <v>-13.24</v>
       </c>
       <c r="T13" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.78</v>
       </c>
       <c r="U13" t="n">
-        <v>25.39</v>
+        <v>22.92</v>
       </c>
       <c r="V13" t="n">
-        <v>26.85</v>
+        <v>26.6</v>
       </c>
       <c r="W13" t="n">
-        <v>18.39</v>
+        <v>18.4</v>
       </c>
       <c r="X13" t="n">
         <v>-22.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>361.0416</v>
+        <v>360.167</v>
       </c>
       <c r="AA13" t="n">
-        <v>369.0488</v>
+        <v>369.2143</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>33.3</v>
+        <v>30.7</v>
       </c>
       <c r="AF13" t="n">
         <v>60</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="AH13" t="n">
         <v>756</v>
@@ -2550,20 +2550,20 @@
         <v>338.68</v>
       </c>
       <c r="AK13" t="n">
-        <v>361.71</v>
+        <v>354.79</v>
       </c>
       <c r="AL13" t="n">
         <v>388.92</v>
       </c>
       <c r="AM13" t="n">
-        <v>-4.92</v>
+        <v>-5.48</v>
       </c>
       <c r="AN13" t="n">
-        <v>-6.98</v>
+        <v>-7.8</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 52.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.9%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 51.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.5%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.617000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="F14" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>29.6</v>
+        <v>29.2</v>
       </c>
       <c r="I14" t="n">
-        <v>67.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="J14" t="n">
         <v>31.4</v>
       </c>
       <c r="K14" t="n">
-        <v>67.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="L14" t="n">
-        <v>43.1</v>
+        <v>43.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 8.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-7.39</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.17</v>
+        <v>1.44</v>
       </c>
       <c r="T14" t="n">
-        <v>10.41</v>
+        <v>10.93</v>
       </c>
       <c r="U14" t="n">
-        <v>45.54</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>0.84</v>
       </c>
       <c r="W14" t="n">
-        <v>24.07</v>
+        <v>24.06</v>
       </c>
       <c r="X14" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.5045</v>
+        <v>10.4896</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.131600000000001</v>
+        <v>9.1424</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,13 +2694,13 @@
         <v>65</v>
       </c>
       <c r="AE14" t="n">
-        <v>67.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="AF14" t="n">
         <v>36.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>67.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="AH14" t="n">
         <v>756</v>
@@ -2718,14 +2718,14 @@
         <v>11.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.67</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.32</v>
+        <v>4.79</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base High Risk, score 50.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.4%.</t>
+          <t>INRG.MI: scenario base High Risk, score 50.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.7%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70.27</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>83.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,14 +680,14 @@
         <v>68.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>82.8</v>
+        <v>79</v>
       </c>
       <c r="L2" t="n">
-        <v>83.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-1.99</v>
+        <v>-2.73</v>
       </c>
       <c r="S2" t="n">
-        <v>19.51</v>
+        <v>17.03</v>
       </c>
       <c r="T2" t="n">
-        <v>27.69</v>
+        <v>25.9</v>
       </c>
       <c r="U2" t="n">
-        <v>58.75</v>
+        <v>58.04</v>
       </c>
       <c r="V2" t="n">
-        <v>26.02</v>
+        <v>25.68</v>
       </c>
       <c r="W2" t="n">
         <v>14.04</v>
@@ -732,13 +732,13 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z2" t="n">
-        <v>69.995</v>
+        <v>70.1052</v>
       </c>
       <c r="AA2" t="n">
-        <v>58.0467</v>
+        <v>58.1573</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AE2" t="n">
         <v>100</v>
@@ -756,16 +756,16 @@
         <v>68.90000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>82.8</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI2" t="n">
         <v>69.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="AK2" t="n">
         <v>73.47</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.39</v>
+        <v>-0.49</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.06</v>
+        <v>19.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 83.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.4%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 79.8, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -0.5%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 59.27 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.73 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>165.8</v>
+        <v>165.46</v>
       </c>
       <c r="F3" t="n">
-        <v>76.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>74.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>76.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>67.59999999999999</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S3" t="n">
-        <v>9.289999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="T3" t="n">
-        <v>11.73</v>
+        <v>10.13</v>
       </c>
       <c r="U3" t="n">
-        <v>26.14</v>
+        <v>25.12</v>
       </c>
       <c r="V3" t="n">
-        <v>18.23</v>
+        <v>18.12</v>
       </c>
       <c r="W3" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="X3" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>162.8152</v>
+        <v>162.9648</v>
       </c>
       <c r="AA3" t="n">
-        <v>150.3306</v>
+        <v>150.4622</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>76.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AF3" t="n">
         <v>67.59999999999999</v>
@@ -921,7 +921,7 @@
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AI3" t="n">
         <v>163.44</v>
@@ -936,14 +936,14 @@
         <v>166.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.29</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.8%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.5%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>126.29</v>
+        <v>126.27</v>
       </c>
       <c r="F4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>73.2</v>
       </c>
       <c r="I4" t="n">
-        <v>76.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="J4" t="n">
         <v>66.90000000000001</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>76.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1035,22 +1035,22 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>9.51</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>11.09</v>
+        <v>9.85</v>
       </c>
       <c r="U4" t="n">
-        <v>24.64</v>
+        <v>24.45</v>
       </c>
       <c r="V4" t="n">
-        <v>18.23</v>
+        <v>18.2</v>
       </c>
       <c r="W4" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="X4" t="n">
         <v>-21.63</v>
@@ -1059,10 +1059,10 @@
         <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>123.3504</v>
+        <v>123.4832</v>
       </c>
       <c r="AA4" t="n">
-        <v>114.6722</v>
+        <v>114.7687</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>76.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="AF4" t="n">
         <v>66.90000000000001</v>
@@ -1083,7 +1083,7 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI4" t="n">
         <v>123.73</v>
@@ -1098,14 +1098,14 @@
         <v>126.34</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.13</v>
+        <v>10.02</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>711.62</v>
+        <v>711.96</v>
       </c>
       <c r="F5" t="n">
-        <v>75.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>78.5</v>
+        <v>75.7</v>
       </c>
       <c r="J5" t="n">
         <v>64.3</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>76.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>10.81</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>12.05</v>
+        <v>10.58</v>
       </c>
       <c r="U5" t="n">
-        <v>24.57</v>
+        <v>23.57</v>
       </c>
       <c r="V5" t="n">
-        <v>19.22</v>
+        <v>19.21</v>
       </c>
       <c r="W5" t="n">
-        <v>14.18</v>
+        <v>14.17</v>
       </c>
       <c r="X5" t="n">
         <v>-23.32</v>
@@ -1221,10 +1221,10 @@
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>696.234</v>
+        <v>697</v>
       </c>
       <c r="AA5" t="n">
-        <v>643.9117</v>
+        <v>644.4457</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>78.5</v>
+        <v>75.7</v>
       </c>
       <c r="AF5" t="n">
         <v>64.3</v>
@@ -1245,13 +1245,13 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AI5" t="n">
         <v>696.42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>652.96</v>
+        <v>653.38</v>
       </c>
       <c r="AK5" t="n">
         <v>712.88</v>
@@ -1260,14 +1260,14 @@
         <v>712.88</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.52</v>
+        <v>10.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 652.96 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 653.38 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>77.53</v>
+        <v>77.84</v>
       </c>
       <c r="F6" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>67</v>
+      </c>
+      <c r="I6" t="n">
         <v>74.40000000000001</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Accumulate Carefully</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>75.8</v>
       </c>
       <c r="J6" t="n">
         <v>68.09999999999999</v>
@@ -1331,7 +1331,7 @@
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1359,34 +1359,34 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="S6" t="n">
-        <v>9.539999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>10.99</v>
+        <v>10.13</v>
       </c>
       <c r="U6" t="n">
-        <v>23.3</v>
+        <v>23.73</v>
       </c>
       <c r="V6" t="n">
-        <v>16.34</v>
+        <v>16.47</v>
       </c>
       <c r="W6" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="X6" t="n">
         <v>-20.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>75.0324</v>
+        <v>75.1388</v>
       </c>
       <c r="AA6" t="n">
-        <v>70.2328</v>
+        <v>70.2963</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>75.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AF6" t="n">
         <v>68.09999999999999</v>
@@ -1407,7 +1407,7 @@
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI6" t="n">
         <v>75.3</v>
@@ -1416,25 +1416,25 @@
         <v>71.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>77.53</v>
+        <v>77.84</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.53</v>
+        <v>77.84</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.33</v>
+        <v>3.59</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.39</v>
+        <v>10.73</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 77.53 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 77.84 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64.11</v>
+        <v>64.2</v>
       </c>
       <c r="F7" t="n">
-        <v>74.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>67.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>74.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0.9</v>
       </c>
       <c r="S7" t="n">
-        <v>5.63</v>
+        <v>4.12</v>
       </c>
       <c r="T7" t="n">
-        <v>6.76</v>
+        <v>6.89</v>
       </c>
       <c r="U7" t="n">
-        <v>21.13</v>
+        <v>22.22</v>
       </c>
       <c r="V7" t="n">
-        <v>15.05</v>
+        <v>15.09</v>
       </c>
       <c r="W7" t="n">
-        <v>12.83</v>
+        <v>12.82</v>
       </c>
       <c r="X7" t="n">
         <v>-16.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>62.6136</v>
+        <v>62.6796</v>
       </c>
       <c r="AA7" t="n">
-        <v>59.1981</v>
+        <v>59.249</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,16 +1560,16 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>67.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI7" t="n">
         <v>63.18</v>
@@ -1584,14 +1584,14 @@
         <v>65.06</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.300000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65.26000000000001</v>
+        <v>65.55</v>
       </c>
       <c r="F8" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>64.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="I8" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="J8" t="n">
         <v>78.2</v>
@@ -1679,23 +1679,23 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="S8" t="n">
-        <v>3.41</v>
+        <v>3.64</v>
       </c>
       <c r="T8" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="U8" t="n">
-        <v>5.82</v>
+        <v>5.86</v>
       </c>
       <c r="V8" t="n">
-        <v>8.25</v>
+        <v>8.4</v>
       </c>
       <c r="W8" t="n">
         <v>9.59</v>
@@ -1704,13 +1704,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="Z8" t="n">
-        <v>64.22880000000001</v>
+        <v>64.29179999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>63.3911</v>
+        <v>63.4083</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="AF8" t="n">
         <v>78.2</v>
@@ -1731,10 +1731,10 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI8" t="n">
-        <v>63.44</v>
+        <v>63.52</v>
       </c>
       <c r="AJ8" t="n">
         <v>62.06</v>
@@ -1746,14 +1746,14 @@
         <v>66.20999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>46.8</v>
+        <v>46.245</v>
       </c>
       <c r="F9" t="n">
-        <v>71.2</v>
+        <v>69</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="I9" t="n">
-        <v>79.7</v>
+        <v>72.5</v>
       </c>
       <c r="J9" t="n">
         <v>64.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>77.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>73</v>
+        <v>70.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-3.65</v>
+        <v>-6.05</v>
       </c>
       <c r="S9" t="n">
-        <v>7.67</v>
+        <v>4.21</v>
       </c>
       <c r="T9" t="n">
-        <v>15.43</v>
+        <v>12.41</v>
       </c>
       <c r="U9" t="n">
-        <v>38.65</v>
+        <v>36.68</v>
       </c>
       <c r="V9" t="n">
-        <v>18.74</v>
+        <v>18.24</v>
       </c>
       <c r="W9" t="n">
         <v>16.74</v>
@@ -1866,13 +1866,13 @@
         <v>-19.17</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>47.5861</v>
+        <v>47.576</v>
       </c>
       <c r="AA9" t="n">
-        <v>41.9759</v>
+        <v>42.0232</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,19 +1884,19 @@
         <v>65</v>
       </c>
       <c r="AE9" t="n">
-        <v>79.7</v>
+        <v>72.5</v>
       </c>
       <c r="AF9" t="n">
         <v>64.59999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AH9" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI9" t="n">
-        <v>46.73</v>
+        <v>46.245</v>
       </c>
       <c r="AJ9" t="n">
         <v>43.825</v>
@@ -1908,14 +1908,14 @@
         <v>50.73</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1.65</v>
+        <v>-2.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>11.49</v>
+        <v>10.05</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 71.2, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.6%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 69.0, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -2.8%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.728</v>
+        <v>17.516</v>
       </c>
       <c r="F10" t="n">
-        <v>67.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="I10" t="n">
-        <v>96.7</v>
+        <v>88.5</v>
       </c>
       <c r="J10" t="n">
         <v>44.9</v>
       </c>
       <c r="K10" t="n">
-        <v>78</v>
+        <v>76.2</v>
       </c>
       <c r="L10" t="n">
-        <v>71.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>-2.99</v>
+        <v>-4.92</v>
       </c>
       <c r="S10" t="n">
-        <v>17.7</v>
+        <v>13.67</v>
       </c>
       <c r="T10" t="n">
-        <v>21.36</v>
+        <v>17.72</v>
       </c>
       <c r="U10" t="n">
-        <v>36.33</v>
+        <v>34.9</v>
       </c>
       <c r="V10" t="n">
-        <v>17.47</v>
+        <v>16.98</v>
       </c>
       <c r="W10" t="n">
-        <v>22.18</v>
+        <v>22.17</v>
       </c>
       <c r="X10" t="n">
         <v>-29.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.9344</v>
+        <v>17.9418</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.1436</v>
+        <v>15.1644</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -2046,22 +2046,22 @@
         <v>65</v>
       </c>
       <c r="AE10" t="n">
-        <v>96.7</v>
+        <v>88.5</v>
       </c>
       <c r="AF10" t="n">
         <v>49.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>78</v>
+        <v>76.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI10" t="n">
-        <v>17.63</v>
+        <v>17.516</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.558</v>
+        <v>15.638</v>
       </c>
       <c r="AK10" t="n">
         <v>19.164</v>
@@ -2070,14 +2070,14 @@
         <v>19.164</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.15</v>
+        <v>-2.37</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.07</v>
+        <v>15.51</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.1, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.1%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 64.7, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -2.4%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 15.56 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 15.64 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>590.65</v>
+        <v>565.08</v>
       </c>
       <c r="F11" t="n">
-        <v>64.7</v>
+        <v>63.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>54.3</v>
+        <v>53</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="K11" t="n">
-        <v>78.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>53.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2165,38 +2165,38 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-4.73</v>
+        <v>-12.68</v>
       </c>
       <c r="S11" t="n">
-        <v>30.67</v>
+        <v>24.74</v>
       </c>
       <c r="T11" t="n">
-        <v>51.19</v>
+        <v>44.33</v>
       </c>
       <c r="U11" t="n">
-        <v>107.66</v>
+        <v>94.92</v>
       </c>
       <c r="V11" t="n">
-        <v>55.67</v>
+        <v>53.29</v>
       </c>
       <c r="W11" t="n">
-        <v>36.26</v>
+        <v>36.33</v>
       </c>
       <c r="X11" t="n">
         <v>-35.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="Z11" t="n">
-        <v>595.4124</v>
+        <v>596.5806</v>
       </c>
       <c r="AA11" t="n">
-        <v>436.9928</v>
+        <v>438.2147</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>78.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AI11" t="n">
-        <v>581.45</v>
+        <v>565.08</v>
       </c>
       <c r="AJ11" t="n">
-        <v>463.96</v>
+        <v>464.66</v>
       </c>
       <c r="AK11" t="n">
         <v>668.91</v>
@@ -2232,14 +2232,14 @@
         <v>668.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.8</v>
+        <v>-5.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>35.16</v>
+        <v>28.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 64.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.3%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 463.96 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 464.66 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30.045</v>
+        <v>29.905</v>
       </c>
       <c r="F12" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="J12" t="n">
         <v>14.8</v>
       </c>
       <c r="K12" t="n">
-        <v>47.5</v>
+        <v>51.2</v>
       </c>
       <c r="L12" t="n">
-        <v>31.6</v>
+        <v>34</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2327,38 +2327,38 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 12.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>16.16</v>
+        <v>15.55</v>
       </c>
       <c r="S12" t="n">
-        <v>33.06</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>6.34</v>
+        <v>6.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.26</v>
+        <v>0.05</v>
       </c>
       <c r="V12" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="n">
-        <v>34.47</v>
+        <v>34.45</v>
       </c>
       <c r="X12" t="n">
         <v>-48.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.6348</v>
+        <v>26.7302</v>
       </c>
       <c r="AA12" t="n">
-        <v>26.6394</v>
+        <v>26.6384</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         <v>85</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="AF12" t="n">
         <v>19.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>47.5</v>
+        <v>51.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI12" t="n">
         <v>24.785</v>
@@ -2394,14 +2394,14 @@
         <v>30.11</v>
       </c>
       <c r="AM12" t="n">
-        <v>12.8</v>
+        <v>11.88</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.78</v>
+        <v>12.26</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 53.7, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.8%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 53.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>340.43</v>
+        <v>337.62</v>
       </c>
       <c r="F13" t="n">
-        <v>51.7</v>
+        <v>50.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>30.7</v>
+        <v>27.7</v>
       </c>
       <c r="J13" t="n">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="K13" t="n">
-        <v>67</v>
+        <v>66.3</v>
       </c>
       <c r="L13" t="n">
-        <v>53.6</v>
+        <v>52.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 5.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-5.08</v>
+        <v>-6.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-13.24</v>
+        <v>-14.9</v>
       </c>
       <c r="T13" t="n">
-        <v>-10.78</v>
+        <v>-11.73</v>
       </c>
       <c r="U13" t="n">
-        <v>22.92</v>
+        <v>22.38</v>
       </c>
       <c r="V13" t="n">
-        <v>26.6</v>
+        <v>26.21</v>
       </c>
       <c r="W13" t="n">
-        <v>18.4</v>
+        <v>18.39</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.39</v>
+        <v>-22.63</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>360.167</v>
+        <v>359.161</v>
       </c>
       <c r="AA13" t="n">
-        <v>369.2143</v>
+        <v>369.3628</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,38 +2532,38 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>30.7</v>
+        <v>27.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>67</v>
+        <v>66.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI13" t="n">
-        <v>338.68</v>
+        <v>337.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>338.68</v>
+        <v>337.62</v>
       </c>
       <c r="AK13" t="n">
-        <v>354.79</v>
+        <v>352.3</v>
       </c>
       <c r="AL13" t="n">
         <v>388.92</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.48</v>
+        <v>-6</v>
       </c>
       <c r="AN13" t="n">
-        <v>-7.8</v>
+        <v>-8.59</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 51.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.5%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 50.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.0%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 337.62 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.58</v>
+        <v>9.374000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>50.9</v>
+        <v>48.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>29.2</v>
+        <v>28.7</v>
       </c>
       <c r="I14" t="n">
-        <v>70.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>31.4</v>
       </c>
       <c r="K14" t="n">
-        <v>66.7</v>
+        <v>64</v>
       </c>
       <c r="L14" t="n">
-        <v>43.6</v>
+        <v>41</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2651,38 +2651,38 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prezzo 8.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-8.470000000000001</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>-0.72</v>
       </c>
       <c r="T14" t="n">
-        <v>10.93</v>
+        <v>7.24</v>
       </c>
       <c r="U14" t="n">
-        <v>46.5</v>
+        <v>43.26</v>
       </c>
       <c r="V14" t="n">
-        <v>0.84</v>
+        <v>0.11</v>
       </c>
       <c r="W14" t="n">
-        <v>24.06</v>
+        <v>24.08</v>
       </c>
       <c r="X14" t="n">
         <v>-43.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.4896</v>
+        <v>10.4716</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.1424</v>
+        <v>9.1524</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2694,22 +2694,22 @@
         <v>65</v>
       </c>
       <c r="AE14" t="n">
-        <v>70.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AF14" t="n">
         <v>36.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>66.7</v>
+        <v>64</v>
       </c>
       <c r="AH14" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AI14" t="n">
-        <v>9.483000000000001</v>
+        <v>9.374000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>9.483000000000001</v>
+        <v>9.374000000000001</v>
       </c>
       <c r="AK14" t="n">
         <v>10.872</v>
@@ -2718,14 +2718,14 @@
         <v>11.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>-8.67</v>
+        <v>-10.48</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.79</v>
+        <v>2.42</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base High Risk, score 50.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.7%.</t>
+          <t>INRG.MI: scenario base High Risk, score 48.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -10.5%.</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 9.48 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 9.37 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">

--- a/ETF_Intelligence_Agent_UPDATED.xlsx
+++ b/ETF_Intelligence_Agent_UPDATED.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.76000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F2" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -680,10 +680,10 @@
         <v>68.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>79</v>
+        <v>78.2</v>
       </c>
       <c r="L2" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-2.73</v>
+        <v>-4.07</v>
       </c>
       <c r="S2" t="n">
-        <v>17.03</v>
+        <v>17.1</v>
       </c>
       <c r="T2" t="n">
-        <v>25.9</v>
+        <v>25.77</v>
       </c>
       <c r="U2" t="n">
-        <v>58.04</v>
+        <v>57.16</v>
       </c>
       <c r="V2" t="n">
-        <v>25.68</v>
+        <v>25.45</v>
       </c>
       <c r="W2" t="n">
         <v>14.04</v>
@@ -732,13 +732,13 @@
         <v>-17.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>70.1052</v>
+        <v>70.19499999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>58.1573</v>
+        <v>58.2649</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -756,16 +756,16 @@
         <v>68.90000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>79</v>
+        <v>78.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI2" t="n">
-        <v>69.73</v>
+        <v>69.45</v>
       </c>
       <c r="AJ2" t="n">
-        <v>59.73</v>
+        <v>59.78</v>
       </c>
       <c r="AK2" t="n">
         <v>73.47</v>
@@ -774,14 +774,14 @@
         <v>73.47</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.49</v>
+        <v>-1.06</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.95</v>
+        <v>19.2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 79.8, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -0.5%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 79.6, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -1.1%.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 59.73 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.78 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>165.46</v>
+        <v>163.5</v>
       </c>
       <c r="F3" t="n">
-        <v>75.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>73.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I3" t="n">
-        <v>73.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="J3" t="n">
         <v>67.59999999999999</v>
@@ -845,7 +845,7 @@
         <v>82.8</v>
       </c>
       <c r="L3" t="n">
-        <v>75.7</v>
+        <v>75.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -869,38 +869,38 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.5</v>
+        <v>-1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>7.68</v>
+        <v>6.95</v>
       </c>
       <c r="T3" t="n">
-        <v>10.13</v>
+        <v>9.07</v>
       </c>
       <c r="U3" t="n">
-        <v>25.12</v>
+        <v>25.38</v>
       </c>
       <c r="V3" t="n">
-        <v>18.12</v>
+        <v>17.63</v>
       </c>
       <c r="W3" t="n">
-        <v>12.94</v>
+        <v>12.96</v>
       </c>
       <c r="X3" t="n">
         <v>-21.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>162.9648</v>
+        <v>163.072</v>
       </c>
       <c r="AA3" t="n">
-        <v>150.4622</v>
+        <v>150.5844</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="AE3" t="n">
-        <v>73.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AF3" t="n">
         <v>67.59999999999999</v>
@@ -921,7 +921,7 @@
         <v>82.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI3" t="n">
         <v>163.44</v>
@@ -936,14 +936,14 @@
         <v>166.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.53</v>
+        <v>0.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.970000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.5%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.3%.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>126.27</v>
+        <v>124.86</v>
       </c>
       <c r="F4" t="n">
-        <v>75.2</v>
+        <v>74.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.2</v>
+        <v>72.5</v>
       </c>
       <c r="I4" t="n">
-        <v>73.5</v>
+        <v>71.3</v>
       </c>
       <c r="J4" t="n">
         <v>66.90000000000001</v>
@@ -1007,7 +1007,7 @@
         <v>82.8</v>
       </c>
       <c r="L4" t="n">
-        <v>75.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1031,38 +1031,38 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>0.15</v>
       </c>
       <c r="S4" t="n">
-        <v>8.220000000000001</v>
+        <v>7.44</v>
       </c>
       <c r="T4" t="n">
-        <v>9.85</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>24.45</v>
+        <v>22.34</v>
       </c>
       <c r="V4" t="n">
-        <v>18.2</v>
+        <v>17.73</v>
       </c>
       <c r="W4" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="X4" t="n">
         <v>-21.63</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>123.4832</v>
+        <v>123.5902</v>
       </c>
       <c r="AA4" t="n">
-        <v>114.7687</v>
+        <v>114.8576</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>73.5</v>
+        <v>71.3</v>
       </c>
       <c r="AF4" t="n">
         <v>66.90000000000001</v>
@@ -1083,7 +1083,7 @@
         <v>82.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI4" t="n">
         <v>123.73</v>
@@ -1098,14 +1098,14 @@
         <v>126.34</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.02</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.0%.</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>711.96</v>
+        <v>703.46</v>
       </c>
       <c r="F5" t="n">
-        <v>74.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>75.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>64.3</v>
@@ -1169,7 +1169,7 @@
         <v>82.8</v>
       </c>
       <c r="L5" t="n">
-        <v>75.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1188,43 +1188,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>0.26</v>
       </c>
       <c r="S5" t="n">
-        <v>9.630000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="T5" t="n">
-        <v>10.58</v>
+        <v>9.49</v>
       </c>
       <c r="U5" t="n">
-        <v>23.57</v>
+        <v>24.25</v>
       </c>
       <c r="V5" t="n">
-        <v>19.21</v>
+        <v>18.71</v>
       </c>
       <c r="W5" t="n">
-        <v>14.17</v>
+        <v>14.18</v>
       </c>
       <c r="X5" t="n">
         <v>-23.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>697</v>
+        <v>697.574</v>
       </c>
       <c r="AA5" t="n">
-        <v>644.4457</v>
+        <v>644.9376</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>75.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>64.3</v>
@@ -1245,7 +1245,7 @@
         <v>82.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AI5" t="n">
         <v>696.42</v>
@@ -1260,14 +1260,14 @@
         <v>712.88</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.15</v>
+        <v>0.84</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.48</v>
+        <v>9.07</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1289,29 +1289,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>77.84</v>
+        <v>63.96</v>
       </c>
       <c r="F6" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>67</v>
+        <v>71.8</v>
       </c>
       <c r="I6" t="n">
-        <v>74.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="J6" t="n">
-        <v>68.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>82.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1350,43 +1350,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2.66</v>
+        <v>0.95</v>
       </c>
       <c r="S6" t="n">
-        <v>8.869999999999999</v>
+        <v>4.62</v>
       </c>
       <c r="T6" t="n">
-        <v>10.13</v>
+        <v>7.92</v>
       </c>
       <c r="U6" t="n">
-        <v>23.73</v>
+        <v>20.36</v>
       </c>
       <c r="V6" t="n">
-        <v>16.47</v>
+        <v>14.92</v>
       </c>
       <c r="W6" t="n">
-        <v>12.87</v>
+        <v>12.81</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.6</v>
+        <v>-16.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>75.1388</v>
+        <v>62.7463</v>
       </c>
       <c r="AA6" t="n">
-        <v>70.2963</v>
+        <v>59.2982</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1398,48 +1398,48 @@
         <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>74.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>68.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AG6" t="n">
         <v>82.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="AI6" t="n">
-        <v>75.3</v>
+        <v>63.18</v>
       </c>
       <c r="AJ6" t="n">
-        <v>71.23</v>
+        <v>59.5065</v>
       </c>
       <c r="AK6" t="n">
-        <v>77.84</v>
+        <v>65.06</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.84</v>
+        <v>65.06</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.59</v>
+        <v>1.93</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.73</v>
+        <v>7.86</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 77.84 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 71.23 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1451,29 +1451,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64.2</v>
+        <v>76.92</v>
       </c>
       <c r="F7" t="n">
-        <v>73.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>72.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="I7" t="n">
-        <v>65.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="J7" t="n">
-        <v>71.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>82.8</v>
       </c>
       <c r="L7" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.9</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>4.12</v>
+        <v>7.67</v>
       </c>
       <c r="T7" t="n">
-        <v>6.89</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>22.22</v>
+        <v>21.73</v>
       </c>
       <c r="V7" t="n">
-        <v>15.09</v>
+        <v>15.99</v>
       </c>
       <c r="W7" t="n">
-        <v>12.82</v>
+        <v>12.88</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.33</v>
+        <v>-20.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>62.6796</v>
+        <v>75.22880000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>59.249</v>
+        <v>70.3546</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1560,48 +1560,48 @@
         <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>65.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>71.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AG7" t="n">
         <v>82.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AI7" t="n">
-        <v>63.18</v>
+        <v>75.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>59.5065</v>
+        <v>71.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>65.06</v>
+        <v>77.84</v>
       </c>
       <c r="AL7" t="n">
-        <v>65.06</v>
+        <v>77.84</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.359999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 77.84 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 59.51 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 71.23 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65.55</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>64.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="J8" t="n">
         <v>78.2</v>
@@ -1655,7 +1655,7 @@
         <v>82.8</v>
       </c>
       <c r="L8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2.66</v>
+        <v>4.02</v>
       </c>
       <c r="S8" t="n">
-        <v>3.64</v>
+        <v>4.04</v>
       </c>
       <c r="T8" t="n">
-        <v>3.23</v>
+        <v>4.37</v>
       </c>
       <c r="U8" t="n">
-        <v>5.86</v>
+        <v>6.8</v>
       </c>
       <c r="V8" t="n">
-        <v>8.4</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>9.59</v>
@@ -1704,13 +1704,13 @@
         <v>-12.85</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>64.29179999999999</v>
+        <v>64.36620000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>63.4083</v>
+        <v>63.4266</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
         <v>78.2</v>
@@ -1731,10 +1731,10 @@
         <v>82.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI8" t="n">
-        <v>63.52</v>
+        <v>63.57</v>
       </c>
       <c r="AJ8" t="n">
         <v>62.06</v>
@@ -1746,14 +1746,14 @@
         <v>66.20999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.96</v>
+        <v>2.52</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.38</v>
+        <v>4.04</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 71.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 72.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1794,30 +1794,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>46.245</v>
+        <v>45.295</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>67.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>67.5</v>
+        <v>66.5</v>
       </c>
       <c r="I9" t="n">
-        <v>72.5</v>
+        <v>69.3</v>
       </c>
       <c r="J9" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="K9" t="n">
-        <v>75.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="L9" t="n">
-        <v>70.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1841,38 +1841,38 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-6.05</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>4.21</v>
+        <v>3.28</v>
       </c>
       <c r="T9" t="n">
-        <v>12.41</v>
+        <v>11.1</v>
       </c>
       <c r="U9" t="n">
-        <v>36.68</v>
+        <v>32.19</v>
       </c>
       <c r="V9" t="n">
-        <v>18.24</v>
+        <v>17.4</v>
       </c>
       <c r="W9" t="n">
-        <v>16.74</v>
+        <v>16.77</v>
       </c>
       <c r="X9" t="n">
         <v>-19.17</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>47.576</v>
+        <v>47.5409</v>
       </c>
       <c r="AA9" t="n">
-        <v>42.0232</v>
+        <v>42.0673</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1884,19 +1884,19 @@
         <v>65</v>
       </c>
       <c r="AE9" t="n">
-        <v>72.5</v>
+        <v>69.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>75.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI9" t="n">
-        <v>46.245</v>
+        <v>45.295</v>
       </c>
       <c r="AJ9" t="n">
         <v>43.825</v>
@@ -1908,14 +1908,14 @@
         <v>50.73</v>
       </c>
       <c r="AM9" t="n">
-        <v>-2.8</v>
+        <v>-4.72</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.05</v>
+        <v>7.67</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 69.0, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -2.8%.</t>
+          <t>EIMI.MI: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -4.7%.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1952,14 +1952,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.516</v>
+        <v>558.5599999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>64.7</v>
+        <v>63</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>49.7</v>
+        <v>52.7</v>
       </c>
       <c r="I10" t="n">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>44.9</v>
+        <v>22.8</v>
       </c>
       <c r="K10" t="n">
-        <v>76.2</v>
+        <v>70</v>
       </c>
       <c r="L10" t="n">
-        <v>68.90000000000001</v>
+        <v>53</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2003,42 +2003,42 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 6.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>-4.92</v>
+        <v>-9.32</v>
       </c>
       <c r="S10" t="n">
-        <v>13.67</v>
+        <v>22.81</v>
       </c>
       <c r="T10" t="n">
-        <v>17.72</v>
+        <v>43.83</v>
       </c>
       <c r="U10" t="n">
-        <v>34.9</v>
+        <v>93.69</v>
       </c>
       <c r="V10" t="n">
-        <v>16.98</v>
+        <v>52.61</v>
       </c>
       <c r="W10" t="n">
-        <v>22.17</v>
+        <v>36.3</v>
       </c>
       <c r="X10" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.77</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.9418</v>
+        <v>597.3748000000001</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.1644</v>
+        <v>439.4184</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2046,48 +2046,48 @@
         <v>65</v>
       </c>
       <c r="AE10" t="n">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>49.9</v>
+        <v>27.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>76.2</v>
+        <v>70</v>
       </c>
       <c r="AH10" t="n">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="AI10" t="n">
-        <v>17.516</v>
+        <v>558.5599999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.638</v>
+        <v>476.83</v>
       </c>
       <c r="AK10" t="n">
-        <v>19.164</v>
+        <v>668.91</v>
       </c>
       <c r="AL10" t="n">
-        <v>19.164</v>
+        <v>668.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>-2.37</v>
+        <v>-6.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.51</v>
+        <v>27.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 64.7, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -2.4%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.5%.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 15.64 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 476.83 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2114,14 +2114,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>565.08</v>
+        <v>17.016</v>
       </c>
       <c r="F11" t="n">
-        <v>63.3</v>
+        <v>62.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>53</v>
+        <v>48.6</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>22.8</v>
+        <v>44.8</v>
       </c>
       <c r="K11" t="n">
-        <v>71.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>53.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2165,42 +2165,42 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-12.68</v>
+        <v>-9.42</v>
       </c>
       <c r="S11" t="n">
-        <v>24.74</v>
+        <v>11.39</v>
       </c>
       <c r="T11" t="n">
-        <v>44.33</v>
+        <v>15.11</v>
       </c>
       <c r="U11" t="n">
-        <v>94.92</v>
+        <v>29.52</v>
       </c>
       <c r="V11" t="n">
-        <v>53.29</v>
+        <v>15.83</v>
       </c>
       <c r="W11" t="n">
-        <v>36.33</v>
+        <v>22.22</v>
       </c>
       <c r="X11" t="n">
-        <v>-35.74</v>
+        <v>-29.37</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.47</v>
+        <v>0.71</v>
       </c>
       <c r="Z11" t="n">
-        <v>596.5806</v>
+        <v>17.9361</v>
       </c>
       <c r="AA11" t="n">
-        <v>438.2147</v>
+        <v>15.1827</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2208,48 +2208,48 @@
         <v>65</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AF11" t="n">
-        <v>27.8</v>
+        <v>49.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>71.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AH11" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="AI11" t="n">
-        <v>565.08</v>
+        <v>17.016</v>
       </c>
       <c r="AJ11" t="n">
-        <v>464.66</v>
+        <v>15.75</v>
       </c>
       <c r="AK11" t="n">
-        <v>668.91</v>
+        <v>19.164</v>
       </c>
       <c r="AL11" t="n">
-        <v>668.91</v>
+        <v>19.164</v>
       </c>
       <c r="AM11" t="n">
-        <v>-5.28</v>
+        <v>-5.13</v>
       </c>
       <c r="AN11" t="n">
-        <v>28.95</v>
+        <v>12.07</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.3%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 62.3, trend Constructive. Entry zone: Constructive entry zone. Distanza da MA50: -5.1%.</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 464.66 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 15.75 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>29.905</v>
+        <v>29.71</v>
       </c>
       <c r="F12" t="n">
-        <v>53.9</v>
+        <v>54.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2294,16 +2294,16 @@
         <v>23.4</v>
       </c>
       <c r="I12" t="n">
-        <v>98.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>14.8</v>
       </c>
       <c r="K12" t="n">
-        <v>51.2</v>
+        <v>55.9</v>
       </c>
       <c r="L12" t="n">
-        <v>34</v>
+        <v>37.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2327,26 +2327,26 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prezzo 11.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>15.55</v>
+        <v>18.41</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>29.91</v>
       </c>
       <c r="T12" t="n">
-        <v>6.42</v>
+        <v>7.66</v>
       </c>
       <c r="U12" t="n">
-        <v>0.05</v>
+        <v>1.59</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
-        <v>34.45</v>
+        <v>34.43</v>
       </c>
       <c r="X12" t="n">
         <v>-48.6</v>
@@ -2355,10 +2355,10 @@
         <v>0.01</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.7302</v>
+        <v>26.8357</v>
       </c>
       <c r="AA12" t="n">
-        <v>26.6384</v>
+        <v>26.636</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2370,22 +2370,22 @@
         <v>85</v>
       </c>
       <c r="AE12" t="n">
-        <v>98.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AF12" t="n">
         <v>19.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>51.2</v>
+        <v>55.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AI12" t="n">
         <v>24.785</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22.225</v>
+        <v>22.3</v>
       </c>
       <c r="AK12" t="n">
         <v>30.085</v>
@@ -2394,14 +2394,14 @@
         <v>30.11</v>
       </c>
       <c r="AM12" t="n">
-        <v>11.88</v>
+        <v>10.71</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.26</v>
+        <v>11.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 53.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 54.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.7%.</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 22.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 22.30 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>337.62</v>
+        <v>337.23</v>
       </c>
       <c r="F13" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         <v>66.09999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>27.7</v>
+        <v>28.9</v>
       </c>
       <c r="J13" t="n">
         <v>59.8</v>
       </c>
       <c r="K13" t="n">
-        <v>66.3</v>
+        <v>66.5</v>
       </c>
       <c r="L13" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2489,38 +2489,38 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prezzo 6.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-6.66</v>
+        <v>-4.95</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.9</v>
+        <v>-14.05</v>
       </c>
       <c r="T13" t="n">
-        <v>-11.73</v>
+        <v>-11.51</v>
       </c>
       <c r="U13" t="n">
-        <v>22.38</v>
+        <v>21.92</v>
       </c>
       <c r="V13" t="n">
-        <v>26.21</v>
+        <v>26.12</v>
       </c>
       <c r="W13" t="n">
-        <v>18.39</v>
+        <v>18.38</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.63</v>
+        <v>-22.72</v>
       </c>
       <c r="Y13" t="n">
         <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>359.161</v>
+        <v>358.2014</v>
       </c>
       <c r="AA13" t="n">
-        <v>369.3628</v>
+        <v>369.4934</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2532,48 +2532,48 @@
         <v>35</v>
       </c>
       <c r="AE13" t="n">
-        <v>27.7</v>
+        <v>28.9</v>
       </c>
       <c r="AF13" t="n">
         <v>59.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>66.3</v>
+        <v>66.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AI13" t="n">
-        <v>337.62</v>
+        <v>337.23</v>
       </c>
       <c r="AJ13" t="n">
-        <v>337.62</v>
+        <v>337.23</v>
       </c>
       <c r="AK13" t="n">
         <v>352.3</v>
       </c>
       <c r="AL13" t="n">
-        <v>388.92</v>
+        <v>387.92</v>
       </c>
       <c r="AM13" t="n">
-        <v>-6</v>
+        <v>-5.85</v>
       </c>
       <c r="AN13" t="n">
-        <v>-8.59</v>
+        <v>-8.73</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 50.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.0%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 50.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.8%.</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 388.92 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 387.92 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 337.62 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 337.23 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.37400000